--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDF6BB34-32FF-48F6-B31D-3737EE7CC4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA6D4058-15E6-4D3B-86F7-B6612503E7BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3522" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3543" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1847"/>
+  <dimension ref="A1:C1858"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5124,9 +5124,6 @@
       <c r="B583" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C583" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B584" s="3" t="s">
@@ -5138,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5215,6 +5212,9 @@
       <c r="B594" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C594" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B595" s="3" t="s">
@@ -5226,7 +5226,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5314,7 +5314,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5402,7 +5402,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5490,7 +5490,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5578,7 +5578,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5655,9 +5655,6 @@
       <c r="B649" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C649" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B650" s="3" t="s">
@@ -5669,7 +5666,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5760,7 +5757,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5851,7 +5848,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5942,7 +5939,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6019,6 +6016,9 @@
       <c r="B693" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C693" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="694" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B694" s="3" t="s">
@@ -6030,7 +6030,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6107,9 +6107,6 @@
       <c r="B704" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C704" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="705" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B705" s="3" t="s">
@@ -6121,7 +6118,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6212,7 +6209,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6303,7 +6300,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6394,7 +6391,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6485,7 +6482,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6576,7 +6573,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6667,7 +6664,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6758,7 +6755,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6849,7 +6846,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6940,7 +6937,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -7031,7 +7028,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7122,7 +7119,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7213,7 +7210,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7304,7 +7301,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7395,7 +7392,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7486,7 +7483,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7577,7 +7574,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7668,7 +7665,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7759,7 +7756,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7850,7 +7847,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7941,7 +7938,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -8032,7 +8029,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8123,7 +8120,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8214,7 +8211,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8305,7 +8302,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8396,7 +8393,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8487,7 +8484,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8578,7 +8575,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8669,7 +8666,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8760,7 +8757,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8851,7 +8848,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8942,7 +8939,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -9033,7 +9030,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9110,6 +9107,9 @@
       <c r="B1067" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1067" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1068" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1068" s="3" t="s">
@@ -9121,7 +9121,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9198,9 +9198,6 @@
       <c r="B1078" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1078" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1079" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1079" s="3" t="s">
@@ -9212,7 +9209,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9303,7 +9300,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9394,7 +9391,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9485,7 +9482,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9576,7 +9573,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9667,7 +9664,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9758,7 +9755,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9849,7 +9846,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9940,7 +9937,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -10031,7 +10028,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10100,6 +10097,9 @@
       <c r="B1187" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1187" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1188" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1188" s="3" t="s">
@@ -10119,7 +10119,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10188,9 +10188,6 @@
       <c r="B1198" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1198" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1199" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1199" s="3" t="s">
@@ -10210,7 +10207,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10287,6 +10284,9 @@
       <c r="B1210" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1210" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1211" s="3" t="s">
@@ -10298,7 +10298,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10367,6 +10367,9 @@
       <c r="B1220" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1220" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1221" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1221" s="3" t="s">
@@ -10383,7 +10386,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10452,9 +10455,6 @@
       <c r="B1231" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1231" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1232" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1232" s="3" t="s">
@@ -10471,7 +10471,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10540,6 +10540,9 @@
       <c r="B1242" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1242" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1243" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1243" s="3" t="s">
@@ -10556,7 +10559,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10625,9 +10628,6 @@
       <c r="B1253" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1253" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1254" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1254" s="3" t="s">
@@ -10644,7 +10644,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10732,7 +10732,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10820,7 +10820,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10889,6 +10889,9 @@
       <c r="B1286" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1286" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1287" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1287" s="3" t="s">
@@ -10905,7 +10908,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10990,7 +10993,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11075,7 +11078,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11160,7 +11163,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11245,7 +11248,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11330,7 +11333,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11415,7 +11418,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11500,7 +11503,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11585,7 +11588,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11670,7 +11673,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11755,7 +11758,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11840,7 +11843,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11909,9 +11912,6 @@
       <c r="B1418" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1418" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1419" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1419" s="3" t="s">
@@ -11928,7 +11928,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -11997,6 +11997,9 @@
       <c r="B1429" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1429" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1430" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1430" s="3" t="s">
@@ -12013,7 +12016,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12098,7 +12101,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12183,7 +12186,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12252,9 +12255,6 @@
       <c r="B1462" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1462" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1463" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1463" s="3" t="s">
@@ -12271,7 +12271,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12359,7 +12359,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12428,6 +12428,9 @@
       <c r="B1484" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1484" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1485" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1485" s="3" t="s">
@@ -12444,7 +12447,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12529,7 +12532,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12614,7 +12617,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12699,7 +12702,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12768,9 +12771,6 @@
       <c r="B1528" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1528" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1529" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1529" s="3" t="s">
@@ -12787,7 +12787,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12875,7 +12875,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -12952,9 +12952,6 @@
       <c r="B1551" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1551" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1552" s="3" t="s">
@@ -12966,7 +12963,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13043,6 +13040,9 @@
       <c r="B1562" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1562" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1563" s="3" t="s">
@@ -13054,7 +13054,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13142,7 +13142,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13230,7 +13230,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13318,7 +13318,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13406,7 +13406,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13475,6 +13475,9 @@
       <c r="B1616" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1616" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1617" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1617" s="3" t="s">
@@ -13491,7 +13494,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13552,7 +13555,9 @@
       <c r="B1626" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1626" s="6"/>
+      <c r="C1626" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1627" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1627" s="3" t="s">
@@ -13568,10 +13573,13 @@
       <c r="B1629" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1629" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13632,17 +13640,12 @@
       <c r="B1637" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1637" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1637" s="6"/>
     </row>
     <row r="1638" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1638" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1638" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1639" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1639" s="3" t="s">
@@ -13653,13 +13656,10 @@
       <c r="B1640" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1640" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13747,7 +13747,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13835,7 +13835,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13904,6 +13904,9 @@
       <c r="B1671" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1671" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1672" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1672" s="3" t="s">
@@ -13920,7 +13923,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14005,7 +14008,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14079,9 +14082,6 @@
       <c r="B1694" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1694" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1695" s="3" t="s">
@@ -14093,7 +14093,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14154,7 +14154,9 @@
       <c r="B1703" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1703" s="6"/>
+      <c r="C1703" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1704" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1704" s="3" t="s">
@@ -14165,15 +14167,21 @@
       <c r="B1705" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1705" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1706" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1706" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14234,9 +14242,7 @@
       <c r="B1714" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1714" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1714" s="6"/>
     </row>
     <row r="1715" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1715" s="3" t="s">
@@ -14252,13 +14258,10 @@
       <c r="B1717" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1717" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14327,9 +14330,6 @@
       <c r="B1726" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1726" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1727" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1727" s="3" t="s">
@@ -14346,7 +14346,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14415,6 +14415,9 @@
       <c r="B1737" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1737" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1738" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1738" s="3" t="s">
@@ -14431,7 +14434,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14510,10 +14513,13 @@
       <c r="B1750" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1750" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14592,13 +14598,10 @@
       <c r="B1761" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1761" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14667,9 +14670,6 @@
       <c r="B1770" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1770" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1771" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1771" s="3" t="s">
@@ -14686,7 +14686,7 @@
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14707,19 +14707,25 @@
       <c r="B1775" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1775" s="6"/>
+      <c r="C1775" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1776" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1776" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1776" s="6"/>
+      <c r="C1776" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1777" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1777" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1777" s="6"/>
+      <c r="C1777" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1778" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1778" s="3" t="s">
@@ -14741,12 +14747,17 @@
       <c r="B1780" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1780" s="6"/>
+      <c r="C1780" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1781" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1781" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1781" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1782" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1782" s="3" t="s">
@@ -14757,10 +14768,13 @@
       <c r="B1783" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1783" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14781,25 +14795,19 @@
       <c r="B1786" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1786" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1786" s="6"/>
     </row>
     <row r="1787" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1787" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1787" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1787" s="6"/>
     </row>
     <row r="1788" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1788" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1788" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1788" s="6"/>
     </row>
     <row r="1789" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1789" s="3" t="s">
@@ -14821,17 +14829,12 @@
       <c r="B1791" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1791" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1791" s="6"/>
     </row>
     <row r="1792" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1792" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1792" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1793" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1793" s="3" t="s">
@@ -14842,13 +14845,10 @@
       <c r="B1794" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1794" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14936,7 +14936,7 @@
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15005,6 +15005,9 @@
       <c r="B1814" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1814" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1815" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1815" s="3" t="s">
@@ -15021,7 +15024,7 @@
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15090,9 +15093,6 @@
       <c r="B1825" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1825" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1826" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1826" s="3" t="s">
@@ -15100,19 +15100,19 @@
       </c>
     </row>
     <row r="1827" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1827" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B1827" s="7" t="s">
-        <v>3</v>
+      <c r="B1827" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C1827" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1828" s="3" t="s">
-        <v>4</v>
+      <c r="A1828" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B1828" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1828" s="5" t="s">
         <v>13</v>
@@ -15120,7 +15120,7 @@
     </row>
     <row r="1829" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1829" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1829" s="5" t="s">
         <v>13</v>
@@ -15128,7 +15128,7 @@
     </row>
     <row r="1830" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1830" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1830" s="5" t="s">
         <v>13</v>
@@ -15136,7 +15136,7 @@
     </row>
     <row r="1831" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1831" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1831" s="5" t="s">
         <v>13</v>
@@ -15144,7 +15144,7 @@
     </row>
     <row r="1832" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1832" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1832" s="5" t="s">
         <v>13</v>
@@ -15152,7 +15152,7 @@
     </row>
     <row r="1833" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1833" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1833" s="5" t="s">
         <v>13</v>
@@ -15160,7 +15160,7 @@
     </row>
     <row r="1834" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1834" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1834" s="5" t="s">
         <v>13</v>
@@ -15168,7 +15168,7 @@
     </row>
     <row r="1835" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1835" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1835" s="5" t="s">
         <v>13</v>
@@ -15176,23 +15176,23 @@
     </row>
     <row r="1836" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1836" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C1836" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1837" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1837" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B1837" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1837" s="5" t="s">
-        <v>13</v>
+      <c r="B1837" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="1838" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1838" s="3" t="s">
-        <v>4</v>
+      <c r="A1838" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B1838" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1838" s="5" t="s">
         <v>13</v>
@@ -15200,7 +15200,7 @@
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1839" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1839" s="5" t="s">
         <v>13</v>
@@ -15208,56 +15208,144 @@
     </row>
     <row r="1840" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1840" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1840" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="1841" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="1841" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1841" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1841" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="1842" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="1842" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1842" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1842" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="1843" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="1843" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1843" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1843" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="1844" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="1844" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1844" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1844" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="1845" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="1845" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1845" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1846" spans="2:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C1845" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1846" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1846" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="1847" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B1847" s="3">
+        <v>11</v>
+      </c>
+      <c r="C1846" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1847" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1847" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1848" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1848" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B1848" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1848" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1849" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1849" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1849" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1850" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1850" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1851" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1851" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1851" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1852" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1852" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1852" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1853" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1853" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1853" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1854" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1854" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1854" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1855" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1855" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1855" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1856" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1856" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1857" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1857" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1858" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1858" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA6D4058-15E6-4D3B-86F7-B6612503E7BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A04931-7FB4-4C1C-A087-0EBB34824428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3543" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3564" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1858"/>
+  <dimension ref="A1:C1869"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5212,9 +5212,6 @@
       <c r="B594" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C594" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B595" s="3" t="s">
@@ -5226,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5303,6 +5300,9 @@
       <c r="B605" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C605" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B606" s="3" t="s">
@@ -5314,7 +5314,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5402,7 +5402,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5490,7 +5490,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5578,7 +5578,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5666,7 +5666,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5743,9 +5743,6 @@
       <c r="B660" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C660" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B661" s="3" t="s">
@@ -5757,7 +5754,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5848,7 +5845,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5939,7 +5936,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6030,7 +6027,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6107,6 +6104,9 @@
       <c r="B704" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C704" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="705" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B705" s="3" t="s">
@@ -6118,7 +6118,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6195,9 +6195,6 @@
       <c r="B715" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C715" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="716" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B716" s="3" t="s">
@@ -6209,7 +6206,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6300,7 +6297,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6391,7 +6388,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6482,7 +6479,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6573,7 +6570,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6664,7 +6661,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6755,7 +6752,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6846,7 +6843,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6937,7 +6934,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -7028,7 +7025,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7119,7 +7116,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7210,7 +7207,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7301,7 +7298,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7392,7 +7389,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7483,7 +7480,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7574,7 +7571,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7665,7 +7662,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7756,7 +7753,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7847,7 +7844,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7938,7 +7935,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -8029,7 +8026,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8120,7 +8117,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8211,7 +8208,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8302,7 +8299,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8393,7 +8390,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8484,7 +8481,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8575,7 +8572,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8666,7 +8663,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8757,7 +8754,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8848,7 +8845,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8939,7 +8936,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -9030,7 +9027,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9121,7 +9118,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9198,6 +9195,9 @@
       <c r="B1078" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1078" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1079" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1079" s="3" t="s">
@@ -9209,7 +9209,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9286,9 +9286,6 @@
       <c r="B1089" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1089" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1090" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1090" s="3" t="s">
@@ -9300,7 +9297,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9391,7 +9388,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9482,7 +9479,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9573,7 +9570,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9664,7 +9661,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9755,7 +9752,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9846,7 +9843,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9937,7 +9934,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -10028,7 +10025,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10119,7 +10116,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10188,6 +10185,9 @@
       <c r="B1198" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1198" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1199" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1199" s="3" t="s">
@@ -10207,7 +10207,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10276,9 +10276,6 @@
       <c r="B1209" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1209" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1210" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1210" s="3" t="s">
@@ -10298,7 +10295,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10375,6 +10372,9 @@
       <c r="B1221" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1221" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1222" s="3" t="s">
@@ -10386,7 +10386,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10455,6 +10455,9 @@
       <c r="B1231" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1231" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1232" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1232" s="3" t="s">
@@ -10471,7 +10474,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10540,9 +10543,6 @@
       <c r="B1242" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1242" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1243" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1243" s="3" t="s">
@@ -10559,7 +10559,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10628,6 +10628,9 @@
       <c r="B1253" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1253" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1254" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1254" s="3" t="s">
@@ -10644,7 +10647,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10713,9 +10716,6 @@
       <c r="B1264" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1264" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1265" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1265" s="3" t="s">
@@ -10732,7 +10732,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10820,7 +10820,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10908,7 +10908,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10977,6 +10977,9 @@
       <c r="B1297" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1297" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1298" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1298" s="3" t="s">
@@ -10993,7 +10996,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11078,7 +11081,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11163,7 +11166,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11248,7 +11251,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11333,7 +11336,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11418,7 +11421,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11503,7 +11506,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11588,7 +11591,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11673,7 +11676,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11758,7 +11761,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11843,7 +11846,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11928,7 +11931,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -11997,9 +12000,6 @@
       <c r="B1429" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1429" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1430" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1430" s="3" t="s">
@@ -12016,7 +12016,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12085,6 +12085,9 @@
       <c r="B1440" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1440" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1441" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1441" s="3" t="s">
@@ -12101,7 +12104,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12186,7 +12189,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12271,7 +12274,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12340,9 +12343,6 @@
       <c r="B1473" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1473" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1474" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1474" s="3" t="s">
@@ -12359,7 +12359,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12447,7 +12447,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12516,6 +12516,9 @@
       <c r="B1495" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1495" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1496" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1496" s="3" t="s">
@@ -12532,7 +12535,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12617,7 +12620,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12702,7 +12705,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12787,7 +12790,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12856,9 +12859,6 @@
       <c r="B1539" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1539" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1540" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1540" s="3" t="s">
@@ -12875,7 +12875,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -12963,7 +12963,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13040,9 +13040,6 @@
       <c r="B1562" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1562" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1563" s="3" t="s">
@@ -13054,7 +13051,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13131,6 +13128,9 @@
       <c r="B1573" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1573" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1574" s="3" t="s">
@@ -13142,7 +13142,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13230,7 +13230,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13318,7 +13318,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13406,7 +13406,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13494,7 +13494,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13563,6 +13563,9 @@
       <c r="B1627" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1627" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1628" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1628" s="3" t="s">
@@ -13579,7 +13582,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13640,7 +13643,9 @@
       <c r="B1637" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1637" s="6"/>
+      <c r="C1637" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1638" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1638" s="3" t="s">
@@ -13656,10 +13661,13 @@
       <c r="B1640" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1640" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13720,17 +13728,12 @@
       <c r="B1648" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1648" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1648" s="6"/>
     </row>
     <row r="1649" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1649" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1649" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1650" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1650" s="3" t="s">
@@ -13741,13 +13744,10 @@
       <c r="B1651" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1651" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13835,7 +13835,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13923,7 +13923,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -13992,6 +13992,9 @@
       <c r="B1682" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1682" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1683" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1683" s="3" t="s">
@@ -14008,7 +14011,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14093,7 +14096,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14167,9 +14170,6 @@
       <c r="B1705" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1705" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1706" s="3" t="s">
@@ -14181,7 +14181,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14242,7 +14242,9 @@
       <c r="B1714" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1714" s="6"/>
+      <c r="C1714" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1715" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1715" s="3" t="s">
@@ -14253,15 +14255,21 @@
       <c r="B1716" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1716" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1717" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1717" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14322,9 +14330,7 @@
       <c r="B1725" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1725" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1725" s="6"/>
     </row>
     <row r="1726" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1726" s="3" t="s">
@@ -14340,13 +14346,10 @@
       <c r="B1728" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1728" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14415,9 +14418,6 @@
       <c r="B1737" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1737" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1738" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1738" s="3" t="s">
@@ -14434,7 +14434,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14503,6 +14503,9 @@
       <c r="B1748" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1748" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1749" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1749" s="3" t="s">
@@ -14519,7 +14522,7 @@
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14598,10 +14601,13 @@
       <c r="B1761" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1761" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14680,13 +14686,10 @@
       <c r="B1772" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1772" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14755,9 +14758,6 @@
       <c r="B1781" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1781" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1782" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1782" s="3" t="s">
@@ -14774,7 +14774,7 @@
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14795,19 +14795,25 @@
       <c r="B1786" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1786" s="6"/>
+      <c r="C1786" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1787" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1787" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1787" s="6"/>
+      <c r="C1787" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1788" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1788" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1788" s="6"/>
+      <c r="C1788" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1789" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1789" s="3" t="s">
@@ -14829,12 +14835,17 @@
       <c r="B1791" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1791" s="6"/>
+      <c r="C1791" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1792" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1792" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1792" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1793" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1793" s="3" t="s">
@@ -14845,10 +14856,13 @@
       <c r="B1794" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1794" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14869,25 +14883,19 @@
       <c r="B1797" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1797" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1797" s="6"/>
     </row>
     <row r="1798" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1798" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1798" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1798" s="6"/>
     </row>
     <row r="1799" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1799" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1799" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1799" s="6"/>
     </row>
     <row r="1800" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1800" s="3" t="s">
@@ -14909,17 +14917,12 @@
       <c r="B1802" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1802" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1802" s="6"/>
     </row>
     <row r="1803" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1803" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1803" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1804" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1804" s="3" t="s">
@@ -14930,13 +14933,10 @@
       <c r="B1805" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1805" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15024,7 +15024,7 @@
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15093,6 +15093,9 @@
       <c r="B1825" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1825" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1826" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1826" s="3" t="s">
@@ -15109,7 +15112,7 @@
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15178,9 +15181,6 @@
       <c r="B1836" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1836" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1837" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1837" s="3" t="s">
@@ -15188,19 +15188,19 @@
       </c>
     </row>
     <row r="1838" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1838" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B1838" s="7" t="s">
-        <v>3</v>
+      <c r="B1838" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C1838" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1839" s="3" t="s">
-        <v>4</v>
+      <c r="A1839" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B1839" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1839" s="5" t="s">
         <v>13</v>
@@ -15208,7 +15208,7 @@
     </row>
     <row r="1840" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1840" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1840" s="5" t="s">
         <v>13</v>
@@ -15216,7 +15216,7 @@
     </row>
     <row r="1841" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1841" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1841" s="5" t="s">
         <v>13</v>
@@ -15224,7 +15224,7 @@
     </row>
     <row r="1842" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1842" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1842" s="5" t="s">
         <v>13</v>
@@ -15232,7 +15232,7 @@
     </row>
     <row r="1843" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1843" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1843" s="5" t="s">
         <v>13</v>
@@ -15240,7 +15240,7 @@
     </row>
     <row r="1844" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1844" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1844" s="5" t="s">
         <v>13</v>
@@ -15248,7 +15248,7 @@
     </row>
     <row r="1845" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1845" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1845" s="5" t="s">
         <v>13</v>
@@ -15256,7 +15256,7 @@
     </row>
     <row r="1846" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1846" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1846" s="5" t="s">
         <v>13</v>
@@ -15264,23 +15264,23 @@
     </row>
     <row r="1847" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1847" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C1847" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1848" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1848" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B1848" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1848" s="5" t="s">
-        <v>13</v>
+      <c r="B1848" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="1849" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1849" s="3" t="s">
-        <v>4</v>
+      <c r="A1849" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B1849" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1849" s="5" t="s">
         <v>13</v>
@@ -15288,7 +15288,7 @@
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1850" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1850" s="5" t="s">
         <v>13</v>
@@ -15296,7 +15296,7 @@
     </row>
     <row r="1851" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1851" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1851" s="5" t="s">
         <v>13</v>
@@ -15304,7 +15304,7 @@
     </row>
     <row r="1852" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1852" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1852" s="5" t="s">
         <v>13</v>
@@ -15312,7 +15312,7 @@
     </row>
     <row r="1853" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1853" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1853" s="5" t="s">
         <v>13</v>
@@ -15320,7 +15320,7 @@
     </row>
     <row r="1854" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1854" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1854" s="5" t="s">
         <v>13</v>
@@ -15328,7 +15328,7 @@
     </row>
     <row r="1855" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1855" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1855" s="5" t="s">
         <v>13</v>
@@ -15336,16 +15336,104 @@
     </row>
     <row r="1856" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1856" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1857" spans="2:2" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C1856" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1857" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1857" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="1858" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1858" s="3">
+        <v>11</v>
+      </c>
+      <c r="C1857" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1858" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1858" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1859" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1859" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B1859" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1859" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1860" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1860" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1860" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1861" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1861" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1862" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1862" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1862" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1863" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1863" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1863" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1864" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1864" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1864" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1865" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1865" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1865" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1866" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1866" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1866" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1867" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1867" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1868" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1868" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1869" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1869" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15A04931-7FB4-4C1C-A087-0EBB34824428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2626EA5C-447C-4B59-B052-0C5FBF4BAC8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3564" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3585" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1869"/>
+  <dimension ref="A1:C1880"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5300,9 +5300,6 @@
       <c r="B605" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C605" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B606" s="3" t="s">
@@ -5314,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5391,6 +5388,9 @@
       <c r="B616" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C616" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B617" s="3" t="s">
@@ -5402,7 +5402,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5490,7 +5490,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5578,7 +5578,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5666,7 +5666,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5754,7 +5754,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5831,9 +5831,6 @@
       <c r="B671" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C671" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B672" s="3" t="s">
@@ -5845,7 +5842,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5936,7 +5933,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6027,7 +6024,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6118,7 +6115,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6195,6 +6192,9 @@
       <c r="B715" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C715" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="716" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B716" s="3" t="s">
@@ -6206,7 +6206,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6283,9 +6283,6 @@
       <c r="B726" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C726" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="727" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B727" s="3" t="s">
@@ -6297,7 +6294,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6388,7 +6385,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6479,7 +6476,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6570,7 +6567,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6661,7 +6658,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6752,7 +6749,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6843,7 +6840,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6934,7 +6931,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -7025,7 +7022,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7116,7 +7113,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7207,7 +7204,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7298,7 +7295,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7389,7 +7386,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7480,7 +7477,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7571,7 +7568,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7662,7 +7659,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7753,7 +7750,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7844,7 +7841,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7935,7 +7932,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -8026,7 +8023,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8117,7 +8114,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8208,7 +8205,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8299,7 +8296,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8390,7 +8387,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8481,7 +8478,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8572,7 +8569,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8663,7 +8660,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8754,7 +8751,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8845,7 +8842,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8936,7 +8933,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -9027,7 +9024,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9118,7 +9115,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9209,7 +9206,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9286,6 +9283,9 @@
       <c r="B1089" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1089" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1090" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1090" s="3" t="s">
@@ -9297,7 +9297,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9374,9 +9374,6 @@
       <c r="B1100" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1100" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1101" s="3" t="s">
@@ -9388,7 +9385,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9479,7 +9476,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9570,7 +9567,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9661,7 +9658,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9752,7 +9749,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9843,7 +9840,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9934,7 +9931,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -10025,7 +10022,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10116,7 +10113,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10207,7 +10204,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10276,6 +10273,9 @@
       <c r="B1209" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1209" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1210" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1210" s="3" t="s">
@@ -10295,7 +10295,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10364,9 +10364,6 @@
       <c r="B1220" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1220" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1221" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1221" s="3" t="s">
@@ -10386,7 +10383,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10463,6 +10460,9 @@
       <c r="B1232" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1232" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1233" s="3" t="s">
@@ -10474,7 +10474,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10543,6 +10543,9 @@
       <c r="B1242" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1242" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1243" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1243" s="3" t="s">
@@ -10559,7 +10562,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10628,9 +10631,6 @@
       <c r="B1253" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1253" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1254" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1254" s="3" t="s">
@@ -10647,7 +10647,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10716,6 +10716,9 @@
       <c r="B1264" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1264" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1265" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1265" s="3" t="s">
@@ -10732,7 +10735,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10801,9 +10804,6 @@
       <c r="B1275" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1275" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1276" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1276" s="3" t="s">
@@ -10820,7 +10820,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10908,7 +10908,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10996,7 +10996,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11065,6 +11065,9 @@
       <c r="B1308" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1308" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1309" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1309" s="3" t="s">
@@ -11081,7 +11084,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11166,7 +11169,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11251,7 +11254,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11336,7 +11339,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11421,7 +11424,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11506,7 +11509,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11591,7 +11594,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11676,7 +11679,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11761,7 +11764,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11846,7 +11849,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11931,7 +11934,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12016,7 +12019,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12085,9 +12088,6 @@
       <c r="B1440" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1440" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1441" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1441" s="3" t="s">
@@ -12104,7 +12104,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12173,6 +12173,9 @@
       <c r="B1451" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1451" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1452" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1452" s="3" t="s">
@@ -12189,7 +12192,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12274,7 +12277,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12359,7 +12362,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12428,9 +12431,6 @@
       <c r="B1484" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1484" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1485" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1485" s="3" t="s">
@@ -12447,7 +12447,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12535,7 +12535,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12604,6 +12604,9 @@
       <c r="B1506" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1506" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1507" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1507" s="3" t="s">
@@ -12620,7 +12623,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12705,7 +12708,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12790,7 +12793,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12875,7 +12878,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -12944,9 +12947,6 @@
       <c r="B1550" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1550" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1551" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1551" s="3" t="s">
@@ -12963,7 +12963,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13051,7 +13051,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13128,9 +13128,6 @@
       <c r="B1573" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1573" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1574" s="3" t="s">
@@ -13142,7 +13139,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13219,6 +13216,9 @@
       <c r="B1584" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1584" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1585" s="3" t="s">
@@ -13230,7 +13230,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13318,7 +13318,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13406,7 +13406,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13494,7 +13494,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13582,7 +13582,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13651,6 +13651,9 @@
       <c r="B1638" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1638" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1639" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1639" s="3" t="s">
@@ -13667,7 +13670,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13728,7 +13731,9 @@
       <c r="B1648" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1648" s="6"/>
+      <c r="C1648" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1649" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1649" s="3" t="s">
@@ -13744,10 +13749,13 @@
       <c r="B1651" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1651" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13808,17 +13816,12 @@
       <c r="B1659" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1659" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1659" s="6"/>
     </row>
     <row r="1660" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1660" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1660" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1661" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1661" s="3" t="s">
@@ -13829,13 +13832,10 @@
       <c r="B1662" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1662" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13923,7 +13923,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14011,7 +14011,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14080,6 +14080,9 @@
       <c r="B1693" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1693" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1694" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1694" s="3" t="s">
@@ -14096,7 +14099,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14181,7 +14184,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14255,9 +14258,6 @@
       <c r="B1716" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1716" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1717" s="3" t="s">
@@ -14269,7 +14269,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14330,7 +14330,9 @@
       <c r="B1725" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1725" s="6"/>
+      <c r="C1725" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1726" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1726" s="3" t="s">
@@ -14341,15 +14343,21 @@
       <c r="B1727" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1727" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1728" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1728" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14410,9 +14418,7 @@
       <c r="B1736" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1736" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1736" s="6"/>
     </row>
     <row r="1737" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1737" s="3" t="s">
@@ -14428,13 +14434,10 @@
       <c r="B1739" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1739" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14503,9 +14506,6 @@
       <c r="B1748" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1748" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1749" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1749" s="3" t="s">
@@ -14522,7 +14522,7 @@
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14591,6 +14591,9 @@
       <c r="B1759" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1759" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1760" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1760" s="3" t="s">
@@ -14607,7 +14610,7 @@
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14686,10 +14689,13 @@
       <c r="B1772" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1772" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14768,13 +14774,10 @@
       <c r="B1783" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1783" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14843,9 +14846,6 @@
       <c r="B1792" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1792" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1793" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1793" s="3" t="s">
@@ -14862,7 +14862,7 @@
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14883,19 +14883,25 @@
       <c r="B1797" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1797" s="6"/>
+      <c r="C1797" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1798" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1798" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1798" s="6"/>
+      <c r="C1798" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1799" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1799" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1799" s="6"/>
+      <c r="C1799" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1800" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1800" s="3" t="s">
@@ -14917,12 +14923,17 @@
       <c r="B1802" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1802" s="6"/>
+      <c r="C1802" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1803" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1803" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1803" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1804" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1804" s="3" t="s">
@@ -14933,10 +14944,13 @@
       <c r="B1805" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1805" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -14957,25 +14971,19 @@
       <c r="B1808" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1808" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1808" s="6"/>
     </row>
     <row r="1809" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1809" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1809" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1809" s="6"/>
     </row>
     <row r="1810" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1810" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1810" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1810" s="6"/>
     </row>
     <row r="1811" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1811" s="3" t="s">
@@ -14997,17 +15005,12 @@
       <c r="B1813" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1813" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1813" s="6"/>
     </row>
     <row r="1814" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1814" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1814" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1815" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1815" s="3" t="s">
@@ -15018,13 +15021,10 @@
       <c r="B1816" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1816" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15112,7 +15112,7 @@
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15181,6 +15181,9 @@
       <c r="B1836" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1836" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1837" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1837" s="3" t="s">
@@ -15197,7 +15200,7 @@
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15266,9 +15269,6 @@
       <c r="B1847" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1847" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1848" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1848" s="3" t="s">
@@ -15276,19 +15276,19 @@
       </c>
     </row>
     <row r="1849" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1849" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B1849" s="7" t="s">
-        <v>3</v>
+      <c r="B1849" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C1849" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1850" s="3" t="s">
-        <v>4</v>
+      <c r="A1850" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B1850" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1850" s="5" t="s">
         <v>13</v>
@@ -15296,7 +15296,7 @@
     </row>
     <row r="1851" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1851" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1851" s="5" t="s">
         <v>13</v>
@@ -15304,7 +15304,7 @@
     </row>
     <row r="1852" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1852" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1852" s="5" t="s">
         <v>13</v>
@@ -15312,7 +15312,7 @@
     </row>
     <row r="1853" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1853" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1853" s="5" t="s">
         <v>13</v>
@@ -15320,7 +15320,7 @@
     </row>
     <row r="1854" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1854" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1854" s="5" t="s">
         <v>13</v>
@@ -15328,7 +15328,7 @@
     </row>
     <row r="1855" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1855" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1855" s="5" t="s">
         <v>13</v>
@@ -15336,7 +15336,7 @@
     </row>
     <row r="1856" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1856" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1856" s="5" t="s">
         <v>13</v>
@@ -15344,7 +15344,7 @@
     </row>
     <row r="1857" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1857" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1857" s="5" t="s">
         <v>13</v>
@@ -15352,23 +15352,23 @@
     </row>
     <row r="1858" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1858" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C1858" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1859" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1859" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B1859" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1859" s="5" t="s">
-        <v>13</v>
+      <c r="B1859" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="1860" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1860" s="3" t="s">
-        <v>4</v>
+      <c r="A1860" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B1860" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1860" s="5" t="s">
         <v>13</v>
@@ -15376,7 +15376,7 @@
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1861" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1861" s="5" t="s">
         <v>13</v>
@@ -15384,7 +15384,7 @@
     </row>
     <row r="1862" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1862" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1862" s="5" t="s">
         <v>13</v>
@@ -15392,7 +15392,7 @@
     </row>
     <row r="1863" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1863" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1863" s="5" t="s">
         <v>13</v>
@@ -15400,7 +15400,7 @@
     </row>
     <row r="1864" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1864" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1864" s="5" t="s">
         <v>13</v>
@@ -15408,7 +15408,7 @@
     </row>
     <row r="1865" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1865" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1865" s="5" t="s">
         <v>13</v>
@@ -15416,7 +15416,7 @@
     </row>
     <row r="1866" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1866" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1866" s="5" t="s">
         <v>13</v>
@@ -15424,16 +15424,104 @@
     </row>
     <row r="1867" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1867" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C1867" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1868" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1868" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C1868" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1869" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1869" s="3">
+      <c r="B1869" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1870" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1870" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B1870" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1870" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1871" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1871" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1871" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1872" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1872" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1873" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1873" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1873" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1874" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1874" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1874" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1875" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1875" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1875" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1876" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1876" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1876" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1877" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1877" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1877" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1878" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1878" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1879" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1879" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1880" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1880" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2626EA5C-447C-4B59-B052-0C5FBF4BAC8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B1D261B-E411-46A9-B666-59FBAB77A8CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3585" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3606" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1880"/>
+  <dimension ref="A1:C1891"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5388,9 +5388,6 @@
       <c r="B616" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C616" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="617" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B617" s="3" t="s">
@@ -5402,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5479,6 +5476,9 @@
       <c r="B627" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C627" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B628" s="3" t="s">
@@ -5490,7 +5490,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5578,7 +5578,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5666,7 +5666,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5754,7 +5754,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5842,7 +5842,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5919,9 +5919,6 @@
       <c r="B682" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C682" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B683" s="3" t="s">
@@ -5933,7 +5930,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6024,7 +6021,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6115,7 +6112,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6206,7 +6203,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6283,6 +6280,9 @@
       <c r="B726" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C726" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="727" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B727" s="3" t="s">
@@ -6294,7 +6294,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6371,9 +6371,6 @@
       <c r="B737" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C737" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="738" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B738" s="3" t="s">
@@ -6385,7 +6382,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6476,7 +6473,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6567,7 +6564,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6658,7 +6655,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6749,7 +6746,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6840,7 +6837,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6931,7 +6928,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -7022,7 +7019,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7113,7 +7110,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7204,7 +7201,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7295,7 +7292,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7386,7 +7383,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7477,7 +7474,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7568,7 +7565,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7659,7 +7656,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7750,7 +7747,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7841,7 +7838,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7932,7 +7929,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -8023,7 +8020,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8114,7 +8111,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8205,7 +8202,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8296,7 +8293,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8387,7 +8384,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8478,7 +8475,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8569,7 +8566,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8660,7 +8657,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8751,7 +8748,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8842,7 +8839,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8933,7 +8930,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -9024,7 +9021,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9115,7 +9112,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9206,7 +9203,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9297,7 +9294,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9374,6 +9371,9 @@
       <c r="B1100" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1100" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1101" s="3" t="s">
@@ -9385,7 +9385,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9462,9 +9462,6 @@
       <c r="B1111" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1111" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1112" s="3" t="s">
@@ -9476,7 +9473,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9567,7 +9564,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9658,7 +9655,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9749,7 +9746,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9840,7 +9837,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9931,7 +9928,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -10022,7 +10019,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10113,7 +10110,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10204,7 +10201,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10295,7 +10292,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10364,6 +10361,9 @@
       <c r="B1220" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1220" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1221" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1221" s="3" t="s">
@@ -10383,7 +10383,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10452,9 +10452,6 @@
       <c r="B1231" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1231" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1232" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1232" s="3" t="s">
@@ -10474,7 +10471,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10551,6 +10548,9 @@
       <c r="B1243" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1243" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1244" s="3" t="s">
@@ -10562,7 +10562,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10631,6 +10631,9 @@
       <c r="B1253" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1253" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1254" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1254" s="3" t="s">
@@ -10647,7 +10650,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10716,9 +10719,6 @@
       <c r="B1264" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1264" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1265" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1265" s="3" t="s">
@@ -10735,7 +10735,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10804,6 +10804,9 @@
       <c r="B1275" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1275" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1276" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1276" s="3" t="s">
@@ -10820,7 +10823,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10889,9 +10892,6 @@
       <c r="B1286" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1286" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1287" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1287" s="3" t="s">
@@ -10908,7 +10908,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10996,7 +10996,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11084,7 +11084,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11153,6 +11153,9 @@
       <c r="B1319" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1319" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1320" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1320" s="3" t="s">
@@ -11169,7 +11172,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11254,7 +11257,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11339,7 +11342,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11424,7 +11427,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11509,7 +11512,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11594,7 +11597,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11679,7 +11682,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11764,7 +11767,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11849,7 +11852,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11934,7 +11937,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12019,7 +12022,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12104,7 +12107,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12173,9 +12176,6 @@
       <c r="B1451" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1451" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1452" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1452" s="3" t="s">
@@ -12192,7 +12192,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12261,6 +12261,9 @@
       <c r="B1462" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1462" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1463" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1463" s="3" t="s">
@@ -12277,7 +12280,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12362,7 +12365,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12447,7 +12450,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12516,9 +12519,6 @@
       <c r="B1495" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1495" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1496" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1496" s="3" t="s">
@@ -12535,7 +12535,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12623,7 +12623,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12692,6 +12692,9 @@
       <c r="B1517" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1517" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1518" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1518" s="3" t="s">
@@ -12708,7 +12711,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12793,7 +12796,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12878,7 +12881,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -12963,7 +12966,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13032,9 +13035,6 @@
       <c r="B1561" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1561" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1562" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1562" s="3" t="s">
@@ -13051,7 +13051,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13139,7 +13139,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13216,9 +13216,6 @@
       <c r="B1584" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1584" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1585" s="3" t="s">
@@ -13230,7 +13227,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13307,6 +13304,9 @@
       <c r="B1595" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1595" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1596" s="3" t="s">
@@ -13318,7 +13318,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13406,7 +13406,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13494,7 +13494,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13582,7 +13582,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13670,7 +13670,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13739,6 +13739,9 @@
       <c r="B1649" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1649" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1650" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1650" s="3" t="s">
@@ -13755,7 +13758,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13816,7 +13819,9 @@
       <c r="B1659" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1659" s="6"/>
+      <c r="C1659" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1660" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1660" s="3" t="s">
@@ -13832,10 +13837,13 @@
       <c r="B1662" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1662" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13896,17 +13904,12 @@
       <c r="B1670" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1670" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1670" s="6"/>
     </row>
     <row r="1671" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1671" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1671" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1672" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1672" s="3" t="s">
@@ -13917,13 +13920,10 @@
       <c r="B1673" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1673" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14011,7 +14011,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14099,7 +14099,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14168,6 +14168,9 @@
       <c r="B1704" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1704" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1705" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1705" s="3" t="s">
@@ -14184,7 +14187,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14269,7 +14272,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14343,9 +14346,6 @@
       <c r="B1727" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1727" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1728" s="3" t="s">
@@ -14357,7 +14357,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14418,7 +14418,9 @@
       <c r="B1736" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1736" s="6"/>
+      <c r="C1736" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1737" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1737" s="3" t="s">
@@ -14429,15 +14431,21 @@
       <c r="B1738" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1738" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1739" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1739" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14498,9 +14506,7 @@
       <c r="B1747" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1747" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1747" s="6"/>
     </row>
     <row r="1748" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1748" s="3" t="s">
@@ -14516,13 +14522,10 @@
       <c r="B1750" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1750" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14591,9 +14594,6 @@
       <c r="B1759" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1759" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1760" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1760" s="3" t="s">
@@ -14610,7 +14610,7 @@
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14679,6 +14679,9 @@
       <c r="B1770" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1770" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1771" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1771" s="3" t="s">
@@ -14695,7 +14698,7 @@
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14774,10 +14777,13 @@
       <c r="B1783" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1783" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14856,13 +14862,10 @@
       <c r="B1794" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1794" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14931,9 +14934,6 @@
       <c r="B1803" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1803" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1804" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1804" s="3" t="s">
@@ -14950,7 +14950,7 @@
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -14971,19 +14971,25 @@
       <c r="B1808" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1808" s="6"/>
+      <c r="C1808" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1809" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1809" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1809" s="6"/>
+      <c r="C1809" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1810" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1810" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1810" s="6"/>
+      <c r="C1810" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1811" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1811" s="3" t="s">
@@ -15005,12 +15011,17 @@
       <c r="B1813" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1813" s="6"/>
+      <c r="C1813" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1814" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1814" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1814" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1815" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1815" s="3" t="s">
@@ -15021,10 +15032,13 @@
       <c r="B1816" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1816" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15045,25 +15059,19 @@
       <c r="B1819" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1819" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1819" s="6"/>
     </row>
     <row r="1820" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1820" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1820" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1820" s="6"/>
     </row>
     <row r="1821" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1821" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1821" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1821" s="6"/>
     </row>
     <row r="1822" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1822" s="3" t="s">
@@ -15085,17 +15093,12 @@
       <c r="B1824" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1824" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1824" s="6"/>
     </row>
     <row r="1825" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1825" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1825" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1826" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1826" s="3" t="s">
@@ -15106,13 +15109,10 @@
       <c r="B1827" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1827" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15200,7 +15200,7 @@
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15269,6 +15269,9 @@
       <c r="B1847" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1847" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1848" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1848" s="3" t="s">
@@ -15285,7 +15288,7 @@
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15354,9 +15357,6 @@
       <c r="B1858" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1858" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1859" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1859" s="3" t="s">
@@ -15364,19 +15364,19 @@
       </c>
     </row>
     <row r="1860" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1860" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B1860" s="7" t="s">
-        <v>3</v>
+      <c r="B1860" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C1860" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1861" s="3" t="s">
-        <v>4</v>
+      <c r="A1861" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B1861" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1861" s="5" t="s">
         <v>13</v>
@@ -15384,7 +15384,7 @@
     </row>
     <row r="1862" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1862" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1862" s="5" t="s">
         <v>13</v>
@@ -15392,7 +15392,7 @@
     </row>
     <row r="1863" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1863" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1863" s="5" t="s">
         <v>13</v>
@@ -15400,7 +15400,7 @@
     </row>
     <row r="1864" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1864" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1864" s="5" t="s">
         <v>13</v>
@@ -15408,7 +15408,7 @@
     </row>
     <row r="1865" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1865" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1865" s="5" t="s">
         <v>13</v>
@@ -15416,7 +15416,7 @@
     </row>
     <row r="1866" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1866" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1866" s="5" t="s">
         <v>13</v>
@@ -15424,7 +15424,7 @@
     </row>
     <row r="1867" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1867" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1867" s="5" t="s">
         <v>13</v>
@@ -15432,7 +15432,7 @@
     </row>
     <row r="1868" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1868" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1868" s="5" t="s">
         <v>13</v>
@@ -15440,23 +15440,23 @@
     </row>
     <row r="1869" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1869" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C1869" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1870" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1870" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B1870" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1870" s="5" t="s">
-        <v>13</v>
+      <c r="B1870" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="1871" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1871" s="3" t="s">
-        <v>4</v>
+      <c r="A1871" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B1871" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1871" s="5" t="s">
         <v>13</v>
@@ -15464,64 +15464,152 @@
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1872" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1872" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="1873" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="1873" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1873" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1873" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="1874" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="1874" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1874" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1874" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="1875" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="1875" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1875" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1875" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="1876" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="1876" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1876" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1876" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="1877" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="1877" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1877" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1877" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="1878" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="1878" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1878" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1879" spans="2:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C1878" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1879" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1879" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="1880" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B1880" s="3">
+        <v>11</v>
+      </c>
+      <c r="C1879" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1880" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1880" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1881" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1881" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B1881" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1881" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1882" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1882" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1882" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1883" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1883" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1884" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1884" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1884" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1885" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1885" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1885" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1886" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1886" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1886" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1887" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1887" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1887" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1888" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1888" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1888" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1889" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1889" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1890" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1890" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1891" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B1891" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B1D261B-E411-46A9-B666-59FBAB77A8CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E912D730-BF99-4D9B-A596-B769C95A7B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3606" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3627" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1891"/>
+  <dimension ref="A1:C1902"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5476,9 +5476,6 @@
       <c r="B627" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C627" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B628" s="3" t="s">
@@ -5490,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5567,6 +5564,9 @@
       <c r="B638" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C638" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B639" s="3" t="s">
@@ -5578,7 +5578,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5666,7 +5666,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5754,7 +5754,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5842,7 +5842,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5930,7 +5930,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6007,9 +6007,6 @@
       <c r="B693" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C693" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="694" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B694" s="3" t="s">
@@ -6021,7 +6018,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6112,7 +6109,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6203,7 +6200,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6294,7 +6291,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6371,6 +6368,9 @@
       <c r="B737" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C737" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="738" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B738" s="3" t="s">
@@ -6382,7 +6382,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6459,9 +6459,6 @@
       <c r="B748" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C748" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="749" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B749" s="3" t="s">
@@ -6473,7 +6470,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6564,7 +6561,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6655,7 +6652,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6746,7 +6743,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6837,7 +6834,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6928,7 +6925,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -7019,7 +7016,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7110,7 +7107,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7201,7 +7198,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7292,7 +7289,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7383,7 +7380,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7474,7 +7471,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7565,7 +7562,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7656,7 +7653,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7747,7 +7744,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7838,7 +7835,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7929,7 +7926,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -8020,7 +8017,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8111,7 +8108,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8202,7 +8199,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8293,7 +8290,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8384,7 +8381,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8475,7 +8472,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8566,7 +8563,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8657,7 +8654,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8748,7 +8745,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8839,7 +8836,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8930,7 +8927,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -9021,7 +9018,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9112,7 +9109,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9203,7 +9200,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9294,7 +9291,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9385,7 +9382,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9462,6 +9459,9 @@
       <c r="B1111" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1111" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1112" s="3" t="s">
@@ -9473,7 +9473,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9550,9 +9550,6 @@
       <c r="B1122" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1122" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1123" s="3" t="s">
@@ -9564,7 +9561,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9655,7 +9652,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9746,7 +9743,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9837,7 +9834,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9928,7 +9925,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -10019,7 +10016,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10110,7 +10107,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10201,7 +10198,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10292,7 +10289,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10383,7 +10380,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10452,6 +10449,9 @@
       <c r="B1231" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1231" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1232" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1232" s="3" t="s">
@@ -10471,7 +10471,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10540,9 +10540,6 @@
       <c r="B1242" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1242" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1243" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1243" s="3" t="s">
@@ -10562,7 +10559,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10639,6 +10636,9 @@
       <c r="B1254" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1254" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1255" s="3" t="s">
@@ -10650,7 +10650,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10719,6 +10719,9 @@
       <c r="B1264" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1264" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1265" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1265" s="3" t="s">
@@ -10735,7 +10738,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10804,9 +10807,6 @@
       <c r="B1275" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1275" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1276" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1276" s="3" t="s">
@@ -10823,7 +10823,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10892,6 +10892,9 @@
       <c r="B1286" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1286" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1287" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1287" s="3" t="s">
@@ -10908,7 +10911,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10977,9 +10980,6 @@
       <c r="B1297" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1297" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1298" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1298" s="3" t="s">
@@ -10996,7 +10996,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11084,7 +11084,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11172,7 +11172,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11241,6 +11241,9 @@
       <c r="B1330" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1330" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1331" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1331" s="3" t="s">
@@ -11257,7 +11260,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11342,7 +11345,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11427,7 +11430,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11512,7 +11515,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11597,7 +11600,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11682,7 +11685,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11767,7 +11770,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11852,7 +11855,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11937,7 +11940,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12022,7 +12025,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12107,7 +12110,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12192,7 +12195,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12261,9 +12264,6 @@
       <c r="B1462" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1462" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1463" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1463" s="3" t="s">
@@ -12280,7 +12280,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12349,6 +12349,9 @@
       <c r="B1473" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1473" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1474" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1474" s="3" t="s">
@@ -12365,7 +12368,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12450,7 +12453,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12535,7 +12538,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12604,9 +12607,6 @@
       <c r="B1506" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1506" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1507" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1507" s="3" t="s">
@@ -12623,7 +12623,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12711,7 +12711,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12780,6 +12780,9 @@
       <c r="B1528" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1528" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1529" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1529" s="3" t="s">
@@ -12796,7 +12799,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12881,7 +12884,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -12966,7 +12969,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13051,7 +13054,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13120,9 +13123,6 @@
       <c r="B1572" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1572" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1573" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1573" s="3" t="s">
@@ -13139,7 +13139,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13227,7 +13227,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13304,9 +13304,6 @@
       <c r="B1595" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1595" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1596" s="3" t="s">
@@ -13318,7 +13315,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13395,6 +13392,9 @@
       <c r="B1606" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1606" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1607" s="3" t="s">
@@ -13406,7 +13406,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13494,7 +13494,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13582,7 +13582,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13670,7 +13670,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13758,7 +13758,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13827,6 +13827,9 @@
       <c r="B1660" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1660" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1661" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1661" s="3" t="s">
@@ -13843,7 +13846,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13904,7 +13907,9 @@
       <c r="B1670" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1670" s="6"/>
+      <c r="C1670" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1671" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1671" s="3" t="s">
@@ -13920,10 +13925,13 @@
       <c r="B1673" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1673" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -13984,17 +13992,12 @@
       <c r="B1681" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1681" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1681" s="6"/>
     </row>
     <row r="1682" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1682" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1682" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1683" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1683" s="3" t="s">
@@ -14005,13 +14008,10 @@
       <c r="B1684" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1684" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14099,7 +14099,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14187,7 +14187,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14256,6 +14256,9 @@
       <c r="B1715" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1715" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1716" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1716" s="3" t="s">
@@ -14272,7 +14275,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14357,7 +14360,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14431,9 +14434,6 @@
       <c r="B1738" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1738" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1739" s="3" t="s">
@@ -14445,7 +14445,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14506,7 +14506,9 @@
       <c r="B1747" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1747" s="6"/>
+      <c r="C1747" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1748" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1748" s="3" t="s">
@@ -14517,15 +14519,21 @@
       <c r="B1749" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1749" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1750" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1750" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14586,9 +14594,7 @@
       <c r="B1758" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1758" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1758" s="6"/>
     </row>
     <row r="1759" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1759" s="3" t="s">
@@ -14604,13 +14610,10 @@
       <c r="B1761" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1761" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14679,9 +14682,6 @@
       <c r="B1770" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1770" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1771" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1771" s="3" t="s">
@@ -14698,7 +14698,7 @@
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14767,6 +14767,9 @@
       <c r="B1781" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1781" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1782" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1782" s="3" t="s">
@@ -14783,7 +14786,7 @@
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14862,10 +14865,13 @@
       <c r="B1794" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1794" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14944,13 +14950,10 @@
       <c r="B1805" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1805" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15019,9 +15022,6 @@
       <c r="B1814" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1814" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1815" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1815" s="3" t="s">
@@ -15038,7 +15038,7 @@
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15059,19 +15059,25 @@
       <c r="B1819" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1819" s="6"/>
+      <c r="C1819" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1820" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1820" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1820" s="6"/>
+      <c r="C1820" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1821" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1821" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1821" s="6"/>
+      <c r="C1821" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1822" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1822" s="3" t="s">
@@ -15093,12 +15099,17 @@
       <c r="B1824" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1824" s="6"/>
+      <c r="C1824" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1825" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1825" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1825" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1826" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1826" s="3" t="s">
@@ -15109,10 +15120,13 @@
       <c r="B1827" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1827" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15133,25 +15147,19 @@
       <c r="B1830" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1830" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1830" s="6"/>
     </row>
     <row r="1831" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1831" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1831" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1831" s="6"/>
     </row>
     <row r="1832" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1832" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1832" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1832" s="6"/>
     </row>
     <row r="1833" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1833" s="3" t="s">
@@ -15173,17 +15181,12 @@
       <c r="B1835" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1835" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1835" s="6"/>
     </row>
     <row r="1836" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1836" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1836" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1837" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1837" s="3" t="s">
@@ -15194,13 +15197,10 @@
       <c r="B1838" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1838" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15288,7 +15288,7 @@
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15357,6 +15357,9 @@
       <c r="B1858" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1858" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1859" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1859" s="3" t="s">
@@ -15373,7 +15376,7 @@
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15442,9 +15445,6 @@
       <c r="B1869" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1869" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1870" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1870" s="3" t="s">
@@ -15452,19 +15452,19 @@
       </c>
     </row>
     <row r="1871" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1871" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B1871" s="7" t="s">
-        <v>3</v>
+      <c r="B1871" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C1871" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1872" s="3" t="s">
-        <v>4</v>
+      <c r="A1872" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B1872" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1872" s="5" t="s">
         <v>13</v>
@@ -15472,7 +15472,7 @@
     </row>
     <row r="1873" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1873" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1873" s="5" t="s">
         <v>13</v>
@@ -15480,7 +15480,7 @@
     </row>
     <row r="1874" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1874" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1874" s="5" t="s">
         <v>13</v>
@@ -15488,7 +15488,7 @@
     </row>
     <row r="1875" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1875" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1875" s="5" t="s">
         <v>13</v>
@@ -15496,7 +15496,7 @@
     </row>
     <row r="1876" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1876" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1876" s="5" t="s">
         <v>13</v>
@@ -15504,7 +15504,7 @@
     </row>
     <row r="1877" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1877" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1877" s="5" t="s">
         <v>13</v>
@@ -15512,7 +15512,7 @@
     </row>
     <row r="1878" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1878" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1878" s="5" t="s">
         <v>13</v>
@@ -15520,7 +15520,7 @@
     </row>
     <row r="1879" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1879" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1879" s="5" t="s">
         <v>13</v>
@@ -15528,23 +15528,23 @@
     </row>
     <row r="1880" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1880" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C1880" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1881" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1881" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B1881" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1881" s="5" t="s">
-        <v>13</v>
+      <c r="B1881" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="1882" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1882" s="3" t="s">
-        <v>4</v>
+      <c r="A1882" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B1882" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1882" s="5" t="s">
         <v>13</v>
@@ -15552,7 +15552,7 @@
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1883" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1883" s="5" t="s">
         <v>13</v>
@@ -15560,7 +15560,7 @@
     </row>
     <row r="1884" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1884" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1884" s="5" t="s">
         <v>13</v>
@@ -15568,7 +15568,7 @@
     </row>
     <row r="1885" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1885" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1885" s="5" t="s">
         <v>13</v>
@@ -15576,7 +15576,7 @@
     </row>
     <row r="1886" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1886" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1886" s="5" t="s">
         <v>13</v>
@@ -15584,7 +15584,7 @@
     </row>
     <row r="1887" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1887" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1887" s="5" t="s">
         <v>13</v>
@@ -15592,24 +15592,112 @@
     </row>
     <row r="1888" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1888" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1888" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="1889" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="1889" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1889" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1890" spans="2:2" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C1889" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1890" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1890" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="1891" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B1891" s="3">
+        <v>11</v>
+      </c>
+      <c r="C1890" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1891" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1891" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1892" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1892" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B1892" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1892" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1893" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1893" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1893" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1894" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1894" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1895" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1895" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1895" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1896" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1896" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1896" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1897" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1897" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1897" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1898" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1898" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1898" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1899" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1899" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1899" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1900" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1900" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1901" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1901" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1902" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1902" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E912D730-BF99-4D9B-A596-B769C95A7B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A7E0A3-357A-4E46-8ABB-C50F4480833B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3627" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3648" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1902"/>
+  <dimension ref="A1:C1913"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5564,9 +5564,6 @@
       <c r="B638" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C638" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="639" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B639" s="3" t="s">
@@ -5578,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5655,6 +5652,9 @@
       <c r="B649" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C649" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B650" s="3" t="s">
@@ -5666,7 +5666,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5754,7 +5754,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5842,7 +5842,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5930,7 +5930,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6018,7 +6018,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6095,9 +6095,6 @@
       <c r="B704" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C704" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="705" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B705" s="3" t="s">
@@ -6109,7 +6106,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6200,7 +6197,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6291,7 +6288,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6382,7 +6379,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6459,6 +6456,9 @@
       <c r="B748" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C748" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="749" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B749" s="3" t="s">
@@ -6470,7 +6470,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6547,9 +6547,6 @@
       <c r="B759" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C759" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="760" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B760" s="3" t="s">
@@ -6561,7 +6558,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6652,7 +6649,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6743,7 +6740,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6834,7 +6831,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6925,7 +6922,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -7016,7 +7013,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7107,7 +7104,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7198,7 +7195,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7289,7 +7286,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7380,7 +7377,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7471,7 +7468,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7562,7 +7559,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7653,7 +7650,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7744,7 +7741,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7835,7 +7832,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7926,7 +7923,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -8017,7 +8014,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8108,7 +8105,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8199,7 +8196,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8290,7 +8287,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8381,7 +8378,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8472,7 +8469,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8563,7 +8560,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8654,7 +8651,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8745,7 +8742,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8836,7 +8833,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8927,7 +8924,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -9018,7 +9015,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9109,7 +9106,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9200,7 +9197,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9291,7 +9288,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9382,7 +9379,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9473,7 +9470,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9550,6 +9547,9 @@
       <c r="B1122" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1122" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1123" s="3" t="s">
@@ -9561,7 +9561,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9638,9 +9638,6 @@
       <c r="B1133" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1133" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1134" s="3" t="s">
@@ -9652,7 +9649,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9743,7 +9740,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9834,7 +9831,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9925,7 +9922,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -10016,7 +10013,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10107,7 +10104,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10198,7 +10195,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10289,7 +10286,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10380,7 +10377,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10471,7 +10468,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10540,6 +10537,9 @@
       <c r="B1242" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1242" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1243" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1243" s="3" t="s">
@@ -10559,7 +10559,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10628,9 +10628,6 @@
       <c r="B1253" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1253" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1254" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1254" s="3" t="s">
@@ -10650,7 +10647,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10727,6 +10724,9 @@
       <c r="B1265" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1265" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1266" s="3" t="s">
@@ -10738,7 +10738,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10807,6 +10807,9 @@
       <c r="B1275" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1275" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1276" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1276" s="3" t="s">
@@ -10823,7 +10826,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10892,9 +10895,6 @@
       <c r="B1286" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1286" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1287" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1287" s="3" t="s">
@@ -10911,7 +10911,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10980,6 +10980,9 @@
       <c r="B1297" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1297" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1298" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1298" s="3" t="s">
@@ -10996,7 +10999,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11065,9 +11068,6 @@
       <c r="B1308" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1308" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1309" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1309" s="3" t="s">
@@ -11084,7 +11084,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11172,7 +11172,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11260,7 +11260,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11329,6 +11329,9 @@
       <c r="B1341" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1341" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1342" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1342" s="3" t="s">
@@ -11345,7 +11348,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11430,7 +11433,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11515,7 +11518,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11600,7 +11603,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11685,7 +11688,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11770,7 +11773,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11855,7 +11858,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11940,7 +11943,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12025,7 +12028,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12110,7 +12113,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12195,7 +12198,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12280,7 +12283,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12349,9 +12352,6 @@
       <c r="B1473" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1473" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1474" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1474" s="3" t="s">
@@ -12368,7 +12368,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12437,6 +12437,9 @@
       <c r="B1484" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1484" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1485" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1485" s="3" t="s">
@@ -12453,7 +12456,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12538,7 +12541,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12623,7 +12626,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12692,9 +12695,6 @@
       <c r="B1517" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1517" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1518" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1518" s="3" t="s">
@@ -12711,7 +12711,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12799,7 +12799,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12868,6 +12868,9 @@
       <c r="B1539" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1539" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1540" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1540" s="3" t="s">
@@ -12884,7 +12887,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -12969,7 +12972,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13054,7 +13057,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13139,7 +13142,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13208,9 +13211,6 @@
       <c r="B1583" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1583" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1584" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1584" s="3" t="s">
@@ -13227,7 +13227,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13315,7 +13315,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13392,9 +13392,6 @@
       <c r="B1606" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1606" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1607" s="3" t="s">
@@ -13406,7 +13403,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13483,6 +13480,9 @@
       <c r="B1617" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1617" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1618" s="3" t="s">
@@ -13494,7 +13494,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13582,7 +13582,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13670,7 +13670,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13758,7 +13758,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13846,7 +13846,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13915,6 +13915,9 @@
       <c r="B1671" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1671" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1672" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1672" s="3" t="s">
@@ -13931,7 +13934,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -13992,7 +13995,9 @@
       <c r="B1681" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1681" s="6"/>
+      <c r="C1681" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1682" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1682" s="3" t="s">
@@ -14008,10 +14013,13 @@
       <c r="B1684" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1684" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14072,17 +14080,12 @@
       <c r="B1692" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1692" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1692" s="6"/>
     </row>
     <row r="1693" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1693" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1693" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1694" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1694" s="3" t="s">
@@ -14093,13 +14096,10 @@
       <c r="B1695" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1695" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14187,7 +14187,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14275,7 +14275,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14344,6 +14344,9 @@
       <c r="B1726" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1726" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1727" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1727" s="3" t="s">
@@ -14360,7 +14363,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14445,7 +14448,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14519,9 +14522,6 @@
       <c r="B1749" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1749" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1750" s="3" t="s">
@@ -14533,7 +14533,7 @@
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14594,7 +14594,9 @@
       <c r="B1758" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1758" s="6"/>
+      <c r="C1758" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1759" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1759" s="3" t="s">
@@ -14605,15 +14607,21 @@
       <c r="B1760" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1760" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1761" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1761" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14674,9 +14682,7 @@
       <c r="B1769" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1769" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1769" s="6"/>
     </row>
     <row r="1770" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1770" s="3" t="s">
@@ -14692,13 +14698,10 @@
       <c r="B1772" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1772" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14767,9 +14770,6 @@
       <c r="B1781" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1781" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1782" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1782" s="3" t="s">
@@ -14786,7 +14786,7 @@
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14855,6 +14855,9 @@
       <c r="B1792" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1792" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1793" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1793" s="3" t="s">
@@ -14871,7 +14874,7 @@
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14950,10 +14953,13 @@
       <c r="B1805" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1805" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15032,13 +15038,10 @@
       <c r="B1816" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1816" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15107,9 +15110,6 @@
       <c r="B1825" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1825" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1826" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1826" s="3" t="s">
@@ -15126,7 +15126,7 @@
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15147,19 +15147,25 @@
       <c r="B1830" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1830" s="6"/>
+      <c r="C1830" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1831" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1831" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1831" s="6"/>
+      <c r="C1831" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1832" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1832" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1832" s="6"/>
+      <c r="C1832" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1833" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1833" s="3" t="s">
@@ -15181,12 +15187,17 @@
       <c r="B1835" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1835" s="6"/>
+      <c r="C1835" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1836" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1836" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1836" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1837" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1837" s="3" t="s">
@@ -15197,10 +15208,13 @@
       <c r="B1838" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1838" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15221,25 +15235,19 @@
       <c r="B1841" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1841" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1841" s="6"/>
     </row>
     <row r="1842" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1842" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1842" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1842" s="6"/>
     </row>
     <row r="1843" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1843" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1843" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1843" s="6"/>
     </row>
     <row r="1844" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1844" s="3" t="s">
@@ -15261,17 +15269,12 @@
       <c r="B1846" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1846" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1846" s="6"/>
     </row>
     <row r="1847" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1847" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1847" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1848" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1848" s="3" t="s">
@@ -15282,13 +15285,10 @@
       <c r="B1849" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1849" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15376,7 +15376,7 @@
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15445,6 +15445,9 @@
       <c r="B1869" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1869" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1870" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1870" s="3" t="s">
@@ -15461,7 +15464,7 @@
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1872" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B1872" s="7" t="s">
         <v>3</v>
@@ -15530,9 +15533,6 @@
       <c r="B1880" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1880" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1881" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1881" s="3" t="s">
@@ -15540,19 +15540,19 @@
       </c>
     </row>
     <row r="1882" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1882" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B1882" s="7" t="s">
-        <v>3</v>
+      <c r="B1882" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C1882" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1883" s="3" t="s">
-        <v>4</v>
+      <c r="A1883" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B1883" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1883" s="5" t="s">
         <v>13</v>
@@ -15560,7 +15560,7 @@
     </row>
     <row r="1884" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1884" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1884" s="5" t="s">
         <v>13</v>
@@ -15568,7 +15568,7 @@
     </row>
     <row r="1885" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1885" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1885" s="5" t="s">
         <v>13</v>
@@ -15576,7 +15576,7 @@
     </row>
     <row r="1886" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1886" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1886" s="5" t="s">
         <v>13</v>
@@ -15584,7 +15584,7 @@
     </row>
     <row r="1887" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1887" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1887" s="5" t="s">
         <v>13</v>
@@ -15592,7 +15592,7 @@
     </row>
     <row r="1888" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1888" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1888" s="5" t="s">
         <v>13</v>
@@ -15600,7 +15600,7 @@
     </row>
     <row r="1889" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1889" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1889" s="5" t="s">
         <v>13</v>
@@ -15608,7 +15608,7 @@
     </row>
     <row r="1890" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1890" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1890" s="5" t="s">
         <v>13</v>
@@ -15616,23 +15616,23 @@
     </row>
     <row r="1891" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1891" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C1891" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1892" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1892" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B1892" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1892" s="5" t="s">
-        <v>13</v>
+      <c r="B1892" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="1893" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1893" s="3" t="s">
-        <v>4</v>
+      <c r="A1893" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B1893" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1893" s="5" t="s">
         <v>13</v>
@@ -15640,7 +15640,7 @@
     </row>
     <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1894" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1894" s="5" t="s">
         <v>13</v>
@@ -15648,7 +15648,7 @@
     </row>
     <row r="1895" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1895" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1895" s="5" t="s">
         <v>13</v>
@@ -15656,7 +15656,7 @@
     </row>
     <row r="1896" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1896" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1896" s="5" t="s">
         <v>13</v>
@@ -15664,7 +15664,7 @@
     </row>
     <row r="1897" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1897" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1897" s="5" t="s">
         <v>13</v>
@@ -15672,7 +15672,7 @@
     </row>
     <row r="1898" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1898" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1898" s="5" t="s">
         <v>13</v>
@@ -15680,7 +15680,7 @@
     </row>
     <row r="1899" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1899" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1899" s="5" t="s">
         <v>13</v>
@@ -15688,16 +15688,104 @@
     </row>
     <row r="1900" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1900" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C1900" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1901" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1901" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C1901" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1902" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1902" s="3">
+      <c r="B1902" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1903" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1903" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B1903" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1903" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1904" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1904" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1904" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1905" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1905" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1905" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1906" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1906" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1906" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1907" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1907" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1907" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1908" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1908" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1908" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1909" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1909" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1909" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1910" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1910" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1910" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1911" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1911" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1912" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1912" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1913" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1913" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A7E0A3-357A-4E46-8ABB-C50F4480833B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF844D4-4CF2-4C81-B41E-7A06820669FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3648" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3669" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1913"/>
+  <dimension ref="A1:C1924"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5652,9 +5652,6 @@
       <c r="B649" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C649" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B650" s="3" t="s">
@@ -5666,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5743,6 +5740,9 @@
       <c r="B660" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C660" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B661" s="3" t="s">
@@ -5754,7 +5754,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5842,7 +5842,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5930,7 +5930,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6018,7 +6018,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6106,7 +6106,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6183,9 +6183,6 @@
       <c r="B715" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C715" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="716" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B716" s="3" t="s">
@@ -6197,7 +6194,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6288,7 +6285,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6379,7 +6376,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6470,7 +6467,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6547,6 +6544,9 @@
       <c r="B759" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C759" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="760" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B760" s="3" t="s">
@@ -6558,7 +6558,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6635,9 +6635,6 @@
       <c r="B770" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C770" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="771" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B771" s="3" t="s">
@@ -6649,7 +6646,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6740,7 +6737,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6831,7 +6828,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6922,7 +6919,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -7013,7 +7010,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7104,7 +7101,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7195,7 +7192,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7286,7 +7283,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7377,7 +7374,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7468,7 +7465,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7559,7 +7556,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7650,7 +7647,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7741,7 +7738,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7832,7 +7829,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7923,7 +7920,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -8014,7 +8011,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8105,7 +8102,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8196,7 +8193,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8287,7 +8284,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8378,7 +8375,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8469,7 +8466,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8560,7 +8557,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8651,7 +8648,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8742,7 +8739,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8833,7 +8830,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8924,7 +8921,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -9015,7 +9012,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9106,7 +9103,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9197,7 +9194,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9288,7 +9285,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9379,7 +9376,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9470,7 +9467,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9561,7 +9558,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9638,6 +9635,9 @@
       <c r="B1133" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1133" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1134" s="3" t="s">
@@ -9649,7 +9649,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9726,9 +9726,6 @@
       <c r="B1144" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1144" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1145" s="3" t="s">
@@ -9740,7 +9737,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9831,7 +9828,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9922,7 +9919,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -10013,7 +10010,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10104,7 +10101,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10195,7 +10192,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10286,7 +10283,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10377,7 +10374,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10468,7 +10465,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10559,7 +10556,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10628,6 +10625,9 @@
       <c r="B1253" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1253" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1254" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1254" s="3" t="s">
@@ -10647,7 +10647,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10716,9 +10716,6 @@
       <c r="B1264" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1264" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1265" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1265" s="3" t="s">
@@ -10738,7 +10735,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10815,6 +10812,9 @@
       <c r="B1276" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1276" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1277" s="3" t="s">
@@ -10826,7 +10826,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10895,6 +10895,9 @@
       <c r="B1286" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1286" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1287" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1287" s="3" t="s">
@@ -10911,7 +10914,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10980,9 +10983,6 @@
       <c r="B1297" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1297" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1298" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1298" s="3" t="s">
@@ -10999,7 +10999,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11068,6 +11068,9 @@
       <c r="B1308" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1308" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1309" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1309" s="3" t="s">
@@ -11084,7 +11087,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11153,9 +11156,6 @@
       <c r="B1319" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1319" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1320" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1320" s="3" t="s">
@@ -11172,7 +11172,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11260,7 +11260,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11348,7 +11348,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11417,6 +11417,9 @@
       <c r="B1352" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1352" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1353" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1353" s="3" t="s">
@@ -11433,7 +11436,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11518,7 +11521,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11603,7 +11606,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11688,7 +11691,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11773,7 +11776,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11858,7 +11861,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11943,7 +11946,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12028,7 +12031,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12113,7 +12116,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12198,7 +12201,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12283,7 +12286,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12368,7 +12371,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12437,9 +12440,6 @@
       <c r="B1484" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1484" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1485" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1485" s="3" t="s">
@@ -12456,7 +12456,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12525,6 +12525,9 @@
       <c r="B1495" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1495" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1496" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1496" s="3" t="s">
@@ -12541,7 +12544,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12626,7 +12629,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12711,7 +12714,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12780,9 +12783,6 @@
       <c r="B1528" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1528" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1529" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1529" s="3" t="s">
@@ -12799,7 +12799,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12887,7 +12887,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -12956,6 +12956,9 @@
       <c r="B1550" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1550" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1551" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1551" s="3" t="s">
@@ -12972,7 +12975,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13057,7 +13060,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13142,7 +13145,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13227,7 +13230,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13296,9 +13299,6 @@
       <c r="B1594" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1594" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1595" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1595" s="3" t="s">
@@ -13315,7 +13315,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13403,7 +13403,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13480,9 +13480,6 @@
       <c r="B1617" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1617" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1618" s="3" t="s">
@@ -13494,7 +13491,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13571,6 +13568,9 @@
       <c r="B1628" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1628" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1629" s="3" t="s">
@@ -13582,7 +13582,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13670,7 +13670,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13758,7 +13758,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13846,7 +13846,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13934,7 +13934,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14003,6 +14003,9 @@
       <c r="B1682" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1682" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1683" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1683" s="3" t="s">
@@ -14019,7 +14022,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14080,7 +14083,9 @@
       <c r="B1692" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1692" s="6"/>
+      <c r="C1692" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1693" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1693" s="3" t="s">
@@ -14096,10 +14101,13 @@
       <c r="B1695" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1695" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14160,17 +14168,12 @@
       <c r="B1703" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1703" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1703" s="6"/>
     </row>
     <row r="1704" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1704" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1704" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1705" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1705" s="3" t="s">
@@ -14181,13 +14184,10 @@
       <c r="B1706" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1706" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14275,7 +14275,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14363,7 +14363,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14432,6 +14432,9 @@
       <c r="B1737" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1737" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1738" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1738" s="3" t="s">
@@ -14448,7 +14451,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14533,7 +14536,7 @@
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14607,9 +14610,6 @@
       <c r="B1760" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1760" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1761" s="3" t="s">
@@ -14621,7 +14621,7 @@
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14682,7 +14682,9 @@
       <c r="B1769" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1769" s="6"/>
+      <c r="C1769" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1770" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1770" s="3" t="s">
@@ -14693,15 +14695,21 @@
       <c r="B1771" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1771" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1772" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1772" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14762,9 +14770,7 @@
       <c r="B1780" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1780" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1780" s="6"/>
     </row>
     <row r="1781" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1781" s="3" t="s">
@@ -14780,13 +14786,10 @@
       <c r="B1783" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1783" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14855,9 +14858,6 @@
       <c r="B1792" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1792" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1793" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1793" s="3" t="s">
@@ -14874,7 +14874,7 @@
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14943,6 +14943,9 @@
       <c r="B1803" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1803" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1804" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1804" s="3" t="s">
@@ -14959,7 +14962,7 @@
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15038,10 +15041,13 @@
       <c r="B1816" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1816" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15120,13 +15126,10 @@
       <c r="B1827" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1827" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15195,9 +15198,6 @@
       <c r="B1836" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1836" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1837" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1837" s="3" t="s">
@@ -15214,7 +15214,7 @@
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15235,19 +15235,25 @@
       <c r="B1841" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1841" s="6"/>
+      <c r="C1841" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1842" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1842" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1842" s="6"/>
+      <c r="C1842" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1843" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1843" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1843" s="6"/>
+      <c r="C1843" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1844" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1844" s="3" t="s">
@@ -15269,12 +15275,17 @@
       <c r="B1846" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1846" s="6"/>
+      <c r="C1846" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1847" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1847" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1847" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1848" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1848" s="3" t="s">
@@ -15285,10 +15296,13 @@
       <c r="B1849" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1849" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15309,25 +15323,19 @@
       <c r="B1852" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1852" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1852" s="6"/>
     </row>
     <row r="1853" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1853" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1853" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1853" s="6"/>
     </row>
     <row r="1854" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1854" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1854" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1854" s="6"/>
     </row>
     <row r="1855" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1855" s="3" t="s">
@@ -15349,17 +15357,12 @@
       <c r="B1857" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1857" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1857" s="6"/>
     </row>
     <row r="1858" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1858" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1858" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1859" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1859" s="3" t="s">
@@ -15370,13 +15373,10 @@
       <c r="B1860" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1860" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15464,7 +15464,7 @@
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1872" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B1872" s="7" t="s">
         <v>3</v>
@@ -15533,6 +15533,9 @@
       <c r="B1880" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1880" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1881" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1881" s="3" t="s">
@@ -15549,7 +15552,7 @@
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1883" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B1883" s="7" t="s">
         <v>3</v>
@@ -15618,9 +15621,6 @@
       <c r="B1891" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1891" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1892" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1892" s="3" t="s">
@@ -15628,19 +15628,19 @@
       </c>
     </row>
     <row r="1893" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1893" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B1893" s="7" t="s">
-        <v>3</v>
+      <c r="B1893" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C1893" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1894" s="3" t="s">
-        <v>4</v>
+      <c r="A1894" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B1894" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1894" s="5" t="s">
         <v>13</v>
@@ -15648,7 +15648,7 @@
     </row>
     <row r="1895" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1895" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1895" s="5" t="s">
         <v>13</v>
@@ -15656,7 +15656,7 @@
     </row>
     <row r="1896" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1896" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1896" s="5" t="s">
         <v>13</v>
@@ -15664,7 +15664,7 @@
     </row>
     <row r="1897" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1897" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1897" s="5" t="s">
         <v>13</v>
@@ -15672,7 +15672,7 @@
     </row>
     <row r="1898" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1898" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1898" s="5" t="s">
         <v>13</v>
@@ -15680,7 +15680,7 @@
     </row>
     <row r="1899" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1899" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1899" s="5" t="s">
         <v>13</v>
@@ -15688,7 +15688,7 @@
     </row>
     <row r="1900" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1900" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1900" s="5" t="s">
         <v>13</v>
@@ -15696,7 +15696,7 @@
     </row>
     <row r="1901" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1901" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1901" s="5" t="s">
         <v>13</v>
@@ -15704,88 +15704,176 @@
     </row>
     <row r="1902" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1902" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C1902" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1903" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1903" s="4">
+      <c r="B1903" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1904" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1904" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B1904" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1904" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1905" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1905" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1905" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1906" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1906" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1906" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1907" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1907" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1907" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1908" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1908" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1908" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1909" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1909" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1909" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1910" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1910" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1910" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1911" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1911" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1911" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1912" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1912" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1912" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1913" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1913" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1914" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1914" s="4">
         <v>46042</v>
       </c>
-      <c r="B1903" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1903" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="1904" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1904" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1904" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="1905" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B1905" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1905" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="1906" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B1906" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1906" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="1907" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B1907" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1907" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="1908" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B1908" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1908" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="1909" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B1909" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1909" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="1910" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B1910" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1910" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="1911" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B1911" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1912" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B1912" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="1913" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B1913" s="3">
+      <c r="B1914" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1914" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1915" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1915" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1915" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1916" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1916" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1916" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1917" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1917" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1917" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1918" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1918" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1918" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1919" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1919" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1919" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1920" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1920" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1920" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1921" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1921" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1921" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1922" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1922" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1923" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1923" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1924" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1924" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF844D4-4CF2-4C81-B41E-7A06820669FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592A343E-C71E-4E9C-BA43-20A2C3F4904F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3669" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3690" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1924"/>
+  <dimension ref="A1:C1935"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5740,9 +5740,6 @@
       <c r="B660" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C660" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B661" s="3" t="s">
@@ -5754,7 +5751,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5831,6 +5828,9 @@
       <c r="B671" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C671" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B672" s="3" t="s">
@@ -5842,7 +5842,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5930,7 +5930,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6018,7 +6018,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6106,7 +6106,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6194,7 +6194,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6271,9 +6271,6 @@
       <c r="B726" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C726" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="727" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B727" s="3" t="s">
@@ -6285,7 +6282,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6376,7 +6373,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6467,7 +6464,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6558,7 +6555,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6635,6 +6632,9 @@
       <c r="B770" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C770" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="771" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B771" s="3" t="s">
@@ -6646,7 +6646,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6723,9 +6723,6 @@
       <c r="B781" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C781" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="782" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B782" s="3" t="s">
@@ -6737,7 +6734,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6828,7 +6825,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6919,7 +6916,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -7010,7 +7007,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7101,7 +7098,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7192,7 +7189,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7283,7 +7280,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7374,7 +7371,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7465,7 +7462,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7556,7 +7553,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7647,7 +7644,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7738,7 +7735,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7829,7 +7826,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7920,7 +7917,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -8011,7 +8008,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8102,7 +8099,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8193,7 +8190,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8284,7 +8281,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8375,7 +8372,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8466,7 +8463,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8557,7 +8554,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8648,7 +8645,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8739,7 +8736,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8830,7 +8827,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8921,7 +8918,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -9012,7 +9009,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9103,7 +9100,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9194,7 +9191,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9285,7 +9282,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9376,7 +9373,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9467,7 +9464,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9558,7 +9555,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9649,7 +9646,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9726,6 +9723,9 @@
       <c r="B1144" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1144" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1145" s="3" t="s">
@@ -9737,7 +9737,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9814,9 +9814,6 @@
       <c r="B1155" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1155" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1156" s="3" t="s">
@@ -9828,7 +9825,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9919,7 +9916,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -10010,7 +10007,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10101,7 +10098,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10192,7 +10189,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10283,7 +10280,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10374,7 +10371,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10465,7 +10462,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10556,7 +10553,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10647,7 +10644,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10716,6 +10713,9 @@
       <c r="B1264" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1264" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1265" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1265" s="3" t="s">
@@ -10735,7 +10735,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10804,9 +10804,6 @@
       <c r="B1275" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1275" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1276" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1276" s="3" t="s">
@@ -10826,7 +10823,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10903,6 +10900,9 @@
       <c r="B1287" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1287" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1288" s="3" t="s">
@@ -10914,7 +10914,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10983,6 +10983,9 @@
       <c r="B1297" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1297" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1298" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1298" s="3" t="s">
@@ -10999,7 +11002,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11068,9 +11071,6 @@
       <c r="B1308" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1308" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1309" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1309" s="3" t="s">
@@ -11087,7 +11087,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11156,6 +11156,9 @@
       <c r="B1319" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1319" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1320" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1320" s="3" t="s">
@@ -11172,7 +11175,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11241,9 +11244,6 @@
       <c r="B1330" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1330" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1331" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1331" s="3" t="s">
@@ -11260,7 +11260,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11348,7 +11348,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11436,7 +11436,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11505,6 +11505,9 @@
       <c r="B1363" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1363" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1364" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1364" s="3" t="s">
@@ -11521,7 +11524,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11606,7 +11609,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11691,7 +11694,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11776,7 +11779,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11861,7 +11864,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11946,7 +11949,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12031,7 +12034,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12116,7 +12119,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12201,7 +12204,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12286,7 +12289,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12371,7 +12374,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12456,7 +12459,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12525,9 +12528,6 @@
       <c r="B1495" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1495" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1496" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1496" s="3" t="s">
@@ -12544,7 +12544,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12613,6 +12613,9 @@
       <c r="B1506" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1506" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1507" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1507" s="3" t="s">
@@ -12629,7 +12632,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12714,7 +12717,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12799,7 +12802,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12868,9 +12871,6 @@
       <c r="B1539" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1539" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1540" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1540" s="3" t="s">
@@ -12887,7 +12887,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -12975,7 +12975,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13044,6 +13044,9 @@
       <c r="B1561" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1561" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1562" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1562" s="3" t="s">
@@ -13060,7 +13063,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13145,7 +13148,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13230,7 +13233,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13315,7 +13318,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13384,9 +13387,6 @@
       <c r="B1605" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1605" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1606" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1606" s="3" t="s">
@@ -13403,7 +13403,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13491,7 +13491,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13568,9 +13568,6 @@
       <c r="B1628" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1628" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1629" s="3" t="s">
@@ -13582,7 +13579,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13659,6 +13656,9 @@
       <c r="B1639" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1639" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1640" s="3" t="s">
@@ -13670,7 +13670,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13758,7 +13758,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13846,7 +13846,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13934,7 +13934,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14022,7 +14022,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14091,6 +14091,9 @@
       <c r="B1693" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1693" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1694" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1694" s="3" t="s">
@@ -14107,7 +14110,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14168,7 +14171,9 @@
       <c r="B1703" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1703" s="6"/>
+      <c r="C1703" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1704" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1704" s="3" t="s">
@@ -14184,10 +14189,13 @@
       <c r="B1706" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1706" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14248,17 +14256,12 @@
       <c r="B1714" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1714" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1714" s="6"/>
     </row>
     <row r="1715" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1715" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1715" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1716" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1716" s="3" t="s">
@@ -14269,13 +14272,10 @@
       <c r="B1717" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1717" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14363,7 +14363,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14451,7 +14451,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14520,6 +14520,9 @@
       <c r="B1748" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1748" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1749" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1749" s="3" t="s">
@@ -14536,7 +14539,7 @@
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14621,7 +14624,7 @@
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14695,9 +14698,6 @@
       <c r="B1771" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1771" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1772" s="3" t="s">
@@ -14709,7 +14709,7 @@
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14770,7 +14770,9 @@
       <c r="B1780" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1780" s="6"/>
+      <c r="C1780" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1781" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1781" s="3" t="s">
@@ -14781,15 +14783,21 @@
       <c r="B1782" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1782" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1783" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1783" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14850,9 +14858,7 @@
       <c r="B1791" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1791" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1791" s="6"/>
     </row>
     <row r="1792" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1792" s="3" t="s">
@@ -14868,13 +14874,10 @@
       <c r="B1794" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1794" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14943,9 +14946,6 @@
       <c r="B1803" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1803" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1804" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1804" s="3" t="s">
@@ -14962,7 +14962,7 @@
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15031,6 +15031,9 @@
       <c r="B1814" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1814" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1815" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1815" s="3" t="s">
@@ -15047,7 +15050,7 @@
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15126,10 +15129,13 @@
       <c r="B1827" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1827" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15208,13 +15214,10 @@
       <c r="B1838" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1838" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15283,9 +15286,6 @@
       <c r="B1847" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1847" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1848" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1848" s="3" t="s">
@@ -15302,7 +15302,7 @@
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15323,19 +15323,25 @@
       <c r="B1852" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1852" s="6"/>
+      <c r="C1852" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1853" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1853" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1853" s="6"/>
+      <c r="C1853" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1854" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1854" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1854" s="6"/>
+      <c r="C1854" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1855" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1855" s="3" t="s">
@@ -15357,12 +15363,17 @@
       <c r="B1857" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1857" s="6"/>
+      <c r="C1857" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1858" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1858" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1858" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1859" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1859" s="3" t="s">
@@ -15373,10 +15384,13 @@
       <c r="B1860" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1860" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15397,25 +15411,19 @@
       <c r="B1863" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1863" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1863" s="6"/>
     </row>
     <row r="1864" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1864" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1864" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1864" s="6"/>
     </row>
     <row r="1865" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1865" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1865" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1865" s="6"/>
     </row>
     <row r="1866" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1866" s="3" t="s">
@@ -15437,17 +15445,12 @@
       <c r="B1868" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1868" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1868" s="6"/>
     </row>
     <row r="1869" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1869" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1869" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1870" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1870" s="3" t="s">
@@ -15458,13 +15461,10 @@
       <c r="B1871" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1871" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1872" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B1872" s="7" t="s">
         <v>3</v>
@@ -15552,7 +15552,7 @@
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1883" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B1883" s="7" t="s">
         <v>3</v>
@@ -15621,6 +15621,9 @@
       <c r="B1891" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1891" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1892" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1892" s="3" t="s">
@@ -15637,7 +15640,7 @@
     </row>
     <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1894" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B1894" s="7" t="s">
         <v>3</v>
@@ -15706,9 +15709,6 @@
       <c r="B1902" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1902" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1903" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1903" s="3" t="s">
@@ -15716,19 +15716,19 @@
       </c>
     </row>
     <row r="1904" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1904" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B1904" s="7" t="s">
-        <v>3</v>
+      <c r="B1904" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C1904" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="1905" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1905" s="3" t="s">
-        <v>4</v>
+      <c r="A1905" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B1905" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1905" s="5" t="s">
         <v>13</v>
@@ -15736,7 +15736,7 @@
     </row>
     <row r="1906" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1906" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1906" s="5" t="s">
         <v>13</v>
@@ -15744,7 +15744,7 @@
     </row>
     <row r="1907" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1907" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1907" s="5" t="s">
         <v>13</v>
@@ -15752,7 +15752,7 @@
     </row>
     <row r="1908" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1908" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1908" s="5" t="s">
         <v>13</v>
@@ -15760,7 +15760,7 @@
     </row>
     <row r="1909" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1909" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1909" s="5" t="s">
         <v>13</v>
@@ -15768,7 +15768,7 @@
     </row>
     <row r="1910" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1910" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1910" s="5" t="s">
         <v>13</v>
@@ -15776,7 +15776,7 @@
     </row>
     <row r="1911" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1911" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1911" s="5" t="s">
         <v>13</v>
@@ -15784,7 +15784,7 @@
     </row>
     <row r="1912" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1912" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1912" s="5" t="s">
         <v>13</v>
@@ -15792,23 +15792,23 @@
     </row>
     <row r="1913" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1913" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C1913" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1914" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1914" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B1914" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1914" s="5" t="s">
-        <v>13</v>
+      <c r="B1914" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="1915" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1915" s="3" t="s">
-        <v>4</v>
+      <c r="A1915" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B1915" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1915" s="5" t="s">
         <v>13</v>
@@ -15816,7 +15816,7 @@
     </row>
     <row r="1916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1916" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1916" s="5" t="s">
         <v>13</v>
@@ -15824,7 +15824,7 @@
     </row>
     <row r="1917" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1917" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1917" s="5" t="s">
         <v>13</v>
@@ -15832,7 +15832,7 @@
     </row>
     <row r="1918" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1918" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1918" s="5" t="s">
         <v>13</v>
@@ -15840,7 +15840,7 @@
     </row>
     <row r="1919" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1919" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1919" s="5" t="s">
         <v>13</v>
@@ -15848,32 +15848,120 @@
     </row>
     <row r="1920" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1920" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1920" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="1921" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="1921" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1921" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1921" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="1922" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="1922" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1922" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1923" spans="2:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C1922" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1923" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1923" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="1924" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B1924" s="3">
+        <v>11</v>
+      </c>
+      <c r="C1923" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1924" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1924" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1925" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1925" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B1925" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1925" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1926" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1926" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1926" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1927" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1927" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1927" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1928" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1928" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1928" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1929" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1929" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1929" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1930" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1930" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1930" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1931" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1931" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1931" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1932" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1932" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1932" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1933" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1933" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1934" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1934" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1935" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1935" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592A343E-C71E-4E9C-BA43-20A2C3F4904F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EAAD44D-72DD-4A6E-B097-A0C482ADD820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3690" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3711" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1935"/>
+  <dimension ref="A1:C1946"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5828,9 +5828,6 @@
       <c r="B671" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C671" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="672" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B672" s="3" t="s">
@@ -5842,7 +5839,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5919,6 +5916,9 @@
       <c r="B682" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C682" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B683" s="3" t="s">
@@ -5930,7 +5930,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6018,7 +6018,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6106,7 +6106,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6194,7 +6194,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6282,7 +6282,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6359,9 +6359,6 @@
       <c r="B737" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C737" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="738" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B738" s="3" t="s">
@@ -6373,7 +6370,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6464,7 +6461,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6555,7 +6552,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6646,7 +6643,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6723,6 +6720,9 @@
       <c r="B781" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C781" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="782" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B782" s="3" t="s">
@@ -6734,7 +6734,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6811,9 +6811,6 @@
       <c r="B792" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C792" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="793" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B793" s="3" t="s">
@@ -6825,7 +6822,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6916,7 +6913,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -7007,7 +7004,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7098,7 +7095,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7189,7 +7186,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7280,7 +7277,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7371,7 +7368,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7462,7 +7459,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7553,7 +7550,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7644,7 +7641,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7735,7 +7732,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7826,7 +7823,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7917,7 +7914,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -8008,7 +8005,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8099,7 +8096,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8190,7 +8187,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8281,7 +8278,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8372,7 +8369,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8463,7 +8460,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8554,7 +8551,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8645,7 +8642,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8736,7 +8733,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8827,7 +8824,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8918,7 +8915,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -9009,7 +9006,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9100,7 +9097,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9191,7 +9188,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9282,7 +9279,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9373,7 +9370,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9464,7 +9461,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9555,7 +9552,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9646,7 +9643,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9737,7 +9734,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9814,6 +9811,9 @@
       <c r="B1155" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1155" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1156" s="3" t="s">
@@ -9825,7 +9825,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9902,9 +9902,6 @@
       <c r="B1166" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1166" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1167" s="3" t="s">
@@ -9916,7 +9913,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -10007,7 +10004,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10098,7 +10095,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10189,7 +10186,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10280,7 +10277,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10371,7 +10368,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10462,7 +10459,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10553,7 +10550,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10644,7 +10641,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10735,7 +10732,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10804,6 +10801,9 @@
       <c r="B1275" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1275" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1276" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1276" s="3" t="s">
@@ -10823,7 +10823,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10892,9 +10892,6 @@
       <c r="B1286" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1286" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1287" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1287" s="3" t="s">
@@ -10914,7 +10911,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10991,6 +10988,9 @@
       <c r="B1298" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1298" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1299" s="3" t="s">
@@ -11002,7 +11002,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11071,6 +11071,9 @@
       <c r="B1308" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1308" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1309" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1309" s="3" t="s">
@@ -11087,7 +11090,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11156,9 +11159,6 @@
       <c r="B1319" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1319" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1320" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1320" s="3" t="s">
@@ -11175,7 +11175,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11244,6 +11244,9 @@
       <c r="B1330" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1330" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1331" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1331" s="3" t="s">
@@ -11260,7 +11263,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11329,9 +11332,6 @@
       <c r="B1341" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1341" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1342" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1342" s="3" t="s">
@@ -11348,7 +11348,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11436,7 +11436,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11524,7 +11524,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11593,6 +11593,9 @@
       <c r="B1374" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1374" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1375" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1375" s="3" t="s">
@@ -11609,7 +11612,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11694,7 +11697,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11779,7 +11782,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11864,7 +11867,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11949,7 +11952,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12034,7 +12037,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12119,7 +12122,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12204,7 +12207,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12289,7 +12292,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12374,7 +12377,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12459,7 +12462,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12544,7 +12547,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12613,9 +12616,6 @@
       <c r="B1506" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1506" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1507" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1507" s="3" t="s">
@@ -12632,7 +12632,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12701,6 +12701,9 @@
       <c r="B1517" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1517" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1518" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1518" s="3" t="s">
@@ -12717,7 +12720,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12802,7 +12805,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12887,7 +12890,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -12956,9 +12959,6 @@
       <c r="B1550" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1550" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1551" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1551" s="3" t="s">
@@ -12975,7 +12975,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13063,7 +13063,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13132,6 +13132,9 @@
       <c r="B1572" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1572" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1573" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1573" s="3" t="s">
@@ -13148,7 +13151,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13233,7 +13236,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13318,7 +13321,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13403,7 +13406,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13472,9 +13475,6 @@
       <c r="B1616" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1616" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1617" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1617" s="3" t="s">
@@ -13491,7 +13491,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13579,7 +13579,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13656,9 +13656,6 @@
       <c r="B1639" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1639" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1640" s="3" t="s">
@@ -13670,7 +13667,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13747,6 +13744,9 @@
       <c r="B1650" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1650" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1651" s="3" t="s">
@@ -13758,7 +13758,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13846,7 +13846,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13934,7 +13934,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14022,7 +14022,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14110,7 +14110,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14179,6 +14179,9 @@
       <c r="B1704" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1704" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1705" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1705" s="3" t="s">
@@ -14195,7 +14198,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14256,7 +14259,9 @@
       <c r="B1714" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1714" s="6"/>
+      <c r="C1714" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1715" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1715" s="3" t="s">
@@ -14272,10 +14277,13 @@
       <c r="B1717" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1717" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14336,17 +14344,12 @@
       <c r="B1725" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1725" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1725" s="6"/>
     </row>
     <row r="1726" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1726" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1726" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1727" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1727" s="3" t="s">
@@ -14357,13 +14360,10 @@
       <c r="B1728" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1728" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14451,7 +14451,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14539,7 +14539,7 @@
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14608,6 +14608,9 @@
       <c r="B1759" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1759" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1760" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1760" s="3" t="s">
@@ -14624,7 +14627,7 @@
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14709,7 +14712,7 @@
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14783,9 +14786,6 @@
       <c r="B1782" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1782" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1783" s="3" t="s">
@@ -14797,7 +14797,7 @@
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14858,7 +14858,9 @@
       <c r="B1791" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1791" s="6"/>
+      <c r="C1791" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1792" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1792" s="3" t="s">
@@ -14869,15 +14871,21 @@
       <c r="B1793" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1793" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1794" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1794" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14938,9 +14946,7 @@
       <c r="B1802" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1802" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1802" s="6"/>
     </row>
     <row r="1803" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1803" s="3" t="s">
@@ -14956,13 +14962,10 @@
       <c r="B1805" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1805" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15031,9 +15034,6 @@
       <c r="B1814" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1814" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1815" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1815" s="3" t="s">
@@ -15050,7 +15050,7 @@
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15119,6 +15119,9 @@
       <c r="B1825" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1825" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1826" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1826" s="3" t="s">
@@ -15135,7 +15138,7 @@
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15214,10 +15217,13 @@
       <c r="B1838" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1838" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15296,13 +15302,10 @@
       <c r="B1849" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1849" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15371,9 +15374,6 @@
       <c r="B1858" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1858" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1859" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1859" s="3" t="s">
@@ -15390,7 +15390,7 @@
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15411,19 +15411,25 @@
       <c r="B1863" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1863" s="6"/>
+      <c r="C1863" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1864" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1864" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1864" s="6"/>
+      <c r="C1864" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1865" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1865" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1865" s="6"/>
+      <c r="C1865" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1866" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1866" s="3" t="s">
@@ -15445,12 +15451,17 @@
       <c r="B1868" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1868" s="6"/>
+      <c r="C1868" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1869" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1869" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1869" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1870" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1870" s="3" t="s">
@@ -15461,10 +15472,13 @@
       <c r="B1871" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1871" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1872" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B1872" s="7" t="s">
         <v>3</v>
@@ -15485,25 +15499,19 @@
       <c r="B1874" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1874" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1874" s="6"/>
     </row>
     <row r="1875" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1875" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1875" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1875" s="6"/>
     </row>
     <row r="1876" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1876" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1876" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1876" s="6"/>
     </row>
     <row r="1877" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1877" s="3" t="s">
@@ -15525,17 +15533,12 @@
       <c r="B1879" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1879" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1879" s="6"/>
     </row>
     <row r="1880" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1880" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1880" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1881" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1881" s="3" t="s">
@@ -15546,13 +15549,10 @@
       <c r="B1882" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1882" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1883" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B1883" s="7" t="s">
         <v>3</v>
@@ -15640,7 +15640,7 @@
     </row>
     <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1894" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B1894" s="7" t="s">
         <v>3</v>
@@ -15709,6 +15709,9 @@
       <c r="B1902" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1902" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1903" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1903" s="3" t="s">
@@ -15725,7 +15728,7 @@
     </row>
     <row r="1905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1905" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B1905" s="7" t="s">
         <v>3</v>
@@ -15794,9 +15797,6 @@
       <c r="B1913" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1913" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1914" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1914" s="3" t="s">
@@ -15804,19 +15804,19 @@
       </c>
     </row>
     <row r="1915" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1915" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B1915" s="7" t="s">
-        <v>3</v>
+      <c r="B1915" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C1915" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="1916" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1916" s="3" t="s">
-        <v>4</v>
+      <c r="A1916" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B1916" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1916" s="5" t="s">
         <v>13</v>
@@ -15824,7 +15824,7 @@
     </row>
     <row r="1917" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1917" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1917" s="5" t="s">
         <v>13</v>
@@ -15832,7 +15832,7 @@
     </row>
     <row r="1918" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1918" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1918" s="5" t="s">
         <v>13</v>
@@ -15840,7 +15840,7 @@
     </row>
     <row r="1919" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1919" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1919" s="5" t="s">
         <v>13</v>
@@ -15848,7 +15848,7 @@
     </row>
     <row r="1920" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1920" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1920" s="5" t="s">
         <v>13</v>
@@ -15856,7 +15856,7 @@
     </row>
     <row r="1921" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1921" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1921" s="5" t="s">
         <v>13</v>
@@ -15864,7 +15864,7 @@
     </row>
     <row r="1922" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1922" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1922" s="5" t="s">
         <v>13</v>
@@ -15872,7 +15872,7 @@
     </row>
     <row r="1923" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1923" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1923" s="5" t="s">
         <v>13</v>
@@ -15880,23 +15880,23 @@
     </row>
     <row r="1924" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1924" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C1924" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1925" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1925" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B1925" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1925" s="5" t="s">
-        <v>13</v>
+      <c r="B1925" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="1926" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1926" s="3" t="s">
-        <v>4</v>
+      <c r="A1926" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B1926" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1926" s="5" t="s">
         <v>13</v>
@@ -15904,7 +15904,7 @@
     </row>
     <row r="1927" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1927" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1927" s="5" t="s">
         <v>13</v>
@@ -15912,7 +15912,7 @@
     </row>
     <row r="1928" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1928" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1928" s="5" t="s">
         <v>13</v>
@@ -15920,7 +15920,7 @@
     </row>
     <row r="1929" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1929" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1929" s="5" t="s">
         <v>13</v>
@@ -15928,7 +15928,7 @@
     </row>
     <row r="1930" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1930" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1930" s="5" t="s">
         <v>13</v>
@@ -15936,7 +15936,7 @@
     </row>
     <row r="1931" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1931" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1931" s="5" t="s">
         <v>13</v>
@@ -15944,7 +15944,7 @@
     </row>
     <row r="1932" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1932" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1932" s="5" t="s">
         <v>13</v>
@@ -15952,16 +15952,104 @@
     </row>
     <row r="1933" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1933" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C1933" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1934" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1934" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C1934" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1935" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1935" s="3">
+      <c r="B1935" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1936" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1936" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B1936" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1936" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1937" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1937" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1937" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1938" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1938" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1938" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1939" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1939" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1939" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1940" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1940" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1940" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1941" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1941" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1941" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1942" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1942" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1942" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1943" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1943" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1943" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1944" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1944" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1945" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1945" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1946" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1946" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EAAD44D-72DD-4A6E-B097-A0C482ADD820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FDE1017-EECB-4B69-9D8B-2A29E44DC50D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3711" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3732" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1946"/>
+  <dimension ref="A1:C1957"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5916,9 +5916,6 @@
       <c r="B682" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C682" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B683" s="3" t="s">
@@ -5930,7 +5927,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6007,6 +6004,9 @@
       <c r="B693" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C693" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="694" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B694" s="3" t="s">
@@ -6018,7 +6018,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6106,7 +6106,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6194,7 +6194,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6282,7 +6282,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6370,7 +6370,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6447,9 +6447,6 @@
       <c r="B748" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C748" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="749" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B749" s="3" t="s">
@@ -6461,7 +6458,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6552,7 +6549,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6643,7 +6640,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6734,7 +6731,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6811,6 +6808,9 @@
       <c r="B792" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C792" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="793" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B793" s="3" t="s">
@@ -6822,7 +6822,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6899,9 +6899,6 @@
       <c r="B803" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C803" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="804" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B804" s="3" t="s">
@@ -6913,7 +6910,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -7004,7 +7001,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7095,7 +7092,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7186,7 +7183,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7277,7 +7274,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7368,7 +7365,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7459,7 +7456,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7550,7 +7547,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7641,7 +7638,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7732,7 +7729,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7823,7 +7820,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7914,7 +7911,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -8005,7 +8002,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8096,7 +8093,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8187,7 +8184,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8278,7 +8275,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8369,7 +8366,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8460,7 +8457,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8551,7 +8548,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8642,7 +8639,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8733,7 +8730,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8824,7 +8821,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8915,7 +8912,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -9006,7 +9003,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9097,7 +9094,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9188,7 +9185,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9279,7 +9276,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9370,7 +9367,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9461,7 +9458,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9552,7 +9549,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9643,7 +9640,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9734,7 +9731,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9825,7 +9822,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9902,6 +9899,9 @@
       <c r="B1166" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1166" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1167" s="3" t="s">
@@ -9913,7 +9913,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -9990,9 +9990,6 @@
       <c r="B1177" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1177" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1178" s="3" t="s">
@@ -10004,7 +10001,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10095,7 +10092,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10186,7 +10183,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10277,7 +10274,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10368,7 +10365,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10459,7 +10456,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10550,7 +10547,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10641,7 +10638,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10732,7 +10729,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10823,7 +10820,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10892,6 +10889,9 @@
       <c r="B1286" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1286" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1287" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1287" s="3" t="s">
@@ -10911,7 +10911,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10980,9 +10980,6 @@
       <c r="B1297" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1297" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1298" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1298" s="3" t="s">
@@ -11002,7 +10999,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11079,6 +11076,9 @@
       <c r="B1309" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1309" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1310" s="3" t="s">
@@ -11090,7 +11090,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11159,6 +11159,9 @@
       <c r="B1319" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1319" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1320" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1320" s="3" t="s">
@@ -11175,7 +11178,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11244,9 +11247,6 @@
       <c r="B1330" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1330" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1331" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1331" s="3" t="s">
@@ -11263,7 +11263,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11332,6 +11332,9 @@
       <c r="B1341" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1341" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1342" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1342" s="3" t="s">
@@ -11348,7 +11351,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11417,9 +11420,6 @@
       <c r="B1352" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1352" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1353" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1353" s="3" t="s">
@@ -11436,7 +11436,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11524,7 +11524,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11612,7 +11612,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11681,6 +11681,9 @@
       <c r="B1385" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1385" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1386" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1386" s="3" t="s">
@@ -11697,7 +11700,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11782,7 +11785,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11867,7 +11870,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11952,7 +11955,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12037,7 +12040,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12122,7 +12125,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12207,7 +12210,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12292,7 +12295,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12377,7 +12380,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12462,7 +12465,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12547,7 +12550,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12632,7 +12635,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12701,9 +12704,6 @@
       <c r="B1517" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1517" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1518" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1518" s="3" t="s">
@@ -12720,7 +12720,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12789,6 +12789,9 @@
       <c r="B1528" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1528" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1529" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1529" s="3" t="s">
@@ -12805,7 +12808,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12890,7 +12893,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -12975,7 +12978,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13044,9 +13047,6 @@
       <c r="B1561" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1561" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1562" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1562" s="3" t="s">
@@ -13063,7 +13063,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13151,7 +13151,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13220,6 +13220,9 @@
       <c r="B1583" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1583" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1584" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1584" s="3" t="s">
@@ -13236,7 +13239,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13321,7 +13324,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13406,7 +13409,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13491,7 +13494,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13560,9 +13563,6 @@
       <c r="B1627" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1627" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1628" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1628" s="3" t="s">
@@ -13579,7 +13579,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13667,7 +13667,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13744,9 +13744,6 @@
       <c r="B1650" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1650" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1651" s="3" t="s">
@@ -13758,7 +13755,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13835,6 +13832,9 @@
       <c r="B1661" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1661" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1662" s="3" t="s">
@@ -13846,7 +13846,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13934,7 +13934,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14022,7 +14022,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14110,7 +14110,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14198,7 +14198,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14267,6 +14267,9 @@
       <c r="B1715" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1715" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1716" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1716" s="3" t="s">
@@ -14283,7 +14286,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14344,7 +14347,9 @@
       <c r="B1725" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1725" s="6"/>
+      <c r="C1725" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1726" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1726" s="3" t="s">
@@ -14360,10 +14365,13 @@
       <c r="B1728" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1728" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14424,17 +14432,12 @@
       <c r="B1736" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1736" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1736" s="6"/>
     </row>
     <row r="1737" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1737" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1737" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1738" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1738" s="3" t="s">
@@ -14445,13 +14448,10 @@
       <c r="B1739" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1739" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14539,7 +14539,7 @@
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14627,7 +14627,7 @@
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14696,6 +14696,9 @@
       <c r="B1770" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1770" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1771" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1771" s="3" t="s">
@@ -14712,7 +14715,7 @@
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14797,7 +14800,7 @@
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14871,9 +14874,6 @@
       <c r="B1793" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1793" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1794" s="3" t="s">
@@ -14885,7 +14885,7 @@
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14946,7 +14946,9 @@
       <c r="B1802" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1802" s="6"/>
+      <c r="C1802" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1803" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1803" s="3" t="s">
@@ -14957,15 +14959,21 @@
       <c r="B1804" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1804" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1805" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1805" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15026,9 +15034,7 @@
       <c r="B1813" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1813" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1813" s="6"/>
     </row>
     <row r="1814" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1814" s="3" t="s">
@@ -15044,13 +15050,10 @@
       <c r="B1816" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1816" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15119,9 +15122,6 @@
       <c r="B1825" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1825" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1826" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1826" s="3" t="s">
@@ -15138,7 +15138,7 @@
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15207,6 +15207,9 @@
       <c r="B1836" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1836" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1837" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1837" s="3" t="s">
@@ -15223,7 +15226,7 @@
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15302,10 +15305,13 @@
       <c r="B1849" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1849" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15384,13 +15390,10 @@
       <c r="B1860" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1860" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15459,9 +15462,6 @@
       <c r="B1869" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1869" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1870" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1870" s="3" t="s">
@@ -15478,7 +15478,7 @@
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1872" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B1872" s="7" t="s">
         <v>3</v>
@@ -15499,19 +15499,25 @@
       <c r="B1874" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1874" s="6"/>
+      <c r="C1874" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1875" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1875" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1875" s="6"/>
+      <c r="C1875" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1876" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1876" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1876" s="6"/>
+      <c r="C1876" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1877" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1877" s="3" t="s">
@@ -15533,12 +15539,17 @@
       <c r="B1879" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1879" s="6"/>
+      <c r="C1879" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1880" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1880" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1880" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1881" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1881" s="3" t="s">
@@ -15549,10 +15560,13 @@
       <c r="B1882" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1882" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1883" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B1883" s="7" t="s">
         <v>3</v>
@@ -15573,25 +15587,19 @@
       <c r="B1885" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1885" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1885" s="6"/>
     </row>
     <row r="1886" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1886" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1886" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1886" s="6"/>
     </row>
     <row r="1887" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1887" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1887" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1887" s="6"/>
     </row>
     <row r="1888" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1888" s="3" t="s">
@@ -15613,17 +15621,12 @@
       <c r="B1890" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1890" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1890" s="6"/>
     </row>
     <row r="1891" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1891" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1891" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1892" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1892" s="3" t="s">
@@ -15634,13 +15637,10 @@
       <c r="B1893" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1893" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1894" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B1894" s="7" t="s">
         <v>3</v>
@@ -15728,7 +15728,7 @@
     </row>
     <row r="1905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1905" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B1905" s="7" t="s">
         <v>3</v>
@@ -15797,6 +15797,9 @@
       <c r="B1913" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1913" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1914" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1914" s="3" t="s">
@@ -15813,7 +15816,7 @@
     </row>
     <row r="1916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1916" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B1916" s="7" t="s">
         <v>3</v>
@@ -15882,9 +15885,6 @@
       <c r="B1924" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1924" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1925" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1925" s="3" t="s">
@@ -15892,19 +15892,19 @@
       </c>
     </row>
     <row r="1926" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1926" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B1926" s="7" t="s">
-        <v>3</v>
+      <c r="B1926" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C1926" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="1927" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1927" s="3" t="s">
-        <v>4</v>
+      <c r="A1927" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B1927" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1927" s="5" t="s">
         <v>13</v>
@@ -15912,7 +15912,7 @@
     </row>
     <row r="1928" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1928" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1928" s="5" t="s">
         <v>13</v>
@@ -15920,7 +15920,7 @@
     </row>
     <row r="1929" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1929" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1929" s="5" t="s">
         <v>13</v>
@@ -15928,7 +15928,7 @@
     </row>
     <row r="1930" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1930" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1930" s="5" t="s">
         <v>13</v>
@@ -15936,7 +15936,7 @@
     </row>
     <row r="1931" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1931" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1931" s="5" t="s">
         <v>13</v>
@@ -15944,7 +15944,7 @@
     </row>
     <row r="1932" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1932" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1932" s="5" t="s">
         <v>13</v>
@@ -15952,7 +15952,7 @@
     </row>
     <row r="1933" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1933" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1933" s="5" t="s">
         <v>13</v>
@@ -15960,7 +15960,7 @@
     </row>
     <row r="1934" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1934" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1934" s="5" t="s">
         <v>13</v>
@@ -15968,88 +15968,176 @@
     </row>
     <row r="1935" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1935" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C1935" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1936" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1936" s="4">
+      <c r="B1936" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1937" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1937" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B1937" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1937" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1938" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1938" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1938" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1939" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1939" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1939" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1940" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1940" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1940" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1941" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1941" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1941" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1942" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1942" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1942" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1943" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1943" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1943" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1944" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1944" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1944" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1945" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1945" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1945" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1946" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1946" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1947" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1947" s="4">
         <v>46042</v>
       </c>
-      <c r="B1936" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1936" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="1937" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B1937" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1937" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="1938" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B1938" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1938" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="1939" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B1939" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1939" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="1940" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B1940" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1940" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="1941" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B1941" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1941" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="1942" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B1942" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1942" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="1943" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B1943" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1943" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="1944" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B1944" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1945" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B1945" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="1946" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B1946" s="3">
+      <c r="B1947" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1947" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1948" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1948" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1948" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1949" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1949" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1949" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1950" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1950" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1950" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1951" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1951" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1951" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1952" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1952" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1952" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1953" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1953" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1953" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1954" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1954" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1954" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1955" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1955" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1956" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1956" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1957" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1957" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FDE1017-EECB-4B69-9D8B-2A29E44DC50D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F36BA27-00FF-46F6-A6AC-F05B841B3E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3732" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3753" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1957"/>
+  <dimension ref="A1:C1968"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6004,9 +6004,6 @@
       <c r="B693" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C693" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="694" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B694" s="3" t="s">
@@ -6018,7 +6015,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6095,6 +6092,9 @@
       <c r="B704" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C704" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="705" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B705" s="3" t="s">
@@ -6106,7 +6106,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6194,7 +6194,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6282,7 +6282,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6370,7 +6370,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6458,7 +6458,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6535,9 +6535,6 @@
       <c r="B759" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C759" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="760" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B760" s="3" t="s">
@@ -6549,7 +6546,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6640,7 +6637,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6731,7 +6728,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6822,7 +6819,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6899,6 +6896,9 @@
       <c r="B803" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C803" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="804" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B804" s="3" t="s">
@@ -6910,7 +6910,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6987,9 +6987,6 @@
       <c r="B814" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C814" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="815" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B815" s="3" t="s">
@@ -7001,7 +6998,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7092,7 +7089,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7183,7 +7180,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7274,7 +7271,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7365,7 +7362,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7456,7 +7453,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7547,7 +7544,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7638,7 +7635,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7729,7 +7726,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7820,7 +7817,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7911,7 +7908,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -8002,7 +7999,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8093,7 +8090,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8184,7 +8181,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8275,7 +8272,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8366,7 +8363,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8457,7 +8454,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8548,7 +8545,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8639,7 +8636,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8730,7 +8727,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8821,7 +8818,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8912,7 +8909,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -9003,7 +9000,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9094,7 +9091,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9185,7 +9182,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9276,7 +9273,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9367,7 +9364,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9458,7 +9455,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9549,7 +9546,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9640,7 +9637,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9731,7 +9728,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9822,7 +9819,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9913,7 +9910,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -9990,6 +9987,9 @@
       <c r="B1177" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1177" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1178" s="3" t="s">
@@ -10001,7 +10001,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10078,9 +10078,6 @@
       <c r="B1188" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1188" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1189" s="3" t="s">
@@ -10092,7 +10089,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10183,7 +10180,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10274,7 +10271,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10365,7 +10362,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10456,7 +10453,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10547,7 +10544,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10638,7 +10635,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10729,7 +10726,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10820,7 +10817,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10911,7 +10908,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10980,6 +10977,9 @@
       <c r="B1297" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1297" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1298" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1298" s="3" t="s">
@@ -10999,7 +10999,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11068,9 +11068,6 @@
       <c r="B1308" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1308" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1309" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1309" s="3" t="s">
@@ -11090,7 +11087,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11167,6 +11164,9 @@
       <c r="B1320" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1320" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1321" s="3" t="s">
@@ -11178,7 +11178,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11247,6 +11247,9 @@
       <c r="B1330" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1330" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1331" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1331" s="3" t="s">
@@ -11263,7 +11266,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11332,9 +11335,6 @@
       <c r="B1341" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1341" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1342" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1342" s="3" t="s">
@@ -11351,7 +11351,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11420,6 +11420,9 @@
       <c r="B1352" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1352" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1353" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1353" s="3" t="s">
@@ -11436,7 +11439,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11505,9 +11508,6 @@
       <c r="B1363" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1363" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1364" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1364" s="3" t="s">
@@ -11524,7 +11524,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11612,7 +11612,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11700,7 +11700,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11769,6 +11769,9 @@
       <c r="B1396" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1396" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1397" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1397" s="3" t="s">
@@ -11785,7 +11788,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11870,7 +11873,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11955,7 +11958,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12040,7 +12043,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12125,7 +12128,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12210,7 +12213,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12295,7 +12298,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12380,7 +12383,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12465,7 +12468,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12550,7 +12553,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12635,7 +12638,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12720,7 +12723,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12789,9 +12792,6 @@
       <c r="B1528" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1528" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1529" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1529" s="3" t="s">
@@ -12808,7 +12808,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12877,6 +12877,9 @@
       <c r="B1539" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1539" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1540" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1540" s="3" t="s">
@@ -12893,7 +12896,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -12978,7 +12981,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13063,7 +13066,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13132,9 +13135,6 @@
       <c r="B1572" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1572" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1573" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1573" s="3" t="s">
@@ -13151,7 +13151,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13239,7 +13239,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13308,6 +13308,9 @@
       <c r="B1594" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1594" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1595" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1595" s="3" t="s">
@@ -13324,7 +13327,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13409,7 +13412,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13494,7 +13497,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13579,7 +13582,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13648,9 +13651,6 @@
       <c r="B1638" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1638" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1639" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1639" s="3" t="s">
@@ -13667,7 +13667,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13755,7 +13755,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13832,9 +13832,6 @@
       <c r="B1661" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1661" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1662" s="3" t="s">
@@ -13846,7 +13843,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13923,6 +13920,9 @@
       <c r="B1672" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1672" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1673" s="3" t="s">
@@ -13934,7 +13934,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14022,7 +14022,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14110,7 +14110,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14198,7 +14198,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14286,7 +14286,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14355,6 +14355,9 @@
       <c r="B1726" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1726" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1727" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1727" s="3" t="s">
@@ -14371,7 +14374,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14432,7 +14435,9 @@
       <c r="B1736" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1736" s="6"/>
+      <c r="C1736" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1737" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1737" s="3" t="s">
@@ -14448,10 +14453,13 @@
       <c r="B1739" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1739" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14512,17 +14520,12 @@
       <c r="B1747" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1747" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1747" s="6"/>
     </row>
     <row r="1748" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1748" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1748" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1749" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1749" s="3" t="s">
@@ -14533,13 +14536,10 @@
       <c r="B1750" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1750" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14627,7 +14627,7 @@
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14715,7 +14715,7 @@
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14784,6 +14784,9 @@
       <c r="B1781" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1781" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1782" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1782" s="3" t="s">
@@ -14800,7 +14803,7 @@
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14885,7 +14888,7 @@
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14959,9 +14962,6 @@
       <c r="B1804" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1804" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1805" s="3" t="s">
@@ -14973,7 +14973,7 @@
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15034,7 +15034,9 @@
       <c r="B1813" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1813" s="6"/>
+      <c r="C1813" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1814" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1814" s="3" t="s">
@@ -15045,15 +15047,21 @@
       <c r="B1815" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1815" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1816" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1816" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15114,9 +15122,7 @@
       <c r="B1824" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1824" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1824" s="6"/>
     </row>
     <row r="1825" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1825" s="3" t="s">
@@ -15132,13 +15138,10 @@
       <c r="B1827" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1827" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15207,9 +15210,6 @@
       <c r="B1836" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1836" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1837" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1837" s="3" t="s">
@@ -15226,7 +15226,7 @@
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15295,6 +15295,9 @@
       <c r="B1847" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1847" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1848" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1848" s="3" t="s">
@@ -15311,7 +15314,7 @@
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15390,10 +15393,13 @@
       <c r="B1860" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1860" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15472,13 +15478,10 @@
       <c r="B1871" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1871" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1872" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B1872" s="7" t="s">
         <v>3</v>
@@ -15547,9 +15550,6 @@
       <c r="B1880" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1880" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1881" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1881" s="3" t="s">
@@ -15566,7 +15566,7 @@
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1883" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B1883" s="7" t="s">
         <v>3</v>
@@ -15587,19 +15587,25 @@
       <c r="B1885" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1885" s="6"/>
+      <c r="C1885" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1886" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1886" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1886" s="6"/>
+      <c r="C1886" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1887" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1887" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1887" s="6"/>
+      <c r="C1887" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1888" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1888" s="3" t="s">
@@ -15621,12 +15627,17 @@
       <c r="B1890" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1890" s="6"/>
+      <c r="C1890" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1891" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1891" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1891" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1892" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1892" s="3" t="s">
@@ -15637,10 +15648,13 @@
       <c r="B1893" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1893" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1894" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B1894" s="7" t="s">
         <v>3</v>
@@ -15661,25 +15675,19 @@
       <c r="B1896" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1896" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1896" s="6"/>
     </row>
     <row r="1897" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1897" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1897" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1897" s="6"/>
     </row>
     <row r="1898" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1898" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1898" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1898" s="6"/>
     </row>
     <row r="1899" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1899" s="3" t="s">
@@ -15701,17 +15709,12 @@
       <c r="B1901" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1901" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1901" s="6"/>
     </row>
     <row r="1902" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1902" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1902" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1903" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1903" s="3" t="s">
@@ -15722,13 +15725,10 @@
       <c r="B1904" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1904" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1905" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B1905" s="7" t="s">
         <v>3</v>
@@ -15816,7 +15816,7 @@
     </row>
     <row r="1916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1916" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B1916" s="7" t="s">
         <v>3</v>
@@ -15885,6 +15885,9 @@
       <c r="B1924" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1924" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1925" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1925" s="3" t="s">
@@ -15901,7 +15904,7 @@
     </row>
     <row r="1927" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1927" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B1927" s="7" t="s">
         <v>3</v>
@@ -15970,9 +15973,6 @@
       <c r="B1935" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1935" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1936" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1936" s="3" t="s">
@@ -15980,19 +15980,19 @@
       </c>
     </row>
     <row r="1937" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1937" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B1937" s="7" t="s">
-        <v>3</v>
+      <c r="B1937" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C1937" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="1938" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1938" s="3" t="s">
-        <v>4</v>
+      <c r="A1938" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B1938" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1938" s="5" t="s">
         <v>13</v>
@@ -16000,7 +16000,7 @@
     </row>
     <row r="1939" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1939" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1939" s="5" t="s">
         <v>13</v>
@@ -16008,7 +16008,7 @@
     </row>
     <row r="1940" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1940" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1940" s="5" t="s">
         <v>13</v>
@@ -16016,7 +16016,7 @@
     </row>
     <row r="1941" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1941" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1941" s="5" t="s">
         <v>13</v>
@@ -16024,7 +16024,7 @@
     </row>
     <row r="1942" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1942" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1942" s="5" t="s">
         <v>13</v>
@@ -16032,7 +16032,7 @@
     </row>
     <row r="1943" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1943" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1943" s="5" t="s">
         <v>13</v>
@@ -16040,7 +16040,7 @@
     </row>
     <row r="1944" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1944" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1944" s="5" t="s">
         <v>13</v>
@@ -16048,7 +16048,7 @@
     </row>
     <row r="1945" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1945" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1945" s="5" t="s">
         <v>13</v>
@@ -16056,23 +16056,23 @@
     </row>
     <row r="1946" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1946" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C1946" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1947" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1947" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B1947" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1947" s="5" t="s">
-        <v>13</v>
+      <c r="B1947" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="1948" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1948" s="3" t="s">
-        <v>4</v>
+      <c r="A1948" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B1948" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1948" s="5" t="s">
         <v>13</v>
@@ -16080,7 +16080,7 @@
     </row>
     <row r="1949" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1949" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1949" s="5" t="s">
         <v>13</v>
@@ -16088,7 +16088,7 @@
     </row>
     <row r="1950" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1950" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1950" s="5" t="s">
         <v>13</v>
@@ -16096,7 +16096,7 @@
     </row>
     <row r="1951" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1951" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1951" s="5" t="s">
         <v>13</v>
@@ -16104,40 +16104,128 @@
     </row>
     <row r="1952" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1952" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1952" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="1953" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="1953" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1953" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1953" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="1954" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="1954" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1954" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1954" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="1955" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="1955" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1955" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1956" spans="2:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C1955" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1956" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1956" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="1957" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B1957" s="3">
+        <v>11</v>
+      </c>
+      <c r="C1956" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1957" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1957" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1958" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1958" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B1958" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1958" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1959" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1959" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1959" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1960" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1960" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1960" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1961" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1961" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1961" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1962" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1962" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1962" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1963" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1963" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1963" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1964" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1964" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1964" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1965" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1965" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1965" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1966" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1966" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1967" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1967" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1968" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1968" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F36BA27-00FF-46F6-A6AC-F05B841B3E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC53D487-55B9-4289-89CF-9B8C58BA86D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3753" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3774" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1968"/>
+  <dimension ref="A1:C1979"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6092,9 +6092,6 @@
       <c r="B704" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C704" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="705" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B705" s="3" t="s">
@@ -6106,7 +6103,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6183,6 +6180,9 @@
       <c r="B715" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C715" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="716" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B716" s="3" t="s">
@@ -6194,7 +6194,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6282,7 +6282,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6370,7 +6370,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6458,7 +6458,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6546,7 +6546,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6623,9 +6623,6 @@
       <c r="B770" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C770" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="771" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B771" s="3" t="s">
@@ -6637,7 +6634,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6728,7 +6725,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6819,7 +6816,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6910,7 +6907,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6987,6 +6984,9 @@
       <c r="B814" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C814" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="815" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B815" s="3" t="s">
@@ -6998,7 +6998,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7075,9 +7075,6 @@
       <c r="B825" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C825" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="826" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B826" s="3" t="s">
@@ -7089,7 +7086,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7180,7 +7177,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7271,7 +7268,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7362,7 +7359,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7453,7 +7450,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7544,7 +7541,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7635,7 +7632,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7726,7 +7723,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7817,7 +7814,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7908,7 +7905,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -7999,7 +7996,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8090,7 +8087,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8181,7 +8178,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8272,7 +8269,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8363,7 +8360,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8454,7 +8451,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8545,7 +8542,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8636,7 +8633,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8727,7 +8724,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8818,7 +8815,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8909,7 +8906,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -9000,7 +8997,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9091,7 +9088,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9182,7 +9179,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9273,7 +9270,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9364,7 +9361,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9455,7 +9452,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9546,7 +9543,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9637,7 +9634,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9728,7 +9725,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9819,7 +9816,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9910,7 +9907,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -10001,7 +9998,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10078,6 +10075,9 @@
       <c r="B1188" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1188" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1189" s="3" t="s">
@@ -10089,7 +10089,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10166,9 +10166,6 @@
       <c r="B1199" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1199" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1200" s="3" t="s">
@@ -10180,7 +10177,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10271,7 +10268,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10362,7 +10359,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10453,7 +10450,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10544,7 +10541,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10635,7 +10632,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10726,7 +10723,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10817,7 +10814,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10908,7 +10905,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10999,7 +10996,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11068,6 +11065,9 @@
       <c r="B1308" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1308" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1309" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1309" s="3" t="s">
@@ -11087,7 +11087,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11156,9 +11156,6 @@
       <c r="B1319" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1319" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1320" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1320" s="3" t="s">
@@ -11178,7 +11175,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11255,6 +11252,9 @@
       <c r="B1331" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1331" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1332" s="3" t="s">
@@ -11266,7 +11266,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11335,6 +11335,9 @@
       <c r="B1341" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1341" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1342" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1342" s="3" t="s">
@@ -11351,7 +11354,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11420,9 +11423,6 @@
       <c r="B1352" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1352" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1353" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1353" s="3" t="s">
@@ -11439,7 +11439,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11508,6 +11508,9 @@
       <c r="B1363" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1363" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1364" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1364" s="3" t="s">
@@ -11524,7 +11527,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11593,9 +11596,6 @@
       <c r="B1374" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1374" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1375" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1375" s="3" t="s">
@@ -11612,7 +11612,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11700,7 +11700,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11788,7 +11788,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11857,6 +11857,9 @@
       <c r="B1407" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1407" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1408" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1408" s="3" t="s">
@@ -11873,7 +11876,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11958,7 +11961,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12043,7 +12046,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12128,7 +12131,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12213,7 +12216,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12298,7 +12301,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12383,7 +12386,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12468,7 +12471,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12553,7 +12556,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12638,7 +12641,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12723,7 +12726,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12808,7 +12811,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12877,9 +12880,6 @@
       <c r="B1539" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1539" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1540" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1540" s="3" t="s">
@@ -12896,7 +12896,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -12965,6 +12965,9 @@
       <c r="B1550" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1550" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1551" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1551" s="3" t="s">
@@ -12981,7 +12984,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13066,7 +13069,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13151,7 +13154,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13220,9 +13223,6 @@
       <c r="B1583" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1583" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1584" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1584" s="3" t="s">
@@ -13239,7 +13239,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13327,7 +13327,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13396,6 +13396,9 @@
       <c r="B1605" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1605" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1606" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1606" s="3" t="s">
@@ -13412,7 +13415,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13497,7 +13500,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13582,7 +13585,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13667,7 +13670,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13736,9 +13739,6 @@
       <c r="B1649" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1649" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1650" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1650" s="3" t="s">
@@ -13755,7 +13755,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13843,7 +13843,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13920,9 +13920,6 @@
       <c r="B1672" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1672" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1673" s="3" t="s">
@@ -13934,7 +13931,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14011,6 +14008,9 @@
       <c r="B1683" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1683" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1684" s="3" t="s">
@@ -14022,7 +14022,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14110,7 +14110,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14198,7 +14198,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14286,7 +14286,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14374,7 +14374,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14443,6 +14443,9 @@
       <c r="B1737" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1737" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1738" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1738" s="3" t="s">
@@ -14459,7 +14462,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14520,7 +14523,9 @@
       <c r="B1747" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1747" s="6"/>
+      <c r="C1747" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1748" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1748" s="3" t="s">
@@ -14536,10 +14541,13 @@
       <c r="B1750" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1750" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14600,17 +14608,12 @@
       <c r="B1758" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1758" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1758" s="6"/>
     </row>
     <row r="1759" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1759" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1759" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1760" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1760" s="3" t="s">
@@ -14621,13 +14624,10 @@
       <c r="B1761" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1761" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14715,7 +14715,7 @@
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14803,7 +14803,7 @@
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14872,6 +14872,9 @@
       <c r="B1792" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1792" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1793" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1793" s="3" t="s">
@@ -14888,7 +14891,7 @@
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14973,7 +14976,7 @@
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15047,9 +15050,6 @@
       <c r="B1815" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1815" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1816" s="3" t="s">
@@ -15061,7 +15061,7 @@
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15122,7 +15122,9 @@
       <c r="B1824" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1824" s="6"/>
+      <c r="C1824" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1825" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1825" s="3" t="s">
@@ -15133,15 +15135,21 @@
       <c r="B1826" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1826" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1827" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1827" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15202,9 +15210,7 @@
       <c r="B1835" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1835" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1835" s="6"/>
     </row>
     <row r="1836" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1836" s="3" t="s">
@@ -15220,13 +15226,10 @@
       <c r="B1838" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1838" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15295,9 +15298,6 @@
       <c r="B1847" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1847" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1848" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1848" s="3" t="s">
@@ -15314,7 +15314,7 @@
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15383,6 +15383,9 @@
       <c r="B1858" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1858" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1859" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1859" s="3" t="s">
@@ -15399,7 +15402,7 @@
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15478,10 +15481,13 @@
       <c r="B1871" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1871" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1872" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B1872" s="7" t="s">
         <v>3</v>
@@ -15560,13 +15566,10 @@
       <c r="B1882" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1882" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1883" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B1883" s="7" t="s">
         <v>3</v>
@@ -15635,9 +15638,6 @@
       <c r="B1891" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1891" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1892" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1892" s="3" t="s">
@@ -15654,7 +15654,7 @@
     </row>
     <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1894" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B1894" s="7" t="s">
         <v>3</v>
@@ -15675,19 +15675,25 @@
       <c r="B1896" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1896" s="6"/>
+      <c r="C1896" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1897" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1897" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1897" s="6"/>
+      <c r="C1897" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1898" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1898" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1898" s="6"/>
+      <c r="C1898" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1899" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1899" s="3" t="s">
@@ -15709,12 +15715,17 @@
       <c r="B1901" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1901" s="6"/>
+      <c r="C1901" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1902" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1902" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1902" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1903" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1903" s="3" t="s">
@@ -15725,10 +15736,13 @@
       <c r="B1904" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1904" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1905" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B1905" s="7" t="s">
         <v>3</v>
@@ -15749,25 +15763,19 @@
       <c r="B1907" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1907" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1907" s="6"/>
     </row>
     <row r="1908" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1908" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1908" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1908" s="6"/>
     </row>
     <row r="1909" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1909" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1909" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1909" s="6"/>
     </row>
     <row r="1910" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1910" s="3" t="s">
@@ -15789,17 +15797,12 @@
       <c r="B1912" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1912" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1912" s="6"/>
     </row>
     <row r="1913" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1913" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1913" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1914" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1914" s="3" t="s">
@@ -15810,13 +15813,10 @@
       <c r="B1915" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1915" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1916" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B1916" s="7" t="s">
         <v>3</v>
@@ -15904,7 +15904,7 @@
     </row>
     <row r="1927" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1927" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B1927" s="7" t="s">
         <v>3</v>
@@ -15973,6 +15973,9 @@
       <c r="B1935" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1935" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1936" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1936" s="3" t="s">
@@ -15989,7 +15992,7 @@
     </row>
     <row r="1938" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1938" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B1938" s="7" t="s">
         <v>3</v>
@@ -16058,9 +16061,6 @@
       <c r="B1946" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1946" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1947" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1947" s="3" t="s">
@@ -16068,19 +16068,19 @@
       </c>
     </row>
     <row r="1948" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1948" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B1948" s="7" t="s">
-        <v>3</v>
+      <c r="B1948" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C1948" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="1949" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1949" s="3" t="s">
-        <v>4</v>
+      <c r="A1949" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B1949" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1949" s="5" t="s">
         <v>13</v>
@@ -16088,7 +16088,7 @@
     </row>
     <row r="1950" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1950" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1950" s="5" t="s">
         <v>13</v>
@@ -16096,7 +16096,7 @@
     </row>
     <row r="1951" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1951" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1951" s="5" t="s">
         <v>13</v>
@@ -16104,7 +16104,7 @@
     </row>
     <row r="1952" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1952" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1952" s="5" t="s">
         <v>13</v>
@@ -16112,7 +16112,7 @@
     </row>
     <row r="1953" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1953" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1953" s="5" t="s">
         <v>13</v>
@@ -16120,7 +16120,7 @@
     </row>
     <row r="1954" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1954" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1954" s="5" t="s">
         <v>13</v>
@@ -16128,7 +16128,7 @@
     </row>
     <row r="1955" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1955" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1955" s="5" t="s">
         <v>13</v>
@@ -16136,7 +16136,7 @@
     </row>
     <row r="1956" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1956" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1956" s="5" t="s">
         <v>13</v>
@@ -16144,23 +16144,23 @@
     </row>
     <row r="1957" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1957" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C1957" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1958" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1958" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B1958" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1958" s="5" t="s">
-        <v>13</v>
+      <c r="B1958" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="1959" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1959" s="3" t="s">
-        <v>4</v>
+      <c r="A1959" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B1959" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1959" s="5" t="s">
         <v>13</v>
@@ -16168,7 +16168,7 @@
     </row>
     <row r="1960" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1960" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1960" s="5" t="s">
         <v>13</v>
@@ -16176,7 +16176,7 @@
     </row>
     <row r="1961" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1961" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1961" s="5" t="s">
         <v>13</v>
@@ -16184,7 +16184,7 @@
     </row>
     <row r="1962" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1962" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1962" s="5" t="s">
         <v>13</v>
@@ -16192,7 +16192,7 @@
     </row>
     <row r="1963" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1963" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1963" s="5" t="s">
         <v>13</v>
@@ -16200,7 +16200,7 @@
     </row>
     <row r="1964" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1964" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1964" s="5" t="s">
         <v>13</v>
@@ -16208,7 +16208,7 @@
     </row>
     <row r="1965" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1965" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1965" s="5" t="s">
         <v>13</v>
@@ -16216,16 +16216,104 @@
     </row>
     <row r="1966" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1966" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C1966" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1967" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1967" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C1967" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1968" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1968" s="3">
+      <c r="B1968" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1969" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1969" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B1969" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1969" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1970" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1970" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1970" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1971" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1971" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1971" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1972" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1972" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1972" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1973" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1973" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1973" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1974" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1974" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1974" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1975" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1975" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1975" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1976" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1976" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1976" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1977" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1977" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1978" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1978" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1979" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1979" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC53D487-55B9-4289-89CF-9B8C58BA86D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0BD27A2-56E6-49C0-A153-CA99E39A8C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3774" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3795" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1979"/>
+  <dimension ref="A1:C1990"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6180,9 +6180,6 @@
       <c r="B715" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C715" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="716" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B716" s="3" t="s">
@@ -6194,7 +6191,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6271,6 +6268,9 @@
       <c r="B726" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C726" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="727" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B727" s="3" t="s">
@@ -6282,7 +6282,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6370,7 +6370,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6458,7 +6458,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6546,7 +6546,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6634,7 +6634,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6711,9 +6711,6 @@
       <c r="B781" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C781" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="782" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B782" s="3" t="s">
@@ -6725,7 +6722,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6816,7 +6813,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6907,7 +6904,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6998,7 +6995,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7075,6 +7072,9 @@
       <c r="B825" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C825" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="826" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B826" s="3" t="s">
@@ -7086,7 +7086,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7163,9 +7163,6 @@
       <c r="B836" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C836" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="837" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B837" s="3" t="s">
@@ -7177,7 +7174,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7268,7 +7265,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7359,7 +7356,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7450,7 +7447,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7541,7 +7538,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7632,7 +7629,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7723,7 +7720,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7814,7 +7811,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7905,7 +7902,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -7996,7 +7993,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8087,7 +8084,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8178,7 +8175,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8269,7 +8266,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8360,7 +8357,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8451,7 +8448,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8542,7 +8539,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8633,7 +8630,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8724,7 +8721,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8815,7 +8812,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8906,7 +8903,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -8997,7 +8994,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9088,7 +9085,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9179,7 +9176,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9270,7 +9267,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9361,7 +9358,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9452,7 +9449,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9543,7 +9540,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9634,7 +9631,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9725,7 +9722,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9816,7 +9813,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9907,7 +9904,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -9998,7 +9995,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10089,7 +10086,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10166,6 +10163,9 @@
       <c r="B1199" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1199" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1200" s="3" t="s">
@@ -10177,7 +10177,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10254,9 +10254,6 @@
       <c r="B1210" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1210" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1211" s="3" t="s">
@@ -10268,7 +10265,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10359,7 +10356,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10450,7 +10447,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10541,7 +10538,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10632,7 +10629,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10723,7 +10720,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10814,7 +10811,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10905,7 +10902,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10996,7 +10993,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11087,7 +11084,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11156,6 +11153,9 @@
       <c r="B1319" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1319" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1320" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1320" s="3" t="s">
@@ -11175,7 +11175,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11244,9 +11244,6 @@
       <c r="B1330" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1330" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1331" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1331" s="3" t="s">
@@ -11266,7 +11263,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11343,6 +11340,9 @@
       <c r="B1342" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1342" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1343" s="3" t="s">
@@ -11354,7 +11354,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11423,6 +11423,9 @@
       <c r="B1352" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1352" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1353" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1353" s="3" t="s">
@@ -11439,7 +11442,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11508,9 +11511,6 @@
       <c r="B1363" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1363" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1364" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1364" s="3" t="s">
@@ -11527,7 +11527,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11596,6 +11596,9 @@
       <c r="B1374" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1374" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1375" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1375" s="3" t="s">
@@ -11612,7 +11615,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11681,9 +11684,6 @@
       <c r="B1385" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1385" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1386" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1386" s="3" t="s">
@@ -11700,7 +11700,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11788,7 +11788,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11876,7 +11876,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11945,6 +11945,9 @@
       <c r="B1418" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1418" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1419" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1419" s="3" t="s">
@@ -11961,7 +11964,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12046,7 +12049,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12131,7 +12134,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12216,7 +12219,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12301,7 +12304,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12386,7 +12389,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12471,7 +12474,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12556,7 +12559,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12641,7 +12644,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12726,7 +12729,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12811,7 +12814,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12896,7 +12899,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -12965,9 +12968,6 @@
       <c r="B1550" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1550" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1551" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1551" s="3" t="s">
@@ -12984,7 +12984,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13053,6 +13053,9 @@
       <c r="B1561" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1561" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1562" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1562" s="3" t="s">
@@ -13069,7 +13072,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13154,7 +13157,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13239,7 +13242,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13308,9 +13311,6 @@
       <c r="B1594" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1594" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1595" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1595" s="3" t="s">
@@ -13327,7 +13327,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13415,7 +13415,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13484,6 +13484,9 @@
       <c r="B1616" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1616" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1617" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1617" s="3" t="s">
@@ -13500,7 +13503,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13585,7 +13588,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13670,7 +13673,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13755,7 +13758,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13824,9 +13827,6 @@
       <c r="B1660" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1660" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1661" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1661" s="3" t="s">
@@ -13843,7 +13843,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13931,7 +13931,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14008,9 +14008,6 @@
       <c r="B1683" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1683" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1684" s="3" t="s">
@@ -14022,7 +14019,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14099,6 +14096,9 @@
       <c r="B1694" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1694" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1695" s="3" t="s">
@@ -14110,7 +14110,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14198,7 +14198,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14286,7 +14286,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14374,7 +14374,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14462,7 +14462,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14531,6 +14531,9 @@
       <c r="B1748" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1748" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1749" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1749" s="3" t="s">
@@ -14547,7 +14550,7 @@
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14608,7 +14611,9 @@
       <c r="B1758" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1758" s="6"/>
+      <c r="C1758" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1759" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1759" s="3" t="s">
@@ -14624,10 +14629,13 @@
       <c r="B1761" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1761" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14688,17 +14696,12 @@
       <c r="B1769" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1769" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1769" s="6"/>
     </row>
     <row r="1770" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1770" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1770" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1771" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1771" s="3" t="s">
@@ -14709,13 +14712,10 @@
       <c r="B1772" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1772" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14803,7 +14803,7 @@
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14891,7 +14891,7 @@
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14960,6 +14960,9 @@
       <c r="B1803" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1803" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1804" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1804" s="3" t="s">
@@ -14976,7 +14979,7 @@
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15061,7 +15064,7 @@
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15135,9 +15138,6 @@
       <c r="B1826" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1826" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1827" s="3" t="s">
@@ -15149,7 +15149,7 @@
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15210,7 +15210,9 @@
       <c r="B1835" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1835" s="6"/>
+      <c r="C1835" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1836" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1836" s="3" t="s">
@@ -15221,15 +15223,21 @@
       <c r="B1837" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1837" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1838" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1838" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15290,9 +15298,7 @@
       <c r="B1846" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1846" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1846" s="6"/>
     </row>
     <row r="1847" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1847" s="3" t="s">
@@ -15308,13 +15314,10 @@
       <c r="B1849" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1849" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15383,9 +15386,6 @@
       <c r="B1858" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1858" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1859" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1859" s="3" t="s">
@@ -15402,7 +15402,7 @@
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15471,6 +15471,9 @@
       <c r="B1869" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1869" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1870" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1870" s="3" t="s">
@@ -15487,7 +15490,7 @@
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1872" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B1872" s="7" t="s">
         <v>3</v>
@@ -15566,10 +15569,13 @@
       <c r="B1882" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1882" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1883" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B1883" s="7" t="s">
         <v>3</v>
@@ -15648,13 +15654,10 @@
       <c r="B1893" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1893" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1894" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B1894" s="7" t="s">
         <v>3</v>
@@ -15723,9 +15726,6 @@
       <c r="B1902" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1902" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1903" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1903" s="3" t="s">
@@ -15742,7 +15742,7 @@
     </row>
     <row r="1905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1905" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B1905" s="7" t="s">
         <v>3</v>
@@ -15763,19 +15763,25 @@
       <c r="B1907" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1907" s="6"/>
+      <c r="C1907" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1908" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1908" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1908" s="6"/>
+      <c r="C1908" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1909" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1909" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1909" s="6"/>
+      <c r="C1909" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1910" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1910" s="3" t="s">
@@ -15797,12 +15803,17 @@
       <c r="B1912" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1912" s="6"/>
+      <c r="C1912" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1913" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1913" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1913" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1914" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1914" s="3" t="s">
@@ -15813,10 +15824,13 @@
       <c r="B1915" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1915" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1916" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B1916" s="7" t="s">
         <v>3</v>
@@ -15837,25 +15851,19 @@
       <c r="B1918" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1918" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1918" s="6"/>
     </row>
     <row r="1919" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1919" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1919" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1919" s="6"/>
     </row>
     <row r="1920" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1920" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1920" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1920" s="6"/>
     </row>
     <row r="1921" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1921" s="3" t="s">
@@ -15877,17 +15885,12 @@
       <c r="B1923" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1923" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1923" s="6"/>
     </row>
     <row r="1924" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1924" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1924" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1925" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1925" s="3" t="s">
@@ -15898,13 +15901,10 @@
       <c r="B1926" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1926" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1927" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1927" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B1927" s="7" t="s">
         <v>3</v>
@@ -15992,7 +15992,7 @@
     </row>
     <row r="1938" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1938" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B1938" s="7" t="s">
         <v>3</v>
@@ -16061,6 +16061,9 @@
       <c r="B1946" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1946" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1947" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1947" s="3" t="s">
@@ -16077,7 +16080,7 @@
     </row>
     <row r="1949" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1949" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B1949" s="7" t="s">
         <v>3</v>
@@ -16146,9 +16149,6 @@
       <c r="B1957" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1957" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1958" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1958" s="3" t="s">
@@ -16156,19 +16156,19 @@
       </c>
     </row>
     <row r="1959" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1959" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B1959" s="7" t="s">
-        <v>3</v>
+      <c r="B1959" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C1959" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="1960" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1960" s="3" t="s">
-        <v>4</v>
+      <c r="A1960" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B1960" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1960" s="5" t="s">
         <v>13</v>
@@ -16176,7 +16176,7 @@
     </row>
     <row r="1961" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1961" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1961" s="5" t="s">
         <v>13</v>
@@ -16184,7 +16184,7 @@
     </row>
     <row r="1962" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1962" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1962" s="5" t="s">
         <v>13</v>
@@ -16192,7 +16192,7 @@
     </row>
     <row r="1963" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1963" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1963" s="5" t="s">
         <v>13</v>
@@ -16200,7 +16200,7 @@
     </row>
     <row r="1964" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1964" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1964" s="5" t="s">
         <v>13</v>
@@ -16208,7 +16208,7 @@
     </row>
     <row r="1965" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1965" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1965" s="5" t="s">
         <v>13</v>
@@ -16216,7 +16216,7 @@
     </row>
     <row r="1966" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1966" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1966" s="5" t="s">
         <v>13</v>
@@ -16224,7 +16224,7 @@
     </row>
     <row r="1967" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1967" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1967" s="5" t="s">
         <v>13</v>
@@ -16232,23 +16232,23 @@
     </row>
     <row r="1968" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1968" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C1968" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1969" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1969" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B1969" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1969" s="5" t="s">
-        <v>13</v>
+      <c r="B1969" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="1970" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1970" s="3" t="s">
-        <v>4</v>
+      <c r="A1970" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B1970" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1970" s="5" t="s">
         <v>13</v>
@@ -16256,7 +16256,7 @@
     </row>
     <row r="1971" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1971" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1971" s="5" t="s">
         <v>13</v>
@@ -16264,7 +16264,7 @@
     </row>
     <row r="1972" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1972" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1972" s="5" t="s">
         <v>13</v>
@@ -16272,7 +16272,7 @@
     </row>
     <row r="1973" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1973" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1973" s="5" t="s">
         <v>13</v>
@@ -16280,7 +16280,7 @@
     </row>
     <row r="1974" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1974" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1974" s="5" t="s">
         <v>13</v>
@@ -16288,7 +16288,7 @@
     </row>
     <row r="1975" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1975" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1975" s="5" t="s">
         <v>13</v>
@@ -16296,7 +16296,7 @@
     </row>
     <row r="1976" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1976" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1976" s="5" t="s">
         <v>13</v>
@@ -16304,16 +16304,104 @@
     </row>
     <row r="1977" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1977" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C1977" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1978" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1978" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C1978" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1979" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1979" s="3">
+      <c r="B1979" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1980" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1980" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B1980" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1980" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1981" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1981" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1981" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1982" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1982" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1982" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1983" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1983" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1983" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1984" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1984" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1984" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1985" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1985" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1985" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1986" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1986" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1986" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1987" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1987" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1987" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1988" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1988" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="1989" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1989" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1990" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B1990" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0BD27A2-56E6-49C0-A153-CA99E39A8C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D88F3D0-855C-4471-A33A-DFDBF60DE3C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3795" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3816" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1990"/>
+  <dimension ref="A1:C2001"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6191,7 +6191,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6268,9 +6268,6 @@
       <c r="B726" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C726" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="727" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B727" s="3" t="s">
@@ -6282,7 +6279,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6359,6 +6356,9 @@
       <c r="B737" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C737" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="738" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B738" s="3" t="s">
@@ -6370,7 +6370,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6458,7 +6458,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6546,7 +6546,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6634,7 +6634,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6722,7 +6722,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6799,9 +6799,6 @@
       <c r="B792" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C792" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="793" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B793" s="3" t="s">
@@ -6813,7 +6810,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6904,7 +6901,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6995,7 +6992,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7086,7 +7083,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7163,6 +7160,9 @@
       <c r="B836" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C836" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="837" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B837" s="3" t="s">
@@ -7174,7 +7174,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7251,9 +7251,6 @@
       <c r="B847" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C847" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="848" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B848" s="3" t="s">
@@ -7265,7 +7262,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7356,7 +7353,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7447,7 +7444,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7538,7 +7535,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7629,7 +7626,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7720,7 +7717,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7811,7 +7808,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7902,7 +7899,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -7993,7 +7990,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8084,7 +8081,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8175,7 +8172,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8266,7 +8263,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8357,7 +8354,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8448,7 +8445,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8539,7 +8536,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8630,7 +8627,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8721,7 +8718,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8812,7 +8809,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8903,7 +8900,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -8994,7 +8991,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9085,7 +9082,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9176,7 +9173,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9267,7 +9264,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9358,7 +9355,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9449,7 +9446,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9540,7 +9537,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9631,7 +9628,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9722,7 +9719,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9813,7 +9810,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9904,7 +9901,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -9995,7 +9992,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10086,7 +10083,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10177,7 +10174,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10254,6 +10251,9 @@
       <c r="B1210" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1210" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1211" s="3" t="s">
@@ -10265,7 +10265,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10342,9 +10342,6 @@
       <c r="B1221" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1221" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1222" s="3" t="s">
@@ -10356,7 +10353,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10447,7 +10444,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10538,7 +10535,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10629,7 +10626,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10720,7 +10717,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10811,7 +10808,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10902,7 +10899,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10993,7 +10990,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11084,7 +11081,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11175,7 +11172,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11244,6 +11241,9 @@
       <c r="B1330" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1330" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1331" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1331" s="3" t="s">
@@ -11263,7 +11263,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11332,9 +11332,6 @@
       <c r="B1341" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1341" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1342" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1342" s="3" t="s">
@@ -11354,7 +11351,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11431,6 +11428,9 @@
       <c r="B1353" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1353" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1354" s="3" t="s">
@@ -11442,7 +11442,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11511,6 +11511,9 @@
       <c r="B1363" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1363" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1364" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1364" s="3" t="s">
@@ -11527,7 +11530,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11596,9 +11599,6 @@
       <c r="B1374" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1374" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1375" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1375" s="3" t="s">
@@ -11615,7 +11615,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11684,6 +11684,9 @@
       <c r="B1385" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1385" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1386" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1386" s="3" t="s">
@@ -11700,7 +11703,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11769,9 +11772,6 @@
       <c r="B1396" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1396" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1397" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1397" s="3" t="s">
@@ -11788,7 +11788,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11876,7 +11876,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11964,7 +11964,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12033,6 +12033,9 @@
       <c r="B1429" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1429" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1430" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1430" s="3" t="s">
@@ -12049,7 +12052,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12134,7 +12137,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12219,7 +12222,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12304,7 +12307,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12389,7 +12392,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12474,7 +12477,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12559,7 +12562,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12644,7 +12647,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12729,7 +12732,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12814,7 +12817,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12899,7 +12902,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -12984,7 +12987,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13053,9 +13056,6 @@
       <c r="B1561" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1561" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1562" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1562" s="3" t="s">
@@ -13072,7 +13072,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13141,6 +13141,9 @@
       <c r="B1572" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1572" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1573" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1573" s="3" t="s">
@@ -13157,7 +13160,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13242,7 +13245,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13327,7 +13330,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13396,9 +13399,6 @@
       <c r="B1605" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1605" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1606" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1606" s="3" t="s">
@@ -13415,7 +13415,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13503,7 +13503,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13572,6 +13572,9 @@
       <c r="B1627" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1627" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1628" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1628" s="3" t="s">
@@ -13588,7 +13591,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13673,7 +13676,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13758,7 +13761,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13843,7 +13846,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13912,9 +13915,6 @@
       <c r="B1671" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1671" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1672" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1672" s="3" t="s">
@@ -13931,7 +13931,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14019,7 +14019,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14096,9 +14096,6 @@
       <c r="B1694" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1694" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1695" s="3" t="s">
@@ -14110,7 +14107,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14187,6 +14184,9 @@
       <c r="B1705" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1705" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1706" s="3" t="s">
@@ -14198,7 +14198,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14286,7 +14286,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14374,7 +14374,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14462,7 +14462,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14550,7 +14550,7 @@
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14619,6 +14619,9 @@
       <c r="B1759" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1759" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1760" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1760" s="3" t="s">
@@ -14635,7 +14638,7 @@
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14696,7 +14699,9 @@
       <c r="B1769" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1769" s="6"/>
+      <c r="C1769" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1770" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1770" s="3" t="s">
@@ -14712,10 +14717,13 @@
       <c r="B1772" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1772" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14776,17 +14784,12 @@
       <c r="B1780" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1780" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1780" s="6"/>
     </row>
     <row r="1781" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1781" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1781" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1782" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1782" s="3" t="s">
@@ -14797,13 +14800,10 @@
       <c r="B1783" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1783" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14891,7 +14891,7 @@
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14979,7 +14979,7 @@
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15048,6 +15048,9 @@
       <c r="B1814" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1814" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1815" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1815" s="3" t="s">
@@ -15064,7 +15067,7 @@
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15149,7 +15152,7 @@
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15223,9 +15226,6 @@
       <c r="B1837" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1837" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1838" s="3" t="s">
@@ -15237,7 +15237,7 @@
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15298,7 +15298,9 @@
       <c r="B1846" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1846" s="6"/>
+      <c r="C1846" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1847" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1847" s="3" t="s">
@@ -15309,15 +15311,21 @@
       <c r="B1848" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1848" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1849" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1849" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15378,9 +15386,7 @@
       <c r="B1857" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1857" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1857" s="6"/>
     </row>
     <row r="1858" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1858" s="3" t="s">
@@ -15396,13 +15402,10 @@
       <c r="B1860" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1860" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15471,9 +15474,6 @@
       <c r="B1869" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1869" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1870" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1870" s="3" t="s">
@@ -15490,7 +15490,7 @@
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1872" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B1872" s="7" t="s">
         <v>3</v>
@@ -15559,6 +15559,9 @@
       <c r="B1880" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1880" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1881" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1881" s="3" t="s">
@@ -15575,7 +15578,7 @@
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1883" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B1883" s="7" t="s">
         <v>3</v>
@@ -15654,10 +15657,13 @@
       <c r="B1893" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1893" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1894" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B1894" s="7" t="s">
         <v>3</v>
@@ -15736,13 +15742,10 @@
       <c r="B1904" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1904" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1905" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B1905" s="7" t="s">
         <v>3</v>
@@ -15811,9 +15814,6 @@
       <c r="B1913" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1913" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1914" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1914" s="3" t="s">
@@ -15830,7 +15830,7 @@
     </row>
     <row r="1916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1916" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B1916" s="7" t="s">
         <v>3</v>
@@ -15851,19 +15851,25 @@
       <c r="B1918" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1918" s="6"/>
+      <c r="C1918" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1919" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1919" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1919" s="6"/>
+      <c r="C1919" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1920" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1920" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1920" s="6"/>
+      <c r="C1920" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1921" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1921" s="3" t="s">
@@ -15885,12 +15891,17 @@
       <c r="B1923" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1923" s="6"/>
+      <c r="C1923" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1924" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1924" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1924" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1925" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1925" s="3" t="s">
@@ -15901,10 +15912,13 @@
       <c r="B1926" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1926" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1927" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1927" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B1927" s="7" t="s">
         <v>3</v>
@@ -15925,25 +15939,19 @@
       <c r="B1929" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1929" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1929" s="6"/>
     </row>
     <row r="1930" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1930" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1930" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1930" s="6"/>
     </row>
     <row r="1931" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1931" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1931" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1931" s="6"/>
     </row>
     <row r="1932" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1932" s="3" t="s">
@@ -15965,17 +15973,12 @@
       <c r="B1934" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1934" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1934" s="6"/>
     </row>
     <row r="1935" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1935" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1935" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1936" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1936" s="3" t="s">
@@ -15986,13 +15989,10 @@
       <c r="B1937" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1937" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1938" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1938" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B1938" s="7" t="s">
         <v>3</v>
@@ -16080,7 +16080,7 @@
     </row>
     <row r="1949" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1949" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B1949" s="7" t="s">
         <v>3</v>
@@ -16149,6 +16149,9 @@
       <c r="B1957" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1957" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1958" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1958" s="3" t="s">
@@ -16165,7 +16168,7 @@
     </row>
     <row r="1960" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1960" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B1960" s="7" t="s">
         <v>3</v>
@@ -16234,9 +16237,6 @@
       <c r="B1968" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1968" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1969" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1969" s="3" t="s">
@@ -16244,19 +16244,19 @@
       </c>
     </row>
     <row r="1970" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1970" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B1970" s="7" t="s">
-        <v>3</v>
+      <c r="B1970" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C1970" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="1971" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1971" s="3" t="s">
-        <v>4</v>
+      <c r="A1971" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B1971" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1971" s="5" t="s">
         <v>13</v>
@@ -16264,7 +16264,7 @@
     </row>
     <row r="1972" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1972" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1972" s="5" t="s">
         <v>13</v>
@@ -16272,7 +16272,7 @@
     </row>
     <row r="1973" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1973" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1973" s="5" t="s">
         <v>13</v>
@@ -16280,7 +16280,7 @@
     </row>
     <row r="1974" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1974" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1974" s="5" t="s">
         <v>13</v>
@@ -16288,7 +16288,7 @@
     </row>
     <row r="1975" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1975" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1975" s="5" t="s">
         <v>13</v>
@@ -16296,7 +16296,7 @@
     </row>
     <row r="1976" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1976" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1976" s="5" t="s">
         <v>13</v>
@@ -16304,7 +16304,7 @@
     </row>
     <row r="1977" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1977" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1977" s="5" t="s">
         <v>13</v>
@@ -16312,7 +16312,7 @@
     </row>
     <row r="1978" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1978" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1978" s="5" t="s">
         <v>13</v>
@@ -16320,23 +16320,23 @@
     </row>
     <row r="1979" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1979" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C1979" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1980" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1980" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B1980" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1980" s="5" t="s">
-        <v>13</v>
+      <c r="B1980" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="1981" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1981" s="3" t="s">
-        <v>4</v>
+      <c r="A1981" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B1981" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1981" s="5" t="s">
         <v>13</v>
@@ -16344,7 +16344,7 @@
     </row>
     <row r="1982" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1982" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1982" s="5" t="s">
         <v>13</v>
@@ -16352,7 +16352,7 @@
     </row>
     <row r="1983" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1983" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1983" s="5" t="s">
         <v>13</v>
@@ -16360,48 +16360,136 @@
     </row>
     <row r="1984" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1984" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1984" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="1985" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="1985" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1985" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1985" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="1986" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="1986" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1986" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1986" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="1987" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="1987" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1987" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1987" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="1988" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="1988" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1988" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="1989" spans="2:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C1988" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1989" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1989" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="1990" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B1990" s="3">
+        <v>11</v>
+      </c>
+      <c r="C1989" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1990" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1990" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1991" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1991" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B1991" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1991" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1992" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1992" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1992" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1993" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1993" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1993" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1994" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1994" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1994" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1995" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1995" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1995" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1996" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1996" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1996" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1997" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1997" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1997" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1998" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1998" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1998" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="1999" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B1999" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2000" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2000" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2001" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B2001" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D88F3D0-855C-4471-A33A-DFDBF60DE3C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D84A3D23-8AFC-47B9-B984-24A61048323F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3816" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3837" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2001"/>
+  <dimension ref="A1:C2012"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6191,7 +6191,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6279,7 +6279,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6356,9 +6356,6 @@
       <c r="B737" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C737" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="738" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B738" s="3" t="s">
@@ -6370,7 +6367,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6447,6 +6444,9 @@
       <c r="B748" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C748" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="749" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B749" s="3" t="s">
@@ -6458,7 +6458,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6546,7 +6546,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6634,7 +6634,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6722,7 +6722,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6810,7 +6810,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6887,9 +6887,6 @@
       <c r="B803" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C803" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="804" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B804" s="3" t="s">
@@ -6901,7 +6898,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6992,7 +6989,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7083,7 +7080,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7174,7 +7171,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7251,6 +7248,9 @@
       <c r="B847" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C847" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="848" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B848" s="3" t="s">
@@ -7262,7 +7262,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7339,9 +7339,6 @@
       <c r="B858" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C858" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="859" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B859" s="3" t="s">
@@ -7353,7 +7350,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7444,7 +7441,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7535,7 +7532,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7626,7 +7623,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7717,7 +7714,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7808,7 +7805,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7899,7 +7896,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -7990,7 +7987,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8081,7 +8078,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8172,7 +8169,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8263,7 +8260,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8354,7 +8351,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8445,7 +8442,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8536,7 +8533,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8627,7 +8624,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8718,7 +8715,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8809,7 +8806,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8900,7 +8897,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -8991,7 +8988,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9082,7 +9079,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9173,7 +9170,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9264,7 +9261,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9355,7 +9352,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9446,7 +9443,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9537,7 +9534,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9628,7 +9625,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9719,7 +9716,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9810,7 +9807,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9901,7 +9898,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -9992,7 +9989,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10083,7 +10080,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10174,7 +10171,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10265,7 +10262,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10342,6 +10339,9 @@
       <c r="B1221" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1221" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1222" s="3" t="s">
@@ -10353,7 +10353,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10430,9 +10430,6 @@
       <c r="B1232" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1232" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1233" s="3" t="s">
@@ -10444,7 +10441,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10535,7 +10532,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10626,7 +10623,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10717,7 +10714,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10808,7 +10805,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10899,7 +10896,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10990,7 +10987,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11081,7 +11078,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11172,7 +11169,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11263,7 +11260,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11332,6 +11329,9 @@
       <c r="B1341" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1341" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1342" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1342" s="3" t="s">
@@ -11351,7 +11351,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11420,9 +11420,6 @@
       <c r="B1352" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1352" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1353" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1353" s="3" t="s">
@@ -11442,7 +11439,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11519,6 +11516,9 @@
       <c r="B1364" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1364" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1365" s="3" t="s">
@@ -11530,7 +11530,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11599,6 +11599,9 @@
       <c r="B1374" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1374" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1375" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1375" s="3" t="s">
@@ -11615,7 +11618,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11684,9 +11687,6 @@
       <c r="B1385" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1385" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1386" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1386" s="3" t="s">
@@ -11703,7 +11703,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11772,6 +11772,9 @@
       <c r="B1396" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1396" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1397" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1397" s="3" t="s">
@@ -11788,7 +11791,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11857,9 +11860,6 @@
       <c r="B1407" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1407" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1408" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1408" s="3" t="s">
@@ -11876,7 +11876,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11964,7 +11964,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12052,7 +12052,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12121,6 +12121,9 @@
       <c r="B1440" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1440" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1441" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1441" s="3" t="s">
@@ -12137,7 +12140,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12222,7 +12225,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12307,7 +12310,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12392,7 +12395,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12477,7 +12480,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12562,7 +12565,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12647,7 +12650,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12732,7 +12735,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12817,7 +12820,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12902,7 +12905,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -12987,7 +12990,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13072,7 +13075,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13141,9 +13144,6 @@
       <c r="B1572" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1572" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1573" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1573" s="3" t="s">
@@ -13160,7 +13160,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13229,6 +13229,9 @@
       <c r="B1583" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1583" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1584" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1584" s="3" t="s">
@@ -13245,7 +13248,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13330,7 +13333,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13415,7 +13418,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13484,9 +13487,6 @@
       <c r="B1616" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1616" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1617" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1617" s="3" t="s">
@@ -13503,7 +13503,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13591,7 +13591,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13660,6 +13660,9 @@
       <c r="B1638" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1638" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1639" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1639" s="3" t="s">
@@ -13676,7 +13679,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13761,7 +13764,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13846,7 +13849,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13931,7 +13934,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14000,9 +14003,6 @@
       <c r="B1682" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1682" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1683" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1683" s="3" t="s">
@@ -14019,7 +14019,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14107,7 +14107,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14184,9 +14184,6 @@
       <c r="B1705" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1705" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1706" s="3" t="s">
@@ -14198,7 +14195,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14275,6 +14272,9 @@
       <c r="B1716" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1716" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1717" s="3" t="s">
@@ -14286,7 +14286,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14374,7 +14374,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14462,7 +14462,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14550,7 +14550,7 @@
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14638,7 +14638,7 @@
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14707,6 +14707,9 @@
       <c r="B1770" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1770" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1771" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1771" s="3" t="s">
@@ -14723,7 +14726,7 @@
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14784,7 +14787,9 @@
       <c r="B1780" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1780" s="6"/>
+      <c r="C1780" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1781" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1781" s="3" t="s">
@@ -14800,10 +14805,13 @@
       <c r="B1783" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1783" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14864,17 +14872,12 @@
       <c r="B1791" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1791" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1791" s="6"/>
     </row>
     <row r="1792" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1792" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1792" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1793" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1793" s="3" t="s">
@@ -14885,13 +14888,10 @@
       <c r="B1794" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1794" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14979,7 +14979,7 @@
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15067,7 +15067,7 @@
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15136,6 +15136,9 @@
       <c r="B1825" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1825" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1826" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1826" s="3" t="s">
@@ -15152,7 +15155,7 @@
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15237,7 +15240,7 @@
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15311,9 +15314,6 @@
       <c r="B1848" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1848" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1849" s="3" t="s">
@@ -15325,7 +15325,7 @@
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15386,7 +15386,9 @@
       <c r="B1857" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1857" s="6"/>
+      <c r="C1857" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1858" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1858" s="3" t="s">
@@ -15397,15 +15399,21 @@
       <c r="B1859" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1859" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1860" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1860" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15466,9 +15474,7 @@
       <c r="B1868" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1868" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1868" s="6"/>
     </row>
     <row r="1869" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1869" s="3" t="s">
@@ -15484,13 +15490,10 @@
       <c r="B1871" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1871" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1872" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B1872" s="7" t="s">
         <v>3</v>
@@ -15559,9 +15562,6 @@
       <c r="B1880" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1880" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1881" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1881" s="3" t="s">
@@ -15578,7 +15578,7 @@
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1883" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B1883" s="7" t="s">
         <v>3</v>
@@ -15647,6 +15647,9 @@
       <c r="B1891" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1891" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1892" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1892" s="3" t="s">
@@ -15663,7 +15666,7 @@
     </row>
     <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1894" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B1894" s="7" t="s">
         <v>3</v>
@@ -15742,10 +15745,13 @@
       <c r="B1904" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1904" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1905" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B1905" s="7" t="s">
         <v>3</v>
@@ -15824,13 +15830,10 @@
       <c r="B1915" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1915" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1916" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B1916" s="7" t="s">
         <v>3</v>
@@ -15899,9 +15902,6 @@
       <c r="B1924" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1924" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1925" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1925" s="3" t="s">
@@ -15918,7 +15918,7 @@
     </row>
     <row r="1927" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1927" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B1927" s="7" t="s">
         <v>3</v>
@@ -15939,19 +15939,25 @@
       <c r="B1929" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1929" s="6"/>
+      <c r="C1929" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1930" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1930" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1930" s="6"/>
+      <c r="C1930" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1931" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1931" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1931" s="6"/>
+      <c r="C1931" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1932" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1932" s="3" t="s">
@@ -15973,12 +15979,17 @@
       <c r="B1934" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1934" s="6"/>
+      <c r="C1934" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1935" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1935" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1935" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1936" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1936" s="3" t="s">
@@ -15989,10 +16000,13 @@
       <c r="B1937" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1937" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1938" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1938" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B1938" s="7" t="s">
         <v>3</v>
@@ -16013,25 +16027,19 @@
       <c r="B1940" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1940" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1940" s="6"/>
     </row>
     <row r="1941" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1941" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1941" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1941" s="6"/>
     </row>
     <row r="1942" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1942" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1942" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1942" s="6"/>
     </row>
     <row r="1943" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1943" s="3" t="s">
@@ -16053,17 +16061,12 @@
       <c r="B1945" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1945" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1945" s="6"/>
     </row>
     <row r="1946" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1946" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1946" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1947" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1947" s="3" t="s">
@@ -16074,13 +16077,10 @@
       <c r="B1948" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1948" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1949" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1949" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B1949" s="7" t="s">
         <v>3</v>
@@ -16168,7 +16168,7 @@
     </row>
     <row r="1960" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1960" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B1960" s="7" t="s">
         <v>3</v>
@@ -16237,6 +16237,9 @@
       <c r="B1968" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1968" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1969" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1969" s="3" t="s">
@@ -16253,7 +16256,7 @@
     </row>
     <row r="1971" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1971" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B1971" s="7" t="s">
         <v>3</v>
@@ -16322,9 +16325,6 @@
       <c r="B1979" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1979" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1980" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1980" s="3" t="s">
@@ -16332,19 +16332,19 @@
       </c>
     </row>
     <row r="1981" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1981" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B1981" s="7" t="s">
-        <v>3</v>
+      <c r="B1981" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C1981" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="1982" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1982" s="3" t="s">
-        <v>4</v>
+      <c r="A1982" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B1982" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1982" s="5" t="s">
         <v>13</v>
@@ -16352,7 +16352,7 @@
     </row>
     <row r="1983" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1983" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1983" s="5" t="s">
         <v>13</v>
@@ -16360,7 +16360,7 @@
     </row>
     <row r="1984" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1984" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1984" s="5" t="s">
         <v>13</v>
@@ -16368,7 +16368,7 @@
     </row>
     <row r="1985" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1985" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1985" s="5" t="s">
         <v>13</v>
@@ -16376,7 +16376,7 @@
     </row>
     <row r="1986" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1986" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1986" s="5" t="s">
         <v>13</v>
@@ -16384,7 +16384,7 @@
     </row>
     <row r="1987" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1987" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1987" s="5" t="s">
         <v>13</v>
@@ -16392,7 +16392,7 @@
     </row>
     <row r="1988" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1988" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1988" s="5" t="s">
         <v>13</v>
@@ -16400,7 +16400,7 @@
     </row>
     <row r="1989" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1989" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1989" s="5" t="s">
         <v>13</v>
@@ -16408,23 +16408,23 @@
     </row>
     <row r="1990" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1990" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C1990" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="1991" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1991" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B1991" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1991" s="5" t="s">
-        <v>13</v>
+      <c r="B1991" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="1992" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1992" s="3" t="s">
-        <v>4</v>
+      <c r="A1992" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B1992" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1992" s="5" t="s">
         <v>13</v>
@@ -16432,7 +16432,7 @@
     </row>
     <row r="1993" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1993" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1993" s="5" t="s">
         <v>13</v>
@@ -16440,7 +16440,7 @@
     </row>
     <row r="1994" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1994" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1994" s="5" t="s">
         <v>13</v>
@@ -16448,7 +16448,7 @@
     </row>
     <row r="1995" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1995" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1995" s="5" t="s">
         <v>13</v>
@@ -16456,7 +16456,7 @@
     </row>
     <row r="1996" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1996" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1996" s="5" t="s">
         <v>13</v>
@@ -16464,7 +16464,7 @@
     </row>
     <row r="1997" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1997" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1997" s="5" t="s">
         <v>13</v>
@@ -16472,7 +16472,7 @@
     </row>
     <row r="1998" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1998" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1998" s="5" t="s">
         <v>13</v>
@@ -16480,16 +16480,104 @@
     </row>
     <row r="1999" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1999" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C1999" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2000" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2000" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2001" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B2001" s="3">
+        <v>11</v>
+      </c>
+      <c r="C2000" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2001" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2001" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2002" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2002" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B2002" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2002" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2003" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2003" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2003" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2004" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2004" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2004" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2005" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2005" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2005" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2006" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2006" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2006" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2007" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2007" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2007" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2008" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2008" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2008" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2009" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2009" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2009" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2010" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2010" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2011" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2011" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2012" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2012" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D84A3D23-8AFC-47B9-B984-24A61048323F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81515BD0-6510-4B34-8443-C72377C4232A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3837" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3858" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2012"/>
+  <dimension ref="A1:C2023"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6191,7 +6191,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6279,7 +6279,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6367,7 +6367,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6444,9 +6444,6 @@
       <c r="B748" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C748" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="749" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B749" s="3" t="s">
@@ -6458,7 +6455,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6535,6 +6532,9 @@
       <c r="B759" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C759" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="760" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B760" s="3" t="s">
@@ -6546,7 +6546,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6634,7 +6634,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6722,7 +6722,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6810,7 +6810,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6898,7 +6898,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6975,9 +6975,6 @@
       <c r="B814" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C814" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="815" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B815" s="3" t="s">
@@ -6989,7 +6986,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7080,7 +7077,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7171,7 +7168,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7262,7 +7259,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7339,6 +7336,9 @@
       <c r="B858" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C858" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="859" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B859" s="3" t="s">
@@ -7350,7 +7350,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7427,9 +7427,6 @@
       <c r="B869" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C869" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="870" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B870" s="3" t="s">
@@ -7441,7 +7438,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7532,7 +7529,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7623,7 +7620,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7714,7 +7711,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7805,7 +7802,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7896,7 +7893,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -7987,7 +7984,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8078,7 +8075,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8169,7 +8166,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8260,7 +8257,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8351,7 +8348,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8442,7 +8439,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8533,7 +8530,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8624,7 +8621,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8715,7 +8712,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8806,7 +8803,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8897,7 +8894,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -8988,7 +8985,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9079,7 +9076,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9170,7 +9167,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9261,7 +9258,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9352,7 +9349,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9443,7 +9440,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9534,7 +9531,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9625,7 +9622,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9716,7 +9713,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9807,7 +9804,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9898,7 +9895,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -9989,7 +9986,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10080,7 +10077,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10171,7 +10168,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10262,7 +10259,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10353,7 +10350,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10430,6 +10427,9 @@
       <c r="B1232" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1232" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1233" s="3" t="s">
@@ -10441,7 +10441,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10518,9 +10518,6 @@
       <c r="B1243" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1243" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1244" s="3" t="s">
@@ -10532,7 +10529,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10623,7 +10620,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10714,7 +10711,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10805,7 +10802,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10896,7 +10893,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10987,7 +10984,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11078,7 +11075,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11169,7 +11166,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11260,7 +11257,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11351,7 +11348,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11420,6 +11417,9 @@
       <c r="B1352" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1352" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1353" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1353" s="3" t="s">
@@ -11439,7 +11439,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11508,9 +11508,6 @@
       <c r="B1363" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1363" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1364" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1364" s="3" t="s">
@@ -11530,7 +11527,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11607,6 +11604,9 @@
       <c r="B1375" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1375" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1376" s="3" t="s">
@@ -11618,7 +11618,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11687,6 +11687,9 @@
       <c r="B1385" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1385" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1386" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1386" s="3" t="s">
@@ -11703,7 +11706,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11772,9 +11775,6 @@
       <c r="B1396" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1396" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1397" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1397" s="3" t="s">
@@ -11791,7 +11791,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11860,6 +11860,9 @@
       <c r="B1407" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1407" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1408" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1408" s="3" t="s">
@@ -11876,7 +11879,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11945,9 +11948,6 @@
       <c r="B1418" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1418" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1419" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1419" s="3" t="s">
@@ -11964,7 +11964,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12052,7 +12052,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12140,7 +12140,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12209,6 +12209,9 @@
       <c r="B1451" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1451" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1452" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1452" s="3" t="s">
@@ -12225,7 +12228,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12310,7 +12313,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12395,7 +12398,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12480,7 +12483,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12565,7 +12568,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12650,7 +12653,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12735,7 +12738,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12820,7 +12823,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12905,7 +12908,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -12990,7 +12993,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13075,7 +13078,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13160,7 +13163,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13229,9 +13232,6 @@
       <c r="B1583" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1583" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1584" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1584" s="3" t="s">
@@ -13248,7 +13248,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13317,6 +13317,9 @@
       <c r="B1594" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1594" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1595" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1595" s="3" t="s">
@@ -13333,7 +13336,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13418,7 +13421,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13503,7 +13506,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13572,9 +13575,6 @@
       <c r="B1627" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1627" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1628" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1628" s="3" t="s">
@@ -13591,7 +13591,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13679,7 +13679,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13748,6 +13748,9 @@
       <c r="B1649" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1649" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1650" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1650" s="3" t="s">
@@ -13764,7 +13767,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13849,7 +13852,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13934,7 +13937,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14019,7 +14022,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14088,9 +14091,6 @@
       <c r="B1693" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1693" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1694" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1694" s="3" t="s">
@@ -14107,7 +14107,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14195,7 +14195,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14272,9 +14272,6 @@
       <c r="B1716" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1716" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1717" s="3" t="s">
@@ -14286,7 +14283,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14363,6 +14360,9 @@
       <c r="B1727" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1727" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1728" s="3" t="s">
@@ -14374,7 +14374,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14462,7 +14462,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14550,7 +14550,7 @@
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14638,7 +14638,7 @@
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14726,7 +14726,7 @@
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14795,6 +14795,9 @@
       <c r="B1781" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1781" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1782" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1782" s="3" t="s">
@@ -14811,7 +14814,7 @@
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14872,7 +14875,9 @@
       <c r="B1791" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1791" s="6"/>
+      <c r="C1791" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1792" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1792" s="3" t="s">
@@ -14888,10 +14893,13 @@
       <c r="B1794" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1794" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14952,17 +14960,12 @@
       <c r="B1802" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1802" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1802" s="6"/>
     </row>
     <row r="1803" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1803" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1803" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1804" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1804" s="3" t="s">
@@ -14973,13 +14976,10 @@
       <c r="B1805" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1805" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15067,7 +15067,7 @@
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15155,7 +15155,7 @@
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15224,6 +15224,9 @@
       <c r="B1836" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1836" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1837" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1837" s="3" t="s">
@@ -15240,7 +15243,7 @@
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15325,7 +15328,7 @@
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15399,9 +15402,6 @@
       <c r="B1859" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1859" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1860" s="3" t="s">
@@ -15413,7 +15413,7 @@
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15474,7 +15474,9 @@
       <c r="B1868" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1868" s="6"/>
+      <c r="C1868" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1869" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1869" s="3" t="s">
@@ -15485,15 +15487,21 @@
       <c r="B1870" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1870" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1871" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1871" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1872" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B1872" s="7" t="s">
         <v>3</v>
@@ -15554,9 +15562,7 @@
       <c r="B1879" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1879" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1879" s="6"/>
     </row>
     <row r="1880" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1880" s="3" t="s">
@@ -15572,13 +15578,10 @@
       <c r="B1882" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1882" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1883" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B1883" s="7" t="s">
         <v>3</v>
@@ -15647,9 +15650,6 @@
       <c r="B1891" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1891" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1892" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1892" s="3" t="s">
@@ -15666,7 +15666,7 @@
     </row>
     <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1894" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B1894" s="7" t="s">
         <v>3</v>
@@ -15735,6 +15735,9 @@
       <c r="B1902" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1902" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1903" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1903" s="3" t="s">
@@ -15751,7 +15754,7 @@
     </row>
     <row r="1905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1905" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B1905" s="7" t="s">
         <v>3</v>
@@ -15830,10 +15833,13 @@
       <c r="B1915" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1915" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1916" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B1916" s="7" t="s">
         <v>3</v>
@@ -15912,13 +15918,10 @@
       <c r="B1926" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1926" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1927" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1927" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B1927" s="7" t="s">
         <v>3</v>
@@ -15987,9 +15990,6 @@
       <c r="B1935" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1935" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1936" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1936" s="3" t="s">
@@ -16006,7 +16006,7 @@
     </row>
     <row r="1938" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1938" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B1938" s="7" t="s">
         <v>3</v>
@@ -16027,19 +16027,25 @@
       <c r="B1940" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1940" s="6"/>
+      <c r="C1940" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1941" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1941" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1941" s="6"/>
+      <c r="C1941" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1942" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1942" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1942" s="6"/>
+      <c r="C1942" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1943" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1943" s="3" t="s">
@@ -16061,12 +16067,17 @@
       <c r="B1945" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1945" s="6"/>
+      <c r="C1945" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1946" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1946" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1946" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1947" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1947" s="3" t="s">
@@ -16077,10 +16088,13 @@
       <c r="B1948" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1948" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1949" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1949" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B1949" s="7" t="s">
         <v>3</v>
@@ -16101,25 +16115,19 @@
       <c r="B1951" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1951" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1951" s="6"/>
     </row>
     <row r="1952" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1952" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1952" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1952" s="6"/>
     </row>
     <row r="1953" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1953" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1953" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1953" s="6"/>
     </row>
     <row r="1954" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1954" s="3" t="s">
@@ -16141,17 +16149,12 @@
       <c r="B1956" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1956" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1956" s="6"/>
     </row>
     <row r="1957" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1957" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1957" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1958" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1958" s="3" t="s">
@@ -16162,13 +16165,10 @@
       <c r="B1959" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1959" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1960" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1960" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B1960" s="7" t="s">
         <v>3</v>
@@ -16256,7 +16256,7 @@
     </row>
     <row r="1971" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1971" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B1971" s="7" t="s">
         <v>3</v>
@@ -16325,6 +16325,9 @@
       <c r="B1979" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1979" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1980" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1980" s="3" t="s">
@@ -16341,7 +16344,7 @@
     </row>
     <row r="1982" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1982" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B1982" s="7" t="s">
         <v>3</v>
@@ -16410,9 +16413,6 @@
       <c r="B1990" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1990" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1991" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1991" s="3" t="s">
@@ -16420,19 +16420,19 @@
       </c>
     </row>
     <row r="1992" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1992" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B1992" s="7" t="s">
-        <v>3</v>
+      <c r="B1992" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C1992" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="1993" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B1993" s="3" t="s">
-        <v>4</v>
+      <c r="A1993" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B1993" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C1993" s="5" t="s">
         <v>13</v>
@@ -16440,7 +16440,7 @@
     </row>
     <row r="1994" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1994" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1994" s="5" t="s">
         <v>13</v>
@@ -16448,7 +16448,7 @@
     </row>
     <row r="1995" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1995" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1995" s="5" t="s">
         <v>13</v>
@@ -16456,7 +16456,7 @@
     </row>
     <row r="1996" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1996" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C1996" s="5" t="s">
         <v>13</v>
@@ -16464,7 +16464,7 @@
     </row>
     <row r="1997" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1997" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1997" s="5" t="s">
         <v>13</v>
@@ -16472,7 +16472,7 @@
     </row>
     <row r="1998" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1998" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1998" s="5" t="s">
         <v>13</v>
@@ -16480,7 +16480,7 @@
     </row>
     <row r="1999" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1999" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1999" s="5" t="s">
         <v>13</v>
@@ -16488,7 +16488,7 @@
     </row>
     <row r="2000" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2000" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2000" s="5" t="s">
         <v>13</v>
@@ -16496,23 +16496,23 @@
     </row>
     <row r="2001" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2001" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C2001" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2002" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2002" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B2002" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2002" s="5" t="s">
-        <v>13</v>
+      <c r="B2002" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2003" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2003" s="3" t="s">
-        <v>4</v>
+      <c r="A2003" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B2003" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2003" s="5" t="s">
         <v>13</v>
@@ -16520,7 +16520,7 @@
     </row>
     <row r="2004" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2004" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2004" s="5" t="s">
         <v>13</v>
@@ -16528,7 +16528,7 @@
     </row>
     <row r="2005" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2005" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2005" s="5" t="s">
         <v>13</v>
@@ -16536,7 +16536,7 @@
     </row>
     <row r="2006" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2006" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2006" s="5" t="s">
         <v>13</v>
@@ -16544,7 +16544,7 @@
     </row>
     <row r="2007" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2007" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2007" s="5" t="s">
         <v>13</v>
@@ -16552,7 +16552,7 @@
     </row>
     <row r="2008" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2008" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2008" s="5" t="s">
         <v>13</v>
@@ -16560,7 +16560,7 @@
     </row>
     <row r="2009" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2009" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2009" s="5" t="s">
         <v>13</v>
@@ -16568,16 +16568,104 @@
     </row>
     <row r="2010" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2010" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C2010" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2011" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2011" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C2011" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2012" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2012" s="3">
+      <c r="B2012" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2013" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2013" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B2013" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2013" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2014" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2014" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2014" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2015" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2015" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2015" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2016" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2016" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2016" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2017" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2017" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2017" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2018" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2018" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2018" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2019" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2019" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2019" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2020" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2020" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2020" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2021" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2021" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2022" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2022" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2023" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2023" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81515BD0-6510-4B34-8443-C72377C4232A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{482DE408-D52C-4072-B374-AA04D0525035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29970" yWindow="15" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3858" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3879" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2023"/>
+  <dimension ref="A1:C2034"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6191,7 +6191,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6279,7 +6279,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6367,7 +6367,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6455,7 +6455,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6532,9 +6532,6 @@
       <c r="B759" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C759" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="760" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B760" s="3" t="s">
@@ -6546,7 +6543,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6623,6 +6620,9 @@
       <c r="B770" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C770" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="771" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B771" s="3" t="s">
@@ -6634,7 +6634,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6722,7 +6722,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6810,7 +6810,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6898,7 +6898,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6986,7 +6986,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7063,9 +7063,6 @@
       <c r="B825" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C825" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="826" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B826" s="3" t="s">
@@ -7077,7 +7074,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7168,7 +7165,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7259,7 +7256,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7350,7 +7347,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7427,6 +7424,9 @@
       <c r="B869" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C869" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="870" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B870" s="3" t="s">
@@ -7438,7 +7438,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7515,9 +7515,6 @@
       <c r="B880" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C880" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="881" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B881" s="3" t="s">
@@ -7529,7 +7526,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7620,7 +7617,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7711,7 +7708,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7802,7 +7799,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7893,7 +7890,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -7984,7 +7981,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8075,7 +8072,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8166,7 +8163,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8257,7 +8254,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8348,7 +8345,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8439,7 +8436,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8530,7 +8527,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8621,7 +8618,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8712,7 +8709,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8803,7 +8800,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8894,7 +8891,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -8985,7 +8982,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9076,7 +9073,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9167,7 +9164,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9258,7 +9255,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9349,7 +9346,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9440,7 +9437,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9531,7 +9528,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9622,7 +9619,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9713,7 +9710,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9804,7 +9801,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9895,7 +9892,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -9986,7 +9983,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10077,7 +10074,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10168,7 +10165,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10259,7 +10256,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10350,7 +10347,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10441,7 +10438,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10518,6 +10515,9 @@
       <c r="B1243" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1243" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1244" s="3" t="s">
@@ -10529,7 +10529,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10606,9 +10606,6 @@
       <c r="B1254" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1254" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1255" s="3" t="s">
@@ -10620,7 +10617,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10711,7 +10708,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10802,7 +10799,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10893,7 +10890,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10984,7 +10981,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11075,7 +11072,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11166,7 +11163,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11257,7 +11254,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11348,7 +11345,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11439,7 +11436,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11508,6 +11505,9 @@
       <c r="B1363" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1363" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1364" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1364" s="3" t="s">
@@ -11527,7 +11527,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11596,9 +11596,6 @@
       <c r="B1374" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1374" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1375" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1375" s="3" t="s">
@@ -11618,7 +11615,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11695,6 +11692,9 @@
       <c r="B1386" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1386" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1387" s="3" t="s">
@@ -11706,7 +11706,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11775,6 +11775,9 @@
       <c r="B1396" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1396" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1397" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1397" s="3" t="s">
@@ -11791,7 +11794,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11860,9 +11863,6 @@
       <c r="B1407" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1407" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1408" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1408" s="3" t="s">
@@ -11879,7 +11879,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11948,6 +11948,9 @@
       <c r="B1418" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1418" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1419" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1419" s="3" t="s">
@@ -11964,7 +11967,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12033,9 +12036,6 @@
       <c r="B1429" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1429" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1430" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1430" s="3" t="s">
@@ -12052,7 +12052,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12140,7 +12140,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12228,7 +12228,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12297,6 +12297,9 @@
       <c r="B1462" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1462" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1463" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1463" s="3" t="s">
@@ -12313,7 +12316,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12398,7 +12401,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12483,7 +12486,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12568,7 +12571,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12653,7 +12656,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12738,7 +12741,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12823,7 +12826,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12908,7 +12911,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -12993,7 +12996,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13078,7 +13081,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13163,7 +13166,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13248,7 +13251,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13317,9 +13320,6 @@
       <c r="B1594" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1594" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1595" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1595" s="3" t="s">
@@ -13336,7 +13336,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13405,6 +13405,9 @@
       <c r="B1605" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1605" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1606" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1606" s="3" t="s">
@@ -13421,7 +13424,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13506,7 +13509,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13591,7 +13594,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13660,9 +13663,6 @@
       <c r="B1638" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1638" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1639" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1639" s="3" t="s">
@@ -13679,7 +13679,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13767,7 +13767,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13836,6 +13836,9 @@
       <c r="B1660" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1660" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1661" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1661" s="3" t="s">
@@ -13852,7 +13855,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13937,7 +13940,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14022,7 +14025,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14107,7 +14110,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14176,9 +14179,6 @@
       <c r="B1704" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1704" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1705" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1705" s="3" t="s">
@@ -14195,7 +14195,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14283,7 +14283,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14360,9 +14360,6 @@
       <c r="B1727" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1727" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1728" s="3" t="s">
@@ -14374,7 +14371,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14451,6 +14448,9 @@
       <c r="B1738" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1738" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1739" s="3" t="s">
@@ -14462,7 +14462,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14550,7 +14550,7 @@
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14638,7 +14638,7 @@
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14726,7 +14726,7 @@
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14814,7 +14814,7 @@
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14883,6 +14883,9 @@
       <c r="B1792" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1792" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1793" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1793" s="3" t="s">
@@ -14899,7 +14902,7 @@
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14960,7 +14963,9 @@
       <c r="B1802" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1802" s="6"/>
+      <c r="C1802" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1803" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1803" s="3" t="s">
@@ -14976,10 +14981,13 @@
       <c r="B1805" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1805" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15040,17 +15048,12 @@
       <c r="B1813" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1813" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1813" s="6"/>
     </row>
     <row r="1814" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1814" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1814" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1815" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1815" s="3" t="s">
@@ -15061,13 +15064,10 @@
       <c r="B1816" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1816" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15155,7 +15155,7 @@
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15243,7 +15243,7 @@
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15312,6 +15312,9 @@
       <c r="B1847" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1847" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1848" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1848" s="3" t="s">
@@ -15328,7 +15331,7 @@
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15413,7 +15416,7 @@
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15487,9 +15490,6 @@
       <c r="B1870" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1870" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1871" s="3" t="s">
@@ -15501,7 +15501,7 @@
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1872" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1872" s="7" t="s">
         <v>3</v>
@@ -15562,7 +15562,9 @@
       <c r="B1879" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1879" s="6"/>
+      <c r="C1879" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1880" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1880" s="3" t="s">
@@ -15573,15 +15575,21 @@
       <c r="B1881" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1881" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1882" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1882" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1883" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B1883" s="7" t="s">
         <v>3</v>
@@ -15642,9 +15650,7 @@
       <c r="B1890" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1890" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1890" s="6"/>
     </row>
     <row r="1891" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1891" s="3" t="s">
@@ -15660,13 +15666,10 @@
       <c r="B1893" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1893" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1894" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B1894" s="7" t="s">
         <v>3</v>
@@ -15735,9 +15738,6 @@
       <c r="B1902" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1902" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1903" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1903" s="3" t="s">
@@ -15754,7 +15754,7 @@
     </row>
     <row r="1905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1905" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B1905" s="7" t="s">
         <v>3</v>
@@ -15823,6 +15823,9 @@
       <c r="B1913" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1913" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1914" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1914" s="3" t="s">
@@ -15839,7 +15842,7 @@
     </row>
     <row r="1916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1916" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B1916" s="7" t="s">
         <v>3</v>
@@ -15918,10 +15921,13 @@
       <c r="B1926" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1926" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1927" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1927" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B1927" s="7" t="s">
         <v>3</v>
@@ -16000,13 +16006,10 @@
       <c r="B1937" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1937" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1938" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1938" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B1938" s="7" t="s">
         <v>3</v>
@@ -16075,9 +16078,6 @@
       <c r="B1946" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1946" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1947" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1947" s="3" t="s">
@@ -16094,7 +16094,7 @@
     </row>
     <row r="1949" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1949" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B1949" s="7" t="s">
         <v>3</v>
@@ -16115,19 +16115,25 @@
       <c r="B1951" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1951" s="6"/>
+      <c r="C1951" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1952" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1952" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1952" s="6"/>
+      <c r="C1952" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1953" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1953" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1953" s="6"/>
+      <c r="C1953" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1954" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1954" s="3" t="s">
@@ -16149,12 +16155,17 @@
       <c r="B1956" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1956" s="6"/>
+      <c r="C1956" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1957" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1957" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1957" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1958" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1958" s="3" t="s">
@@ -16165,10 +16176,13 @@
       <c r="B1959" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1959" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1960" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1960" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B1960" s="7" t="s">
         <v>3</v>
@@ -16189,25 +16203,19 @@
       <c r="B1962" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1962" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1962" s="6"/>
     </row>
     <row r="1963" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1963" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1963" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1963" s="6"/>
     </row>
     <row r="1964" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1964" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1964" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1964" s="6"/>
     </row>
     <row r="1965" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1965" s="3" t="s">
@@ -16229,17 +16237,12 @@
       <c r="B1967" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1967" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1967" s="6"/>
     </row>
     <row r="1968" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1968" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1968" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1969" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1969" s="3" t="s">
@@ -16250,13 +16253,10 @@
       <c r="B1970" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1970" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1971" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1971" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B1971" s="7" t="s">
         <v>3</v>
@@ -16344,7 +16344,7 @@
     </row>
     <row r="1982" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1982" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B1982" s="7" t="s">
         <v>3</v>
@@ -16413,6 +16413,9 @@
       <c r="B1990" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1990" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1991" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1991" s="3" t="s">
@@ -16429,7 +16432,7 @@
     </row>
     <row r="1993" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1993" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B1993" s="7" t="s">
         <v>3</v>
@@ -16498,9 +16501,6 @@
       <c r="B2001" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2001" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2002" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2002" s="3" t="s">
@@ -16508,19 +16508,19 @@
       </c>
     </row>
     <row r="2003" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2003" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B2003" s="7" t="s">
-        <v>3</v>
+      <c r="B2003" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C2003" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2004" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2004" s="3" t="s">
-        <v>4</v>
+      <c r="A2004" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B2004" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2004" s="5" t="s">
         <v>13</v>
@@ -16528,7 +16528,7 @@
     </row>
     <row r="2005" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2005" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2005" s="5" t="s">
         <v>13</v>
@@ -16536,7 +16536,7 @@
     </row>
     <row r="2006" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2006" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2006" s="5" t="s">
         <v>13</v>
@@ -16544,7 +16544,7 @@
     </row>
     <row r="2007" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2007" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2007" s="5" t="s">
         <v>13</v>
@@ -16552,7 +16552,7 @@
     </row>
     <row r="2008" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2008" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2008" s="5" t="s">
         <v>13</v>
@@ -16560,7 +16560,7 @@
     </row>
     <row r="2009" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2009" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2009" s="5" t="s">
         <v>13</v>
@@ -16568,7 +16568,7 @@
     </row>
     <row r="2010" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2010" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2010" s="5" t="s">
         <v>13</v>
@@ -16576,7 +16576,7 @@
     </row>
     <row r="2011" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2011" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2011" s="5" t="s">
         <v>13</v>
@@ -16584,23 +16584,23 @@
     </row>
     <row r="2012" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2012" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C2012" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2013" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2013" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B2013" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2013" s="5" t="s">
-        <v>13</v>
+      <c r="B2013" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2014" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2014" s="3" t="s">
-        <v>4</v>
+      <c r="A2014" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B2014" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2014" s="5" t="s">
         <v>13</v>
@@ -16608,7 +16608,7 @@
     </row>
     <row r="2015" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2015" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2015" s="5" t="s">
         <v>13</v>
@@ -16616,56 +16616,144 @@
     </row>
     <row r="2016" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2016" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2016" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2017" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2017" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2017" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2017" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2018" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2018" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2018" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2018" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2019" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2019" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2019" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2019" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2020" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2020" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2020" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2020" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2021" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2021" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2021" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2022" spans="2:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C2021" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2022" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2022" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2023" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2023" s="3">
+        <v>11</v>
+      </c>
+      <c r="C2022" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2023" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2023" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2024" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2024" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B2024" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2024" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2025" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2025" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2025" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2026" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2026" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2026" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2027" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2027" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2027" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2028" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2028" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2028" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2029" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2029" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2029" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2030" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2030" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2030" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2031" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2031" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2031" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2032" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2032" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2033" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B2033" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2034" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B2034" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{482DE408-D52C-4072-B374-AA04D0525035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2374D4E2-DAC9-4F05-84C9-EE0493686B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29970" yWindow="15" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3879" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3900" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2034"/>
+  <dimension ref="A1:C2045"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6191,7 +6191,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6279,7 +6279,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6367,7 +6367,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6455,7 +6455,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6543,7 +6543,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6620,9 +6620,6 @@
       <c r="B770" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C770" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="771" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B771" s="3" t="s">
@@ -6634,7 +6631,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6711,6 +6708,9 @@
       <c r="B781" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C781" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="782" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B782" s="3" t="s">
@@ -6722,7 +6722,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6810,7 +6810,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6898,7 +6898,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6986,7 +6986,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7074,7 +7074,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7151,9 +7151,6 @@
       <c r="B836" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C836" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="837" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B837" s="3" t="s">
@@ -7165,7 +7162,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7256,7 +7253,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7347,7 +7344,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7438,7 +7435,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7515,6 +7512,9 @@
       <c r="B880" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C880" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="881" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B881" s="3" t="s">
@@ -7526,7 +7526,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7603,9 +7603,6 @@
       <c r="B891" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C891" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="892" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B892" s="3" t="s">
@@ -7617,7 +7614,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7708,7 +7705,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7799,7 +7796,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7890,7 +7887,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -7981,7 +7978,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8072,7 +8069,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8163,7 +8160,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8254,7 +8251,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8345,7 +8342,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8436,7 +8433,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8527,7 +8524,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8618,7 +8615,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8709,7 +8706,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8800,7 +8797,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8891,7 +8888,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -8982,7 +8979,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9073,7 +9070,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9164,7 +9161,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9255,7 +9252,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9346,7 +9343,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9437,7 +9434,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9528,7 +9525,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9619,7 +9616,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9710,7 +9707,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9801,7 +9798,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9892,7 +9889,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -9983,7 +9980,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10074,7 +10071,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10165,7 +10162,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10256,7 +10253,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10347,7 +10344,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10438,7 +10435,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10529,7 +10526,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10606,6 +10603,9 @@
       <c r="B1254" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1254" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1255" s="3" t="s">
@@ -10617,7 +10617,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10694,9 +10694,6 @@
       <c r="B1265" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1265" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1266" s="3" t="s">
@@ -10708,7 +10705,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10799,7 +10796,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10890,7 +10887,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10981,7 +10978,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11072,7 +11069,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11163,7 +11160,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11254,7 +11251,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11345,7 +11342,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11436,7 +11433,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11527,7 +11524,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11596,6 +11593,9 @@
       <c r="B1374" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1374" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1375" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1375" s="3" t="s">
@@ -11615,7 +11615,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11684,9 +11684,6 @@
       <c r="B1385" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1385" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1386" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1386" s="3" t="s">
@@ -11706,7 +11703,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11783,6 +11780,9 @@
       <c r="B1397" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1397" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1398" s="3" t="s">
@@ -11794,7 +11794,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11863,6 +11863,9 @@
       <c r="B1407" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1407" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1408" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1408" s="3" t="s">
@@ -11879,7 +11882,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11948,9 +11951,6 @@
       <c r="B1418" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1418" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1419" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1419" s="3" t="s">
@@ -11967,7 +11967,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12036,6 +12036,9 @@
       <c r="B1429" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1429" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1430" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1430" s="3" t="s">
@@ -12052,7 +12055,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12121,9 +12124,6 @@
       <c r="B1440" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1440" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1441" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1441" s="3" t="s">
@@ -12140,7 +12140,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12228,7 +12228,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12316,7 +12316,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12385,6 +12385,9 @@
       <c r="B1473" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1473" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1474" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1474" s="3" t="s">
@@ -12401,7 +12404,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12486,7 +12489,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12571,7 +12574,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12656,7 +12659,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12741,7 +12744,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12826,7 +12829,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12911,7 +12914,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -12996,7 +12999,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13081,7 +13084,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13166,7 +13169,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13251,7 +13254,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13336,7 +13339,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13405,9 +13408,6 @@
       <c r="B1605" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1605" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1606" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1606" s="3" t="s">
@@ -13424,7 +13424,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13493,6 +13493,9 @@
       <c r="B1616" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1616" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1617" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1617" s="3" t="s">
@@ -13509,7 +13512,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13594,7 +13597,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13679,7 +13682,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13748,9 +13751,6 @@
       <c r="B1649" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1649" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1650" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1650" s="3" t="s">
@@ -13767,7 +13767,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13855,7 +13855,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13924,6 +13924,9 @@
       <c r="B1671" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1671" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1672" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1672" s="3" t="s">
@@ -13940,7 +13943,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14025,7 +14028,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14110,7 +14113,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14195,7 +14198,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14264,9 +14267,6 @@
       <c r="B1715" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1715" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1716" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1716" s="3" t="s">
@@ -14283,7 +14283,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14371,7 +14371,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14448,9 +14448,6 @@
       <c r="B1738" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1738" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1739" s="3" t="s">
@@ -14462,7 +14459,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14539,6 +14536,9 @@
       <c r="B1749" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1749" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1750" s="3" t="s">
@@ -14550,7 +14550,7 @@
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14638,7 +14638,7 @@
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14726,7 +14726,7 @@
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14814,7 +14814,7 @@
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14902,7 +14902,7 @@
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14971,6 +14971,9 @@
       <c r="B1803" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1803" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1804" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1804" s="3" t="s">
@@ -14987,7 +14990,7 @@
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15048,7 +15051,9 @@
       <c r="B1813" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1813" s="6"/>
+      <c r="C1813" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1814" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1814" s="3" t="s">
@@ -15064,10 +15069,13 @@
       <c r="B1816" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1816" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15128,17 +15136,12 @@
       <c r="B1824" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1824" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1824" s="6"/>
     </row>
     <row r="1825" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1825" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1825" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1826" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1826" s="3" t="s">
@@ -15149,13 +15152,10 @@
       <c r="B1827" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1827" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15243,7 +15243,7 @@
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15331,7 +15331,7 @@
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15400,6 +15400,9 @@
       <c r="B1858" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1858" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1859" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1859" s="3" t="s">
@@ -15416,7 +15419,7 @@
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15501,7 +15504,7 @@
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1872" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1872" s="7" t="s">
         <v>3</v>
@@ -15575,9 +15578,6 @@
       <c r="B1881" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1881" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1882" s="3" t="s">
@@ -15589,7 +15589,7 @@
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1883" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1883" s="7" t="s">
         <v>3</v>
@@ -15650,7 +15650,9 @@
       <c r="B1890" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1890" s="6"/>
+      <c r="C1890" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1891" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1891" s="3" t="s">
@@ -15661,15 +15663,21 @@
       <c r="B1892" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1892" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1893" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1893" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1894" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B1894" s="7" t="s">
         <v>3</v>
@@ -15730,9 +15738,7 @@
       <c r="B1901" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1901" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1901" s="6"/>
     </row>
     <row r="1902" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1902" s="3" t="s">
@@ -15748,13 +15754,10 @@
       <c r="B1904" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1904" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1905" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B1905" s="7" t="s">
         <v>3</v>
@@ -15823,9 +15826,6 @@
       <c r="B1913" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1913" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1914" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1914" s="3" t="s">
@@ -15842,7 +15842,7 @@
     </row>
     <row r="1916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1916" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B1916" s="7" t="s">
         <v>3</v>
@@ -15911,6 +15911,9 @@
       <c r="B1924" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1924" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1925" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1925" s="3" t="s">
@@ -15927,7 +15930,7 @@
     </row>
     <row r="1927" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1927" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B1927" s="7" t="s">
         <v>3</v>
@@ -16006,10 +16009,13 @@
       <c r="B1937" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1937" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1938" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1938" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B1938" s="7" t="s">
         <v>3</v>
@@ -16088,13 +16094,10 @@
       <c r="B1948" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1948" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1949" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1949" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B1949" s="7" t="s">
         <v>3</v>
@@ -16163,9 +16166,6 @@
       <c r="B1957" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1957" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1958" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1958" s="3" t="s">
@@ -16182,7 +16182,7 @@
     </row>
     <row r="1960" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1960" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B1960" s="7" t="s">
         <v>3</v>
@@ -16203,19 +16203,25 @@
       <c r="B1962" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1962" s="6"/>
+      <c r="C1962" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1963" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1963" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1963" s="6"/>
+      <c r="C1963" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1964" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1964" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1964" s="6"/>
+      <c r="C1964" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1965" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1965" s="3" t="s">
@@ -16237,12 +16243,17 @@
       <c r="B1967" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1967" s="6"/>
+      <c r="C1967" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1968" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1968" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1968" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1969" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1969" s="3" t="s">
@@ -16253,10 +16264,13 @@
       <c r="B1970" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1970" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1971" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1971" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B1971" s="7" t="s">
         <v>3</v>
@@ -16277,25 +16291,19 @@
       <c r="B1973" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1973" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1973" s="6"/>
     </row>
     <row r="1974" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1974" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1974" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1974" s="6"/>
     </row>
     <row r="1975" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1975" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1975" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1975" s="6"/>
     </row>
     <row r="1976" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1976" s="3" t="s">
@@ -16317,17 +16325,12 @@
       <c r="B1978" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1978" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1978" s="6"/>
     </row>
     <row r="1979" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1979" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1979" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1980" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1980" s="3" t="s">
@@ -16338,13 +16341,10 @@
       <c r="B1981" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1981" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1982" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1982" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B1982" s="7" t="s">
         <v>3</v>
@@ -16432,7 +16432,7 @@
     </row>
     <row r="1993" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1993" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B1993" s="7" t="s">
         <v>3</v>
@@ -16501,6 +16501,9 @@
       <c r="B2001" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2001" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2002" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2002" s="3" t="s">
@@ -16517,7 +16520,7 @@
     </row>
     <row r="2004" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2004" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B2004" s="7" t="s">
         <v>3</v>
@@ -16586,9 +16589,6 @@
       <c r="B2012" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2012" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2013" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2013" s="3" t="s">
@@ -16596,19 +16596,19 @@
       </c>
     </row>
     <row r="2014" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2014" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B2014" s="7" t="s">
-        <v>3</v>
+      <c r="B2014" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C2014" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2015" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2015" s="3" t="s">
-        <v>4</v>
+      <c r="A2015" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B2015" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2015" s="5" t="s">
         <v>13</v>
@@ -16616,7 +16616,7 @@
     </row>
     <row r="2016" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2016" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2016" s="5" t="s">
         <v>13</v>
@@ -16624,7 +16624,7 @@
     </row>
     <row r="2017" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2017" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2017" s="5" t="s">
         <v>13</v>
@@ -16632,7 +16632,7 @@
     </row>
     <row r="2018" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2018" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2018" s="5" t="s">
         <v>13</v>
@@ -16640,7 +16640,7 @@
     </row>
     <row r="2019" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2019" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2019" s="5" t="s">
         <v>13</v>
@@ -16648,7 +16648,7 @@
     </row>
     <row r="2020" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2020" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2020" s="5" t="s">
         <v>13</v>
@@ -16656,7 +16656,7 @@
     </row>
     <row r="2021" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2021" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2021" s="5" t="s">
         <v>13</v>
@@ -16664,7 +16664,7 @@
     </row>
     <row r="2022" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2022" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2022" s="5" t="s">
         <v>13</v>
@@ -16672,23 +16672,23 @@
     </row>
     <row r="2023" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2023" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C2023" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2024" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2024" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B2024" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2024" s="5" t="s">
-        <v>13</v>
+      <c r="B2024" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2025" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2025" s="3" t="s">
-        <v>4</v>
+      <c r="A2025" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B2025" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2025" s="5" t="s">
         <v>13</v>
@@ -16696,7 +16696,7 @@
     </row>
     <row r="2026" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2026" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2026" s="5" t="s">
         <v>13</v>
@@ -16704,7 +16704,7 @@
     </row>
     <row r="2027" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2027" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2027" s="5" t="s">
         <v>13</v>
@@ -16712,7 +16712,7 @@
     </row>
     <row r="2028" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2028" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2028" s="5" t="s">
         <v>13</v>
@@ -16720,7 +16720,7 @@
     </row>
     <row r="2029" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2029" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2029" s="5" t="s">
         <v>13</v>
@@ -16728,7 +16728,7 @@
     </row>
     <row r="2030" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2030" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2030" s="5" t="s">
         <v>13</v>
@@ -16736,7 +16736,7 @@
     </row>
     <row r="2031" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2031" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2031" s="5" t="s">
         <v>13</v>
@@ -16744,16 +16744,104 @@
     </row>
     <row r="2032" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2032" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2033" spans="2:2" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C2032" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2033" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2033" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2034" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B2034" s="3">
+        <v>11</v>
+      </c>
+      <c r="C2033" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2034" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2034" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2035" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2035" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B2035" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2035" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2036" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2036" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2036" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2037" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2037" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2037" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2038" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2038" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2038" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2039" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2039" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2039" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2040" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2040" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2040" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2041" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2041" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2041" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2042" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2042" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2042" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2043" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2043" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2044" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2044" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2045" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2045" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2374D4E2-DAC9-4F05-84C9-EE0493686B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{477B6C15-DEFD-4096-A60D-175F186A8ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29970" yWindow="15" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3900" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3921" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2045"/>
+  <dimension ref="A1:C2056"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6191,7 +6191,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6279,7 +6279,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6367,7 +6367,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6455,7 +6455,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6543,7 +6543,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6631,7 +6631,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6708,9 +6708,6 @@
       <c r="B781" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C781" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="782" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B782" s="3" t="s">
@@ -6722,7 +6719,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6799,6 +6796,9 @@
       <c r="B792" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C792" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="793" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B793" s="3" t="s">
@@ -6810,7 +6810,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6898,7 +6898,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6986,7 +6986,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7074,7 +7074,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7162,7 +7162,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7239,9 +7239,6 @@
       <c r="B847" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C847" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="848" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B848" s="3" t="s">
@@ -7253,7 +7250,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7344,7 +7341,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7435,7 +7432,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7526,7 +7523,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7603,6 +7600,9 @@
       <c r="B891" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C891" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="892" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B892" s="3" t="s">
@@ -7614,7 +7614,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7691,9 +7691,6 @@
       <c r="B902" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C902" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="903" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B903" s="3" t="s">
@@ -7705,7 +7702,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7796,7 +7793,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7887,7 +7884,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -7978,7 +7975,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8069,7 +8066,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8160,7 +8157,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8251,7 +8248,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8342,7 +8339,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8433,7 +8430,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8524,7 +8521,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8615,7 +8612,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8706,7 +8703,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8797,7 +8794,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8888,7 +8885,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -8979,7 +8976,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9070,7 +9067,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9161,7 +9158,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9252,7 +9249,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9343,7 +9340,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9434,7 +9431,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9525,7 +9522,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9616,7 +9613,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9707,7 +9704,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9798,7 +9795,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9889,7 +9886,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -9980,7 +9977,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10071,7 +10068,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10162,7 +10159,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10253,7 +10250,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10344,7 +10341,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10435,7 +10432,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10526,7 +10523,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10617,7 +10614,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10694,6 +10691,9 @@
       <c r="B1265" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1265" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1266" s="3" t="s">
@@ -10705,7 +10705,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10782,9 +10782,6 @@
       <c r="B1276" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1276" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1277" s="3" t="s">
@@ -10796,7 +10793,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10887,7 +10884,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10978,7 +10975,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11069,7 +11066,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11160,7 +11157,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11251,7 +11248,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11342,7 +11339,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11433,7 +11430,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11524,7 +11521,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11615,7 +11612,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11684,6 +11681,9 @@
       <c r="B1385" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1385" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1386" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1386" s="3" t="s">
@@ -11703,7 +11703,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11772,9 +11772,6 @@
       <c r="B1396" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1396" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1397" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1397" s="3" t="s">
@@ -11794,7 +11791,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11871,6 +11868,9 @@
       <c r="B1408" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1408" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1409" s="3" t="s">
@@ -11882,7 +11882,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11951,6 +11951,9 @@
       <c r="B1418" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1418" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1419" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1419" s="3" t="s">
@@ -11967,7 +11970,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12036,9 +12039,6 @@
       <c r="B1429" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1429" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1430" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1430" s="3" t="s">
@@ -12055,7 +12055,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12124,6 +12124,9 @@
       <c r="B1440" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1440" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1441" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1441" s="3" t="s">
@@ -12140,7 +12143,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12209,9 +12212,6 @@
       <c r="B1451" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1451" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1452" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1452" s="3" t="s">
@@ -12228,7 +12228,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12316,7 +12316,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12404,7 +12404,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12473,6 +12473,9 @@
       <c r="B1484" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1484" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1485" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1485" s="3" t="s">
@@ -12489,7 +12492,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12574,7 +12577,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12659,7 +12662,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12744,7 +12747,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12829,7 +12832,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12914,7 +12917,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -12999,7 +13002,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13084,7 +13087,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13169,7 +13172,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13254,7 +13257,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13339,7 +13342,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13424,7 +13427,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13493,9 +13496,6 @@
       <c r="B1616" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1616" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1617" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1617" s="3" t="s">
@@ -13512,7 +13512,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13581,6 +13581,9 @@
       <c r="B1627" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1627" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1628" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1628" s="3" t="s">
@@ -13597,7 +13600,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13682,7 +13685,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13767,7 +13770,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13836,9 +13839,6 @@
       <c r="B1660" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1660" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1661" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1661" s="3" t="s">
@@ -13855,7 +13855,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13943,7 +13943,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14012,6 +14012,9 @@
       <c r="B1682" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1682" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1683" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1683" s="3" t="s">
@@ -14028,7 +14031,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14113,7 +14116,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14198,7 +14201,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14283,7 +14286,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14352,9 +14355,6 @@
       <c r="B1726" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1726" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1727" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1727" s="3" t="s">
@@ -14371,7 +14371,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14459,7 +14459,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14536,9 +14536,6 @@
       <c r="B1749" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1749" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1750" s="3" t="s">
@@ -14550,7 +14547,7 @@
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14627,6 +14624,9 @@
       <c r="B1760" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1760" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1761" s="3" t="s">
@@ -14638,7 +14638,7 @@
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14726,7 +14726,7 @@
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14814,7 +14814,7 @@
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14902,7 +14902,7 @@
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14990,7 +14990,7 @@
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15059,6 +15059,9 @@
       <c r="B1814" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1814" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1815" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1815" s="3" t="s">
@@ -15075,7 +15078,7 @@
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15136,7 +15139,9 @@
       <c r="B1824" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1824" s="6"/>
+      <c r="C1824" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1825" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1825" s="3" t="s">
@@ -15152,10 +15157,13 @@
       <c r="B1827" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1827" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15216,17 +15224,12 @@
       <c r="B1835" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1835" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1835" s="6"/>
     </row>
     <row r="1836" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1836" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1836" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1837" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1837" s="3" t="s">
@@ -15237,13 +15240,10 @@
       <c r="B1838" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1838" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15331,7 +15331,7 @@
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15419,7 +15419,7 @@
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15488,6 +15488,9 @@
       <c r="B1869" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1869" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1870" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1870" s="3" t="s">
@@ -15504,7 +15507,7 @@
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1872" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1872" s="7" t="s">
         <v>3</v>
@@ -15589,7 +15592,7 @@
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1883" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1883" s="7" t="s">
         <v>3</v>
@@ -15663,9 +15666,6 @@
       <c r="B1892" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1892" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1893" s="3" t="s">
@@ -15677,7 +15677,7 @@
     </row>
     <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1894" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1894" s="7" t="s">
         <v>3</v>
@@ -15738,7 +15738,9 @@
       <c r="B1901" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1901" s="6"/>
+      <c r="C1901" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1902" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1902" s="3" t="s">
@@ -15749,15 +15751,21 @@
       <c r="B1903" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1903" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1904" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1904" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1905" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B1905" s="7" t="s">
         <v>3</v>
@@ -15818,9 +15826,7 @@
       <c r="B1912" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1912" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1912" s="6"/>
     </row>
     <row r="1913" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1913" s="3" t="s">
@@ -15836,13 +15842,10 @@
       <c r="B1915" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1915" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1916" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B1916" s="7" t="s">
         <v>3</v>
@@ -15911,9 +15914,6 @@
       <c r="B1924" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1924" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1925" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1925" s="3" t="s">
@@ -15930,7 +15930,7 @@
     </row>
     <row r="1927" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1927" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B1927" s="7" t="s">
         <v>3</v>
@@ -15999,6 +15999,9 @@
       <c r="B1935" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1935" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1936" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1936" s="3" t="s">
@@ -16015,7 +16018,7 @@
     </row>
     <row r="1938" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1938" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B1938" s="7" t="s">
         <v>3</v>
@@ -16094,10 +16097,13 @@
       <c r="B1948" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1948" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1949" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1949" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B1949" s="7" t="s">
         <v>3</v>
@@ -16176,13 +16182,10 @@
       <c r="B1959" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1959" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1960" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1960" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B1960" s="7" t="s">
         <v>3</v>
@@ -16251,9 +16254,6 @@
       <c r="B1968" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1968" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1969" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1969" s="3" t="s">
@@ -16270,7 +16270,7 @@
     </row>
     <row r="1971" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1971" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B1971" s="7" t="s">
         <v>3</v>
@@ -16291,19 +16291,25 @@
       <c r="B1973" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1973" s="6"/>
+      <c r="C1973" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1974" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1974" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1974" s="6"/>
+      <c r="C1974" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1975" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1975" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1975" s="6"/>
+      <c r="C1975" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1976" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1976" s="3" t="s">
@@ -16325,12 +16331,17 @@
       <c r="B1978" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1978" s="6"/>
+      <c r="C1978" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1979" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1979" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1979" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1980" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1980" s="3" t="s">
@@ -16341,10 +16352,13 @@
       <c r="B1981" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1981" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1982" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1982" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B1982" s="7" t="s">
         <v>3</v>
@@ -16365,25 +16379,19 @@
       <c r="B1984" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1984" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1984" s="6"/>
     </row>
     <row r="1985" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1985" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1985" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1985" s="6"/>
     </row>
     <row r="1986" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1986" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1986" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1986" s="6"/>
     </row>
     <row r="1987" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1987" s="3" t="s">
@@ -16405,17 +16413,12 @@
       <c r="B1989" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1989" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1989" s="6"/>
     </row>
     <row r="1990" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1990" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1990" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1991" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1991" s="3" t="s">
@@ -16426,13 +16429,10 @@
       <c r="B1992" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1992" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1993" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1993" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B1993" s="7" t="s">
         <v>3</v>
@@ -16520,7 +16520,7 @@
     </row>
     <row r="2004" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2004" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B2004" s="7" t="s">
         <v>3</v>
@@ -16589,6 +16589,9 @@
       <c r="B2012" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2012" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2013" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2013" s="3" t="s">
@@ -16605,7 +16608,7 @@
     </row>
     <row r="2015" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2015" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B2015" s="7" t="s">
         <v>3</v>
@@ -16674,9 +16677,6 @@
       <c r="B2023" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2023" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2024" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2024" s="3" t="s">
@@ -16684,19 +16684,19 @@
       </c>
     </row>
     <row r="2025" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2025" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B2025" s="7" t="s">
-        <v>3</v>
+      <c r="B2025" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C2025" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2026" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2026" s="3" t="s">
-        <v>4</v>
+      <c r="A2026" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B2026" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2026" s="5" t="s">
         <v>13</v>
@@ -16704,7 +16704,7 @@
     </row>
     <row r="2027" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2027" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2027" s="5" t="s">
         <v>13</v>
@@ -16712,7 +16712,7 @@
     </row>
     <row r="2028" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2028" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2028" s="5" t="s">
         <v>13</v>
@@ -16720,7 +16720,7 @@
     </row>
     <row r="2029" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2029" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2029" s="5" t="s">
         <v>13</v>
@@ -16728,7 +16728,7 @@
     </row>
     <row r="2030" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2030" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2030" s="5" t="s">
         <v>13</v>
@@ -16736,7 +16736,7 @@
     </row>
     <row r="2031" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2031" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2031" s="5" t="s">
         <v>13</v>
@@ -16744,7 +16744,7 @@
     </row>
     <row r="2032" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2032" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2032" s="5" t="s">
         <v>13</v>
@@ -16752,7 +16752,7 @@
     </row>
     <row r="2033" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2033" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2033" s="5" t="s">
         <v>13</v>
@@ -16760,23 +16760,23 @@
     </row>
     <row r="2034" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2034" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C2034" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2035" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2035" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B2035" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2035" s="5" t="s">
-        <v>13</v>
+      <c r="B2035" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2036" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2036" s="3" t="s">
-        <v>4</v>
+      <c r="A2036" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B2036" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2036" s="5" t="s">
         <v>13</v>
@@ -16784,7 +16784,7 @@
     </row>
     <row r="2037" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2037" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2037" s="5" t="s">
         <v>13</v>
@@ -16792,7 +16792,7 @@
     </row>
     <row r="2038" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2038" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2038" s="5" t="s">
         <v>13</v>
@@ -16800,7 +16800,7 @@
     </row>
     <row r="2039" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2039" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2039" s="5" t="s">
         <v>13</v>
@@ -16808,7 +16808,7 @@
     </row>
     <row r="2040" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2040" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2040" s="5" t="s">
         <v>13</v>
@@ -16816,7 +16816,7 @@
     </row>
     <row r="2041" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2041" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2041" s="5" t="s">
         <v>13</v>
@@ -16824,7 +16824,7 @@
     </row>
     <row r="2042" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2042" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2042" s="5" t="s">
         <v>13</v>
@@ -16832,16 +16832,104 @@
     </row>
     <row r="2043" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2043" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C2043" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2044" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2044" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C2044" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2045" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2045" s="3">
+      <c r="B2045" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2046" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2046" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B2046" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2046" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2047" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2047" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2047" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2048" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2048" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2048" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2049" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2049" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2049" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2050" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2050" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2050" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2051" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2051" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2051" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2052" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2052" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2052" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2053" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2053" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2053" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2054" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2054" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2055" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2055" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2056" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2056" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{477B6C15-DEFD-4096-A60D-175F186A8ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26E392EF-440C-4579-A00A-85EEECD56288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29970" yWindow="15" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3921" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3942" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2056"/>
+  <dimension ref="A1:C2067"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6191,7 +6191,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6279,7 +6279,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6367,7 +6367,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6455,7 +6455,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6543,7 +6543,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6631,7 +6631,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6719,7 +6719,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6796,9 +6796,6 @@
       <c r="B792" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C792" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="793" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B793" s="3" t="s">
@@ -6810,7 +6807,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6887,6 +6884,9 @@
       <c r="B803" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C803" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="804" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B804" s="3" t="s">
@@ -6898,7 +6898,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6986,7 +6986,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7074,7 +7074,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7162,7 +7162,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7250,7 +7250,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7327,9 +7327,6 @@
       <c r="B858" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C858" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="859" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B859" s="3" t="s">
@@ -7341,7 +7338,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7432,7 +7429,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7523,7 +7520,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7614,7 +7611,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7691,6 +7688,9 @@
       <c r="B902" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C902" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="903" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B903" s="3" t="s">
@@ -7702,7 +7702,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7779,9 +7779,6 @@
       <c r="B913" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C913" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="914" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B914" s="3" t="s">
@@ -7793,7 +7790,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7884,7 +7881,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -7975,7 +7972,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8066,7 +8063,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8157,7 +8154,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8248,7 +8245,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8339,7 +8336,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8430,7 +8427,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8521,7 +8518,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8612,7 +8609,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8703,7 +8700,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8794,7 +8791,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8885,7 +8882,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -8976,7 +8973,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9067,7 +9064,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9158,7 +9155,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9249,7 +9246,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9340,7 +9337,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9431,7 +9428,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9522,7 +9519,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9613,7 +9610,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9704,7 +9701,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9795,7 +9792,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9886,7 +9883,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -9977,7 +9974,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10068,7 +10065,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10159,7 +10156,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10250,7 +10247,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10341,7 +10338,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10432,7 +10429,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10523,7 +10520,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10614,7 +10611,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10705,7 +10702,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10782,6 +10779,9 @@
       <c r="B1276" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1276" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1277" s="3" t="s">
@@ -10793,7 +10793,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10870,9 +10870,6 @@
       <c r="B1287" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1287" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1288" s="3" t="s">
@@ -10884,7 +10881,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10975,7 +10972,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11066,7 +11063,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11157,7 +11154,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11248,7 +11245,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11339,7 +11336,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11430,7 +11427,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11521,7 +11518,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11612,7 +11609,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11703,7 +11700,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11772,6 +11769,9 @@
       <c r="B1396" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1396" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1397" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1397" s="3" t="s">
@@ -11791,7 +11791,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11860,9 +11860,6 @@
       <c r="B1407" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1407" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1408" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1408" s="3" t="s">
@@ -11882,7 +11879,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11959,6 +11956,9 @@
       <c r="B1419" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1419" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1420" s="3" t="s">
@@ -11970,7 +11970,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12039,6 +12039,9 @@
       <c r="B1429" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1429" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1430" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1430" s="3" t="s">
@@ -12055,7 +12058,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12124,9 +12127,6 @@
       <c r="B1440" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1440" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1441" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1441" s="3" t="s">
@@ -12143,7 +12143,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12212,6 +12212,9 @@
       <c r="B1451" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1451" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1452" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1452" s="3" t="s">
@@ -12228,7 +12231,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12297,9 +12300,6 @@
       <c r="B1462" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1462" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1463" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1463" s="3" t="s">
@@ -12316,7 +12316,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12404,7 +12404,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12492,7 +12492,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12561,6 +12561,9 @@
       <c r="B1495" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1495" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1496" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1496" s="3" t="s">
@@ -12577,7 +12580,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12662,7 +12665,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12747,7 +12750,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12832,7 +12835,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12917,7 +12920,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -13002,7 +13005,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13087,7 +13090,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13172,7 +13175,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13257,7 +13260,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13342,7 +13345,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13427,7 +13430,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13512,7 +13515,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13581,9 +13584,6 @@
       <c r="B1627" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1627" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1628" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1628" s="3" t="s">
@@ -13600,7 +13600,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13669,6 +13669,9 @@
       <c r="B1638" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1638" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1639" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1639" s="3" t="s">
@@ -13685,7 +13688,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13770,7 +13773,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13855,7 +13858,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13924,9 +13927,6 @@
       <c r="B1671" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1671" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1672" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1672" s="3" t="s">
@@ -13943,7 +13943,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14031,7 +14031,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14100,6 +14100,9 @@
       <c r="B1693" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1693" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1694" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1694" s="3" t="s">
@@ -14116,7 +14119,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14201,7 +14204,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14286,7 +14289,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14371,7 +14374,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14440,9 +14443,6 @@
       <c r="B1737" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1737" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1738" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1738" s="3" t="s">
@@ -14459,7 +14459,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14547,7 +14547,7 @@
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14624,9 +14624,6 @@
       <c r="B1760" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1760" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1761" s="3" t="s">
@@ -14638,7 +14635,7 @@
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14715,6 +14712,9 @@
       <c r="B1771" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1771" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1772" s="3" t="s">
@@ -14726,7 +14726,7 @@
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14814,7 +14814,7 @@
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14902,7 +14902,7 @@
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14990,7 +14990,7 @@
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15078,7 +15078,7 @@
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15147,6 +15147,9 @@
       <c r="B1825" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1825" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1826" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1826" s="3" t="s">
@@ -15163,7 +15166,7 @@
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15224,7 +15227,9 @@
       <c r="B1835" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1835" s="6"/>
+      <c r="C1835" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1836" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1836" s="3" t="s">
@@ -15240,10 +15245,13 @@
       <c r="B1838" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1838" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15304,17 +15312,12 @@
       <c r="B1846" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1846" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1846" s="6"/>
     </row>
     <row r="1847" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1847" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1847" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1848" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1848" s="3" t="s">
@@ -15325,13 +15328,10 @@
       <c r="B1849" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1849" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15419,7 +15419,7 @@
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15507,7 +15507,7 @@
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1872" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1872" s="7" t="s">
         <v>3</v>
@@ -15576,6 +15576,9 @@
       <c r="B1880" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1880" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1881" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1881" s="3" t="s">
@@ -15592,7 +15595,7 @@
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1883" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1883" s="7" t="s">
         <v>3</v>
@@ -15677,7 +15680,7 @@
     </row>
     <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1894" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1894" s="7" t="s">
         <v>3</v>
@@ -15751,9 +15754,6 @@
       <c r="B1903" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1903" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1904" s="3" t="s">
@@ -15765,7 +15765,7 @@
     </row>
     <row r="1905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1905" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1905" s="7" t="s">
         <v>3</v>
@@ -15826,7 +15826,9 @@
       <c r="B1912" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1912" s="6"/>
+      <c r="C1912" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1913" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1913" s="3" t="s">
@@ -15837,15 +15839,21 @@
       <c r="B1914" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1914" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1915" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1915" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1916" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B1916" s="7" t="s">
         <v>3</v>
@@ -15906,9 +15914,7 @@
       <c r="B1923" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1923" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1923" s="6"/>
     </row>
     <row r="1924" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1924" s="3" t="s">
@@ -15924,13 +15930,10 @@
       <c r="B1926" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1926" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1927" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1927" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B1927" s="7" t="s">
         <v>3</v>
@@ -15999,9 +16002,6 @@
       <c r="B1935" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1935" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1936" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1936" s="3" t="s">
@@ -16018,7 +16018,7 @@
     </row>
     <row r="1938" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1938" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B1938" s="7" t="s">
         <v>3</v>
@@ -16087,6 +16087,9 @@
       <c r="B1946" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1946" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1947" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1947" s="3" t="s">
@@ -16103,7 +16106,7 @@
     </row>
     <row r="1949" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1949" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B1949" s="7" t="s">
         <v>3</v>
@@ -16182,10 +16185,13 @@
       <c r="B1959" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1959" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1960" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1960" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B1960" s="7" t="s">
         <v>3</v>
@@ -16264,13 +16270,10 @@
       <c r="B1970" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1970" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1971" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1971" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B1971" s="7" t="s">
         <v>3</v>
@@ -16339,9 +16342,6 @@
       <c r="B1979" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1979" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1980" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1980" s="3" t="s">
@@ -16358,7 +16358,7 @@
     </row>
     <row r="1982" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1982" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B1982" s="7" t="s">
         <v>3</v>
@@ -16379,19 +16379,25 @@
       <c r="B1984" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1984" s="6"/>
+      <c r="C1984" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1985" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1985" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1985" s="6"/>
+      <c r="C1985" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1986" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1986" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1986" s="6"/>
+      <c r="C1986" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1987" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1987" s="3" t="s">
@@ -16413,12 +16419,17 @@
       <c r="B1989" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1989" s="6"/>
+      <c r="C1989" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1990" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1990" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1990" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1991" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1991" s="3" t="s">
@@ -16429,10 +16440,13 @@
       <c r="B1992" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1992" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1993" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1993" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B1993" s="7" t="s">
         <v>3</v>
@@ -16453,25 +16467,19 @@
       <c r="B1995" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1995" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1995" s="6"/>
     </row>
     <row r="1996" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1996" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1996" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1996" s="6"/>
     </row>
     <row r="1997" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1997" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1997" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1997" s="6"/>
     </row>
     <row r="1998" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1998" s="3" t="s">
@@ -16493,17 +16501,12 @@
       <c r="B2000" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2000" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2000" s="6"/>
     </row>
     <row r="2001" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2001" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2001" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2002" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2002" s="3" t="s">
@@ -16514,13 +16517,10 @@
       <c r="B2003" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2003" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2004" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2004" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B2004" s="7" t="s">
         <v>3</v>
@@ -16608,7 +16608,7 @@
     </row>
     <row r="2015" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2015" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B2015" s="7" t="s">
         <v>3</v>
@@ -16677,6 +16677,9 @@
       <c r="B2023" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2023" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2024" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2024" s="3" t="s">
@@ -16693,7 +16696,7 @@
     </row>
     <row r="2026" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2026" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B2026" s="7" t="s">
         <v>3</v>
@@ -16762,9 +16765,6 @@
       <c r="B2034" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2034" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2035" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2035" s="3" t="s">
@@ -16772,19 +16772,19 @@
       </c>
     </row>
     <row r="2036" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2036" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B2036" s="7" t="s">
-        <v>3</v>
+      <c r="B2036" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C2036" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2037" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2037" s="3" t="s">
-        <v>4</v>
+      <c r="A2037" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B2037" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2037" s="5" t="s">
         <v>13</v>
@@ -16792,7 +16792,7 @@
     </row>
     <row r="2038" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2038" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2038" s="5" t="s">
         <v>13</v>
@@ -16800,7 +16800,7 @@
     </row>
     <row r="2039" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2039" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2039" s="5" t="s">
         <v>13</v>
@@ -16808,7 +16808,7 @@
     </row>
     <row r="2040" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2040" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2040" s="5" t="s">
         <v>13</v>
@@ -16816,7 +16816,7 @@
     </row>
     <row r="2041" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2041" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2041" s="5" t="s">
         <v>13</v>
@@ -16824,7 +16824,7 @@
     </row>
     <row r="2042" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2042" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2042" s="5" t="s">
         <v>13</v>
@@ -16832,7 +16832,7 @@
     </row>
     <row r="2043" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2043" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2043" s="5" t="s">
         <v>13</v>
@@ -16840,7 +16840,7 @@
     </row>
     <row r="2044" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2044" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2044" s="5" t="s">
         <v>13</v>
@@ -16848,23 +16848,23 @@
     </row>
     <row r="2045" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2045" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C2045" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2046" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2046" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B2046" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2046" s="5" t="s">
-        <v>13</v>
+      <c r="B2046" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2047" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2047" s="3" t="s">
-        <v>4</v>
+      <c r="A2047" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B2047" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2047" s="5" t="s">
         <v>13</v>
@@ -16872,64 +16872,152 @@
     </row>
     <row r="2048" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2048" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2048" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2049" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2049" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2049" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2049" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2050" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2050" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2050" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2050" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2051" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2051" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2051" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2051" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2052" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2052" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2052" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2052" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2053" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2053" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2053" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2053" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2054" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2054" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2054" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2055" spans="2:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C2054" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2055" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2055" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2056" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2056" s="3">
+        <v>11</v>
+      </c>
+      <c r="C2055" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2056" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2056" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2057" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2057" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B2057" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2057" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2058" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2058" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2058" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2059" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2059" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2059" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2060" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2060" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2060" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2061" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2061" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2061" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2062" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2062" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2062" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2063" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2063" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2063" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2064" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2064" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2064" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2065" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B2065" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2066" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B2066" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2067" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B2067" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26E392EF-440C-4579-A00A-85EEECD56288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE52D114-E77C-46F3-A63B-940A4BBC9290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3942" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3963" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2067"/>
+  <dimension ref="A1:C2078"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6191,7 +6191,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6279,7 +6279,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6367,7 +6367,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6455,7 +6455,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6543,7 +6543,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6631,7 +6631,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6719,7 +6719,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6807,7 +6807,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6884,9 +6884,6 @@
       <c r="B803" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C803" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="804" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B804" s="3" t="s">
@@ -6898,7 +6895,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6975,6 +6972,9 @@
       <c r="B814" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C814" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="815" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B815" s="3" t="s">
@@ -6986,7 +6986,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7074,7 +7074,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7162,7 +7162,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7250,7 +7250,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7338,7 +7338,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7415,9 +7415,6 @@
       <c r="B869" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C869" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="870" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B870" s="3" t="s">
@@ -7429,7 +7426,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7520,7 +7517,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7611,7 +7608,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7702,7 +7699,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7779,6 +7776,9 @@
       <c r="B913" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C913" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="914" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B914" s="3" t="s">
@@ -7790,7 +7790,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7867,9 +7867,6 @@
       <c r="B924" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C924" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="925" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B925" s="3" t="s">
@@ -7881,7 +7878,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -7972,7 +7969,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8063,7 +8060,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8154,7 +8151,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8245,7 +8242,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8336,7 +8333,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8427,7 +8424,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8518,7 +8515,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8609,7 +8606,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8700,7 +8697,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8791,7 +8788,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8882,7 +8879,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -8973,7 +8970,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9064,7 +9061,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9155,7 +9152,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9246,7 +9243,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9337,7 +9334,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9428,7 +9425,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9519,7 +9516,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9610,7 +9607,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9701,7 +9698,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9792,7 +9789,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9883,7 +9880,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -9974,7 +9971,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10065,7 +10062,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10156,7 +10153,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10247,7 +10244,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10338,7 +10335,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10429,7 +10426,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10520,7 +10517,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10611,7 +10608,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10702,7 +10699,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10793,7 +10790,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10870,6 +10867,9 @@
       <c r="B1287" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1287" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1288" s="3" t="s">
@@ -10881,7 +10881,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10958,9 +10958,6 @@
       <c r="B1298" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1298" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1299" s="3" t="s">
@@ -10972,7 +10969,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11063,7 +11060,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11154,7 +11151,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11245,7 +11242,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11336,7 +11333,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11427,7 +11424,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11518,7 +11515,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11609,7 +11606,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11700,7 +11697,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11791,7 +11788,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11860,6 +11857,9 @@
       <c r="B1407" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1407" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1408" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1408" s="3" t="s">
@@ -11879,7 +11879,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11948,9 +11948,6 @@
       <c r="B1418" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1418" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1419" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1419" s="3" t="s">
@@ -11970,7 +11967,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12047,6 +12044,9 @@
       <c r="B1430" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1430" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1431" s="3" t="s">
@@ -12058,7 +12058,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12127,6 +12127,9 @@
       <c r="B1440" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1440" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1441" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1441" s="3" t="s">
@@ -12143,7 +12146,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12212,9 +12215,6 @@
       <c r="B1451" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1451" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1452" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1452" s="3" t="s">
@@ -12231,7 +12231,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12300,6 +12300,9 @@
       <c r="B1462" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1462" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1463" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1463" s="3" t="s">
@@ -12316,7 +12319,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12385,9 +12388,6 @@
       <c r="B1473" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1473" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1474" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1474" s="3" t="s">
@@ -12404,7 +12404,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12492,7 +12492,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12580,7 +12580,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12649,6 +12649,9 @@
       <c r="B1506" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1506" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1507" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1507" s="3" t="s">
@@ -12665,7 +12668,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12750,7 +12753,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12835,7 +12838,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12920,7 +12923,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -13005,7 +13008,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13090,7 +13093,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13175,7 +13178,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13260,7 +13263,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13345,7 +13348,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13430,7 +13433,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13515,7 +13518,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13600,7 +13603,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13669,9 +13672,6 @@
       <c r="B1638" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1638" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1639" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1639" s="3" t="s">
@@ -13688,7 +13688,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13757,6 +13757,9 @@
       <c r="B1649" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1649" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1650" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1650" s="3" t="s">
@@ -13773,7 +13776,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13858,7 +13861,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13943,7 +13946,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14012,9 +14015,6 @@
       <c r="B1682" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1682" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1683" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1683" s="3" t="s">
@@ -14031,7 +14031,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14119,7 +14119,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14188,6 +14188,9 @@
       <c r="B1704" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1704" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1705" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1705" s="3" t="s">
@@ -14204,7 +14207,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14289,7 +14292,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14374,7 +14377,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14459,7 +14462,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14528,9 +14531,6 @@
       <c r="B1748" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1748" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1749" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1749" s="3" t="s">
@@ -14547,7 +14547,7 @@
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14635,7 +14635,7 @@
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14712,9 +14712,6 @@
       <c r="B1771" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1771" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1772" s="3" t="s">
@@ -14726,7 +14723,7 @@
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14803,6 +14800,9 @@
       <c r="B1782" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1782" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1783" s="3" t="s">
@@ -14814,7 +14814,7 @@
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14902,7 +14902,7 @@
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14990,7 +14990,7 @@
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15078,7 +15078,7 @@
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15166,7 +15166,7 @@
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15235,6 +15235,9 @@
       <c r="B1836" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1836" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1837" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1837" s="3" t="s">
@@ -15251,7 +15254,7 @@
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15312,7 +15315,9 @@
       <c r="B1846" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1846" s="6"/>
+      <c r="C1846" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1847" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1847" s="3" t="s">
@@ -15328,10 +15333,13 @@
       <c r="B1849" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1849" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15392,17 +15400,12 @@
       <c r="B1857" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1857" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1857" s="6"/>
     </row>
     <row r="1858" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1858" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1858" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1859" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1859" s="3" t="s">
@@ -15413,13 +15416,10 @@
       <c r="B1860" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1860" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15507,7 +15507,7 @@
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1872" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1872" s="7" t="s">
         <v>3</v>
@@ -15595,7 +15595,7 @@
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1883" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1883" s="7" t="s">
         <v>3</v>
@@ -15664,6 +15664,9 @@
       <c r="B1891" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1891" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1892" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1892" s="3" t="s">
@@ -15680,7 +15683,7 @@
     </row>
     <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1894" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1894" s="7" t="s">
         <v>3</v>
@@ -15765,7 +15768,7 @@
     </row>
     <row r="1905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1905" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1905" s="7" t="s">
         <v>3</v>
@@ -15839,9 +15842,6 @@
       <c r="B1914" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1914" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1915" s="3" t="s">
@@ -15853,7 +15853,7 @@
     </row>
     <row r="1916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1916" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1916" s="7" t="s">
         <v>3</v>
@@ -15914,7 +15914,9 @@
       <c r="B1923" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1923" s="6"/>
+      <c r="C1923" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1924" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1924" s="3" t="s">
@@ -15925,15 +15927,21 @@
       <c r="B1925" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1925" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1926" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1926" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1927" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1927" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B1927" s="7" t="s">
         <v>3</v>
@@ -15994,9 +16002,7 @@
       <c r="B1934" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1934" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1934" s="6"/>
     </row>
     <row r="1935" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1935" s="3" t="s">
@@ -16012,13 +16018,10 @@
       <c r="B1937" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1937" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1938" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1938" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B1938" s="7" t="s">
         <v>3</v>
@@ -16087,9 +16090,6 @@
       <c r="B1946" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1946" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1947" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1947" s="3" t="s">
@@ -16106,7 +16106,7 @@
     </row>
     <row r="1949" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1949" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B1949" s="7" t="s">
         <v>3</v>
@@ -16175,6 +16175,9 @@
       <c r="B1957" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1957" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1958" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1958" s="3" t="s">
@@ -16191,7 +16194,7 @@
     </row>
     <row r="1960" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1960" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B1960" s="7" t="s">
         <v>3</v>
@@ -16270,10 +16273,13 @@
       <c r="B1970" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1970" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1971" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1971" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B1971" s="7" t="s">
         <v>3</v>
@@ -16352,13 +16358,10 @@
       <c r="B1981" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1981" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1982" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1982" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B1982" s="7" t="s">
         <v>3</v>
@@ -16427,9 +16430,6 @@
       <c r="B1990" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1990" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1991" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1991" s="3" t="s">
@@ -16446,7 +16446,7 @@
     </row>
     <row r="1993" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1993" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B1993" s="7" t="s">
         <v>3</v>
@@ -16467,19 +16467,25 @@
       <c r="B1995" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C1995" s="6"/>
+      <c r="C1995" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1996" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1996" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1996" s="6"/>
+      <c r="C1996" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1997" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1997" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C1997" s="6"/>
+      <c r="C1997" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1998" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1998" s="3" t="s">
@@ -16501,12 +16507,17 @@
       <c r="B2000" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2000" s="6"/>
+      <c r="C2000" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2001" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2001" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2001" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2002" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2002" s="3" t="s">
@@ -16517,10 +16528,13 @@
       <c r="B2003" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C2003" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2004" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2004" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B2004" s="7" t="s">
         <v>3</v>
@@ -16541,25 +16555,19 @@
       <c r="B2006" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2006" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2006" s="6"/>
     </row>
     <row r="2007" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2007" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2007" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2007" s="6"/>
     </row>
     <row r="2008" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2008" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2008" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2008" s="6"/>
     </row>
     <row r="2009" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2009" s="3" t="s">
@@ -16581,17 +16589,12 @@
       <c r="B2011" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2011" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2011" s="6"/>
     </row>
     <row r="2012" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2012" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2012" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2013" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2013" s="3" t="s">
@@ -16602,13 +16605,10 @@
       <c r="B2014" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2014" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2015" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2015" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B2015" s="7" t="s">
         <v>3</v>
@@ -16696,7 +16696,7 @@
     </row>
     <row r="2026" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2026" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B2026" s="7" t="s">
         <v>3</v>
@@ -16765,6 +16765,9 @@
       <c r="B2034" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2034" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2035" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2035" s="3" t="s">
@@ -16781,7 +16784,7 @@
     </row>
     <row r="2037" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2037" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B2037" s="7" t="s">
         <v>3</v>
@@ -16850,9 +16853,6 @@
       <c r="B2045" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2045" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2046" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2046" s="3" t="s">
@@ -16860,19 +16860,19 @@
       </c>
     </row>
     <row r="2047" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2047" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B2047" s="7" t="s">
-        <v>3</v>
+      <c r="B2047" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C2047" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2048" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2048" s="3" t="s">
-        <v>4</v>
+      <c r="A2048" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B2048" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2048" s="5" t="s">
         <v>13</v>
@@ -16880,7 +16880,7 @@
     </row>
     <row r="2049" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2049" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2049" s="5" t="s">
         <v>13</v>
@@ -16888,7 +16888,7 @@
     </row>
     <row r="2050" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2050" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2050" s="5" t="s">
         <v>13</v>
@@ -16896,7 +16896,7 @@
     </row>
     <row r="2051" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2051" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2051" s="5" t="s">
         <v>13</v>
@@ -16904,7 +16904,7 @@
     </row>
     <row r="2052" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2052" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2052" s="5" t="s">
         <v>13</v>
@@ -16912,7 +16912,7 @@
     </row>
     <row r="2053" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2053" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2053" s="5" t="s">
         <v>13</v>
@@ -16920,7 +16920,7 @@
     </row>
     <row r="2054" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2054" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2054" s="5" t="s">
         <v>13</v>
@@ -16928,7 +16928,7 @@
     </row>
     <row r="2055" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2055" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2055" s="5" t="s">
         <v>13</v>
@@ -16936,23 +16936,23 @@
     </row>
     <row r="2056" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2056" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C2056" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2057" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2057" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B2057" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2057" s="5" t="s">
-        <v>13</v>
+      <c r="B2057" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2058" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2058" s="3" t="s">
-        <v>4</v>
+      <c r="A2058" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B2058" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2058" s="5" t="s">
         <v>13</v>
@@ -16960,7 +16960,7 @@
     </row>
     <row r="2059" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2059" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2059" s="5" t="s">
         <v>13</v>
@@ -16968,7 +16968,7 @@
     </row>
     <row r="2060" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2060" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2060" s="5" t="s">
         <v>13</v>
@@ -16976,7 +16976,7 @@
     </row>
     <row r="2061" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2061" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2061" s="5" t="s">
         <v>13</v>
@@ -16984,7 +16984,7 @@
     </row>
     <row r="2062" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2062" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2062" s="5" t="s">
         <v>13</v>
@@ -16992,7 +16992,7 @@
     </row>
     <row r="2063" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2063" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2063" s="5" t="s">
         <v>13</v>
@@ -17000,24 +17000,112 @@
     </row>
     <row r="2064" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2064" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2064" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2065" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="2065" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2065" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2066" spans="2:2" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C2065" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2066" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2066" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2067" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B2067" s="3">
+        <v>11</v>
+      </c>
+      <c r="C2066" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2067" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2067" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2068" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2068" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B2068" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2068" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2069" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2069" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2069" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2070" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2070" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2070" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2071" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2071" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2071" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2072" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2072" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2072" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2073" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2073" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2073" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2074" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2074" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2074" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2075" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2075" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2075" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2076" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2076" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2077" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2077" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2078" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2078" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE52D114-E77C-46F3-A63B-940A4BBC9290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C83BBD-4480-46DB-BF45-06C4E800374A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3963" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3984" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2078"/>
+  <dimension ref="A1:C2089"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6191,7 +6191,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6279,7 +6279,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6367,7 +6367,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6455,7 +6455,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6543,7 +6543,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6631,7 +6631,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6719,7 +6719,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6807,7 +6807,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6895,7 +6895,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6972,9 +6972,6 @@
       <c r="B814" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C814" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="815" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B815" s="3" t="s">
@@ -6986,7 +6983,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7063,6 +7060,9 @@
       <c r="B825" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C825" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="826" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B826" s="3" t="s">
@@ -7074,7 +7074,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7162,7 +7162,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7250,7 +7250,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7338,7 +7338,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7426,7 +7426,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7503,9 +7503,6 @@
       <c r="B880" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C880" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="881" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B881" s="3" t="s">
@@ -7517,7 +7514,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7608,7 +7605,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7699,7 +7696,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7790,7 +7787,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7867,6 +7864,9 @@
       <c r="B924" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C924" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="925" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B925" s="3" t="s">
@@ -7878,7 +7878,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -7955,9 +7955,6 @@
       <c r="B935" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C935" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="936" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B936" s="3" t="s">
@@ -7969,7 +7966,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8060,7 +8057,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8151,7 +8148,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8242,7 +8239,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8333,7 +8330,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8424,7 +8421,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8515,7 +8512,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8606,7 +8603,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8697,7 +8694,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8788,7 +8785,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8879,7 +8876,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -8970,7 +8967,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9061,7 +9058,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9152,7 +9149,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9243,7 +9240,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9334,7 +9331,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9425,7 +9422,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9516,7 +9513,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9607,7 +9604,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9698,7 +9695,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9789,7 +9786,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9880,7 +9877,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -9971,7 +9968,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10062,7 +10059,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10153,7 +10150,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10244,7 +10241,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10335,7 +10332,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10426,7 +10423,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10517,7 +10514,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10608,7 +10605,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10699,7 +10696,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10790,7 +10787,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10881,7 +10878,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10958,6 +10955,9 @@
       <c r="B1298" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1298" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1299" s="3" t="s">
@@ -10969,7 +10969,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11046,9 +11046,6 @@
       <c r="B1309" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1309" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1310" s="3" t="s">
@@ -11060,7 +11057,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11151,7 +11148,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11242,7 +11239,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11333,7 +11330,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11424,7 +11421,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11515,7 +11512,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11606,7 +11603,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11697,7 +11694,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11788,7 +11785,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11879,7 +11876,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11948,6 +11945,9 @@
       <c r="B1418" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1418" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1419" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1419" s="3" t="s">
@@ -11967,7 +11967,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12036,9 +12036,6 @@
       <c r="B1429" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1429" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1430" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1430" s="3" t="s">
@@ -12058,7 +12055,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12135,6 +12132,9 @@
       <c r="B1441" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1441" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1442" s="3" t="s">
@@ -12146,7 +12146,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12215,6 +12215,9 @@
       <c r="B1451" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1451" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1452" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1452" s="3" t="s">
@@ -12231,7 +12234,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12300,9 +12303,6 @@
       <c r="B1462" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1462" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1463" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1463" s="3" t="s">
@@ -12319,7 +12319,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12388,6 +12388,9 @@
       <c r="B1473" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1473" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1474" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1474" s="3" t="s">
@@ -12404,7 +12407,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12473,9 +12476,6 @@
       <c r="B1484" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1484" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1485" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1485" s="3" t="s">
@@ -12492,7 +12492,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12580,7 +12580,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12668,7 +12668,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12737,6 +12737,9 @@
       <c r="B1517" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1517" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1518" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1518" s="3" t="s">
@@ -12753,7 +12756,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12838,7 +12841,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12923,7 +12926,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -13008,7 +13011,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13093,7 +13096,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13178,7 +13181,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13263,7 +13266,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13348,7 +13351,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13433,7 +13436,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13518,7 +13521,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13603,7 +13606,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13688,7 +13691,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13757,9 +13760,6 @@
       <c r="B1649" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1649" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1650" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1650" s="3" t="s">
@@ -13776,7 +13776,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13845,6 +13845,9 @@
       <c r="B1660" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1660" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1661" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1661" s="3" t="s">
@@ -13861,7 +13864,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13946,7 +13949,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14031,7 +14034,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14100,9 +14103,6 @@
       <c r="B1693" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1693" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1694" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1694" s="3" t="s">
@@ -14119,7 +14119,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14207,7 +14207,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14276,6 +14276,9 @@
       <c r="B1715" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1715" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1716" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1716" s="3" t="s">
@@ -14292,7 +14295,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14377,7 +14380,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14462,7 +14465,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14547,7 +14550,7 @@
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14616,9 +14619,6 @@
       <c r="B1759" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1759" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1760" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1760" s="3" t="s">
@@ -14635,7 +14635,7 @@
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14723,7 +14723,7 @@
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14800,9 +14800,6 @@
       <c r="B1782" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1782" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1783" s="3" t="s">
@@ -14814,7 +14811,7 @@
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14891,6 +14888,9 @@
       <c r="B1793" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1793" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1794" s="3" t="s">
@@ -14902,7 +14902,7 @@
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14990,7 +14990,7 @@
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15078,7 +15078,7 @@
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15166,7 +15166,7 @@
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15254,7 +15254,7 @@
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15323,6 +15323,9 @@
       <c r="B1847" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1847" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1848" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1848" s="3" t="s">
@@ -15339,7 +15342,7 @@
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15400,7 +15403,9 @@
       <c r="B1857" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1857" s="6"/>
+      <c r="C1857" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1858" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1858" s="3" t="s">
@@ -15416,10 +15421,13 @@
       <c r="B1860" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1860" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15480,17 +15488,12 @@
       <c r="B1868" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1868" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1868" s="6"/>
     </row>
     <row r="1869" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1869" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1869" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1870" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1870" s="3" t="s">
@@ -15501,13 +15504,10 @@
       <c r="B1871" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1871" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1872" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1872" s="7" t="s">
         <v>3</v>
@@ -15595,7 +15595,7 @@
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1883" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1883" s="7" t="s">
         <v>3</v>
@@ -15683,7 +15683,7 @@
     </row>
     <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1894" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1894" s="7" t="s">
         <v>3</v>
@@ -15752,6 +15752,9 @@
       <c r="B1902" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1902" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1903" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1903" s="3" t="s">
@@ -15768,7 +15771,7 @@
     </row>
     <row r="1905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1905" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1905" s="7" t="s">
         <v>3</v>
@@ -15853,7 +15856,7 @@
     </row>
     <row r="1916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1916" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1916" s="7" t="s">
         <v>3</v>
@@ -15927,9 +15930,6 @@
       <c r="B1925" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1925" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1926" s="3" t="s">
@@ -15941,7 +15941,7 @@
     </row>
     <row r="1927" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1927" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1927" s="7" t="s">
         <v>3</v>
@@ -16002,7 +16002,9 @@
       <c r="B1934" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1934" s="6"/>
+      <c r="C1934" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1935" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1935" s="3" t="s">
@@ -16013,15 +16015,21 @@
       <c r="B1936" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1936" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1937" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1937" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1938" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1938" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B1938" s="7" t="s">
         <v>3</v>
@@ -16082,9 +16090,7 @@
       <c r="B1945" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1945" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1945" s="6"/>
     </row>
     <row r="1946" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1946" s="3" t="s">
@@ -16100,13 +16106,10 @@
       <c r="B1948" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1948" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1949" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1949" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B1949" s="7" t="s">
         <v>3</v>
@@ -16175,9 +16178,6 @@
       <c r="B1957" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1957" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1958" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1958" s="3" t="s">
@@ -16194,7 +16194,7 @@
     </row>
     <row r="1960" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1960" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B1960" s="7" t="s">
         <v>3</v>
@@ -16263,6 +16263,9 @@
       <c r="B1968" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1968" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1969" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1969" s="3" t="s">
@@ -16279,7 +16282,7 @@
     </row>
     <row r="1971" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1971" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B1971" s="7" t="s">
         <v>3</v>
@@ -16358,10 +16361,13 @@
       <c r="B1981" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1981" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1982" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1982" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B1982" s="7" t="s">
         <v>3</v>
@@ -16440,13 +16446,10 @@
       <c r="B1992" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1992" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1993" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1993" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B1993" s="7" t="s">
         <v>3</v>
@@ -16515,9 +16518,6 @@
       <c r="B2001" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2001" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2002" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2002" s="3" t="s">
@@ -16534,7 +16534,7 @@
     </row>
     <row r="2004" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2004" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B2004" s="7" t="s">
         <v>3</v>
@@ -16555,19 +16555,25 @@
       <c r="B2006" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2006" s="6"/>
+      <c r="C2006" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2007" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2007" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2007" s="6"/>
+      <c r="C2007" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2008" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2008" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2008" s="6"/>
+      <c r="C2008" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2009" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2009" s="3" t="s">
@@ -16589,12 +16595,17 @@
       <c r="B2011" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2011" s="6"/>
+      <c r="C2011" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2012" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2012" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2012" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2013" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2013" s="3" t="s">
@@ -16605,10 +16616,13 @@
       <c r="B2014" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C2014" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2015" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2015" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B2015" s="7" t="s">
         <v>3</v>
@@ -16629,25 +16643,19 @@
       <c r="B2017" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2017" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2017" s="6"/>
     </row>
     <row r="2018" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2018" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2018" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2018" s="6"/>
     </row>
     <row r="2019" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2019" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2019" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2019" s="6"/>
     </row>
     <row r="2020" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2020" s="3" t="s">
@@ -16669,17 +16677,12 @@
       <c r="B2022" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2022" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2022" s="6"/>
     </row>
     <row r="2023" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2023" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2023" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2024" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2024" s="3" t="s">
@@ -16690,13 +16693,10 @@
       <c r="B2025" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2025" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2026" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2026" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B2026" s="7" t="s">
         <v>3</v>
@@ -16784,7 +16784,7 @@
     </row>
     <row r="2037" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2037" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B2037" s="7" t="s">
         <v>3</v>
@@ -16853,6 +16853,9 @@
       <c r="B2045" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2045" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2046" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2046" s="3" t="s">
@@ -16869,7 +16872,7 @@
     </row>
     <row r="2048" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2048" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B2048" s="7" t="s">
         <v>3</v>
@@ -16938,9 +16941,6 @@
       <c r="B2056" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2056" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2057" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2057" s="3" t="s">
@@ -16948,19 +16948,19 @@
       </c>
     </row>
     <row r="2058" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2058" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B2058" s="7" t="s">
-        <v>3</v>
+      <c r="B2058" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C2058" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2059" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2059" s="3" t="s">
-        <v>4</v>
+      <c r="A2059" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B2059" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2059" s="5" t="s">
         <v>13</v>
@@ -16968,7 +16968,7 @@
     </row>
     <row r="2060" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2060" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2060" s="5" t="s">
         <v>13</v>
@@ -16976,7 +16976,7 @@
     </row>
     <row r="2061" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2061" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2061" s="5" t="s">
         <v>13</v>
@@ -16984,7 +16984,7 @@
     </row>
     <row r="2062" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2062" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2062" s="5" t="s">
         <v>13</v>
@@ -16992,7 +16992,7 @@
     </row>
     <row r="2063" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2063" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2063" s="5" t="s">
         <v>13</v>
@@ -17000,7 +17000,7 @@
     </row>
     <row r="2064" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2064" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2064" s="5" t="s">
         <v>13</v>
@@ -17008,7 +17008,7 @@
     </row>
     <row r="2065" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2065" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2065" s="5" t="s">
         <v>13</v>
@@ -17016,7 +17016,7 @@
     </row>
     <row r="2066" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2066" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2066" s="5" t="s">
         <v>13</v>
@@ -17024,23 +17024,23 @@
     </row>
     <row r="2067" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2067" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C2067" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2068" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2068" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B2068" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2068" s="5" t="s">
-        <v>13</v>
+      <c r="B2068" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2069" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2069" s="3" t="s">
-        <v>4</v>
+      <c r="A2069" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B2069" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2069" s="5" t="s">
         <v>13</v>
@@ -17048,7 +17048,7 @@
     </row>
     <row r="2070" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2070" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2070" s="5" t="s">
         <v>13</v>
@@ -17056,7 +17056,7 @@
     </row>
     <row r="2071" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2071" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2071" s="5" t="s">
         <v>13</v>
@@ -17064,7 +17064,7 @@
     </row>
     <row r="2072" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2072" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2072" s="5" t="s">
         <v>13</v>
@@ -17072,7 +17072,7 @@
     </row>
     <row r="2073" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2073" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2073" s="5" t="s">
         <v>13</v>
@@ -17080,7 +17080,7 @@
     </row>
     <row r="2074" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2074" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2074" s="5" t="s">
         <v>13</v>
@@ -17088,7 +17088,7 @@
     </row>
     <row r="2075" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2075" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2075" s="5" t="s">
         <v>13</v>
@@ -17096,16 +17096,104 @@
     </row>
     <row r="2076" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2076" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C2076" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2077" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2077" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C2077" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2078" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2078" s="3">
+      <c r="B2078" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2079" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2079" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B2079" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2079" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2080" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2080" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2080" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2081" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2081" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2081" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2082" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2082" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2082" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2083" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2083" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2083" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2084" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2084" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2084" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2085" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2085" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2085" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2086" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2086" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2086" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2087" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2087" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2088" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2088" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2089" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2089" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C83BBD-4480-46DB-BF45-06C4E800374A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6EDBA09-CD5E-4ECB-947A-C6CF9B82A162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3984" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4005" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2089"/>
+  <dimension ref="A1:C2100"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -493,7 +493,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
-        <v>46266</v>
+        <v>46296</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>3</v>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6191,7 +6191,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6279,7 +6279,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6367,7 +6367,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6455,7 +6455,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6543,7 +6543,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6631,7 +6631,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6719,7 +6719,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6807,7 +6807,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6895,7 +6895,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6983,7 +6983,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7060,9 +7060,6 @@
       <c r="B825" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C825" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="826" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B826" s="3" t="s">
@@ -7074,7 +7071,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7151,6 +7148,9 @@
       <c r="B836" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C836" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="837" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B837" s="3" t="s">
@@ -7162,7 +7162,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7250,7 +7250,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7338,7 +7338,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7426,7 +7426,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7514,7 +7514,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7591,9 +7591,6 @@
       <c r="B891" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C891" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="892" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B892" s="3" t="s">
@@ -7605,7 +7602,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7696,7 +7693,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7787,7 +7784,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7878,7 +7875,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -7955,6 +7952,9 @@
       <c r="B935" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C935" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="936" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B936" s="3" t="s">
@@ -7966,7 +7966,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8043,9 +8043,6 @@
       <c r="B946" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C946" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="947" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B947" s="3" t="s">
@@ -8057,7 +8054,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8148,7 +8145,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8239,7 +8236,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8330,7 +8327,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8421,7 +8418,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8512,7 +8509,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8603,7 +8600,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8694,7 +8691,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8785,7 +8782,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8876,7 +8873,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -8967,7 +8964,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9058,7 +9055,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9149,7 +9146,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9240,7 +9237,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9331,7 +9328,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9422,7 +9419,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9513,7 +9510,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9604,7 +9601,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9695,7 +9692,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9786,7 +9783,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9877,7 +9874,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -9968,7 +9965,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10059,7 +10056,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10150,7 +10147,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10241,7 +10238,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10332,7 +10329,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10423,7 +10420,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10514,7 +10511,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10605,7 +10602,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10696,7 +10693,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10787,7 +10784,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10878,7 +10875,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10969,7 +10966,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11046,6 +11043,9 @@
       <c r="B1309" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1309" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1310" s="3" t="s">
@@ -11057,7 +11057,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11134,9 +11134,6 @@
       <c r="B1320" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1320" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1321" s="3" t="s">
@@ -11148,7 +11145,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11239,7 +11236,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11330,7 +11327,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11421,7 +11418,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11512,7 +11509,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11603,7 +11600,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11694,7 +11691,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11785,7 +11782,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11876,7 +11873,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11967,7 +11964,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12036,6 +12033,9 @@
       <c r="B1429" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1429" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1430" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1430" s="3" t="s">
@@ -12055,7 +12055,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12124,9 +12124,6 @@
       <c r="B1440" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1440" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1441" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1441" s="3" t="s">
@@ -12146,7 +12143,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12223,6 +12220,9 @@
       <c r="B1452" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1452" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1453" s="3" t="s">
@@ -12234,7 +12234,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12303,6 +12303,9 @@
       <c r="B1462" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1462" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1463" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1463" s="3" t="s">
@@ -12319,7 +12322,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12388,9 +12391,6 @@
       <c r="B1473" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1473" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1474" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1474" s="3" t="s">
@@ -12407,7 +12407,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12476,6 +12476,9 @@
       <c r="B1484" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1484" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1485" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1485" s="3" t="s">
@@ -12492,7 +12495,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12561,9 +12564,6 @@
       <c r="B1495" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1495" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1496" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1496" s="3" t="s">
@@ -12580,7 +12580,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12668,7 +12668,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12756,7 +12756,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12825,6 +12825,9 @@
       <c r="B1528" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1528" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1529" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1529" s="3" t="s">
@@ -12841,7 +12844,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12926,7 +12929,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -13011,7 +13014,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13096,7 +13099,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13181,7 +13184,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13266,7 +13269,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13351,7 +13354,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13436,7 +13439,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13521,7 +13524,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13606,7 +13609,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13691,7 +13694,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13776,7 +13779,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13845,9 +13848,6 @@
       <c r="B1660" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1660" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1661" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1661" s="3" t="s">
@@ -13864,7 +13864,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13933,6 +13933,9 @@
       <c r="B1671" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1671" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1672" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1672" s="3" t="s">
@@ -13949,7 +13952,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14034,7 +14037,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14119,7 +14122,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14188,9 +14191,6 @@
       <c r="B1704" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1704" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1705" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1705" s="3" t="s">
@@ -14207,7 +14207,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14295,7 +14295,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14364,6 +14364,9 @@
       <c r="B1726" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1726" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1727" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1727" s="3" t="s">
@@ -14380,7 +14383,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14465,7 +14468,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14550,7 +14553,7 @@
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14635,7 +14638,7 @@
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14704,9 +14707,6 @@
       <c r="B1770" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1770" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1771" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1771" s="3" t="s">
@@ -14723,7 +14723,7 @@
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14811,7 +14811,7 @@
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14888,9 +14888,6 @@
       <c r="B1793" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1793" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1794" s="3" t="s">
@@ -14902,7 +14899,7 @@
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14979,6 +14976,9 @@
       <c r="B1804" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1804" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1805" s="3" t="s">
@@ -14990,7 +14990,7 @@
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15078,7 +15078,7 @@
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15166,7 +15166,7 @@
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15254,7 +15254,7 @@
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15342,7 +15342,7 @@
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15411,6 +15411,9 @@
       <c r="B1858" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1858" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1859" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1859" s="3" t="s">
@@ -15427,7 +15430,7 @@
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15488,7 +15491,9 @@
       <c r="B1868" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1868" s="6"/>
+      <c r="C1868" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1869" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1869" s="3" t="s">
@@ -15504,10 +15509,13 @@
       <c r="B1871" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1871" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1872" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1872" s="7" t="s">
         <v>3</v>
@@ -15568,17 +15576,12 @@
       <c r="B1879" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1879" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1879" s="6"/>
     </row>
     <row r="1880" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1880" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1880" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1881" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1881" s="3" t="s">
@@ -15589,13 +15592,10 @@
       <c r="B1882" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1882" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1883" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1883" s="7" t="s">
         <v>3</v>
@@ -15683,7 +15683,7 @@
     </row>
     <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1894" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1894" s="7" t="s">
         <v>3</v>
@@ -15771,7 +15771,7 @@
     </row>
     <row r="1905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1905" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1905" s="7" t="s">
         <v>3</v>
@@ -15840,6 +15840,9 @@
       <c r="B1913" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1913" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1914" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1914" s="3" t="s">
@@ -15856,7 +15859,7 @@
     </row>
     <row r="1916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1916" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1916" s="7" t="s">
         <v>3</v>
@@ -15941,7 +15944,7 @@
     </row>
     <row r="1927" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1927" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1927" s="7" t="s">
         <v>3</v>
@@ -16015,9 +16018,6 @@
       <c r="B1936" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1936" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1937" s="3" t="s">
@@ -16029,7 +16029,7 @@
     </row>
     <row r="1938" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1938" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1938" s="7" t="s">
         <v>3</v>
@@ -16090,7 +16090,9 @@
       <c r="B1945" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1945" s="6"/>
+      <c r="C1945" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1946" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1946" s="3" t="s">
@@ -16101,15 +16103,21 @@
       <c r="B1947" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1947" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1948" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1948" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1949" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1949" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B1949" s="7" t="s">
         <v>3</v>
@@ -16170,9 +16178,7 @@
       <c r="B1956" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1956" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1956" s="6"/>
     </row>
     <row r="1957" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1957" s="3" t="s">
@@ -16188,13 +16194,10 @@
       <c r="B1959" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1959" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1960" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1960" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B1960" s="7" t="s">
         <v>3</v>
@@ -16263,9 +16266,6 @@
       <c r="B1968" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1968" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1969" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1969" s="3" t="s">
@@ -16282,7 +16282,7 @@
     </row>
     <row r="1971" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1971" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B1971" s="7" t="s">
         <v>3</v>
@@ -16351,6 +16351,9 @@
       <c r="B1979" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1979" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1980" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1980" s="3" t="s">
@@ -16367,7 +16370,7 @@
     </row>
     <row r="1982" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1982" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B1982" s="7" t="s">
         <v>3</v>
@@ -16446,10 +16449,13 @@
       <c r="B1992" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1992" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1993" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1993" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B1993" s="7" t="s">
         <v>3</v>
@@ -16528,13 +16534,10 @@
       <c r="B2003" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2003" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2004" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2004" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B2004" s="7" t="s">
         <v>3</v>
@@ -16603,9 +16606,6 @@
       <c r="B2012" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2012" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2013" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2013" s="3" t="s">
@@ -16622,7 +16622,7 @@
     </row>
     <row r="2015" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2015" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B2015" s="7" t="s">
         <v>3</v>
@@ -16643,19 +16643,25 @@
       <c r="B2017" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2017" s="6"/>
+      <c r="C2017" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2018" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2018" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2018" s="6"/>
+      <c r="C2018" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2019" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2019" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2019" s="6"/>
+      <c r="C2019" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2020" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2020" s="3" t="s">
@@ -16677,12 +16683,17 @@
       <c r="B2022" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2022" s="6"/>
+      <c r="C2022" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2023" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2023" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2023" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2024" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2024" s="3" t="s">
@@ -16693,10 +16704,13 @@
       <c r="B2025" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C2025" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2026" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2026" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B2026" s="7" t="s">
         <v>3</v>
@@ -16717,25 +16731,19 @@
       <c r="B2028" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2028" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2028" s="6"/>
     </row>
     <row r="2029" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2029" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2029" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2029" s="6"/>
     </row>
     <row r="2030" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2030" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2030" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2030" s="6"/>
     </row>
     <row r="2031" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2031" s="3" t="s">
@@ -16757,17 +16765,12 @@
       <c r="B2033" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2033" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2033" s="6"/>
     </row>
     <row r="2034" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2034" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2034" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2035" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2035" s="3" t="s">
@@ -16778,13 +16781,10 @@
       <c r="B2036" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2036" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2037" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2037" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B2037" s="7" t="s">
         <v>3</v>
@@ -16872,7 +16872,7 @@
     </row>
     <row r="2048" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2048" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B2048" s="7" t="s">
         <v>3</v>
@@ -16941,6 +16941,9 @@
       <c r="B2056" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2056" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2057" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2057" s="3" t="s">
@@ -16957,7 +16960,7 @@
     </row>
     <row r="2059" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2059" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B2059" s="7" t="s">
         <v>3</v>
@@ -17026,9 +17029,6 @@
       <c r="B2067" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2067" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2068" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2068" s="3" t="s">
@@ -17036,19 +17036,19 @@
       </c>
     </row>
     <row r="2069" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2069" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B2069" s="7" t="s">
-        <v>3</v>
+      <c r="B2069" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C2069" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2070" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2070" s="3" t="s">
-        <v>4</v>
+      <c r="A2070" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B2070" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2070" s="5" t="s">
         <v>13</v>
@@ -17056,7 +17056,7 @@
     </row>
     <row r="2071" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2071" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2071" s="5" t="s">
         <v>13</v>
@@ -17064,7 +17064,7 @@
     </row>
     <row r="2072" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2072" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2072" s="5" t="s">
         <v>13</v>
@@ -17072,7 +17072,7 @@
     </row>
     <row r="2073" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2073" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2073" s="5" t="s">
         <v>13</v>
@@ -17080,7 +17080,7 @@
     </row>
     <row r="2074" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2074" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2074" s="5" t="s">
         <v>13</v>
@@ -17088,7 +17088,7 @@
     </row>
     <row r="2075" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2075" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2075" s="5" t="s">
         <v>13</v>
@@ -17096,7 +17096,7 @@
     </row>
     <row r="2076" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2076" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2076" s="5" t="s">
         <v>13</v>
@@ -17104,7 +17104,7 @@
     </row>
     <row r="2077" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2077" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2077" s="5" t="s">
         <v>13</v>
@@ -17112,88 +17112,176 @@
     </row>
     <row r="2078" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2078" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C2078" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2079" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2079" s="4">
+      <c r="B2079" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2080" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2080" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B2080" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2080" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2081" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2081" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2081" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2082" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2082" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2082" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2083" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2083" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2083" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2084" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2084" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2084" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2085" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2085" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2085" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2086" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2086" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2086" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2087" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2087" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2087" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2088" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2088" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2088" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2089" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2089" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2090" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2090" s="4">
         <v>46042</v>
       </c>
-      <c r="B2079" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2079" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2080" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2080" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2080" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2081" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2081" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2081" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2082" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2082" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2082" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2083" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2083" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2083" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2084" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2084" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2084" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2085" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2085" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2085" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2086" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2086" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2086" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2087" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2087" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2088" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2088" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2089" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2089" s="3">
+      <c r="B2090" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2090" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2091" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2091" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2091" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2092" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2092" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2092" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2093" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2093" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2093" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2094" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2094" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2094" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2095" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2095" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2095" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2096" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2096" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2096" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2097" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2097" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2097" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2098" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2098" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2099" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2099" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2100" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2100" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6EDBA09-CD5E-4ECB-947A-C6CF9B82A162}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91D60C9-1873-4FC5-A920-EDD45187D4C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4005" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4026" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2100"/>
+  <dimension ref="A1:C2111"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6191,7 +6191,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6279,7 +6279,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6367,7 +6367,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6455,7 +6455,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6543,7 +6543,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6631,7 +6631,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6719,7 +6719,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6807,7 +6807,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6895,7 +6895,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6983,7 +6983,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7071,7 +7071,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7148,9 +7148,6 @@
       <c r="B836" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C836" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="837" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B837" s="3" t="s">
@@ -7162,7 +7159,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7239,6 +7236,9 @@
       <c r="B847" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C847" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="848" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B848" s="3" t="s">
@@ -7250,7 +7250,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7338,7 +7338,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7426,7 +7426,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7514,7 +7514,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7602,7 +7602,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7679,9 +7679,6 @@
       <c r="B902" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C902" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="903" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B903" s="3" t="s">
@@ -7693,7 +7690,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7784,7 +7781,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7875,7 +7872,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -7966,7 +7963,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8043,6 +8040,9 @@
       <c r="B946" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C946" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="947" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B947" s="3" t="s">
@@ -8054,7 +8054,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8131,9 +8131,6 @@
       <c r="B957" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C957" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="958" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B958" s="3" t="s">
@@ -8145,7 +8142,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8236,7 +8233,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8327,7 +8324,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8418,7 +8415,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8509,7 +8506,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8600,7 +8597,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8691,7 +8688,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8782,7 +8779,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8873,7 +8870,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -8964,7 +8961,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9055,7 +9052,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9146,7 +9143,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9237,7 +9234,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9328,7 +9325,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9419,7 +9416,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9510,7 +9507,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9601,7 +9598,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9692,7 +9689,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9783,7 +9780,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9874,7 +9871,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -9965,7 +9962,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10056,7 +10053,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10147,7 +10144,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10238,7 +10235,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10329,7 +10326,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10420,7 +10417,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10511,7 +10508,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10602,7 +10599,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10693,7 +10690,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10784,7 +10781,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10875,7 +10872,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10966,7 +10963,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11057,7 +11054,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11134,6 +11131,9 @@
       <c r="B1320" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1320" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1321" s="3" t="s">
@@ -11145,7 +11145,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11222,9 +11222,6 @@
       <c r="B1331" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1331" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1332" s="3" t="s">
@@ -11236,7 +11233,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11327,7 +11324,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11418,7 +11415,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11509,7 +11506,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11600,7 +11597,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11691,7 +11688,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11782,7 +11779,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11873,7 +11870,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11964,7 +11961,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12055,7 +12052,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12124,6 +12121,9 @@
       <c r="B1440" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1440" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1441" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1441" s="3" t="s">
@@ -12143,7 +12143,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12212,9 +12212,6 @@
       <c r="B1451" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1451" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1452" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1452" s="3" t="s">
@@ -12234,7 +12231,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12311,6 +12308,9 @@
       <c r="B1463" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1463" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1464" s="3" t="s">
@@ -12322,7 +12322,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12391,6 +12391,9 @@
       <c r="B1473" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1473" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1474" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1474" s="3" t="s">
@@ -12407,7 +12410,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12476,9 +12479,6 @@
       <c r="B1484" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1484" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1485" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1485" s="3" t="s">
@@ -12495,7 +12495,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12564,6 +12564,9 @@
       <c r="B1495" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1495" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1496" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1496" s="3" t="s">
@@ -12580,7 +12583,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12649,9 +12652,6 @@
       <c r="B1506" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1506" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1507" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1507" s="3" t="s">
@@ -12668,7 +12668,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12756,7 +12756,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12844,7 +12844,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12913,6 +12913,9 @@
       <c r="B1539" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1539" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1540" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1540" s="3" t="s">
@@ -12929,7 +12932,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -13014,7 +13017,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13099,7 +13102,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13184,7 +13187,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13269,7 +13272,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13354,7 +13357,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13439,7 +13442,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13524,7 +13527,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13609,7 +13612,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13694,7 +13697,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13779,7 +13782,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13864,7 +13867,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13933,9 +13936,6 @@
       <c r="B1671" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1671" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1672" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1672" s="3" t="s">
@@ -13952,7 +13952,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14021,6 +14021,9 @@
       <c r="B1682" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1682" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1683" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1683" s="3" t="s">
@@ -14037,7 +14040,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14122,7 +14125,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14207,7 +14210,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14276,9 +14279,6 @@
       <c r="B1715" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1715" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1716" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1716" s="3" t="s">
@@ -14295,7 +14295,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14383,7 +14383,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14452,6 +14452,9 @@
       <c r="B1737" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1737" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1738" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1738" s="3" t="s">
@@ -14468,7 +14471,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14553,7 +14556,7 @@
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14638,7 +14641,7 @@
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14723,7 +14726,7 @@
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14792,9 +14795,6 @@
       <c r="B1781" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1781" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1782" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1782" s="3" t="s">
@@ -14811,7 +14811,7 @@
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14899,7 +14899,7 @@
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14976,9 +14976,6 @@
       <c r="B1804" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1804" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1805" s="3" t="s">
@@ -14990,7 +14987,7 @@
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15067,6 +15064,9 @@
       <c r="B1815" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1815" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1816" s="3" t="s">
@@ -15078,7 +15078,7 @@
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15166,7 +15166,7 @@
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15254,7 +15254,7 @@
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15342,7 +15342,7 @@
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15430,7 +15430,7 @@
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15499,6 +15499,9 @@
       <c r="B1869" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1869" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1870" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1870" s="3" t="s">
@@ -15515,7 +15518,7 @@
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1872" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1872" s="7" t="s">
         <v>3</v>
@@ -15576,7 +15579,9 @@
       <c r="B1879" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1879" s="6"/>
+      <c r="C1879" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1880" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1880" s="3" t="s">
@@ -15592,10 +15597,13 @@
       <c r="B1882" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1882" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1883" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1883" s="7" t="s">
         <v>3</v>
@@ -15656,17 +15664,12 @@
       <c r="B1890" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1890" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1890" s="6"/>
     </row>
     <row r="1891" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1891" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1891" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1892" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1892" s="3" t="s">
@@ -15677,13 +15680,10 @@
       <c r="B1893" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1893" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1894" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1894" s="7" t="s">
         <v>3</v>
@@ -15771,7 +15771,7 @@
     </row>
     <row r="1905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1905" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1905" s="7" t="s">
         <v>3</v>
@@ -15859,7 +15859,7 @@
     </row>
     <row r="1916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1916" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1916" s="7" t="s">
         <v>3</v>
@@ -15928,6 +15928,9 @@
       <c r="B1924" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1924" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1925" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1925" s="3" t="s">
@@ -15944,7 +15947,7 @@
     </row>
     <row r="1927" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1927" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1927" s="7" t="s">
         <v>3</v>
@@ -16029,7 +16032,7 @@
     </row>
     <row r="1938" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1938" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1938" s="7" t="s">
         <v>3</v>
@@ -16103,9 +16106,6 @@
       <c r="B1947" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1947" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1948" s="3" t="s">
@@ -16117,7 +16117,7 @@
     </row>
     <row r="1949" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1949" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1949" s="7" t="s">
         <v>3</v>
@@ -16178,7 +16178,9 @@
       <c r="B1956" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1956" s="6"/>
+      <c r="C1956" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1957" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1957" s="3" t="s">
@@ -16189,15 +16191,21 @@
       <c r="B1958" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1958" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1959" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1959" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1960" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1960" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B1960" s="7" t="s">
         <v>3</v>
@@ -16258,9 +16266,7 @@
       <c r="B1967" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1967" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1967" s="6"/>
     </row>
     <row r="1968" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1968" s="3" t="s">
@@ -16276,13 +16282,10 @@
       <c r="B1970" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1970" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1971" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1971" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B1971" s="7" t="s">
         <v>3</v>
@@ -16351,9 +16354,6 @@
       <c r="B1979" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1979" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1980" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1980" s="3" t="s">
@@ -16370,7 +16370,7 @@
     </row>
     <row r="1982" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1982" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B1982" s="7" t="s">
         <v>3</v>
@@ -16439,6 +16439,9 @@
       <c r="B1990" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1990" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1991" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1991" s="3" t="s">
@@ -16455,7 +16458,7 @@
     </row>
     <row r="1993" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1993" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B1993" s="7" t="s">
         <v>3</v>
@@ -16534,10 +16537,13 @@
       <c r="B2003" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C2003" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2004" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2004" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B2004" s="7" t="s">
         <v>3</v>
@@ -16616,13 +16622,10 @@
       <c r="B2014" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2014" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2015" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2015" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B2015" s="7" t="s">
         <v>3</v>
@@ -16691,9 +16694,6 @@
       <c r="B2023" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2023" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2024" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2024" s="3" t="s">
@@ -16710,7 +16710,7 @@
     </row>
     <row r="2026" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2026" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B2026" s="7" t="s">
         <v>3</v>
@@ -16731,19 +16731,25 @@
       <c r="B2028" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2028" s="6"/>
+      <c r="C2028" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2029" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2029" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2029" s="6"/>
+      <c r="C2029" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2030" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2030" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2030" s="6"/>
+      <c r="C2030" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2031" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2031" s="3" t="s">
@@ -16765,12 +16771,17 @@
       <c r="B2033" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2033" s="6"/>
+      <c r="C2033" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2034" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2034" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2034" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2035" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2035" s="3" t="s">
@@ -16781,10 +16792,13 @@
       <c r="B2036" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C2036" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2037" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2037" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B2037" s="7" t="s">
         <v>3</v>
@@ -16805,25 +16819,19 @@
       <c r="B2039" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2039" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2039" s="6"/>
     </row>
     <row r="2040" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2040" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2040" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2040" s="6"/>
     </row>
     <row r="2041" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2041" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2041" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2041" s="6"/>
     </row>
     <row r="2042" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2042" s="3" t="s">
@@ -16845,17 +16853,12 @@
       <c r="B2044" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2044" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2044" s="6"/>
     </row>
     <row r="2045" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2045" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2045" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2046" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2046" s="3" t="s">
@@ -16866,13 +16869,10 @@
       <c r="B2047" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2047" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2048" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2048" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B2048" s="7" t="s">
         <v>3</v>
@@ -16960,7 +16960,7 @@
     </row>
     <row r="2059" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2059" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B2059" s="7" t="s">
         <v>3</v>
@@ -17029,6 +17029,9 @@
       <c r="B2067" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2067" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2068" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2068" s="3" t="s">
@@ -17045,7 +17048,7 @@
     </row>
     <row r="2070" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2070" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B2070" s="7" t="s">
         <v>3</v>
@@ -17114,9 +17117,6 @@
       <c r="B2078" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2078" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2079" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2079" s="3" t="s">
@@ -17124,19 +17124,19 @@
       </c>
     </row>
     <row r="2080" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2080" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B2080" s="7" t="s">
-        <v>3</v>
+      <c r="B2080" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C2080" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2081" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2081" s="3" t="s">
-        <v>4</v>
+      <c r="A2081" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B2081" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2081" s="5" t="s">
         <v>13</v>
@@ -17144,7 +17144,7 @@
     </row>
     <row r="2082" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2082" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2082" s="5" t="s">
         <v>13</v>
@@ -17152,7 +17152,7 @@
     </row>
     <row r="2083" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2083" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2083" s="5" t="s">
         <v>13</v>
@@ -17160,7 +17160,7 @@
     </row>
     <row r="2084" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2084" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2084" s="5" t="s">
         <v>13</v>
@@ -17168,7 +17168,7 @@
     </row>
     <row r="2085" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2085" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2085" s="5" t="s">
         <v>13</v>
@@ -17176,7 +17176,7 @@
     </row>
     <row r="2086" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2086" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2086" s="5" t="s">
         <v>13</v>
@@ -17184,7 +17184,7 @@
     </row>
     <row r="2087" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2087" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2087" s="5" t="s">
         <v>13</v>
@@ -17192,7 +17192,7 @@
     </row>
     <row r="2088" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2088" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2088" s="5" t="s">
         <v>13</v>
@@ -17200,23 +17200,23 @@
     </row>
     <row r="2089" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2089" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C2089" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2090" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2090" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B2090" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2090" s="5" t="s">
-        <v>13</v>
+      <c r="B2090" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2091" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2091" s="3" t="s">
-        <v>4</v>
+      <c r="A2091" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B2091" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2091" s="5" t="s">
         <v>13</v>
@@ -17224,7 +17224,7 @@
     </row>
     <row r="2092" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2092" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2092" s="5" t="s">
         <v>13</v>
@@ -17232,7 +17232,7 @@
     </row>
     <row r="2093" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2093" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2093" s="5" t="s">
         <v>13</v>
@@ -17240,7 +17240,7 @@
     </row>
     <row r="2094" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2094" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2094" s="5" t="s">
         <v>13</v>
@@ -17248,7 +17248,7 @@
     </row>
     <row r="2095" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2095" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2095" s="5" t="s">
         <v>13</v>
@@ -17256,32 +17256,120 @@
     </row>
     <row r="2096" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2096" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2096" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2097" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2097" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2097" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2097" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2098" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2098" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2098" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2099" spans="2:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C2098" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2099" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2099" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2100" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2100" s="3">
+        <v>11</v>
+      </c>
+      <c r="C2099" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2100" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2101" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B2101" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2101" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2102" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2103" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2103" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2104" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2104" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2105" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2105" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2106" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2106" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2107" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2107" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2108" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2108" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2109" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2110" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2111" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91D60C9-1873-4FC5-A920-EDD45187D4C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2CC0B6A-1D32-4907-99F3-55BD40BD4212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4026" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4047" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2111"/>
+  <dimension ref="A1:C2122"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6191,7 +6191,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6279,7 +6279,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6367,7 +6367,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6455,7 +6455,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6543,7 +6543,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6631,7 +6631,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6719,7 +6719,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6807,7 +6807,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6895,7 +6895,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6983,7 +6983,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7071,7 +7071,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7159,7 +7159,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7236,9 +7236,6 @@
       <c r="B847" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C847" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="848" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B848" s="3" t="s">
@@ -7250,7 +7247,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7327,6 +7324,9 @@
       <c r="B858" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C858" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="859" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B859" s="3" t="s">
@@ -7338,7 +7338,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7426,7 +7426,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7514,7 +7514,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7602,7 +7602,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7690,7 +7690,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7767,9 +7767,6 @@
       <c r="B913" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C913" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="914" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B914" s="3" t="s">
@@ -7781,7 +7778,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7872,7 +7869,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -7963,7 +7960,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8054,7 +8051,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8131,6 +8128,9 @@
       <c r="B957" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C957" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="958" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B958" s="3" t="s">
@@ -8142,7 +8142,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8219,9 +8219,6 @@
       <c r="B968" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C968" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="969" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B969" s="3" t="s">
@@ -8233,7 +8230,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8324,7 +8321,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8415,7 +8412,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8506,7 +8503,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8597,7 +8594,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8688,7 +8685,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8779,7 +8776,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8870,7 +8867,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -8961,7 +8958,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9052,7 +9049,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9143,7 +9140,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9234,7 +9231,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9325,7 +9322,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9416,7 +9413,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9507,7 +9504,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9598,7 +9595,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9689,7 +9686,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9780,7 +9777,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9871,7 +9868,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -9962,7 +9959,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10053,7 +10050,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10144,7 +10141,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10235,7 +10232,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10326,7 +10323,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10417,7 +10414,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10508,7 +10505,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10599,7 +10596,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10690,7 +10687,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10781,7 +10778,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10872,7 +10869,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10963,7 +10960,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11054,7 +11051,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11145,7 +11142,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11222,6 +11219,9 @@
       <c r="B1331" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1331" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1332" s="3" t="s">
@@ -11233,7 +11233,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11310,9 +11310,6 @@
       <c r="B1342" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1342" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1343" s="3" t="s">
@@ -11324,7 +11321,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11415,7 +11412,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11506,7 +11503,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11597,7 +11594,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11688,7 +11685,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11779,7 +11776,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11870,7 +11867,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11961,7 +11958,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12052,7 +12049,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12143,7 +12140,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12212,6 +12209,9 @@
       <c r="B1451" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1451" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1452" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1452" s="3" t="s">
@@ -12231,7 +12231,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12300,9 +12300,6 @@
       <c r="B1462" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1462" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1463" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1463" s="3" t="s">
@@ -12322,7 +12319,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12399,6 +12396,9 @@
       <c r="B1474" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1474" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1475" s="3" t="s">
@@ -12410,7 +12410,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12479,6 +12479,9 @@
       <c r="B1484" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1484" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1485" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1485" s="3" t="s">
@@ -12495,7 +12498,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12564,9 +12567,6 @@
       <c r="B1495" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1495" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1496" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1496" s="3" t="s">
@@ -12583,7 +12583,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12652,6 +12652,9 @@
       <c r="B1506" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1506" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1507" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1507" s="3" t="s">
@@ -12668,7 +12671,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12737,9 +12740,6 @@
       <c r="B1517" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1517" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1518" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1518" s="3" t="s">
@@ -12756,7 +12756,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12844,7 +12844,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12932,7 +12932,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -13001,6 +13001,9 @@
       <c r="B1550" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1550" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1551" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1551" s="3" t="s">
@@ -13017,7 +13020,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13102,7 +13105,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13187,7 +13190,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13272,7 +13275,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13357,7 +13360,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13442,7 +13445,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13527,7 +13530,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13612,7 +13615,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13697,7 +13700,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13782,7 +13785,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13867,7 +13870,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13952,7 +13955,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14021,9 +14024,6 @@
       <c r="B1682" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1682" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1683" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1683" s="3" t="s">
@@ -14040,7 +14040,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14109,6 +14109,9 @@
       <c r="B1693" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1693" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1694" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1694" s="3" t="s">
@@ -14125,7 +14128,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14210,7 +14213,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14295,7 +14298,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14364,9 +14367,6 @@
       <c r="B1726" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1726" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1727" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1727" s="3" t="s">
@@ -14383,7 +14383,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14471,7 +14471,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14540,6 +14540,9 @@
       <c r="B1748" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1748" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1749" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1749" s="3" t="s">
@@ -14556,7 +14559,7 @@
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14641,7 +14644,7 @@
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14726,7 +14729,7 @@
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14811,7 +14814,7 @@
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14880,9 +14883,6 @@
       <c r="B1792" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1792" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1793" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1793" s="3" t="s">
@@ -14899,7 +14899,7 @@
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14987,7 +14987,7 @@
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15064,9 +15064,6 @@
       <c r="B1815" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1815" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1816" s="3" t="s">
@@ -15078,7 +15075,7 @@
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15155,6 +15152,9 @@
       <c r="B1826" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1826" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1827" s="3" t="s">
@@ -15166,7 +15166,7 @@
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15254,7 +15254,7 @@
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15342,7 +15342,7 @@
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15430,7 +15430,7 @@
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15518,7 +15518,7 @@
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1872" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1872" s="7" t="s">
         <v>3</v>
@@ -15587,6 +15587,9 @@
       <c r="B1880" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1880" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1881" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1881" s="3" t="s">
@@ -15603,7 +15606,7 @@
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1883" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1883" s="7" t="s">
         <v>3</v>
@@ -15664,7 +15667,9 @@
       <c r="B1890" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1890" s="6"/>
+      <c r="C1890" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1891" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1891" s="3" t="s">
@@ -15680,10 +15685,13 @@
       <c r="B1893" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1893" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1894" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1894" s="7" t="s">
         <v>3</v>
@@ -15744,17 +15752,12 @@
       <c r="B1901" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1901" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1901" s="6"/>
     </row>
     <row r="1902" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1902" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1902" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1903" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1903" s="3" t="s">
@@ -15765,13 +15768,10 @@
       <c r="B1904" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1904" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1905" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1905" s="7" t="s">
         <v>3</v>
@@ -15859,7 +15859,7 @@
     </row>
     <row r="1916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1916" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1916" s="7" t="s">
         <v>3</v>
@@ -15947,7 +15947,7 @@
     </row>
     <row r="1927" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1927" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1927" s="7" t="s">
         <v>3</v>
@@ -16016,6 +16016,9 @@
       <c r="B1935" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1935" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1936" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1936" s="3" t="s">
@@ -16032,7 +16035,7 @@
     </row>
     <row r="1938" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1938" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1938" s="7" t="s">
         <v>3</v>
@@ -16117,7 +16120,7 @@
     </row>
     <row r="1949" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1949" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1949" s="7" t="s">
         <v>3</v>
@@ -16191,9 +16194,6 @@
       <c r="B1958" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1958" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1959" s="3" t="s">
@@ -16205,7 +16205,7 @@
     </row>
     <row r="1960" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1960" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1960" s="7" t="s">
         <v>3</v>
@@ -16266,7 +16266,9 @@
       <c r="B1967" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1967" s="6"/>
+      <c r="C1967" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1968" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1968" s="3" t="s">
@@ -16277,15 +16279,21 @@
       <c r="B1969" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1969" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1970" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1970" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1971" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1971" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B1971" s="7" t="s">
         <v>3</v>
@@ -16346,9 +16354,7 @@
       <c r="B1978" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1978" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1978" s="6"/>
     </row>
     <row r="1979" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1979" s="3" t="s">
@@ -16364,13 +16370,10 @@
       <c r="B1981" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1981" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1982" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1982" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B1982" s="7" t="s">
         <v>3</v>
@@ -16439,9 +16442,6 @@
       <c r="B1990" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1990" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1991" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1991" s="3" t="s">
@@ -16458,7 +16458,7 @@
     </row>
     <row r="1993" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1993" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B1993" s="7" t="s">
         <v>3</v>
@@ -16527,6 +16527,9 @@
       <c r="B2001" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2001" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2002" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2002" s="3" t="s">
@@ -16543,7 +16546,7 @@
     </row>
     <row r="2004" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2004" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B2004" s="7" t="s">
         <v>3</v>
@@ -16622,10 +16625,13 @@
       <c r="B2014" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C2014" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2015" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2015" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B2015" s="7" t="s">
         <v>3</v>
@@ -16704,13 +16710,10 @@
       <c r="B2025" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2025" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2026" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2026" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B2026" s="7" t="s">
         <v>3</v>
@@ -16779,9 +16782,6 @@
       <c r="B2034" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2034" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2035" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2035" s="3" t="s">
@@ -16798,7 +16798,7 @@
     </row>
     <row r="2037" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2037" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B2037" s="7" t="s">
         <v>3</v>
@@ -16819,19 +16819,25 @@
       <c r="B2039" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2039" s="6"/>
+      <c r="C2039" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2040" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2040" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2040" s="6"/>
+      <c r="C2040" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2041" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2041" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2041" s="6"/>
+      <c r="C2041" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2042" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2042" s="3" t="s">
@@ -16853,12 +16859,17 @@
       <c r="B2044" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2044" s="6"/>
+      <c r="C2044" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2045" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2045" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2045" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2046" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2046" s="3" t="s">
@@ -16869,10 +16880,13 @@
       <c r="B2047" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C2047" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2048" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2048" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B2048" s="7" t="s">
         <v>3</v>
@@ -16893,25 +16907,19 @@
       <c r="B2050" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2050" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2050" s="6"/>
     </row>
     <row r="2051" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2051" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2051" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2051" s="6"/>
     </row>
     <row r="2052" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2052" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2052" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2052" s="6"/>
     </row>
     <row r="2053" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2053" s="3" t="s">
@@ -16933,17 +16941,12 @@
       <c r="B2055" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2055" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2055" s="6"/>
     </row>
     <row r="2056" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2056" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2056" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2057" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2057" s="3" t="s">
@@ -16954,13 +16957,10 @@
       <c r="B2058" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2058" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2059" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2059" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B2059" s="7" t="s">
         <v>3</v>
@@ -17048,7 +17048,7 @@
     </row>
     <row r="2070" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2070" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B2070" s="7" t="s">
         <v>3</v>
@@ -17117,6 +17117,9 @@
       <c r="B2078" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2078" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2079" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2079" s="3" t="s">
@@ -17133,7 +17136,7 @@
     </row>
     <row r="2081" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2081" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B2081" s="7" t="s">
         <v>3</v>
@@ -17202,9 +17205,6 @@
       <c r="B2089" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2089" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2090" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2090" s="3" t="s">
@@ -17212,19 +17212,19 @@
       </c>
     </row>
     <row r="2091" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2091" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B2091" s="7" t="s">
-        <v>3</v>
+      <c r="B2091" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C2091" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2092" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2092" s="3" t="s">
-        <v>4</v>
+      <c r="A2092" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B2092" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2092" s="5" t="s">
         <v>13</v>
@@ -17232,7 +17232,7 @@
     </row>
     <row r="2093" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2093" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2093" s="5" t="s">
         <v>13</v>
@@ -17240,7 +17240,7 @@
     </row>
     <row r="2094" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2094" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2094" s="5" t="s">
         <v>13</v>
@@ -17248,7 +17248,7 @@
     </row>
     <row r="2095" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2095" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2095" s="5" t="s">
         <v>13</v>
@@ -17256,7 +17256,7 @@
     </row>
     <row r="2096" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2096" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2096" s="5" t="s">
         <v>13</v>
@@ -17264,7 +17264,7 @@
     </row>
     <row r="2097" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2097" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2097" s="5" t="s">
         <v>13</v>
@@ -17272,7 +17272,7 @@
     </row>
     <row r="2098" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2098" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2098" s="5" t="s">
         <v>13</v>
@@ -17280,7 +17280,7 @@
     </row>
     <row r="2099" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2099" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2099" s="5" t="s">
         <v>13</v>
@@ -17288,23 +17288,23 @@
     </row>
     <row r="2100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2100" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C2100" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2101" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2101" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B2101" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2101" s="5" t="s">
-        <v>13</v>
+      <c r="B2101" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2102" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2102" s="3" t="s">
-        <v>4</v>
+      <c r="A2102" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B2102" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2102" s="5" t="s">
         <v>13</v>
@@ -17312,7 +17312,7 @@
     </row>
     <row r="2103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2103" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2103" s="5" t="s">
         <v>13</v>
@@ -17320,7 +17320,7 @@
     </row>
     <row r="2104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2104" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2104" s="5" t="s">
         <v>13</v>
@@ -17328,7 +17328,7 @@
     </row>
     <row r="2105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2105" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2105" s="5" t="s">
         <v>13</v>
@@ -17336,7 +17336,7 @@
     </row>
     <row r="2106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2106" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2106" s="5" t="s">
         <v>13</v>
@@ -17344,7 +17344,7 @@
     </row>
     <row r="2107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2107" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2107" s="5" t="s">
         <v>13</v>
@@ -17352,7 +17352,7 @@
     </row>
     <row r="2108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2108" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2108" s="5" t="s">
         <v>13</v>
@@ -17360,16 +17360,104 @@
     </row>
     <row r="2109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2109" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C2109" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2110" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C2110" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2111" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2111" s="3">
+      <c r="B2111" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2112" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B2112" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2112" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2113" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2113" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2113" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2114" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2114" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2114" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2115" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2115" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2115" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2116" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2116" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2116" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2117" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2117" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2117" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2118" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2118" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2118" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2119" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2119" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2119" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2120" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2120" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2121" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2121" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2122" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2122" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2CC0B6A-1D32-4907-99F3-55BD40BD4212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F7C3108-48A6-4C82-95CA-317236DA44D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4047" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4068" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2122"/>
+  <dimension ref="A1:C2133"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6191,7 +6191,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6279,7 +6279,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6367,7 +6367,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6455,7 +6455,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6543,7 +6543,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6631,7 +6631,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6719,7 +6719,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6807,7 +6807,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6895,7 +6895,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6983,7 +6983,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7071,7 +7071,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7159,7 +7159,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7247,7 +7247,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7324,9 +7324,6 @@
       <c r="B858" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C858" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="859" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B859" s="3" t="s">
@@ -7338,7 +7335,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7415,6 +7412,9 @@
       <c r="B869" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C869" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="870" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B870" s="3" t="s">
@@ -7426,7 +7426,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7514,7 +7514,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7602,7 +7602,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7690,7 +7690,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7778,7 +7778,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7855,9 +7855,6 @@
       <c r="B924" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C924" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="925" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B925" s="3" t="s">
@@ -7869,7 +7866,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -7960,7 +7957,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8051,7 +8048,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8142,7 +8139,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8219,6 +8216,9 @@
       <c r="B968" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C968" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="969" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B969" s="3" t="s">
@@ -8230,7 +8230,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8307,9 +8307,6 @@
       <c r="B979" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C979" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="980" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B980" s="3" t="s">
@@ -8321,7 +8318,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8412,7 +8409,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8503,7 +8500,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8594,7 +8591,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8685,7 +8682,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8776,7 +8773,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8867,7 +8864,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -8958,7 +8955,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9049,7 +9046,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9140,7 +9137,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9231,7 +9228,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9322,7 +9319,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9413,7 +9410,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9504,7 +9501,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9595,7 +9592,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9686,7 +9683,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9777,7 +9774,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9868,7 +9865,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -9959,7 +9956,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10050,7 +10047,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10141,7 +10138,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10232,7 +10229,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10323,7 +10320,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10414,7 +10411,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10505,7 +10502,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10596,7 +10593,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10687,7 +10684,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10778,7 +10775,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10869,7 +10866,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10960,7 +10957,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11051,7 +11048,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11142,7 +11139,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11233,7 +11230,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11310,6 +11307,9 @@
       <c r="B1342" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1342" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1343" s="3" t="s">
@@ -11321,7 +11321,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11398,9 +11398,6 @@
       <c r="B1353" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1353" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1354" s="3" t="s">
@@ -11412,7 +11409,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11503,7 +11500,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11594,7 +11591,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11685,7 +11682,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11776,7 +11773,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11867,7 +11864,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11958,7 +11955,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12049,7 +12046,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12140,7 +12137,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12231,7 +12228,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12300,6 +12297,9 @@
       <c r="B1462" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1462" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1463" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1463" s="3" t="s">
@@ -12319,7 +12319,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12388,9 +12388,6 @@
       <c r="B1473" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1473" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1474" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1474" s="3" t="s">
@@ -12410,7 +12407,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12487,6 +12484,9 @@
       <c r="B1485" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1485" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1486" s="3" t="s">
@@ -12498,7 +12498,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12567,6 +12567,9 @@
       <c r="B1495" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1495" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1496" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1496" s="3" t="s">
@@ -12583,7 +12586,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12652,9 +12655,6 @@
       <c r="B1506" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1506" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1507" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1507" s="3" t="s">
@@ -12671,7 +12671,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12740,6 +12740,9 @@
       <c r="B1517" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1517" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1518" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1518" s="3" t="s">
@@ -12756,7 +12759,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12825,9 +12828,6 @@
       <c r="B1528" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1528" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1529" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1529" s="3" t="s">
@@ -12844,7 +12844,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12932,7 +12932,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -13020,7 +13020,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13089,6 +13089,9 @@
       <c r="B1561" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1561" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1562" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1562" s="3" t="s">
@@ -13105,7 +13108,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13190,7 +13193,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13275,7 +13278,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13360,7 +13363,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13445,7 +13448,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13530,7 +13533,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13615,7 +13618,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13700,7 +13703,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13785,7 +13788,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13870,7 +13873,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13955,7 +13958,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14040,7 +14043,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14109,9 +14112,6 @@
       <c r="B1693" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1693" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1694" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1694" s="3" t="s">
@@ -14128,7 +14128,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14197,6 +14197,9 @@
       <c r="B1704" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1704" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1705" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1705" s="3" t="s">
@@ -14213,7 +14216,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14298,7 +14301,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14383,7 +14386,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14452,9 +14455,6 @@
       <c r="B1737" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1737" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1738" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1738" s="3" t="s">
@@ -14471,7 +14471,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14559,7 +14559,7 @@
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14628,6 +14628,9 @@
       <c r="B1759" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1759" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1760" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1760" s="3" t="s">
@@ -14644,7 +14647,7 @@
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14729,7 +14732,7 @@
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14814,7 +14817,7 @@
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14899,7 +14902,7 @@
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14968,9 +14971,6 @@
       <c r="B1803" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1803" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1804" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1804" s="3" t="s">
@@ -14987,7 +14987,7 @@
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15075,7 +15075,7 @@
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15152,9 +15152,6 @@
       <c r="B1826" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1826" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1827" s="3" t="s">
@@ -15166,7 +15163,7 @@
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15243,6 +15240,9 @@
       <c r="B1837" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1837" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1838" s="3" t="s">
@@ -15254,7 +15254,7 @@
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15342,7 +15342,7 @@
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15430,7 +15430,7 @@
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15518,7 +15518,7 @@
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1872" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1872" s="7" t="s">
         <v>3</v>
@@ -15606,7 +15606,7 @@
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1883" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1883" s="7" t="s">
         <v>3</v>
@@ -15675,6 +15675,9 @@
       <c r="B1891" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1891" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1892" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1892" s="3" t="s">
@@ -15691,7 +15694,7 @@
     </row>
     <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1894" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1894" s="7" t="s">
         <v>3</v>
@@ -15752,7 +15755,9 @@
       <c r="B1901" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1901" s="6"/>
+      <c r="C1901" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1902" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1902" s="3" t="s">
@@ -15768,10 +15773,13 @@
       <c r="B1904" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1904" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1905" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1905" s="7" t="s">
         <v>3</v>
@@ -15832,17 +15840,12 @@
       <c r="B1912" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1912" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1912" s="6"/>
     </row>
     <row r="1913" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1913" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1913" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1914" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1914" s="3" t="s">
@@ -15853,13 +15856,10 @@
       <c r="B1915" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1915" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1916" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1916" s="7" t="s">
         <v>3</v>
@@ -15947,7 +15947,7 @@
     </row>
     <row r="1927" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1927" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1927" s="7" t="s">
         <v>3</v>
@@ -16035,7 +16035,7 @@
     </row>
     <row r="1938" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1938" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1938" s="7" t="s">
         <v>3</v>
@@ -16104,6 +16104,9 @@
       <c r="B1946" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1946" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1947" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1947" s="3" t="s">
@@ -16120,7 +16123,7 @@
     </row>
     <row r="1949" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1949" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1949" s="7" t="s">
         <v>3</v>
@@ -16205,7 +16208,7 @@
     </row>
     <row r="1960" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1960" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1960" s="7" t="s">
         <v>3</v>
@@ -16279,9 +16282,6 @@
       <c r="B1969" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1969" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1970" s="3" t="s">
@@ -16293,7 +16293,7 @@
     </row>
     <row r="1971" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1971" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1971" s="7" t="s">
         <v>3</v>
@@ -16354,7 +16354,9 @@
       <c r="B1978" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1978" s="6"/>
+      <c r="C1978" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1979" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1979" s="3" t="s">
@@ -16365,15 +16367,21 @@
       <c r="B1980" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1980" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1981" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1981" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1982" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1982" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B1982" s="7" t="s">
         <v>3</v>
@@ -16434,9 +16442,7 @@
       <c r="B1989" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1989" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1989" s="6"/>
     </row>
     <row r="1990" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1990" s="3" t="s">
@@ -16452,13 +16458,10 @@
       <c r="B1992" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1992" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1993" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1993" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B1993" s="7" t="s">
         <v>3</v>
@@ -16527,9 +16530,6 @@
       <c r="B2001" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2001" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2002" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2002" s="3" t="s">
@@ -16546,7 +16546,7 @@
     </row>
     <row r="2004" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2004" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B2004" s="7" t="s">
         <v>3</v>
@@ -16615,6 +16615,9 @@
       <c r="B2012" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2012" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2013" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2013" s="3" t="s">
@@ -16631,7 +16634,7 @@
     </row>
     <row r="2015" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2015" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B2015" s="7" t="s">
         <v>3</v>
@@ -16710,10 +16713,13 @@
       <c r="B2025" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C2025" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2026" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2026" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B2026" s="7" t="s">
         <v>3</v>
@@ -16792,13 +16798,10 @@
       <c r="B2036" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2036" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2037" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2037" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B2037" s="7" t="s">
         <v>3</v>
@@ -16867,9 +16870,6 @@
       <c r="B2045" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2045" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2046" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2046" s="3" t="s">
@@ -16886,7 +16886,7 @@
     </row>
     <row r="2048" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2048" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B2048" s="7" t="s">
         <v>3</v>
@@ -16907,19 +16907,25 @@
       <c r="B2050" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2050" s="6"/>
+      <c r="C2050" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2051" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2051" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2051" s="6"/>
+      <c r="C2051" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2052" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2052" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2052" s="6"/>
+      <c r="C2052" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2053" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2053" s="3" t="s">
@@ -16941,12 +16947,17 @@
       <c r="B2055" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2055" s="6"/>
+      <c r="C2055" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2056" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2056" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2056" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2057" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2057" s="3" t="s">
@@ -16957,10 +16968,13 @@
       <c r="B2058" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C2058" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2059" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2059" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B2059" s="7" t="s">
         <v>3</v>
@@ -16981,25 +16995,19 @@
       <c r="B2061" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2061" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2061" s="6"/>
     </row>
     <row r="2062" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2062" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2062" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2062" s="6"/>
     </row>
     <row r="2063" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2063" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2063" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2063" s="6"/>
     </row>
     <row r="2064" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2064" s="3" t="s">
@@ -17021,17 +17029,12 @@
       <c r="B2066" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2066" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2066" s="6"/>
     </row>
     <row r="2067" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2067" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2067" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2068" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2068" s="3" t="s">
@@ -17042,13 +17045,10 @@
       <c r="B2069" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2069" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2070" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2070" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B2070" s="7" t="s">
         <v>3</v>
@@ -17136,7 +17136,7 @@
     </row>
     <row r="2081" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2081" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B2081" s="7" t="s">
         <v>3</v>
@@ -17205,6 +17205,9 @@
       <c r="B2089" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2089" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2090" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2090" s="3" t="s">
@@ -17221,7 +17224,7 @@
     </row>
     <row r="2092" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2092" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B2092" s="7" t="s">
         <v>3</v>
@@ -17290,9 +17293,6 @@
       <c r="B2100" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2100" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2101" s="3" t="s">
@@ -17300,19 +17300,19 @@
       </c>
     </row>
     <row r="2102" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2102" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B2102" s="7" t="s">
-        <v>3</v>
+      <c r="B2102" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C2102" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2103" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2103" s="3" t="s">
-        <v>4</v>
+      <c r="A2103" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B2103" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2103" s="5" t="s">
         <v>13</v>
@@ -17320,7 +17320,7 @@
     </row>
     <row r="2104" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2104" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2104" s="5" t="s">
         <v>13</v>
@@ -17328,7 +17328,7 @@
     </row>
     <row r="2105" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2105" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2105" s="5" t="s">
         <v>13</v>
@@ -17336,7 +17336,7 @@
     </row>
     <row r="2106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2106" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2106" s="5" t="s">
         <v>13</v>
@@ -17344,7 +17344,7 @@
     </row>
     <row r="2107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2107" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2107" s="5" t="s">
         <v>13</v>
@@ -17352,7 +17352,7 @@
     </row>
     <row r="2108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2108" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2108" s="5" t="s">
         <v>13</v>
@@ -17360,7 +17360,7 @@
     </row>
     <row r="2109" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2109" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2109" s="5" t="s">
         <v>13</v>
@@ -17368,7 +17368,7 @@
     </row>
     <row r="2110" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2110" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2110" s="5" t="s">
         <v>13</v>
@@ -17376,88 +17376,176 @@
     </row>
     <row r="2111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2111" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C2111" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2112" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2112" s="4">
+      <c r="B2112" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2113" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B2113" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2113" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2114" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2114" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2115" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2115" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2116" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2116" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2117" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2117" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2118" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2118" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2119" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2119" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2120" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2120" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2121" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2121" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2122" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2123" s="4">
         <v>46042</v>
       </c>
-      <c r="B2112" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2112" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2113" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2113" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2113" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2114" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2114" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2114" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2115" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2115" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2115" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2116" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2116" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2116" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2117" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2117" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2117" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2118" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2118" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2118" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2119" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2119" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2119" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2120" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2120" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2121" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2121" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2122" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2122" s="3">
+      <c r="B2123" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2123" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2124" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2124" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2125" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2125" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2126" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2126" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2127" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2127" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2127" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2128" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2128" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2128" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2129" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2129" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2129" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2130" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2130" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2130" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2131" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2131" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2132" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2132" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2133" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2133" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F7C3108-48A6-4C82-95CA-317236DA44D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76ABECD-F275-4014-813C-A6D27C5398F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4068" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4089" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2133"/>
+  <dimension ref="A1:C2144"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6191,7 +6191,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6279,7 +6279,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6367,7 +6367,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6455,7 +6455,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6543,7 +6543,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6631,7 +6631,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6719,7 +6719,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6807,7 +6807,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6895,7 +6895,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6983,7 +6983,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7071,7 +7071,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7159,7 +7159,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7247,7 +7247,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7335,7 +7335,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7412,9 +7412,6 @@
       <c r="B869" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C869" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="870" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B870" s="3" t="s">
@@ -7426,7 +7423,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7503,6 +7500,9 @@
       <c r="B880" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C880" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="881" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B881" s="3" t="s">
@@ -7514,7 +7514,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7602,7 +7602,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7690,7 +7690,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7778,7 +7778,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7866,7 +7866,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -7943,9 +7943,6 @@
       <c r="B935" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C935" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="936" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B936" s="3" t="s">
@@ -7957,7 +7954,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8048,7 +8045,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8139,7 +8136,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8230,7 +8227,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8307,6 +8304,9 @@
       <c r="B979" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C979" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="980" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B980" s="3" t="s">
@@ -8318,7 +8318,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8395,9 +8395,6 @@
       <c r="B990" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C990" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="991" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B991" s="3" t="s">
@@ -8409,7 +8406,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8500,7 +8497,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8591,7 +8588,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8682,7 +8679,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8773,7 +8770,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8864,7 +8861,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -8955,7 +8952,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9046,7 +9043,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9137,7 +9134,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9228,7 +9225,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9319,7 +9316,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9410,7 +9407,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9501,7 +9498,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9592,7 +9589,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9683,7 +9680,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9774,7 +9771,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9865,7 +9862,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -9956,7 +9953,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10047,7 +10044,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10138,7 +10135,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10229,7 +10226,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10320,7 +10317,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10411,7 +10408,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10502,7 +10499,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10593,7 +10590,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10684,7 +10681,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10775,7 +10772,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10866,7 +10863,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10957,7 +10954,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11048,7 +11045,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11139,7 +11136,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11230,7 +11227,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11321,7 +11318,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11398,6 +11395,9 @@
       <c r="B1353" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1353" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1354" s="3" t="s">
@@ -11409,7 +11409,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11486,9 +11486,6 @@
       <c r="B1364" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1364" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1365" s="3" t="s">
@@ -11500,7 +11497,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11591,7 +11588,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11682,7 +11679,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11773,7 +11770,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11864,7 +11861,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11955,7 +11952,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12046,7 +12043,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12137,7 +12134,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12228,7 +12225,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12319,7 +12316,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12388,6 +12385,9 @@
       <c r="B1473" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1473" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1474" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1474" s="3" t="s">
@@ -12407,7 +12407,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12476,9 +12476,6 @@
       <c r="B1484" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1484" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1485" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1485" s="3" t="s">
@@ -12498,7 +12495,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12575,6 +12572,9 @@
       <c r="B1496" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1496" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1497" s="3" t="s">
@@ -12586,7 +12586,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12655,6 +12655,9 @@
       <c r="B1506" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1506" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1507" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1507" s="3" t="s">
@@ -12671,7 +12674,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12740,9 +12743,6 @@
       <c r="B1517" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1517" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1518" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1518" s="3" t="s">
@@ -12759,7 +12759,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12828,6 +12828,9 @@
       <c r="B1528" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1528" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1529" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1529" s="3" t="s">
@@ -12844,7 +12847,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12913,9 +12916,6 @@
       <c r="B1539" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1539" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1540" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1540" s="3" t="s">
@@ -12932,7 +12932,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -13020,7 +13020,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13108,7 +13108,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13177,6 +13177,9 @@
       <c r="B1572" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1572" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1573" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1573" s="3" t="s">
@@ -13193,7 +13196,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13278,7 +13281,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13363,7 +13366,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13448,7 +13451,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13533,7 +13536,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13618,7 +13621,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13703,7 +13706,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13788,7 +13791,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13873,7 +13876,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13958,7 +13961,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14043,7 +14046,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14128,7 +14131,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14197,9 +14200,6 @@
       <c r="B1704" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1704" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1705" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1705" s="3" t="s">
@@ -14216,7 +14216,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14285,6 +14285,9 @@
       <c r="B1715" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1715" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1716" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1716" s="3" t="s">
@@ -14301,7 +14304,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14386,7 +14389,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14471,7 +14474,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14540,9 +14543,6 @@
       <c r="B1748" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1748" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1749" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1749" s="3" t="s">
@@ -14559,7 +14559,7 @@
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14647,7 +14647,7 @@
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14716,6 +14716,9 @@
       <c r="B1770" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1770" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1771" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1771" s="3" t="s">
@@ -14732,7 +14735,7 @@
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14817,7 +14820,7 @@
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14902,7 +14905,7 @@
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14987,7 +14990,7 @@
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15056,9 +15059,6 @@
       <c r="B1814" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1814" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1815" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1815" s="3" t="s">
@@ -15075,7 +15075,7 @@
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15163,7 +15163,7 @@
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15240,9 +15240,6 @@
       <c r="B1837" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1837" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1838" s="3" t="s">
@@ -15254,7 +15251,7 @@
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15331,6 +15328,9 @@
       <c r="B1848" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1848" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1849" s="3" t="s">
@@ -15342,7 +15342,7 @@
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15430,7 +15430,7 @@
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15518,7 +15518,7 @@
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1872" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1872" s="7" t="s">
         <v>3</v>
@@ -15606,7 +15606,7 @@
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1883" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1883" s="7" t="s">
         <v>3</v>
@@ -15694,7 +15694,7 @@
     </row>
     <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1894" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1894" s="7" t="s">
         <v>3</v>
@@ -15763,6 +15763,9 @@
       <c r="B1902" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1902" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1903" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1903" s="3" t="s">
@@ -15779,7 +15782,7 @@
     </row>
     <row r="1905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1905" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1905" s="7" t="s">
         <v>3</v>
@@ -15840,7 +15843,9 @@
       <c r="B1912" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1912" s="6"/>
+      <c r="C1912" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1913" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1913" s="3" t="s">
@@ -15856,10 +15861,13 @@
       <c r="B1915" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1915" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1916" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1916" s="7" t="s">
         <v>3</v>
@@ -15920,17 +15928,12 @@
       <c r="B1923" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1923" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1923" s="6"/>
     </row>
     <row r="1924" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1924" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1924" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1925" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1925" s="3" t="s">
@@ -15941,13 +15944,10 @@
       <c r="B1926" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1926" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1927" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1927" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1927" s="7" t="s">
         <v>3</v>
@@ -16035,7 +16035,7 @@
     </row>
     <row r="1938" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1938" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1938" s="7" t="s">
         <v>3</v>
@@ -16123,7 +16123,7 @@
     </row>
     <row r="1949" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1949" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1949" s="7" t="s">
         <v>3</v>
@@ -16192,6 +16192,9 @@
       <c r="B1957" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1957" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1958" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1958" s="3" t="s">
@@ -16208,7 +16211,7 @@
     </row>
     <row r="1960" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1960" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1960" s="7" t="s">
         <v>3</v>
@@ -16293,7 +16296,7 @@
     </row>
     <row r="1971" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1971" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1971" s="7" t="s">
         <v>3</v>
@@ -16367,9 +16370,6 @@
       <c r="B1980" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1980" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1981" s="3" t="s">
@@ -16381,7 +16381,7 @@
     </row>
     <row r="1982" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1982" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1982" s="7" t="s">
         <v>3</v>
@@ -16442,7 +16442,9 @@
       <c r="B1989" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1989" s="6"/>
+      <c r="C1989" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1990" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1990" s="3" t="s">
@@ -16453,15 +16455,21 @@
       <c r="B1991" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1991" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1992" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1992" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1993" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1993" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B1993" s="7" t="s">
         <v>3</v>
@@ -16522,9 +16530,7 @@
       <c r="B2000" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2000" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2000" s="6"/>
     </row>
     <row r="2001" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2001" s="3" t="s">
@@ -16540,13 +16546,10 @@
       <c r="B2003" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2003" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2004" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2004" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B2004" s="7" t="s">
         <v>3</v>
@@ -16615,9 +16618,6 @@
       <c r="B2012" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2012" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2013" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2013" s="3" t="s">
@@ -16634,7 +16634,7 @@
     </row>
     <row r="2015" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2015" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B2015" s="7" t="s">
         <v>3</v>
@@ -16703,6 +16703,9 @@
       <c r="B2023" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2023" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2024" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2024" s="3" t="s">
@@ -16719,7 +16722,7 @@
     </row>
     <row r="2026" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2026" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B2026" s="7" t="s">
         <v>3</v>
@@ -16798,10 +16801,13 @@
       <c r="B2036" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C2036" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2037" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2037" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B2037" s="7" t="s">
         <v>3</v>
@@ -16880,13 +16886,10 @@
       <c r="B2047" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2047" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2048" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2048" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B2048" s="7" t="s">
         <v>3</v>
@@ -16955,9 +16958,6 @@
       <c r="B2056" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2056" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2057" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2057" s="3" t="s">
@@ -16974,7 +16974,7 @@
     </row>
     <row r="2059" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2059" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B2059" s="7" t="s">
         <v>3</v>
@@ -16995,19 +16995,25 @@
       <c r="B2061" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2061" s="6"/>
+      <c r="C2061" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2062" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2062" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2062" s="6"/>
+      <c r="C2062" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2063" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2063" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2063" s="6"/>
+      <c r="C2063" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2064" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2064" s="3" t="s">
@@ -17029,12 +17035,17 @@
       <c r="B2066" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2066" s="6"/>
+      <c r="C2066" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2067" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2067" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2067" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2068" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2068" s="3" t="s">
@@ -17045,10 +17056,13 @@
       <c r="B2069" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C2069" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2070" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2070" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B2070" s="7" t="s">
         <v>3</v>
@@ -17069,25 +17083,19 @@
       <c r="B2072" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2072" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2072" s="6"/>
     </row>
     <row r="2073" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2073" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2073" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2073" s="6"/>
     </row>
     <row r="2074" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2074" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2074" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2074" s="6"/>
     </row>
     <row r="2075" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2075" s="3" t="s">
@@ -17109,17 +17117,12 @@
       <c r="B2077" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2077" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2077" s="6"/>
     </row>
     <row r="2078" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2078" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2078" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2079" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2079" s="3" t="s">
@@ -17130,13 +17133,10 @@
       <c r="B2080" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2080" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2081" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2081" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B2081" s="7" t="s">
         <v>3</v>
@@ -17224,7 +17224,7 @@
     </row>
     <row r="2092" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2092" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B2092" s="7" t="s">
         <v>3</v>
@@ -17293,6 +17293,9 @@
       <c r="B2100" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2100" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2101" s="3" t="s">
@@ -17309,7 +17312,7 @@
     </row>
     <row r="2103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2103" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B2103" s="7" t="s">
         <v>3</v>
@@ -17378,9 +17381,6 @@
       <c r="B2111" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2111" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2112" s="3" t="s">
@@ -17388,19 +17388,19 @@
       </c>
     </row>
     <row r="2113" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2113" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B2113" s="7" t="s">
-        <v>3</v>
+      <c r="B2113" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C2113" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2114" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2114" s="3" t="s">
-        <v>4</v>
+      <c r="A2114" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B2114" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2114" s="5" t="s">
         <v>13</v>
@@ -17408,7 +17408,7 @@
     </row>
     <row r="2115" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2115" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2115" s="5" t="s">
         <v>13</v>
@@ -17416,7 +17416,7 @@
     </row>
     <row r="2116" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2116" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2116" s="5" t="s">
         <v>13</v>
@@ -17424,7 +17424,7 @@
     </row>
     <row r="2117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2117" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2117" s="5" t="s">
         <v>13</v>
@@ -17432,7 +17432,7 @@
     </row>
     <row r="2118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2118" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2118" s="5" t="s">
         <v>13</v>
@@ -17440,7 +17440,7 @@
     </row>
     <row r="2119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2119" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2119" s="5" t="s">
         <v>13</v>
@@ -17448,7 +17448,7 @@
     </row>
     <row r="2120" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2120" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2120" s="5" t="s">
         <v>13</v>
@@ -17456,7 +17456,7 @@
     </row>
     <row r="2121" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2121" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2121" s="5" t="s">
         <v>13</v>
@@ -17464,23 +17464,23 @@
     </row>
     <row r="2122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2122" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C2122" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2123" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2123" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B2123" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2123" s="5" t="s">
-        <v>13</v>
+      <c r="B2123" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2124" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2124" s="3" t="s">
-        <v>4</v>
+      <c r="A2124" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B2124" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2124" s="5" t="s">
         <v>13</v>
@@ -17488,7 +17488,7 @@
     </row>
     <row r="2125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2125" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2125" s="5" t="s">
         <v>13</v>
@@ -17496,7 +17496,7 @@
     </row>
     <row r="2126" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2126" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2126" s="5" t="s">
         <v>13</v>
@@ -17504,7 +17504,7 @@
     </row>
     <row r="2127" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2127" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2127" s="5" t="s">
         <v>13</v>
@@ -17512,40 +17512,128 @@
     </row>
     <row r="2128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2128" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2128" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2129" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2129" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2129" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2130" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2130" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2130" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2131" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2131" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2132" spans="2:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C2131" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2132" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2133" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2133" s="3">
+        <v>11</v>
+      </c>
+      <c r="C2132" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2133" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2133" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2134" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2134" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B2134" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2134" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2135" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2135" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2135" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2136" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2136" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2136" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2137" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2137" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2137" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2138" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2138" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2138" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2139" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2139" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2139" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2140" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2140" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2140" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2141" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2141" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2141" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2142" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2142" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2143" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2143" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2144" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2144" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76ABECD-F275-4014-813C-A6D27C5398F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47787811-4B03-445F-85C1-2BF6F106884D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4089" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4110" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2144"/>
+  <dimension ref="A1:C2155"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6191,7 +6191,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6279,7 +6279,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6367,7 +6367,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6455,7 +6455,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6543,7 +6543,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6631,7 +6631,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6719,7 +6719,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6807,7 +6807,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6895,7 +6895,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6983,7 +6983,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7071,7 +7071,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7159,7 +7159,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7247,7 +7247,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7335,7 +7335,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7423,7 +7423,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7500,9 +7500,6 @@
       <c r="B880" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C880" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="881" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B881" s="3" t="s">
@@ -7514,7 +7511,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7591,6 +7588,9 @@
       <c r="B891" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C891" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="892" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B892" s="3" t="s">
@@ -7602,7 +7602,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7690,7 +7690,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7778,7 +7778,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7866,7 +7866,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -7954,7 +7954,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8031,9 +8031,6 @@
       <c r="B946" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C946" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="947" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B947" s="3" t="s">
@@ -8045,7 +8042,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8136,7 +8133,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8227,7 +8224,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8318,7 +8315,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8395,6 +8392,9 @@
       <c r="B990" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C990" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="991" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B991" s="3" t="s">
@@ -8406,7 +8406,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8483,9 +8483,6 @@
       <c r="B1001" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1001" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1002" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1002" s="3" t="s">
@@ -8497,7 +8494,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8588,7 +8585,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8679,7 +8676,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8770,7 +8767,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8861,7 +8858,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -8952,7 +8949,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9043,7 +9040,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9134,7 +9131,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9225,7 +9222,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9316,7 +9313,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9407,7 +9404,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9498,7 +9495,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9589,7 +9586,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9680,7 +9677,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9771,7 +9768,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9862,7 +9859,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -9953,7 +9950,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10044,7 +10041,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10135,7 +10132,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10226,7 +10223,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10317,7 +10314,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10408,7 +10405,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10499,7 +10496,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10590,7 +10587,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10681,7 +10678,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10772,7 +10769,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10863,7 +10860,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10954,7 +10951,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11045,7 +11042,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11136,7 +11133,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11227,7 +11224,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11318,7 +11315,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11409,7 +11406,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11486,6 +11483,9 @@
       <c r="B1364" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1364" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1365" s="3" t="s">
@@ -11497,7 +11497,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11574,9 +11574,6 @@
       <c r="B1375" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1375" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1376" s="3" t="s">
@@ -11588,7 +11585,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11679,7 +11676,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11770,7 +11767,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11861,7 +11858,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11952,7 +11949,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12043,7 +12040,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12134,7 +12131,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12225,7 +12222,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12316,7 +12313,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12407,7 +12404,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12476,6 +12473,9 @@
       <c r="B1484" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1484" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1485" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1485" s="3" t="s">
@@ -12495,7 +12495,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12564,9 +12564,6 @@
       <c r="B1495" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1495" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1496" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1496" s="3" t="s">
@@ -12586,7 +12583,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12663,6 +12660,9 @@
       <c r="B1507" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1507" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1508" s="3" t="s">
@@ -12674,7 +12674,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12743,6 +12743,9 @@
       <c r="B1517" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1517" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1518" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1518" s="3" t="s">
@@ -12759,7 +12762,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12828,9 +12831,6 @@
       <c r="B1528" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1528" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1529" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1529" s="3" t="s">
@@ -12847,7 +12847,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12916,6 +12916,9 @@
       <c r="B1539" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1539" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1540" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1540" s="3" t="s">
@@ -12932,7 +12935,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -13001,9 +13004,6 @@
       <c r="B1550" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1550" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1551" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1551" s="3" t="s">
@@ -13020,7 +13020,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13108,7 +13108,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13196,7 +13196,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13265,6 +13265,9 @@
       <c r="B1583" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1583" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1584" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1584" s="3" t="s">
@@ -13281,7 +13284,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13366,7 +13369,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13451,7 +13454,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13536,7 +13539,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13621,7 +13624,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13706,7 +13709,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13791,7 +13794,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13876,7 +13879,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13961,7 +13964,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14046,7 +14049,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14131,7 +14134,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14216,7 +14219,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14285,9 +14288,6 @@
       <c r="B1715" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1715" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1716" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1716" s="3" t="s">
@@ -14304,7 +14304,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14373,6 +14373,9 @@
       <c r="B1726" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1726" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1727" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1727" s="3" t="s">
@@ -14389,7 +14392,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14474,7 +14477,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14559,7 +14562,7 @@
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14628,9 +14631,6 @@
       <c r="B1759" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1759" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1760" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1760" s="3" t="s">
@@ -14647,7 +14647,7 @@
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14735,7 +14735,7 @@
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14804,6 +14804,9 @@
       <c r="B1781" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1781" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1782" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1782" s="3" t="s">
@@ -14820,7 +14823,7 @@
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14905,7 +14908,7 @@
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14990,7 +14993,7 @@
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15075,7 +15078,7 @@
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15144,9 +15147,6 @@
       <c r="B1825" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1825" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1826" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1826" s="3" t="s">
@@ -15163,7 +15163,7 @@
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15251,7 +15251,7 @@
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15328,9 +15328,6 @@
       <c r="B1848" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1848" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1849" s="3" t="s">
@@ -15342,7 +15339,7 @@
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15419,6 +15416,9 @@
       <c r="B1859" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1859" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1860" s="3" t="s">
@@ -15430,7 +15430,7 @@
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15518,7 +15518,7 @@
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1872" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1872" s="7" t="s">
         <v>3</v>
@@ -15606,7 +15606,7 @@
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1883" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1883" s="7" t="s">
         <v>3</v>
@@ -15694,7 +15694,7 @@
     </row>
     <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1894" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1894" s="7" t="s">
         <v>3</v>
@@ -15782,7 +15782,7 @@
     </row>
     <row r="1905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1905" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1905" s="7" t="s">
         <v>3</v>
@@ -15851,6 +15851,9 @@
       <c r="B1913" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1913" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1914" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1914" s="3" t="s">
@@ -15867,7 +15870,7 @@
     </row>
     <row r="1916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1916" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1916" s="7" t="s">
         <v>3</v>
@@ -15928,7 +15931,9 @@
       <c r="B1923" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1923" s="6"/>
+      <c r="C1923" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1924" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1924" s="3" t="s">
@@ -15944,10 +15949,13 @@
       <c r="B1926" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1926" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1927" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1927" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1927" s="7" t="s">
         <v>3</v>
@@ -16008,17 +16016,12 @@
       <c r="B1934" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1934" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1934" s="6"/>
     </row>
     <row r="1935" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1935" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1935" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1936" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1936" s="3" t="s">
@@ -16029,13 +16032,10 @@
       <c r="B1937" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1937" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1938" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1938" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1938" s="7" t="s">
         <v>3</v>
@@ -16123,7 +16123,7 @@
     </row>
     <row r="1949" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1949" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1949" s="7" t="s">
         <v>3</v>
@@ -16211,7 +16211,7 @@
     </row>
     <row r="1960" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1960" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1960" s="7" t="s">
         <v>3</v>
@@ -16280,6 +16280,9 @@
       <c r="B1968" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1968" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1969" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1969" s="3" t="s">
@@ -16296,7 +16299,7 @@
     </row>
     <row r="1971" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1971" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1971" s="7" t="s">
         <v>3</v>
@@ -16381,7 +16384,7 @@
     </row>
     <row r="1982" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1982" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1982" s="7" t="s">
         <v>3</v>
@@ -16455,9 +16458,6 @@
       <c r="B1991" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1991" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1992" s="3" t="s">
@@ -16469,7 +16469,7 @@
     </row>
     <row r="1993" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1993" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B1993" s="7" t="s">
         <v>3</v>
@@ -16530,7 +16530,9 @@
       <c r="B2000" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2000" s="6"/>
+      <c r="C2000" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2001" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2001" s="3" t="s">
@@ -16541,15 +16543,21 @@
       <c r="B2002" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C2002" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2003" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C2003" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2004" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2004" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B2004" s="7" t="s">
         <v>3</v>
@@ -16610,9 +16618,7 @@
       <c r="B2011" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2011" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2011" s="6"/>
     </row>
     <row r="2012" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2012" s="3" t="s">
@@ -16628,13 +16634,10 @@
       <c r="B2014" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2014" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2015" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2015" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B2015" s="7" t="s">
         <v>3</v>
@@ -16703,9 +16706,6 @@
       <c r="B2023" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2023" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2024" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2024" s="3" t="s">
@@ -16722,7 +16722,7 @@
     </row>
     <row r="2026" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2026" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B2026" s="7" t="s">
         <v>3</v>
@@ -16791,6 +16791,9 @@
       <c r="B2034" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2034" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2035" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2035" s="3" t="s">
@@ -16807,7 +16810,7 @@
     </row>
     <row r="2037" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2037" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B2037" s="7" t="s">
         <v>3</v>
@@ -16886,10 +16889,13 @@
       <c r="B2047" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C2047" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2048" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2048" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B2048" s="7" t="s">
         <v>3</v>
@@ -16968,13 +16974,10 @@
       <c r="B2058" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2058" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2059" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2059" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B2059" s="7" t="s">
         <v>3</v>
@@ -17043,9 +17046,6 @@
       <c r="B2067" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2067" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2068" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2068" s="3" t="s">
@@ -17062,7 +17062,7 @@
     </row>
     <row r="2070" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2070" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B2070" s="7" t="s">
         <v>3</v>
@@ -17083,19 +17083,25 @@
       <c r="B2072" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2072" s="6"/>
+      <c r="C2072" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2073" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2073" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2073" s="6"/>
+      <c r="C2073" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2074" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2074" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2074" s="6"/>
+      <c r="C2074" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2075" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2075" s="3" t="s">
@@ -17117,12 +17123,17 @@
       <c r="B2077" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2077" s="6"/>
+      <c r="C2077" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2078" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2078" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2078" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2079" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2079" s="3" t="s">
@@ -17133,10 +17144,13 @@
       <c r="B2080" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C2080" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2081" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2081" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B2081" s="7" t="s">
         <v>3</v>
@@ -17157,25 +17171,19 @@
       <c r="B2083" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2083" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2083" s="6"/>
     </row>
     <row r="2084" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2084" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2084" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2084" s="6"/>
     </row>
     <row r="2085" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2085" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2085" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2085" s="6"/>
     </row>
     <row r="2086" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2086" s="3" t="s">
@@ -17197,17 +17205,12 @@
       <c r="B2088" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2088" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2088" s="6"/>
     </row>
     <row r="2089" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2089" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2089" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2090" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2090" s="3" t="s">
@@ -17218,13 +17221,10 @@
       <c r="B2091" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2091" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2092" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2092" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B2092" s="7" t="s">
         <v>3</v>
@@ -17312,7 +17312,7 @@
     </row>
     <row r="2103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2103" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B2103" s="7" t="s">
         <v>3</v>
@@ -17381,6 +17381,9 @@
       <c r="B2111" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2111" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2112" s="3" t="s">
@@ -17397,7 +17400,7 @@
     </row>
     <row r="2114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2114" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B2114" s="7" t="s">
         <v>3</v>
@@ -17466,9 +17469,6 @@
       <c r="B2122" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2122" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2123" s="3" t="s">
@@ -17476,19 +17476,19 @@
       </c>
     </row>
     <row r="2124" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2124" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B2124" s="7" t="s">
-        <v>3</v>
+      <c r="B2124" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C2124" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2125" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2125" s="3" t="s">
-        <v>4</v>
+      <c r="A2125" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B2125" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2125" s="5" t="s">
         <v>13</v>
@@ -17496,7 +17496,7 @@
     </row>
     <row r="2126" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2126" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2126" s="5" t="s">
         <v>13</v>
@@ -17504,7 +17504,7 @@
     </row>
     <row r="2127" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2127" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2127" s="5" t="s">
         <v>13</v>
@@ -17512,7 +17512,7 @@
     </row>
     <row r="2128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2128" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2128" s="5" t="s">
         <v>13</v>
@@ -17520,7 +17520,7 @@
     </row>
     <row r="2129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2129" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2129" s="5" t="s">
         <v>13</v>
@@ -17528,7 +17528,7 @@
     </row>
     <row r="2130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2130" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2130" s="5" t="s">
         <v>13</v>
@@ -17536,7 +17536,7 @@
     </row>
     <row r="2131" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2131" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2131" s="5" t="s">
         <v>13</v>
@@ -17544,7 +17544,7 @@
     </row>
     <row r="2132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2132" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2132" s="5" t="s">
         <v>13</v>
@@ -17552,23 +17552,23 @@
     </row>
     <row r="2133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2133" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C2133" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2134" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2134" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B2134" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2134" s="5" t="s">
-        <v>13</v>
+      <c r="B2134" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2135" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2135" s="3" t="s">
-        <v>4</v>
+      <c r="A2135" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B2135" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2135" s="5" t="s">
         <v>13</v>
@@ -17576,7 +17576,7 @@
     </row>
     <row r="2136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2136" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2136" s="5" t="s">
         <v>13</v>
@@ -17584,7 +17584,7 @@
     </row>
     <row r="2137" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2137" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2137" s="5" t="s">
         <v>13</v>
@@ -17592,7 +17592,7 @@
     </row>
     <row r="2138" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2138" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2138" s="5" t="s">
         <v>13</v>
@@ -17600,7 +17600,7 @@
     </row>
     <row r="2139" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2139" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2139" s="5" t="s">
         <v>13</v>
@@ -17608,7 +17608,7 @@
     </row>
     <row r="2140" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2140" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2140" s="5" t="s">
         <v>13</v>
@@ -17616,7 +17616,7 @@
     </row>
     <row r="2141" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2141" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2141" s="5" t="s">
         <v>13</v>
@@ -17624,16 +17624,104 @@
     </row>
     <row r="2142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2142" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C2142" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2143" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C2143" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2144" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2144" s="3">
+      <c r="B2144" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2145" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2145" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B2145" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2145" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2146" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2146" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2146" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2147" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2147" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2147" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2148" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2148" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2148" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2149" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2149" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2149" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2150" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2150" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2150" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2151" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2151" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2151" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2152" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2152" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2152" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2153" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2153" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2154" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2154" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2155" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2155" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47787811-4B03-445F-85C1-2BF6F106884D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3F97D6-3656-4800-A4CF-D6388F61E174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4110" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4131" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2155"/>
+  <dimension ref="A1:C2166"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6191,7 +6191,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6279,7 +6279,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6367,7 +6367,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6455,7 +6455,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6543,7 +6543,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6631,7 +6631,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6719,7 +6719,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6807,7 +6807,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6895,7 +6895,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6983,7 +6983,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7071,7 +7071,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7159,7 +7159,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7247,7 +7247,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7335,7 +7335,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7423,7 +7423,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7511,7 +7511,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7588,9 +7588,6 @@
       <c r="B891" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C891" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="892" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B892" s="3" t="s">
@@ -7602,7 +7599,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7679,6 +7676,9 @@
       <c r="B902" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C902" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="903" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B903" s="3" t="s">
@@ -7690,7 +7690,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7778,7 +7778,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7866,7 +7866,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -7954,7 +7954,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8042,7 +8042,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8119,9 +8119,6 @@
       <c r="B957" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C957" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="958" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B958" s="3" t="s">
@@ -8133,7 +8130,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8224,7 +8221,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8315,7 +8312,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8406,7 +8403,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8483,6 +8480,9 @@
       <c r="B1001" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1001" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1002" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1002" s="3" t="s">
@@ -8494,7 +8494,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8571,9 +8571,6 @@
       <c r="B1012" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1012" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1013" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1013" s="3" t="s">
@@ -8585,7 +8582,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8676,7 +8673,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8767,7 +8764,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8858,7 +8855,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -8949,7 +8946,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9040,7 +9037,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9131,7 +9128,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9222,7 +9219,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9313,7 +9310,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9404,7 +9401,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9495,7 +9492,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9586,7 +9583,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9677,7 +9674,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9768,7 +9765,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9859,7 +9856,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -9950,7 +9947,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10041,7 +10038,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10132,7 +10129,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10223,7 +10220,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10314,7 +10311,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10405,7 +10402,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10496,7 +10493,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10587,7 +10584,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10678,7 +10675,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10769,7 +10766,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10860,7 +10857,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10951,7 +10948,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11042,7 +11039,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11133,7 +11130,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11224,7 +11221,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11315,7 +11312,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11406,7 +11403,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11497,7 +11494,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11574,6 +11571,9 @@
       <c r="B1375" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1375" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1376" s="3" t="s">
@@ -11585,7 +11585,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11662,9 +11662,6 @@
       <c r="B1386" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1386" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1387" s="3" t="s">
@@ -11676,7 +11673,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11767,7 +11764,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11858,7 +11855,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11949,7 +11946,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12040,7 +12037,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12131,7 +12128,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12222,7 +12219,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12313,7 +12310,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12404,7 +12401,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12495,7 +12492,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12564,6 +12561,9 @@
       <c r="B1495" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1495" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1496" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1496" s="3" t="s">
@@ -12583,7 +12583,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12652,9 +12652,6 @@
       <c r="B1506" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1506" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1507" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1507" s="3" t="s">
@@ -12674,7 +12671,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12751,6 +12748,9 @@
       <c r="B1518" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1518" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1519" s="3" t="s">
@@ -12762,7 +12762,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12831,6 +12831,9 @@
       <c r="B1528" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1528" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1529" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1529" s="3" t="s">
@@ -12847,7 +12850,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12916,9 +12919,6 @@
       <c r="B1539" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1539" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1540" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1540" s="3" t="s">
@@ -12935,7 +12935,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -13004,6 +13004,9 @@
       <c r="B1550" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1550" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1551" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1551" s="3" t="s">
@@ -13020,7 +13023,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13089,9 +13092,6 @@
       <c r="B1561" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1561" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1562" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1562" s="3" t="s">
@@ -13108,7 +13108,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13196,7 +13196,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13284,7 +13284,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13353,6 +13353,9 @@
       <c r="B1594" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1594" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1595" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1595" s="3" t="s">
@@ -13369,7 +13372,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13454,7 +13457,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13539,7 +13542,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13624,7 +13627,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13709,7 +13712,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13794,7 +13797,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13879,7 +13882,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13964,7 +13967,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14049,7 +14052,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14134,7 +14137,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14219,7 +14222,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14304,7 +14307,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14373,9 +14376,6 @@
       <c r="B1726" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1726" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1727" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1727" s="3" t="s">
@@ -14392,7 +14392,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14461,6 +14461,9 @@
       <c r="B1737" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1737" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1738" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1738" s="3" t="s">
@@ -14477,7 +14480,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14562,7 +14565,7 @@
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14647,7 +14650,7 @@
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14716,9 +14719,6 @@
       <c r="B1770" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1770" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1771" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1771" s="3" t="s">
@@ -14735,7 +14735,7 @@
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14823,7 +14823,7 @@
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14892,6 +14892,9 @@
       <c r="B1792" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1792" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1793" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1793" s="3" t="s">
@@ -14908,7 +14911,7 @@
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14993,7 +14996,7 @@
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15078,7 +15081,7 @@
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15163,7 +15166,7 @@
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15232,9 +15235,6 @@
       <c r="B1836" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1836" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1837" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1837" s="3" t="s">
@@ -15251,7 +15251,7 @@
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15339,7 +15339,7 @@
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15416,9 +15416,6 @@
       <c r="B1859" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1859" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1860" s="3" t="s">
@@ -15430,7 +15427,7 @@
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15507,6 +15504,9 @@
       <c r="B1870" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1870" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1871" s="3" t="s">
@@ -15518,7 +15518,7 @@
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1872" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1872" s="7" t="s">
         <v>3</v>
@@ -15606,7 +15606,7 @@
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1883" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1883" s="7" t="s">
         <v>3</v>
@@ -15694,7 +15694,7 @@
     </row>
     <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1894" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1894" s="7" t="s">
         <v>3</v>
@@ -15782,7 +15782,7 @@
     </row>
     <row r="1905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1905" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1905" s="7" t="s">
         <v>3</v>
@@ -15870,7 +15870,7 @@
     </row>
     <row r="1916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1916" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1916" s="7" t="s">
         <v>3</v>
@@ -15939,6 +15939,9 @@
       <c r="B1924" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1924" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1925" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1925" s="3" t="s">
@@ -15955,7 +15958,7 @@
     </row>
     <row r="1927" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1927" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1927" s="7" t="s">
         <v>3</v>
@@ -16016,7 +16019,9 @@
       <c r="B1934" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1934" s="6"/>
+      <c r="C1934" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1935" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1935" s="3" t="s">
@@ -16032,10 +16037,13 @@
       <c r="B1937" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1937" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1938" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1938" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1938" s="7" t="s">
         <v>3</v>
@@ -16096,17 +16104,12 @@
       <c r="B1945" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1945" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1945" s="6"/>
     </row>
     <row r="1946" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1946" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1946" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1947" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1947" s="3" t="s">
@@ -16117,13 +16120,10 @@
       <c r="B1948" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1948" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1949" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1949" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1949" s="7" t="s">
         <v>3</v>
@@ -16211,7 +16211,7 @@
     </row>
     <row r="1960" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1960" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1960" s="7" t="s">
         <v>3</v>
@@ -16299,7 +16299,7 @@
     </row>
     <row r="1971" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1971" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1971" s="7" t="s">
         <v>3</v>
@@ -16368,6 +16368,9 @@
       <c r="B1979" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1979" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1980" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1980" s="3" t="s">
@@ -16384,7 +16387,7 @@
     </row>
     <row r="1982" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1982" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1982" s="7" t="s">
         <v>3</v>
@@ -16469,7 +16472,7 @@
     </row>
     <row r="1993" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1993" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B1993" s="7" t="s">
         <v>3</v>
@@ -16543,9 +16546,6 @@
       <c r="B2002" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2002" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2003" s="3" t="s">
@@ -16557,7 +16557,7 @@
     </row>
     <row r="2004" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2004" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B2004" s="7" t="s">
         <v>3</v>
@@ -16618,7 +16618,9 @@
       <c r="B2011" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2011" s="6"/>
+      <c r="C2011" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2012" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2012" s="3" t="s">
@@ -16629,15 +16631,21 @@
       <c r="B2013" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C2013" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2014" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C2014" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2015" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2015" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B2015" s="7" t="s">
         <v>3</v>
@@ -16698,9 +16706,7 @@
       <c r="B2022" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2022" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2022" s="6"/>
     </row>
     <row r="2023" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2023" s="3" t="s">
@@ -16716,13 +16722,10 @@
       <c r="B2025" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2025" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2026" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2026" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B2026" s="7" t="s">
         <v>3</v>
@@ -16791,9 +16794,6 @@
       <c r="B2034" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2034" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2035" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2035" s="3" t="s">
@@ -16810,7 +16810,7 @@
     </row>
     <row r="2037" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2037" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B2037" s="7" t="s">
         <v>3</v>
@@ -16879,6 +16879,9 @@
       <c r="B2045" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2045" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2046" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2046" s="3" t="s">
@@ -16895,7 +16898,7 @@
     </row>
     <row r="2048" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2048" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B2048" s="7" t="s">
         <v>3</v>
@@ -16974,10 +16977,13 @@
       <c r="B2058" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C2058" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2059" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2059" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B2059" s="7" t="s">
         <v>3</v>
@@ -17056,13 +17062,10 @@
       <c r="B2069" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2069" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2070" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2070" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B2070" s="7" t="s">
         <v>3</v>
@@ -17131,9 +17134,6 @@
       <c r="B2078" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2078" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2079" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2079" s="3" t="s">
@@ -17150,7 +17150,7 @@
     </row>
     <row r="2081" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2081" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B2081" s="7" t="s">
         <v>3</v>
@@ -17171,19 +17171,25 @@
       <c r="B2083" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2083" s="6"/>
+      <c r="C2083" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2084" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2084" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2084" s="6"/>
+      <c r="C2084" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2085" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2085" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2085" s="6"/>
+      <c r="C2085" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2086" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2086" s="3" t="s">
@@ -17205,12 +17211,17 @@
       <c r="B2088" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2088" s="6"/>
+      <c r="C2088" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2089" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2089" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2089" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2090" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2090" s="3" t="s">
@@ -17221,10 +17232,13 @@
       <c r="B2091" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C2091" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2092" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2092" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B2092" s="7" t="s">
         <v>3</v>
@@ -17245,25 +17259,19 @@
       <c r="B2094" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2094" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2094" s="6"/>
     </row>
     <row r="2095" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2095" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2095" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2095" s="6"/>
     </row>
     <row r="2096" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2096" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2096" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2096" s="6"/>
     </row>
     <row r="2097" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2097" s="3" t="s">
@@ -17285,17 +17293,12 @@
       <c r="B2099" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2099" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2099" s="6"/>
     </row>
     <row r="2100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2100" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2100" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2101" s="3" t="s">
@@ -17306,13 +17309,10 @@
       <c r="B2102" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2102" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2103" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B2103" s="7" t="s">
         <v>3</v>
@@ -17400,7 +17400,7 @@
     </row>
     <row r="2114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2114" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B2114" s="7" t="s">
         <v>3</v>
@@ -17469,6 +17469,9 @@
       <c r="B2122" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2122" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2123" s="3" t="s">
@@ -17485,7 +17488,7 @@
     </row>
     <row r="2125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2125" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B2125" s="7" t="s">
         <v>3</v>
@@ -17554,9 +17557,6 @@
       <c r="B2133" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2133" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2134" s="3" t="s">
@@ -17564,19 +17564,19 @@
       </c>
     </row>
     <row r="2135" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2135" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B2135" s="7" t="s">
-        <v>3</v>
+      <c r="B2135" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C2135" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2136" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2136" s="3" t="s">
-        <v>4</v>
+      <c r="A2136" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B2136" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2136" s="5" t="s">
         <v>13</v>
@@ -17584,7 +17584,7 @@
     </row>
     <row r="2137" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2137" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2137" s="5" t="s">
         <v>13</v>
@@ -17592,7 +17592,7 @@
     </row>
     <row r="2138" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2138" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2138" s="5" t="s">
         <v>13</v>
@@ -17600,7 +17600,7 @@
     </row>
     <row r="2139" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2139" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2139" s="5" t="s">
         <v>13</v>
@@ -17608,7 +17608,7 @@
     </row>
     <row r="2140" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2140" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2140" s="5" t="s">
         <v>13</v>
@@ -17616,7 +17616,7 @@
     </row>
     <row r="2141" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2141" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2141" s="5" t="s">
         <v>13</v>
@@ -17624,7 +17624,7 @@
     </row>
     <row r="2142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2142" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2142" s="5" t="s">
         <v>13</v>
@@ -17632,7 +17632,7 @@
     </row>
     <row r="2143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2143" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2143" s="5" t="s">
         <v>13</v>
@@ -17640,23 +17640,23 @@
     </row>
     <row r="2144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2144" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C2144" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2145" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2145" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B2145" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2145" s="5" t="s">
-        <v>13</v>
+      <c r="B2145" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2146" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2146" s="3" t="s">
-        <v>4</v>
+      <c r="A2146" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B2146" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2146" s="5" t="s">
         <v>13</v>
@@ -17664,7 +17664,7 @@
     </row>
     <row r="2147" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2147" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2147" s="5" t="s">
         <v>13</v>
@@ -17672,7 +17672,7 @@
     </row>
     <row r="2148" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2148" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2148" s="5" t="s">
         <v>13</v>
@@ -17680,7 +17680,7 @@
     </row>
     <row r="2149" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2149" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2149" s="5" t="s">
         <v>13</v>
@@ -17688,7 +17688,7 @@
     </row>
     <row r="2150" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2150" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2150" s="5" t="s">
         <v>13</v>
@@ -17696,7 +17696,7 @@
     </row>
     <row r="2151" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2151" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2151" s="5" t="s">
         <v>13</v>
@@ -17704,7 +17704,7 @@
     </row>
     <row r="2152" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2152" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2152" s="5" t="s">
         <v>13</v>
@@ -17712,16 +17712,104 @@
     </row>
     <row r="2153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2153" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C2153" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2154" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C2154" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2155" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2155" s="3">
+      <c r="B2155" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2156" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2156" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B2156" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2156" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2157" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2157" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2157" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2158" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2158" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2158" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2159" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2159" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2159" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2160" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2160" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2160" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2161" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2161" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2161" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2162" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2162" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2162" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2163" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2163" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2163" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2164" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2164" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2165" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2165" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2166" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2166" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3F97D6-3656-4800-A4CF-D6388F61E174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{733A9C1E-37AC-4197-AAEC-595BFEF78B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4131" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4152" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2166"/>
+  <dimension ref="A1:C2177"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6191,7 +6191,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6279,7 +6279,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6367,7 +6367,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6455,7 +6455,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6543,7 +6543,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6631,7 +6631,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6719,7 +6719,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6807,7 +6807,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6895,7 +6895,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6983,7 +6983,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7071,7 +7071,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7159,7 +7159,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7247,7 +7247,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7335,7 +7335,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7423,7 +7423,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7511,7 +7511,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7599,7 +7599,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7676,9 +7676,6 @@
       <c r="B902" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C902" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="903" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B903" s="3" t="s">
@@ -7690,7 +7687,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7767,6 +7764,9 @@
       <c r="B913" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C913" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="914" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B914" s="3" t="s">
@@ -7778,7 +7778,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7866,7 +7866,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -7954,7 +7954,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8042,7 +8042,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8130,7 +8130,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8207,9 +8207,6 @@
       <c r="B968" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C968" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="969" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B969" s="3" t="s">
@@ -8221,7 +8218,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8312,7 +8309,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8403,7 +8400,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8494,7 +8491,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8571,6 +8568,9 @@
       <c r="B1012" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1012" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1013" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1013" s="3" t="s">
@@ -8582,7 +8582,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8659,9 +8659,6 @@
       <c r="B1023" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1023" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1024" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1024" s="3" t="s">
@@ -8673,7 +8670,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8764,7 +8761,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8855,7 +8852,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -8946,7 +8943,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9037,7 +9034,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9128,7 +9125,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9219,7 +9216,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9310,7 +9307,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9401,7 +9398,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9492,7 +9489,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9583,7 +9580,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9674,7 +9671,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9765,7 +9762,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9856,7 +9853,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -9947,7 +9944,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10038,7 +10035,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10129,7 +10126,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10220,7 +10217,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10311,7 +10308,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10402,7 +10399,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10493,7 +10490,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10584,7 +10581,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10675,7 +10672,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10766,7 +10763,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10857,7 +10854,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10948,7 +10945,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11039,7 +11036,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11130,7 +11127,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11221,7 +11218,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11312,7 +11309,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11403,7 +11400,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11494,7 +11491,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11585,7 +11582,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11662,6 +11659,9 @@
       <c r="B1386" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1386" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1387" s="3" t="s">
@@ -11673,7 +11673,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11750,9 +11750,6 @@
       <c r="B1397" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1397" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1398" s="3" t="s">
@@ -11764,7 +11761,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11855,7 +11852,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11946,7 +11943,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12037,7 +12034,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12128,7 +12125,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12219,7 +12216,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12310,7 +12307,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12401,7 +12398,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12492,7 +12489,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12583,7 +12580,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12652,6 +12649,9 @@
       <c r="B1506" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1506" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1507" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1507" s="3" t="s">
@@ -12671,7 +12671,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12740,9 +12740,6 @@
       <c r="B1517" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1517" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1518" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1518" s="3" t="s">
@@ -12762,7 +12759,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12839,6 +12836,9 @@
       <c r="B1529" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1529" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1530" s="3" t="s">
@@ -12850,7 +12850,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12919,6 +12919,9 @@
       <c r="B1539" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1539" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1540" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1540" s="3" t="s">
@@ -12935,7 +12938,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -13004,9 +13007,6 @@
       <c r="B1550" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1550" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1551" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1551" s="3" t="s">
@@ -13023,7 +13023,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13092,6 +13092,9 @@
       <c r="B1561" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1561" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1562" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1562" s="3" t="s">
@@ -13108,7 +13111,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13177,9 +13180,6 @@
       <c r="B1572" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1572" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1573" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1573" s="3" t="s">
@@ -13196,7 +13196,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13284,7 +13284,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13372,7 +13372,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13441,6 +13441,9 @@
       <c r="B1605" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1605" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1606" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1606" s="3" t="s">
@@ -13457,7 +13460,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13542,7 +13545,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13627,7 +13630,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13712,7 +13715,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13797,7 +13800,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13882,7 +13885,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13967,7 +13970,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14052,7 +14055,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14137,7 +14140,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14222,7 +14225,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14307,7 +14310,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14392,7 +14395,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14461,9 +14464,6 @@
       <c r="B1737" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1737" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1738" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1738" s="3" t="s">
@@ -14480,7 +14480,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14549,6 +14549,9 @@
       <c r="B1748" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1748" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1749" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1749" s="3" t="s">
@@ -14565,7 +14568,7 @@
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14650,7 +14653,7 @@
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14735,7 +14738,7 @@
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14804,9 +14807,6 @@
       <c r="B1781" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1781" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1782" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1782" s="3" t="s">
@@ -14823,7 +14823,7 @@
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14911,7 +14911,7 @@
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14980,6 +14980,9 @@
       <c r="B1803" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1803" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1804" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1804" s="3" t="s">
@@ -14996,7 +14999,7 @@
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15081,7 +15084,7 @@
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15166,7 +15169,7 @@
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15251,7 +15254,7 @@
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15320,9 +15323,6 @@
       <c r="B1847" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1847" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1848" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1848" s="3" t="s">
@@ -15339,7 +15339,7 @@
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15427,7 +15427,7 @@
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15504,9 +15504,6 @@
       <c r="B1870" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1870" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1871" s="3" t="s">
@@ -15518,7 +15515,7 @@
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1872" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1872" s="7" t="s">
         <v>3</v>
@@ -15595,6 +15592,9 @@
       <c r="B1881" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1881" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1882" s="3" t="s">
@@ -15606,7 +15606,7 @@
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1883" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1883" s="7" t="s">
         <v>3</v>
@@ -15694,7 +15694,7 @@
     </row>
     <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1894" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1894" s="7" t="s">
         <v>3</v>
@@ -15782,7 +15782,7 @@
     </row>
     <row r="1905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1905" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1905" s="7" t="s">
         <v>3</v>
@@ -15870,7 +15870,7 @@
     </row>
     <row r="1916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1916" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1916" s="7" t="s">
         <v>3</v>
@@ -15958,7 +15958,7 @@
     </row>
     <row r="1927" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1927" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1927" s="7" t="s">
         <v>3</v>
@@ -16027,6 +16027,9 @@
       <c r="B1935" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1935" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1936" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1936" s="3" t="s">
@@ -16043,7 +16046,7 @@
     </row>
     <row r="1938" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1938" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1938" s="7" t="s">
         <v>3</v>
@@ -16104,7 +16107,9 @@
       <c r="B1945" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1945" s="6"/>
+      <c r="C1945" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1946" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1946" s="3" t="s">
@@ -16120,10 +16125,13 @@
       <c r="B1948" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1948" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1949" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1949" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1949" s="7" t="s">
         <v>3</v>
@@ -16184,17 +16192,12 @@
       <c r="B1956" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1956" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1956" s="6"/>
     </row>
     <row r="1957" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1957" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1957" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1958" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1958" s="3" t="s">
@@ -16205,13 +16208,10 @@
       <c r="B1959" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1959" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1960" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1960" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1960" s="7" t="s">
         <v>3</v>
@@ -16299,7 +16299,7 @@
     </row>
     <row r="1971" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1971" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1971" s="7" t="s">
         <v>3</v>
@@ -16387,7 +16387,7 @@
     </row>
     <row r="1982" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1982" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1982" s="7" t="s">
         <v>3</v>
@@ -16456,6 +16456,9 @@
       <c r="B1990" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1990" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1991" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1991" s="3" t="s">
@@ -16472,7 +16475,7 @@
     </row>
     <row r="1993" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1993" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B1993" s="7" t="s">
         <v>3</v>
@@ -16557,7 +16560,7 @@
     </row>
     <row r="2004" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2004" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B2004" s="7" t="s">
         <v>3</v>
@@ -16631,9 +16634,6 @@
       <c r="B2013" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2013" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2014" s="3" t="s">
@@ -16645,7 +16645,7 @@
     </row>
     <row r="2015" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2015" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B2015" s="7" t="s">
         <v>3</v>
@@ -16706,7 +16706,9 @@
       <c r="B2022" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2022" s="6"/>
+      <c r="C2022" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2023" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2023" s="3" t="s">
@@ -16717,15 +16719,21 @@
       <c r="B2024" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C2024" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2025" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C2025" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2026" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2026" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B2026" s="7" t="s">
         <v>3</v>
@@ -16786,9 +16794,7 @@
       <c r="B2033" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2033" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2033" s="6"/>
     </row>
     <row r="2034" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2034" s="3" t="s">
@@ -16804,13 +16810,10 @@
       <c r="B2036" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2036" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2037" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2037" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B2037" s="7" t="s">
         <v>3</v>
@@ -16879,9 +16882,6 @@
       <c r="B2045" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2045" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2046" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2046" s="3" t="s">
@@ -16898,7 +16898,7 @@
     </row>
     <row r="2048" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2048" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B2048" s="7" t="s">
         <v>3</v>
@@ -16967,6 +16967,9 @@
       <c r="B2056" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2056" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2057" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2057" s="3" t="s">
@@ -16983,7 +16986,7 @@
     </row>
     <row r="2059" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2059" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B2059" s="7" t="s">
         <v>3</v>
@@ -17062,10 +17065,13 @@
       <c r="B2069" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C2069" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2070" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2070" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B2070" s="7" t="s">
         <v>3</v>
@@ -17144,13 +17150,10 @@
       <c r="B2080" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2080" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2081" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2081" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B2081" s="7" t="s">
         <v>3</v>
@@ -17219,9 +17222,6 @@
       <c r="B2089" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2089" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2090" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2090" s="3" t="s">
@@ -17238,7 +17238,7 @@
     </row>
     <row r="2092" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2092" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B2092" s="7" t="s">
         <v>3</v>
@@ -17259,19 +17259,25 @@
       <c r="B2094" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2094" s="6"/>
+      <c r="C2094" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2095" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2095" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2095" s="6"/>
+      <c r="C2095" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2096" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2096" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2096" s="6"/>
+      <c r="C2096" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2097" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2097" s="3" t="s">
@@ -17293,12 +17299,17 @@
       <c r="B2099" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2099" s="6"/>
+      <c r="C2099" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2100" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2100" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2100" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2101" s="3" t="s">
@@ -17309,10 +17320,13 @@
       <c r="B2102" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C2102" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2103" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B2103" s="7" t="s">
         <v>3</v>
@@ -17333,25 +17347,19 @@
       <c r="B2105" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2105" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2105" s="6"/>
     </row>
     <row r="2106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2106" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2106" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2106" s="6"/>
     </row>
     <row r="2107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2107" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2107" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2107" s="6"/>
     </row>
     <row r="2108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2108" s="3" t="s">
@@ -17373,17 +17381,12 @@
       <c r="B2110" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2110" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2110" s="6"/>
     </row>
     <row r="2111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2111" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2111" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2112" s="3" t="s">
@@ -17394,13 +17397,10 @@
       <c r="B2113" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2113" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2114" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B2114" s="7" t="s">
         <v>3</v>
@@ -17488,7 +17488,7 @@
     </row>
     <row r="2125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2125" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B2125" s="7" t="s">
         <v>3</v>
@@ -17557,6 +17557,9 @@
       <c r="B2133" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2133" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2134" s="3" t="s">
@@ -17573,7 +17576,7 @@
     </row>
     <row r="2136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2136" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B2136" s="7" t="s">
         <v>3</v>
@@ -17642,9 +17645,6 @@
       <c r="B2144" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2144" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2145" s="3" t="s">
@@ -17652,19 +17652,19 @@
       </c>
     </row>
     <row r="2146" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2146" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B2146" s="7" t="s">
-        <v>3</v>
+      <c r="B2146" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C2146" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2147" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2147" s="3" t="s">
-        <v>4</v>
+      <c r="A2147" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B2147" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2147" s="5" t="s">
         <v>13</v>
@@ -17672,7 +17672,7 @@
     </row>
     <row r="2148" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2148" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2148" s="5" t="s">
         <v>13</v>
@@ -17680,7 +17680,7 @@
     </row>
     <row r="2149" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2149" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2149" s="5" t="s">
         <v>13</v>
@@ -17688,7 +17688,7 @@
     </row>
     <row r="2150" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2150" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2150" s="5" t="s">
         <v>13</v>
@@ -17696,7 +17696,7 @@
     </row>
     <row r="2151" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2151" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2151" s="5" t="s">
         <v>13</v>
@@ -17704,7 +17704,7 @@
     </row>
     <row r="2152" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2152" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2152" s="5" t="s">
         <v>13</v>
@@ -17712,7 +17712,7 @@
     </row>
     <row r="2153" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2153" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2153" s="5" t="s">
         <v>13</v>
@@ -17720,7 +17720,7 @@
     </row>
     <row r="2154" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2154" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2154" s="5" t="s">
         <v>13</v>
@@ -17728,23 +17728,23 @@
     </row>
     <row r="2155" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2155" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C2155" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2156" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2156" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B2156" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2156" s="5" t="s">
-        <v>13</v>
+      <c r="B2156" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2157" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2157" s="3" t="s">
-        <v>4</v>
+      <c r="A2157" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B2157" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2157" s="5" t="s">
         <v>13</v>
@@ -17752,7 +17752,7 @@
     </row>
     <row r="2158" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2158" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2158" s="5" t="s">
         <v>13</v>
@@ -17760,7 +17760,7 @@
     </row>
     <row r="2159" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2159" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2159" s="5" t="s">
         <v>13</v>
@@ -17768,48 +17768,136 @@
     </row>
     <row r="2160" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2160" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2160" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2161" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2161" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2161" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2161" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2162" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2162" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2162" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2162" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2163" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2163" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2163" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2163" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2164" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="2164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2164" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2165" spans="2:3" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="C2164" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2165" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2166" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B2166" s="3">
+        <v>11</v>
+      </c>
+      <c r="C2165" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2166" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2166" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2167" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2167" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B2167" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2167" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2168" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2168" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2168" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2169" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2169" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2169" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2170" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2170" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2170" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2171" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2171" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2171" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2172" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2172" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2172" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2173" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2173" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2173" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2174" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2174" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2174" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2175" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2175" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2176" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2176" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2177" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B2177" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{733A9C1E-37AC-4197-AAEC-595BFEF78B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B45C3984-88AA-4C6D-A68D-9CD932E7DE63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4152" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4173" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2177"/>
+  <dimension ref="A1:C2188"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6191,7 +6191,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6279,7 +6279,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6367,7 +6367,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6455,7 +6455,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6543,7 +6543,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6631,7 +6631,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6719,7 +6719,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6807,7 +6807,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6895,7 +6895,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6983,7 +6983,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7071,7 +7071,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7159,7 +7159,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7247,7 +7247,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7335,7 +7335,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7423,7 +7423,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7511,7 +7511,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7599,7 +7599,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7687,7 +7687,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7764,9 +7764,6 @@
       <c r="B913" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C913" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="914" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B914" s="3" t="s">
@@ -7778,7 +7775,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7855,6 +7852,9 @@
       <c r="B924" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C924" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="925" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B925" s="3" t="s">
@@ -7866,7 +7866,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -7954,7 +7954,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8042,7 +8042,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8130,7 +8130,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8218,7 +8218,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8295,9 +8295,6 @@
       <c r="B979" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C979" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="980" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B980" s="3" t="s">
@@ -8309,7 +8306,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8400,7 +8397,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8491,7 +8488,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8582,7 +8579,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8659,6 +8656,9 @@
       <c r="B1023" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1023" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1024" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1024" s="3" t="s">
@@ -8670,7 +8670,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8747,9 +8747,6 @@
       <c r="B1034" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1034" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1035" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1035" s="3" t="s">
@@ -8761,7 +8758,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8852,7 +8849,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -8943,7 +8940,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9034,7 +9031,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9125,7 +9122,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9216,7 +9213,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9307,7 +9304,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9398,7 +9395,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9489,7 +9486,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9580,7 +9577,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9671,7 +9668,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9762,7 +9759,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9853,7 +9850,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -9944,7 +9941,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10035,7 +10032,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10126,7 +10123,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10217,7 +10214,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10308,7 +10305,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10399,7 +10396,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10490,7 +10487,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10581,7 +10578,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10672,7 +10669,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10763,7 +10760,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10854,7 +10851,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10945,7 +10942,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11036,7 +11033,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11127,7 +11124,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11218,7 +11215,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11309,7 +11306,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11400,7 +11397,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11491,7 +11488,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11582,7 +11579,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11673,7 +11670,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11750,6 +11747,9 @@
       <c r="B1397" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1397" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1398" s="3" t="s">
@@ -11761,7 +11761,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11838,9 +11838,6 @@
       <c r="B1408" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1408" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1409" s="3" t="s">
@@ -11852,7 +11849,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11943,7 +11940,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12034,7 +12031,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12125,7 +12122,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12216,7 +12213,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12307,7 +12304,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12398,7 +12395,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12489,7 +12486,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12580,7 +12577,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12671,7 +12668,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12740,6 +12737,9 @@
       <c r="B1517" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1517" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1518" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1518" s="3" t="s">
@@ -12759,7 +12759,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12828,9 +12828,6 @@
       <c r="B1528" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1528" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1529" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1529" s="3" t="s">
@@ -12850,7 +12847,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12927,6 +12924,9 @@
       <c r="B1540" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1540" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1541" s="3" t="s">
@@ -12938,7 +12938,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -13007,6 +13007,9 @@
       <c r="B1550" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1550" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1551" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1551" s="3" t="s">
@@ -13023,7 +13026,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13092,9 +13095,6 @@
       <c r="B1561" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1561" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1562" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1562" s="3" t="s">
@@ -13111,7 +13111,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13180,6 +13180,9 @@
       <c r="B1572" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1572" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1573" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1573" s="3" t="s">
@@ -13196,7 +13199,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13265,9 +13268,6 @@
       <c r="B1583" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1583" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1584" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1584" s="3" t="s">
@@ -13284,7 +13284,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13372,7 +13372,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13460,7 +13460,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13529,6 +13529,9 @@
       <c r="B1616" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1616" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1617" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1617" s="3" t="s">
@@ -13545,7 +13548,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13630,7 +13633,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13715,7 +13718,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13800,7 +13803,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13885,7 +13888,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13970,7 +13973,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14055,7 +14058,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14140,7 +14143,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14225,7 +14228,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14310,7 +14313,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14395,7 +14398,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14480,7 +14483,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14549,9 +14552,6 @@
       <c r="B1748" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1748" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1749" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1749" s="3" t="s">
@@ -14568,7 +14568,7 @@
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14637,6 +14637,9 @@
       <c r="B1759" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1759" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1760" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1760" s="3" t="s">
@@ -14653,7 +14656,7 @@
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14738,7 +14741,7 @@
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14823,7 +14826,7 @@
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14892,9 +14895,6 @@
       <c r="B1792" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1792" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1793" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1793" s="3" t="s">
@@ -14911,7 +14911,7 @@
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14999,7 +14999,7 @@
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15068,6 +15068,9 @@
       <c r="B1814" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1814" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1815" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1815" s="3" t="s">
@@ -15084,7 +15087,7 @@
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15169,7 +15172,7 @@
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15254,7 +15257,7 @@
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15339,7 +15342,7 @@
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15408,9 +15411,6 @@
       <c r="B1858" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1858" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1859" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1859" s="3" t="s">
@@ -15427,7 +15427,7 @@
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15515,7 +15515,7 @@
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1872" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1872" s="7" t="s">
         <v>3</v>
@@ -15592,9 +15592,6 @@
       <c r="B1881" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1881" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1882" s="3" t="s">
@@ -15606,7 +15603,7 @@
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1883" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1883" s="7" t="s">
         <v>3</v>
@@ -15683,6 +15680,9 @@
       <c r="B1892" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1892" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1893" s="3" t="s">
@@ -15694,7 +15694,7 @@
     </row>
     <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1894" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1894" s="7" t="s">
         <v>3</v>
@@ -15782,7 +15782,7 @@
     </row>
     <row r="1905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1905" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1905" s="7" t="s">
         <v>3</v>
@@ -15870,7 +15870,7 @@
     </row>
     <row r="1916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1916" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1916" s="7" t="s">
         <v>3</v>
@@ -15958,7 +15958,7 @@
     </row>
     <row r="1927" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1927" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1927" s="7" t="s">
         <v>3</v>
@@ -16046,7 +16046,7 @@
     </row>
     <row r="1938" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1938" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1938" s="7" t="s">
         <v>3</v>
@@ -16115,6 +16115,9 @@
       <c r="B1946" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1946" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1947" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1947" s="3" t="s">
@@ -16131,7 +16134,7 @@
     </row>
     <row r="1949" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1949" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1949" s="7" t="s">
         <v>3</v>
@@ -16192,7 +16195,9 @@
       <c r="B1956" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1956" s="6"/>
+      <c r="C1956" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1957" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1957" s="3" t="s">
@@ -16208,10 +16213,13 @@
       <c r="B1959" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1959" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1960" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1960" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1960" s="7" t="s">
         <v>3</v>
@@ -16272,17 +16280,12 @@
       <c r="B1967" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1967" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1967" s="6"/>
     </row>
     <row r="1968" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1968" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1968" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1969" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1969" s="3" t="s">
@@ -16293,13 +16296,10 @@
       <c r="B1970" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1970" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1971" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1971" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1971" s="7" t="s">
         <v>3</v>
@@ -16387,7 +16387,7 @@
     </row>
     <row r="1982" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1982" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1982" s="7" t="s">
         <v>3</v>
@@ -16475,7 +16475,7 @@
     </row>
     <row r="1993" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1993" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B1993" s="7" t="s">
         <v>3</v>
@@ -16544,6 +16544,9 @@
       <c r="B2001" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2001" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2002" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2002" s="3" t="s">
@@ -16560,7 +16563,7 @@
     </row>
     <row r="2004" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2004" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B2004" s="7" t="s">
         <v>3</v>
@@ -16645,7 +16648,7 @@
     </row>
     <row r="2015" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2015" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B2015" s="7" t="s">
         <v>3</v>
@@ -16719,9 +16722,6 @@
       <c r="B2024" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2024" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2025" s="3" t="s">
@@ -16733,7 +16733,7 @@
     </row>
     <row r="2026" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2026" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B2026" s="7" t="s">
         <v>3</v>
@@ -16794,7 +16794,9 @@
       <c r="B2033" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2033" s="6"/>
+      <c r="C2033" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2034" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2034" s="3" t="s">
@@ -16805,15 +16807,21 @@
       <c r="B2035" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C2035" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2036" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C2036" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2037" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2037" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B2037" s="7" t="s">
         <v>3</v>
@@ -16874,9 +16882,7 @@
       <c r="B2044" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2044" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2044" s="6"/>
     </row>
     <row r="2045" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2045" s="3" t="s">
@@ -16892,13 +16898,10 @@
       <c r="B2047" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2047" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2048" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2048" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B2048" s="7" t="s">
         <v>3</v>
@@ -16967,9 +16970,6 @@
       <c r="B2056" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2056" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2057" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2057" s="3" t="s">
@@ -16986,7 +16986,7 @@
     </row>
     <row r="2059" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2059" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B2059" s="7" t="s">
         <v>3</v>
@@ -17055,6 +17055,9 @@
       <c r="B2067" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2067" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2068" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2068" s="3" t="s">
@@ -17071,7 +17074,7 @@
     </row>
     <row r="2070" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2070" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B2070" s="7" t="s">
         <v>3</v>
@@ -17150,10 +17153,13 @@
       <c r="B2080" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C2080" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2081" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2081" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B2081" s="7" t="s">
         <v>3</v>
@@ -17232,13 +17238,10 @@
       <c r="B2091" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2091" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2092" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2092" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B2092" s="7" t="s">
         <v>3</v>
@@ -17307,9 +17310,6 @@
       <c r="B2100" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2100" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2101" s="3" t="s">
@@ -17326,7 +17326,7 @@
     </row>
     <row r="2103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2103" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B2103" s="7" t="s">
         <v>3</v>
@@ -17347,19 +17347,25 @@
       <c r="B2105" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2105" s="6"/>
+      <c r="C2105" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2106" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2106" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2106" s="6"/>
+      <c r="C2106" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2107" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2107" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2107" s="6"/>
+      <c r="C2107" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2108" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2108" s="3" t="s">
@@ -17381,12 +17387,17 @@
       <c r="B2110" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2110" s="6"/>
+      <c r="C2110" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2111" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2111" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2111" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2112" s="3" t="s">
@@ -17397,10 +17408,13 @@
       <c r="B2113" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C2113" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2114" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B2114" s="7" t="s">
         <v>3</v>
@@ -17421,25 +17435,19 @@
       <c r="B2116" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2116" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2116" s="6"/>
     </row>
     <row r="2117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2117" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2117" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2117" s="6"/>
     </row>
     <row r="2118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2118" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2118" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2118" s="6"/>
     </row>
     <row r="2119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2119" s="3" t="s">
@@ -17461,17 +17469,12 @@
       <c r="B2121" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2121" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2121" s="6"/>
     </row>
     <row r="2122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2122" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2122" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2123" s="3" t="s">
@@ -17482,13 +17485,10 @@
       <c r="B2124" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2124" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2125" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B2125" s="7" t="s">
         <v>3</v>
@@ -17576,7 +17576,7 @@
     </row>
     <row r="2136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2136" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B2136" s="7" t="s">
         <v>3</v>
@@ -17645,6 +17645,9 @@
       <c r="B2144" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2144" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2145" s="3" t="s">
@@ -17661,7 +17664,7 @@
     </row>
     <row r="2147" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2147" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B2147" s="7" t="s">
         <v>3</v>
@@ -17730,9 +17733,6 @@
       <c r="B2155" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2155" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2156" s="3" t="s">
@@ -17740,19 +17740,19 @@
       </c>
     </row>
     <row r="2157" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2157" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B2157" s="7" t="s">
-        <v>3</v>
+      <c r="B2157" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C2157" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2158" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2158" s="3" t="s">
-        <v>4</v>
+      <c r="A2158" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B2158" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2158" s="5" t="s">
         <v>13</v>
@@ -17760,7 +17760,7 @@
     </row>
     <row r="2159" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2159" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2159" s="5" t="s">
         <v>13</v>
@@ -17768,7 +17768,7 @@
     </row>
     <row r="2160" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2160" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2160" s="5" t="s">
         <v>13</v>
@@ -17776,7 +17776,7 @@
     </row>
     <row r="2161" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2161" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2161" s="5" t="s">
         <v>13</v>
@@ -17784,7 +17784,7 @@
     </row>
     <row r="2162" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2162" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2162" s="5" t="s">
         <v>13</v>
@@ -17792,7 +17792,7 @@
     </row>
     <row r="2163" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2163" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2163" s="5" t="s">
         <v>13</v>
@@ -17800,7 +17800,7 @@
     </row>
     <row r="2164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2164" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2164" s="5" t="s">
         <v>13</v>
@@ -17808,7 +17808,7 @@
     </row>
     <row r="2165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2165" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2165" s="5" t="s">
         <v>13</v>
@@ -17816,23 +17816,23 @@
     </row>
     <row r="2166" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2166" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C2166" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2167" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2167" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B2167" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2167" s="5" t="s">
-        <v>13</v>
+      <c r="B2167" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2168" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2168" s="3" t="s">
-        <v>4</v>
+      <c r="A2168" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B2168" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2168" s="5" t="s">
         <v>13</v>
@@ -17840,7 +17840,7 @@
     </row>
     <row r="2169" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2169" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2169" s="5" t="s">
         <v>13</v>
@@ -17848,7 +17848,7 @@
     </row>
     <row r="2170" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2170" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2170" s="5" t="s">
         <v>13</v>
@@ -17856,7 +17856,7 @@
     </row>
     <row r="2171" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2171" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2171" s="5" t="s">
         <v>13</v>
@@ -17864,7 +17864,7 @@
     </row>
     <row r="2172" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2172" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2172" s="5" t="s">
         <v>13</v>
@@ -17872,7 +17872,7 @@
     </row>
     <row r="2173" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2173" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2173" s="5" t="s">
         <v>13</v>
@@ -17880,7 +17880,7 @@
     </row>
     <row r="2174" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2174" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2174" s="5" t="s">
         <v>13</v>
@@ -17888,16 +17888,104 @@
     </row>
     <row r="2175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2175" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C2175" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2176" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2177" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B2177" s="3">
+        <v>11</v>
+      </c>
+      <c r="C2176" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2177" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2177" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2178" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2178" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B2178" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2178" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2179" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2179" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2179" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2180" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2180" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2181" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2181" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2181" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2182" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2182" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2183" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2183" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2183" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2184" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2184" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2185" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2185" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2186" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2187" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2188" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B45C3984-88AA-4C6D-A68D-9CD932E7DE63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3AC747F-BB23-4A86-96E0-3E52ED28B9FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4173" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4194" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2188"/>
+  <dimension ref="A1:C2199"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6191,7 +6191,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6279,7 +6279,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6367,7 +6367,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6455,7 +6455,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6543,7 +6543,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6631,7 +6631,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6719,7 +6719,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6807,7 +6807,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6895,7 +6895,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6983,7 +6983,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7071,7 +7071,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7159,7 +7159,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7247,7 +7247,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7335,7 +7335,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7423,7 +7423,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7511,7 +7511,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7599,7 +7599,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7687,7 +7687,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7775,7 +7775,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7852,9 +7852,6 @@
       <c r="B924" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C924" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="925" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B925" s="3" t="s">
@@ -7866,7 +7863,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -7943,6 +7940,9 @@
       <c r="B935" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C935" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="936" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B936" s="3" t="s">
@@ -7954,7 +7954,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8042,7 +8042,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8130,7 +8130,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8218,7 +8218,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8306,7 +8306,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>3</v>
@@ -8383,9 +8383,6 @@
       <c r="B990" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C990" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="991" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B991" s="3" t="s">
@@ -8397,7 +8394,7 @@
     </row>
     <row r="992" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A992" s="4">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B992" s="7" t="s">
         <v>3</v>
@@ -8488,7 +8485,7 @@
     </row>
     <row r="1003" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1003" s="4">
-        <v>46207</v>
+        <v>46208</v>
       </c>
       <c r="B1003" s="7" t="s">
         <v>3</v>
@@ -8579,7 +8576,7 @@
     </row>
     <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1014" s="4">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B1014" s="7" t="s">
         <v>3</v>
@@ -8670,7 +8667,7 @@
     </row>
     <row r="1025" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1025" s="4">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B1025" s="7" t="s">
         <v>3</v>
@@ -8747,6 +8744,9 @@
       <c r="B1034" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1034" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1035" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1035" s="3" t="s">
@@ -8758,7 +8758,7 @@
     </row>
     <row r="1036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1036" s="4">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B1036" s="7" t="s">
         <v>3</v>
@@ -8835,9 +8835,6 @@
       <c r="B1045" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1045" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1046" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1046" s="3" t="s">
@@ -8849,7 +8846,7 @@
     </row>
     <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1047" s="4">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B1047" s="7" t="s">
         <v>3</v>
@@ -8940,7 +8937,7 @@
     </row>
     <row r="1058" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1058" s="4">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B1058" s="7" t="s">
         <v>3</v>
@@ -9031,7 +9028,7 @@
     </row>
     <row r="1069" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1069" s="4">
-        <v>46200</v>
+        <v>46202</v>
       </c>
       <c r="B1069" s="7" t="s">
         <v>3</v>
@@ -9122,7 +9119,7 @@
     </row>
     <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1080" s="4">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="B1080" s="7" t="s">
         <v>3</v>
@@ -9213,7 +9210,7 @@
     </row>
     <row r="1091" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1091" s="4">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B1091" s="7" t="s">
         <v>3</v>
@@ -9304,7 +9301,7 @@
     </row>
     <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1102" s="4">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B1102" s="7" t="s">
         <v>3</v>
@@ -9395,7 +9392,7 @@
     </row>
     <row r="1113" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1113" s="4">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B1113" s="7" t="s">
         <v>3</v>
@@ -9486,7 +9483,7 @@
     </row>
     <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1124" s="4">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B1124" s="7" t="s">
         <v>3</v>
@@ -9577,7 +9574,7 @@
     </row>
     <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1135" s="4">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B1135" s="7" t="s">
         <v>3</v>
@@ -9668,7 +9665,7 @@
     </row>
     <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1146" s="4">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B1146" s="7" t="s">
         <v>3</v>
@@ -9759,7 +9756,7 @@
     </row>
     <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1157" s="4">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="B1157" s="7" t="s">
         <v>3</v>
@@ -9850,7 +9847,7 @@
     </row>
     <row r="1168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1168" s="4">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B1168" s="7" t="s">
         <v>3</v>
@@ -9941,7 +9938,7 @@
     </row>
     <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1179" s="4">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B1179" s="7" t="s">
         <v>3</v>
@@ -10032,7 +10029,7 @@
     </row>
     <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1190" s="4">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B1190" s="7" t="s">
         <v>3</v>
@@ -10123,7 +10120,7 @@
     </row>
     <row r="1201" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1201" s="4">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B1201" s="7" t="s">
         <v>3</v>
@@ -10214,7 +10211,7 @@
     </row>
     <row r="1212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1212" s="4">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B1212" s="7" t="s">
         <v>3</v>
@@ -10305,7 +10302,7 @@
     </row>
     <row r="1223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1223" s="4">
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="B1223" s="7" t="s">
         <v>3</v>
@@ -10396,7 +10393,7 @@
     </row>
     <row r="1234" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1234" s="4">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="B1234" s="7" t="s">
         <v>3</v>
@@ -10487,7 +10484,7 @@
     </row>
     <row r="1245" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1245" s="4">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B1245" s="7" t="s">
         <v>3</v>
@@ -10578,7 +10575,7 @@
     </row>
     <row r="1256" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1256" s="4">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B1256" s="7" t="s">
         <v>3</v>
@@ -10669,7 +10666,7 @@
     </row>
     <row r="1267" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1267" s="4">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B1267" s="7" t="s">
         <v>3</v>
@@ -10760,7 +10757,7 @@
     </row>
     <row r="1278" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1278" s="4">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B1278" s="7" t="s">
         <v>3</v>
@@ -10851,7 +10848,7 @@
     </row>
     <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1289" s="4">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B1289" s="7" t="s">
         <v>3</v>
@@ -10942,7 +10939,7 @@
     </row>
     <row r="1300" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1300" s="4">
-        <v>46178</v>
+        <v>46180</v>
       </c>
       <c r="B1300" s="7" t="s">
         <v>3</v>
@@ -11033,7 +11030,7 @@
     </row>
     <row r="1311" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1311" s="4">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B1311" s="7" t="s">
         <v>3</v>
@@ -11124,7 +11121,7 @@
     </row>
     <row r="1322" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1322" s="4">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B1322" s="7" t="s">
         <v>3</v>
@@ -11215,7 +11212,7 @@
     </row>
     <row r="1333" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1333" s="4">
-        <v>46171</v>
+        <v>46176</v>
       </c>
       <c r="B1333" s="7" t="s">
         <v>3</v>
@@ -11306,7 +11303,7 @@
     </row>
     <row r="1344" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1344" s="4">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B1344" s="7" t="s">
         <v>3</v>
@@ -11397,7 +11394,7 @@
     </row>
     <row r="1355" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1355" s="4">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B1355" s="7" t="s">
         <v>3</v>
@@ -11488,7 +11485,7 @@
     </row>
     <row r="1366" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1366" s="4">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B1366" s="7" t="s">
         <v>3</v>
@@ -11579,7 +11576,7 @@
     </row>
     <row r="1377" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1377" s="4">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="B1377" s="7" t="s">
         <v>3</v>
@@ -11670,7 +11667,7 @@
     </row>
     <row r="1388" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1388" s="4">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="B1388" s="7" t="s">
         <v>3</v>
@@ -11761,7 +11758,7 @@
     </row>
     <row r="1399" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1399" s="4">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="B1399" s="7" t="s">
         <v>3</v>
@@ -11838,6 +11835,9 @@
       <c r="B1408" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1408" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1409" s="3" t="s">
@@ -11849,7 +11849,7 @@
     </row>
     <row r="1410" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1410" s="4">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B1410" s="7" t="s">
         <v>3</v>
@@ -11926,9 +11926,6 @@
       <c r="B1419" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1419" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1420" s="3" t="s">
@@ -11940,7 +11937,7 @@
     </row>
     <row r="1421" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1421" s="4">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B1421" s="7" t="s">
         <v>3</v>
@@ -12031,7 +12028,7 @@
     </row>
     <row r="1432" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1432" s="4">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B1432" s="7" t="s">
         <v>3</v>
@@ -12122,7 +12119,7 @@
     </row>
     <row r="1443" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1443" s="4">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B1443" s="7" t="s">
         <v>3</v>
@@ -12213,7 +12210,7 @@
     </row>
     <row r="1454" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1454" s="4">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="B1454" s="7" t="s">
         <v>3</v>
@@ -12304,7 +12301,7 @@
     </row>
     <row r="1465" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1465" s="4">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="B1465" s="7" t="s">
         <v>3</v>
@@ -12395,7 +12392,7 @@
     </row>
     <row r="1476" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1476" s="4">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="B1476" s="7" t="s">
         <v>3</v>
@@ -12486,7 +12483,7 @@
     </row>
     <row r="1487" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1487" s="4">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B1487" s="7" t="s">
         <v>3</v>
@@ -12577,7 +12574,7 @@
     </row>
     <row r="1498" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1498" s="4">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B1498" s="7" t="s">
         <v>3</v>
@@ -12668,7 +12665,7 @@
     </row>
     <row r="1509" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1509" s="4">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B1509" s="7" t="s">
         <v>3</v>
@@ -12759,7 +12756,7 @@
     </row>
     <row r="1520" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1520" s="4">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B1520" s="7" t="s">
         <v>3</v>
@@ -12828,6 +12825,9 @@
       <c r="B1528" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1528" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1529" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1529" s="3" t="s">
@@ -12847,7 +12847,7 @@
     </row>
     <row r="1531" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1531" s="4">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="B1531" s="7" t="s">
         <v>3</v>
@@ -12916,9 +12916,6 @@
       <c r="B1539" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1539" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1540" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1540" s="3" t="s">
@@ -12938,7 +12935,7 @@
     </row>
     <row r="1542" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1542" s="4">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B1542" s="7" t="s">
         <v>3</v>
@@ -13015,6 +13012,9 @@
       <c r="B1551" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1551" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1552" s="3" t="s">
@@ -13026,7 +13026,7 @@
     </row>
     <row r="1553" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1553" s="4">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="B1553" s="7" t="s">
         <v>3</v>
@@ -13095,6 +13095,9 @@
       <c r="B1561" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1561" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1562" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1562" s="3" t="s">
@@ -13111,7 +13114,7 @@
     </row>
     <row r="1564" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1564" s="4">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B1564" s="7" t="s">
         <v>3</v>
@@ -13180,9 +13183,6 @@
       <c r="B1572" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1572" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1573" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1573" s="3" t="s">
@@ -13199,7 +13199,7 @@
     </row>
     <row r="1575" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1575" s="4">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B1575" s="7" t="s">
         <v>3</v>
@@ -13268,6 +13268,9 @@
       <c r="B1583" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1583" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1584" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1584" s="3" t="s">
@@ -13284,7 +13287,7 @@
     </row>
     <row r="1586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1586" s="4">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B1586" s="7" t="s">
         <v>3</v>
@@ -13353,9 +13356,6 @@
       <c r="B1594" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1594" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1595" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1595" s="3" t="s">
@@ -13372,7 +13372,7 @@
     </row>
     <row r="1597" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1597" s="4">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B1597" s="7" t="s">
         <v>3</v>
@@ -13460,7 +13460,7 @@
     </row>
     <row r="1608" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1608" s="4">
-        <v>46145</v>
+        <v>46146</v>
       </c>
       <c r="B1608" s="7" t="s">
         <v>3</v>
@@ -13548,7 +13548,7 @@
     </row>
     <row r="1619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1619" s="4">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="B1619" s="7" t="s">
         <v>3</v>
@@ -13617,6 +13617,9 @@
       <c r="B1627" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1627" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1628" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1628" s="3" t="s">
@@ -13633,7 +13636,7 @@
     </row>
     <row r="1630" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1630" s="4">
-        <v>46143</v>
+        <v>46144</v>
       </c>
       <c r="B1630" s="7" t="s">
         <v>3</v>
@@ -13718,7 +13721,7 @@
     </row>
     <row r="1641" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1641" s="4">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B1641" s="7" t="s">
         <v>3</v>
@@ -13803,7 +13806,7 @@
     </row>
     <row r="1652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1652" s="4">
-        <v>46138</v>
+        <v>46142</v>
       </c>
       <c r="B1652" s="7" t="s">
         <v>3</v>
@@ -13888,7 +13891,7 @@
     </row>
     <row r="1663" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1663" s="4">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="B1663" s="7" t="s">
         <v>3</v>
@@ -13973,7 +13976,7 @@
     </row>
     <row r="1674" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1674" s="4">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="B1674" s="7" t="s">
         <v>3</v>
@@ -14058,7 +14061,7 @@
     </row>
     <row r="1685" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1685" s="4">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B1685" s="7" t="s">
         <v>3</v>
@@ -14143,7 +14146,7 @@
     </row>
     <row r="1696" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1696" s="4">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B1696" s="7" t="s">
         <v>3</v>
@@ -14228,7 +14231,7 @@
     </row>
     <row r="1707" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1707" s="4">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B1707" s="7" t="s">
         <v>3</v>
@@ -14313,7 +14316,7 @@
     </row>
     <row r="1718" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1718" s="4">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B1718" s="7" t="s">
         <v>3</v>
@@ -14398,7 +14401,7 @@
     </row>
     <row r="1729" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1729" s="4">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="B1729" s="7" t="s">
         <v>3</v>
@@ -14483,7 +14486,7 @@
     </row>
     <row r="1740" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1740" s="4">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="B1740" s="7" t="s">
         <v>3</v>
@@ -14568,7 +14571,7 @@
     </row>
     <row r="1751" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1751" s="4">
-        <v>46128</v>
+        <v>46130</v>
       </c>
       <c r="B1751" s="7" t="s">
         <v>3</v>
@@ -14637,9 +14640,6 @@
       <c r="B1759" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1759" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1760" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1760" s="3" t="s">
@@ -14656,7 +14656,7 @@
     </row>
     <row r="1762" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1762" s="4">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B1762" s="7" t="s">
         <v>3</v>
@@ -14725,6 +14725,9 @@
       <c r="B1770" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1770" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1771" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1771" s="3" t="s">
@@ -14741,7 +14744,7 @@
     </row>
     <row r="1773" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1773" s="4">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B1773" s="7" t="s">
         <v>3</v>
@@ -14826,7 +14829,7 @@
     </row>
     <row r="1784" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1784" s="4">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B1784" s="7" t="s">
         <v>3</v>
@@ -14911,7 +14914,7 @@
     </row>
     <row r="1795" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1795" s="4">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="B1795" s="7" t="s">
         <v>3</v>
@@ -14980,9 +14983,6 @@
       <c r="B1803" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1803" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1804" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1804" s="3" t="s">
@@ -14999,7 +14999,7 @@
     </row>
     <row r="1806" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1806" s="4">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="B1806" s="7" t="s">
         <v>3</v>
@@ -15087,7 +15087,7 @@
     </row>
     <row r="1817" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1817" s="4">
-        <v>46120</v>
+        <v>46123</v>
       </c>
       <c r="B1817" s="7" t="s">
         <v>3</v>
@@ -15156,6 +15156,9 @@
       <c r="B1825" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1825" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1826" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1826" s="3" t="s">
@@ -15172,7 +15175,7 @@
     </row>
     <row r="1828" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1828" s="4">
-        <v>46101</v>
+        <v>46120</v>
       </c>
       <c r="B1828" s="7" t="s">
         <v>3</v>
@@ -15257,7 +15260,7 @@
     </row>
     <row r="1839" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1839" s="4">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B1839" s="7" t="s">
         <v>3</v>
@@ -15342,7 +15345,7 @@
     </row>
     <row r="1850" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1850" s="4">
-        <v>46088</v>
+        <v>46100</v>
       </c>
       <c r="B1850" s="7" t="s">
         <v>3</v>
@@ -15427,7 +15430,7 @@
     </row>
     <row r="1861" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1861" s="4">
-        <v>46077</v>
+        <v>46088</v>
       </c>
       <c r="B1861" s="7" t="s">
         <v>3</v>
@@ -15496,9 +15499,6 @@
       <c r="B1869" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1869" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1870" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1870" s="3" t="s">
@@ -15515,7 +15515,7 @@
     </row>
     <row r="1872" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1872" s="4">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B1872" s="7" t="s">
         <v>3</v>
@@ -15603,7 +15603,7 @@
     </row>
     <row r="1883" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1883" s="4">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B1883" s="7" t="s">
         <v>3</v>
@@ -15680,9 +15680,6 @@
       <c r="B1892" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1892" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1893" s="3" t="s">
@@ -15694,7 +15691,7 @@
     </row>
     <row r="1894" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1894" s="4">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B1894" s="7" t="s">
         <v>3</v>
@@ -15771,6 +15768,9 @@
       <c r="B1903" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C1903" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1904" s="3" t="s">
@@ -15782,7 +15782,7 @@
     </row>
     <row r="1905" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1905" s="4">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="B1905" s="7" t="s">
         <v>3</v>
@@ -15870,7 +15870,7 @@
     </row>
     <row r="1916" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1916" s="4">
-        <v>46068</v>
+        <v>46069</v>
       </c>
       <c r="B1916" s="7" t="s">
         <v>3</v>
@@ -15958,7 +15958,7 @@
     </row>
     <row r="1927" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1927" s="4">
-        <v>46067</v>
+        <v>46068</v>
       </c>
       <c r="B1927" s="7" t="s">
         <v>3</v>
@@ -16046,7 +16046,7 @@
     </row>
     <row r="1938" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1938" s="4">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B1938" s="7" t="s">
         <v>3</v>
@@ -16134,7 +16134,7 @@
     </row>
     <row r="1949" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1949" s="4">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B1949" s="7" t="s">
         <v>3</v>
@@ -16203,6 +16203,9 @@
       <c r="B1957" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C1957" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1958" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1958" s="3" t="s">
@@ -16219,7 +16222,7 @@
     </row>
     <row r="1960" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1960" s="4">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B1960" s="7" t="s">
         <v>3</v>
@@ -16280,7 +16283,9 @@
       <c r="B1967" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1967" s="6"/>
+      <c r="C1967" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1968" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1968" s="3" t="s">
@@ -16296,10 +16301,13 @@
       <c r="B1970" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C1970" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="1971" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1971" s="4">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B1971" s="7" t="s">
         <v>3</v>
@@ -16360,17 +16368,12 @@
       <c r="B1978" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C1978" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C1978" s="6"/>
     </row>
     <row r="1979" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1979" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C1979" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1980" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1980" s="3" t="s">
@@ -16381,13 +16384,10 @@
       <c r="B1981" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1981" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="1982" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1982" s="4">
-        <v>46061</v>
+        <v>46062</v>
       </c>
       <c r="B1982" s="7" t="s">
         <v>3</v>
@@ -16475,7 +16475,7 @@
     </row>
     <row r="1993" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1993" s="4">
-        <v>46060</v>
+        <v>46061</v>
       </c>
       <c r="B1993" s="7" t="s">
         <v>3</v>
@@ -16563,7 +16563,7 @@
     </row>
     <row r="2004" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2004" s="4">
-        <v>46059</v>
+        <v>46060</v>
       </c>
       <c r="B2004" s="7" t="s">
         <v>3</v>
@@ -16632,6 +16632,9 @@
       <c r="B2012" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2012" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2013" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2013" s="3" t="s">
@@ -16648,7 +16651,7 @@
     </row>
     <row r="2015" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2015" s="4">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B2015" s="7" t="s">
         <v>3</v>
@@ -16733,7 +16736,7 @@
     </row>
     <row r="2026" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2026" s="4">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B2026" s="7" t="s">
         <v>3</v>
@@ -16807,9 +16810,6 @@
       <c r="B2035" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2035" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2036" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2036" s="3" t="s">
@@ -16821,7 +16821,7 @@
     </row>
     <row r="2037" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2037" s="4">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B2037" s="7" t="s">
         <v>3</v>
@@ -16882,7 +16882,9 @@
       <c r="B2044" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2044" s="6"/>
+      <c r="C2044" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2045" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2045" s="3" t="s">
@@ -16893,15 +16895,21 @@
       <c r="B2046" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C2046" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2047" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2047" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C2047" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2048" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2048" s="4">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="B2048" s="7" t="s">
         <v>3</v>
@@ -16962,9 +16970,7 @@
       <c r="B2055" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2055" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2055" s="6"/>
     </row>
     <row r="2056" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2056" s="3" t="s">
@@ -16980,13 +16986,10 @@
       <c r="B2058" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2058" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2059" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2059" s="4">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B2059" s="7" t="s">
         <v>3</v>
@@ -17055,9 +17058,6 @@
       <c r="B2067" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2067" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2068" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2068" s="3" t="s">
@@ -17074,7 +17074,7 @@
     </row>
     <row r="2070" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2070" s="4">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B2070" s="7" t="s">
         <v>3</v>
@@ -17143,6 +17143,9 @@
       <c r="B2078" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2078" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2079" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2079" s="3" t="s">
@@ -17159,7 +17162,7 @@
     </row>
     <row r="2081" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2081" s="4">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B2081" s="7" t="s">
         <v>3</v>
@@ -17238,10 +17241,13 @@
       <c r="B2091" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C2091" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2092" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2092" s="4">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B2092" s="7" t="s">
         <v>3</v>
@@ -17320,13 +17326,10 @@
       <c r="B2102" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2102" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2103" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2103" s="4">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B2103" s="7" t="s">
         <v>3</v>
@@ -17395,9 +17398,6 @@
       <c r="B2111" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2111" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2112" s="3" t="s">
@@ -17414,7 +17414,7 @@
     </row>
     <row r="2114" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2114" s="4">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B2114" s="7" t="s">
         <v>3</v>
@@ -17435,19 +17435,25 @@
       <c r="B2116" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2116" s="6"/>
+      <c r="C2116" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2117" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2117" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2117" s="6"/>
+      <c r="C2117" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2118" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2118" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2118" s="6"/>
+      <c r="C2118" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2119" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2119" s="3" t="s">
@@ -17469,12 +17475,17 @@
       <c r="B2121" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2121" s="6"/>
+      <c r="C2121" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2122" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2122" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2122" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2123" s="3" t="s">
@@ -17485,10 +17496,13 @@
       <c r="B2124" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="C2124" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2125" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2125" s="4">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="B2125" s="7" t="s">
         <v>3</v>
@@ -17509,25 +17523,19 @@
       <c r="B2127" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2127" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2127" s="6"/>
     </row>
     <row r="2128" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2128" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2128" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2128" s="6"/>
     </row>
     <row r="2129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2129" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2129" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2129" s="6"/>
     </row>
     <row r="2130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2130" s="3" t="s">
@@ -17549,17 +17557,12 @@
       <c r="B2132" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2132" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="C2132" s="6"/>
     </row>
     <row r="2133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2133" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2133" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2134" s="3" t="s">
@@ -17570,13 +17573,10 @@
       <c r="B2135" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2135" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2136" s="4">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="B2136" s="7" t="s">
         <v>3</v>
@@ -17664,7 +17664,7 @@
     </row>
     <row r="2147" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2147" s="4">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="B2147" s="7" t="s">
         <v>3</v>
@@ -17733,6 +17733,9 @@
       <c r="B2155" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="C2155" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2156" s="3" t="s">
@@ -17749,7 +17752,7 @@
     </row>
     <row r="2158" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2158" s="4">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B2158" s="7" t="s">
         <v>3</v>
@@ -17818,9 +17821,6 @@
       <c r="B2166" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2166" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="2167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2167" s="3" t="s">
@@ -17828,19 +17828,19 @@
       </c>
     </row>
     <row r="2168" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2168" s="4">
-        <v>46043</v>
-      </c>
-      <c r="B2168" s="7" t="s">
-        <v>3</v>
+      <c r="B2168" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="C2168" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2169" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2169" s="3" t="s">
-        <v>4</v>
+      <c r="A2169" s="4">
+        <v>46044</v>
+      </c>
+      <c r="B2169" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2169" s="5" t="s">
         <v>13</v>
@@ -17848,7 +17848,7 @@
     </row>
     <row r="2170" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2170" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2170" s="5" t="s">
         <v>13</v>
@@ -17856,7 +17856,7 @@
     </row>
     <row r="2171" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2171" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2171" s="5" t="s">
         <v>13</v>
@@ -17864,7 +17864,7 @@
     </row>
     <row r="2172" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2172" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2172" s="5" t="s">
         <v>13</v>
@@ -17872,7 +17872,7 @@
     </row>
     <row r="2173" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2173" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2173" s="5" t="s">
         <v>13</v>
@@ -17880,7 +17880,7 @@
     </row>
     <row r="2174" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2174" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2174" s="5" t="s">
         <v>13</v>
@@ -17888,7 +17888,7 @@
     </row>
     <row r="2175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2175" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2175" s="5" t="s">
         <v>13</v>
@@ -17896,7 +17896,7 @@
     </row>
     <row r="2176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2176" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2176" s="5" t="s">
         <v>13</v>
@@ -17904,23 +17904,23 @@
     </row>
     <row r="2177" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2177" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C2177" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2178" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2178" s="4">
-        <v>46042</v>
-      </c>
-      <c r="B2178" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2178" s="5" t="s">
-        <v>13</v>
+      <c r="B2178" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="2179" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2179" s="3" t="s">
-        <v>4</v>
+      <c r="A2179" s="4">
+        <v>46043</v>
+      </c>
+      <c r="B2179" s="7" t="s">
+        <v>3</v>
       </c>
       <c r="C2179" s="5" t="s">
         <v>13</v>
@@ -17928,7 +17928,7 @@
     </row>
     <row r="2180" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2180" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2180" s="5" t="s">
         <v>13</v>
@@ -17936,7 +17936,7 @@
     </row>
     <row r="2181" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2181" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2181" s="5" t="s">
         <v>13</v>
@@ -17944,7 +17944,7 @@
     </row>
     <row r="2182" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2182" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2182" s="5" t="s">
         <v>13</v>
@@ -17952,7 +17952,7 @@
     </row>
     <row r="2183" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2183" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2183" s="5" t="s">
         <v>13</v>
@@ -17960,7 +17960,7 @@
     </row>
     <row r="2184" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2184" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2184" s="5" t="s">
         <v>13</v>
@@ -17968,7 +17968,7 @@
     </row>
     <row r="2185" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2185" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2185" s="5" t="s">
         <v>13</v>
@@ -17976,16 +17976,104 @@
     </row>
     <row r="2186" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2186" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
+      </c>
+      <c r="C2186" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2187" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2187" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="C2187" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="2188" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2188" s="3">
+      <c r="B2188" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2189" s="4">
+        <v>46042</v>
+      </c>
+      <c r="B2189" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2189" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2190" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2190" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2191" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2191" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B2192" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2192" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2193" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2193" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2193" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2194" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2194" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2194" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2195" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2195" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2195" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2196" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2196" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2196" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2197" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2197" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2198" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2198" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2199" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B2199" s="3">
         <v>11</v>
       </c>
     </row>

--- a/成王败寇.xlsx
+++ b/成王败寇.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\GitHub\WinnerTakeAll\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3AC747F-BB23-4A86-96E0-3E52ED28B9FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD70E473-DC9A-45D2-A38F-C19A76D1EEBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4194" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4215" uniqueCount="15">
   <si>
     <t>时间</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -471,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2199"/>
+  <dimension ref="A1:C2210"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.25" style="2" customWidth="1"/>
@@ -559,7 +559,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
-        <v>46305</v>
+        <v>46307</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>3</v>
@@ -647,7 +647,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>3</v>
@@ -735,7 +735,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>3</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>3</v>
@@ -911,7 +911,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>3</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>3</v>
@@ -1087,7 +1087,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>3</v>
@@ -1175,7 +1175,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>3</v>
@@ -1263,7 +1263,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>3</v>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A112" s="4">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>3</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A123" s="4">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>3</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="4">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="B134" s="7" t="s">
         <v>3</v>
@@ -1615,7 +1615,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A145" s="4">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>3</v>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A156" s="4">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="B156" s="7" t="s">
         <v>3</v>
@@ -1791,7 +1791,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="4">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="B167" s="7" t="s">
         <v>3</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A178" s="4">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="B178" s="7" t="s">
         <v>3</v>
@@ -1967,7 +1967,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A189" s="4">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="B189" s="7" t="s">
         <v>3</v>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A200" s="4">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="B200" s="7" t="s">
         <v>3</v>
@@ -2143,7 +2143,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="4">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B211" s="7" t="s">
         <v>3</v>
@@ -2231,7 +2231,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="4">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="B222" s="7" t="s">
         <v>3</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A233" s="4">
-        <v>46284</v>
+        <v>46285</v>
       </c>
       <c r="B233" s="7" t="s">
         <v>3</v>
@@ -2407,7 +2407,7 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A244" s="4">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="B244" s="7" t="s">
         <v>3</v>
@@ -2495,7 +2495,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A255" s="4">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B255" s="7" t="s">
         <v>3</v>
@@ -2583,7 +2583,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A266" s="4">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="B266" s="7" t="s">
         <v>3</v>
@@ -2671,7 +2671,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A277" s="4">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="B277" s="7" t="s">
         <v>3</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A288" s="4">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="B288" s="7" t="s">
         <v>3</v>
@@ -2847,7 +2847,7 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A299" s="4">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="B299" s="7" t="s">
         <v>3</v>
@@ -2935,7 +2935,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A310" s="4">
-        <v>46277</v>
+        <v>46278</v>
       </c>
       <c r="B310" s="7" t="s">
         <v>3</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A321" s="4">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="B321" s="7" t="s">
         <v>3</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A332" s="4">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B332" s="7" t="s">
         <v>3</v>
@@ -3199,7 +3199,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A343" s="4">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>3</v>
@@ -3287,7 +3287,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A354" s="4">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="B354" s="7" t="s">
         <v>3</v>
@@ -3375,7 +3375,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A365" s="4">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="B365" s="7" t="s">
         <v>3</v>
@@ -3463,7 +3463,7 @@
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A376" s="4">
-        <v>46270</v>
+        <v>46271</v>
       </c>
       <c r="B376" s="7" t="s">
         <v>3</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A387" s="4">
-        <v>46269</v>
+        <v>46270</v>
       </c>
       <c r="B387" s="7" t="s">
         <v>3</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A398" s="4">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B398" s="7" t="s">
         <v>3</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A409" s="4">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B409" s="7" t="s">
         <v>3</v>
@@ -3815,7 +3815,7 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A420" s="4">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B420" s="7" t="s">
         <v>3</v>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A431" s="4">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="B431" s="7" t="s">
         <v>3</v>
@@ -3991,7 +3991,7 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A442" s="4">
-        <v>46263</v>
+        <v>46264</v>
       </c>
       <c r="B442" s="7" t="s">
         <v>3</v>
@@ -4079,7 +4079,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A453" s="4">
-        <v>46262</v>
+        <v>46263</v>
       </c>
       <c r="B453" s="7" t="s">
         <v>3</v>
@@ -4167,7 +4167,7 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A464" s="4">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B464" s="7" t="s">
         <v>3</v>
@@ -4255,7 +4255,7 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A475" s="4">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B475" s="7" t="s">
         <v>3</v>
@@ -4343,7 +4343,7 @@
     </row>
     <row r="486" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A486" s="4">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B486" s="7" t="s">
         <v>3</v>
@@ -4431,7 +4431,7 @@
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A497" s="4">
-        <v>46257</v>
+        <v>46259</v>
       </c>
       <c r="B497" s="7" t="s">
         <v>3</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A508" s="4">
-        <v>46256</v>
+        <v>46257</v>
       </c>
       <c r="B508" s="7" t="s">
         <v>3</v>
@@ -4607,7 +4607,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A519" s="4">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="B519" s="7" t="s">
         <v>3</v>
@@ -4695,7 +4695,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A530" s="4">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B530" s="7" t="s">
         <v>3</v>
@@ -4783,7 +4783,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A541" s="4">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B541" s="7" t="s">
         <v>3</v>
@@ -4871,7 +4871,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A552" s="4">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B552" s="7" t="s">
         <v>3</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A563" s="4">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="B563" s="7" t="s">
         <v>3</v>
@@ -5047,7 +5047,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A574" s="4">
-        <v>46249</v>
+        <v>46250</v>
       </c>
       <c r="B574" s="7" t="s">
         <v>3</v>
@@ -5135,7 +5135,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="4">
-        <v>46248</v>
+        <v>46249</v>
       </c>
       <c r="B585" s="7" t="s">
         <v>3</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A596" s="4">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B596" s="7" t="s">
         <v>3</v>
@@ -5311,7 +5311,7 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A607" s="4">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B607" s="7" t="s">
         <v>3</v>
@@ -5399,7 +5399,7 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A618" s="4">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B618" s="7" t="s">
         <v>3</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A629" s="4">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B629" s="7" t="s">
         <v>3</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="4">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="B640" s="7" t="s">
         <v>3</v>
@@ -5663,7 +5663,7 @@
     </row>
     <row r="651" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A651" s="4">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B651" s="7" t="s">
         <v>3</v>
@@ -5751,7 +5751,7 @@
     </row>
     <row r="662" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A662" s="4">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="B662" s="7" t="s">
         <v>3</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="4">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B673" s="7" t="s">
         <v>3</v>
@@ -5927,7 +5927,7 @@
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A684" s="4">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B684" s="7" t="s">
         <v>3</v>
@@ -6015,7 +6015,7 @@
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A695" s="4">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B695" s="7" t="s">
         <v>3</v>
@@ -6103,7 +6103,7 @@
     </row>
     <row r="706" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A706" s="4">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B706" s="7" t="s">
         <v>3</v>
@@ -6191,7 +6191,7 @@
     </row>
     <row r="717" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A717" s="4">
-        <v>46236</v>
+        <v>46237</v>
       </c>
       <c r="B717" s="7" t="s">
         <v>3</v>
@@ -6279,7 +6279,7 @@
     </row>
     <row r="728" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A728" s="4">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B728" s="7" t="s">
         <v>3</v>
@@ -6367,7 +6367,7 @@
     </row>
     <row r="739" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A739" s="4">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="B739" s="7" t="s">
         <v>3</v>
@@ -6455,7 +6455,7 @@
     </row>
     <row r="750" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A750" s="4">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B750" s="7" t="s">
         <v>3</v>
@@ -6543,7 +6543,7 @@
     </row>
     <row r="761" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A761" s="4">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B761" s="7" t="s">
         <v>3</v>
@@ -6631,7 +6631,7 @@
     </row>
     <row r="772" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A772" s="4">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B772" s="7" t="s">
         <v>3</v>
@@ -6719,7 +6719,7 @@
     </row>
     <row r="783" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A783" s="4">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B783" s="7" t="s">
         <v>3</v>
@@ -6807,7 +6807,7 @@
     </row>
     <row r="794" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A794" s="4">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="B794" s="7" t="s">
         <v>3</v>
@@ -6895,7 +6895,7 @@
     </row>
     <row r="805" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A805" s="4">
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="B805" s="7" t="s">
         <v>3</v>
@@ -6983,7 +6983,7 @@
     </row>
     <row r="816" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A816" s="4">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B816" s="7" t="s">
         <v>3</v>
@@ -7071,7 +7071,7 @@
     </row>
     <row r="827" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A827" s="4">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>3</v>
@@ -7159,7 +7159,7 @@
     </row>
     <row r="838" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A838" s="4">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>3</v>
@@ -7247,7 +7247,7 @@
     </row>
     <row r="849" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A849" s="4">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>3</v>
@@ -7335,7 +7335,7 @@
     </row>
     <row r="860" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A860" s="4">
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>3</v>
@@ -7423,7 +7423,7 @@
     </row>
     <row r="871" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A871" s="4">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>3</v>
@@ -7511,7 +7511,7 @@
     </row>
     <row r="882" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A882" s="4">
-        <v>46220</v>
+        <v>46221</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>3</v>
@@ -7599,7 +7599,7 @@
     </row>
     <row r="893" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A893" s="4">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>3</v>
@@ -7687,7 +7687,7 @@
     </row>
     <row r="904" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A904" s="4">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>3</v>
@@ -7775,7 +7775,7 @@
     </row>
     <row r="915" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A915" s="4">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>3</v>
@@ -7863,7 +7863,7 @@
     </row>
     <row r="926" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A926" s="4">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>3</v>
@@ -7940,9 +7940,6 @@
       <c r="B935" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C935" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="936" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B936" s="3" t="s">
@@ -7954,7 +7951,7 @@
     </row>
     <row r="937" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A937" s="4">
-        <v>46214</v>
+        <v>46215</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>3</v>
@@ -8031,6 +8028,9 @@
       <c r="B946" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="C946" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="947" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B947" s="3" t="s">
@@ -8042,7 +8042,7 @@
     </row>
     <row r="948" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A948" s="4">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>3</v>
@@ -8130,7 +8130,7 @@
     </row>
     <row r="959" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A959" s="4">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>3</v>
@@ -8218,7 +8218,7 @@
     </row>
     <row r="970" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A970" s="4">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>3</v>
@@ -8306,7 +8306,7 @@
     </row>
     <row r="981" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A981" s="4">
-        <v>46210</v>
+        <v>46211</v>
       </c>
    